--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="78">
+  <fonts count="80">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -468,6 +468,16 @@
       <color rgb="00334155"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -702,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="268">
+  <borders count="290">
     <border>
       <left/>
       <right/>
@@ -3580,11 +3590,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="326">
+  <cellXfs count="397">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4313,6 +4539,169 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4387,39 +4776,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4774,2036 +5130,2304 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="inlineStr"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="269" t="inlineStr">
+      <c r="A1" s="326" t="inlineStr"/>
+      <c r="B1" s="390" t="n"/>
+      <c r="C1" s="390" t="n"/>
+      <c r="D1" s="390" t="n"/>
+      <c r="E1" s="390" t="n"/>
+      <c r="F1" s="390" t="n"/>
+      <c r="G1" s="390" t="n"/>
+      <c r="H1" s="390" t="n"/>
+      <c r="I1" s="328" t="inlineStr">
         <is>
           <t>WIP Tag</t>
         </is>
       </c>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="268" t="n"/>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="270" t="inlineStr">
+      <c r="J1" s="390" t="n"/>
+      <c r="K1" s="390" t="n"/>
+      <c r="L1" s="390" t="n"/>
+      <c r="M1" s="390" t="n"/>
+      <c r="N1" s="390" t="n"/>
+      <c r="O1" s="390" t="n"/>
+      <c r="P1" s="390" t="n"/>
+      <c r="Q1" s="390" t="n"/>
+      <c r="R1" s="390" t="n"/>
+      <c r="S1" s="390" t="n"/>
+      <c r="T1" s="390" t="n"/>
+      <c r="U1" s="390" t="n"/>
+      <c r="V1" s="390" t="n"/>
+      <c r="W1" s="390" t="n"/>
+      <c r="X1" s="390" t="n"/>
+      <c r="Y1" s="390" t="n"/>
+      <c r="Z1" s="390" t="n"/>
+      <c r="AA1" s="390" t="n"/>
+      <c r="AB1" s="390" t="n"/>
+      <c r="AC1" s="390" t="n"/>
+      <c r="AD1" s="390" t="n"/>
+      <c r="AE1" s="329" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="271" t="n"/>
-      <c r="AG1" s="271" t="n"/>
-      <c r="AH1" s="272" t="n"/>
-      <c r="AI1" s="273" t="inlineStr">
+      <c r="AF1" s="391" t="n"/>
+      <c r="AG1" s="391" t="n"/>
+      <c r="AH1" s="392" t="n"/>
+      <c r="AI1" s="332" t="inlineStr">
         <is>
           <t>FRM-703</t>
         </is>
       </c>
-      <c r="AJ1" s="271" t="n"/>
-      <c r="AK1" s="271" t="n"/>
-      <c r="AL1" s="271" t="n"/>
-      <c r="AM1" s="271" t="n"/>
-      <c r="AN1" s="274" t="n"/>
+      <c r="AJ1" s="391" t="n"/>
+      <c r="AK1" s="391" t="n"/>
+      <c r="AL1" s="391" t="n"/>
+      <c r="AM1" s="391" t="n"/>
+      <c r="AN1" s="392" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="I2" s="275" t="n"/>
-      <c r="AE2" s="276" t="inlineStr">
+      <c r="A2" s="393" t="n"/>
+      <c r="I2" s="393" t="n"/>
+      <c r="AE2" s="335" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="277" t="n"/>
-      <c r="AG2" s="277" t="n"/>
-      <c r="AH2" s="278" t="n"/>
-      <c r="AI2" s="279" t="inlineStr">
+      <c r="AF2" s="394" t="n"/>
+      <c r="AG2" s="394" t="n"/>
+      <c r="AH2" s="395" t="n"/>
+      <c r="AI2" s="338" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="277" t="n"/>
-      <c r="AK2" s="277" t="n"/>
-      <c r="AL2" s="277" t="n"/>
-      <c r="AM2" s="277" t="n"/>
-      <c r="AN2" s="280" t="n"/>
+      <c r="AJ2" s="394" t="n"/>
+      <c r="AK2" s="394" t="n"/>
+      <c r="AL2" s="394" t="n"/>
+      <c r="AM2" s="394" t="n"/>
+      <c r="AN2" s="395" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="I3" s="281" t="n"/>
-      <c r="J3" s="277" t="n"/>
-      <c r="K3" s="277" t="n"/>
-      <c r="L3" s="277" t="n"/>
-      <c r="M3" s="277" t="n"/>
-      <c r="N3" s="277" t="n"/>
-      <c r="O3" s="277" t="n"/>
-      <c r="P3" s="277" t="n"/>
-      <c r="Q3" s="277" t="n"/>
-      <c r="R3" s="277" t="n"/>
-      <c r="S3" s="277" t="n"/>
-      <c r="T3" s="277" t="n"/>
-      <c r="U3" s="277" t="n"/>
-      <c r="V3" s="277" t="n"/>
-      <c r="W3" s="277" t="n"/>
-      <c r="X3" s="277" t="n"/>
-      <c r="Y3" s="277" t="n"/>
-      <c r="Z3" s="277" t="n"/>
-      <c r="AA3" s="277" t="n"/>
-      <c r="AB3" s="277" t="n"/>
-      <c r="AC3" s="277" t="n"/>
-      <c r="AD3" s="277" t="n"/>
-      <c r="AE3" s="276" t="inlineStr">
+      <c r="A3" s="393" t="n"/>
+      <c r="I3" s="396" t="n"/>
+      <c r="J3" s="394" t="n"/>
+      <c r="K3" s="394" t="n"/>
+      <c r="L3" s="394" t="n"/>
+      <c r="M3" s="394" t="n"/>
+      <c r="N3" s="394" t="n"/>
+      <c r="O3" s="394" t="n"/>
+      <c r="P3" s="394" t="n"/>
+      <c r="Q3" s="394" t="n"/>
+      <c r="R3" s="394" t="n"/>
+      <c r="S3" s="394" t="n"/>
+      <c r="T3" s="394" t="n"/>
+      <c r="U3" s="394" t="n"/>
+      <c r="V3" s="394" t="n"/>
+      <c r="W3" s="394" t="n"/>
+      <c r="X3" s="394" t="n"/>
+      <c r="Y3" s="394" t="n"/>
+      <c r="Z3" s="394" t="n"/>
+      <c r="AA3" s="394" t="n"/>
+      <c r="AB3" s="394" t="n"/>
+      <c r="AC3" s="394" t="n"/>
+      <c r="AD3" s="394" t="n"/>
+      <c r="AE3" s="335" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="277" t="n"/>
-      <c r="AG3" s="277" t="n"/>
-      <c r="AH3" s="278" t="n"/>
-      <c r="AI3" s="279" t="inlineStr">
+      <c r="AF3" s="394" t="n"/>
+      <c r="AG3" s="394" t="n"/>
+      <c r="AH3" s="395" t="n"/>
+      <c r="AI3" s="338" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="277" t="n"/>
-      <c r="AK3" s="277" t="n"/>
-      <c r="AL3" s="277" t="n"/>
-      <c r="AM3" s="277" t="n"/>
-      <c r="AN3" s="280" t="n"/>
+      <c r="AJ3" s="394" t="n"/>
+      <c r="AK3" s="394" t="n"/>
+      <c r="AL3" s="394" t="n"/>
+      <c r="AM3" s="394" t="n"/>
+      <c r="AN3" s="395" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="A4" s="393" t="n"/>
+      <c r="I4" s="340" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="276" t="inlineStr">
+      <c r="AE4" s="335" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="277" t="n"/>
-      <c r="AG4" s="277" t="n"/>
-      <c r="AH4" s="278" t="n"/>
-      <c r="AI4" s="279" t="inlineStr">
+      <c r="AF4" s="394" t="n"/>
+      <c r="AG4" s="394" t="n"/>
+      <c r="AH4" s="395" t="n"/>
+      <c r="AI4" s="338" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="277" t="n"/>
-      <c r="AK4" s="277" t="n"/>
-      <c r="AL4" s="277" t="n"/>
-      <c r="AM4" s="277" t="n"/>
-      <c r="AN4" s="280" t="n"/>
+      <c r="AJ4" s="394" t="n"/>
+      <c r="AK4" s="394" t="n"/>
+      <c r="AL4" s="394" t="n"/>
+      <c r="AM4" s="394" t="n"/>
+      <c r="AN4" s="395" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="283" t="n"/>
-      <c r="C5" s="283" t="n"/>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="A5" s="396" t="n"/>
+      <c r="B5" s="394" t="n"/>
+      <c r="C5" s="394" t="n"/>
+      <c r="D5" s="394" t="n"/>
+      <c r="E5" s="394" t="n"/>
+      <c r="F5" s="394" t="n"/>
+      <c r="G5" s="394" t="n"/>
+      <c r="H5" s="394" t="n"/>
+      <c r="I5" s="341" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="283" t="n"/>
-      <c r="M5" s="283" t="n"/>
-      <c r="N5" s="283" t="n"/>
-      <c r="O5" s="283" t="n"/>
-      <c r="P5" s="283" t="n"/>
-      <c r="Q5" s="283" t="n"/>
-      <c r="R5" s="283" t="n"/>
-      <c r="S5" s="283" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="283" t="n"/>
-      <c r="X5" s="283" t="n"/>
-      <c r="Y5" s="283" t="n"/>
-      <c r="Z5" s="283" t="n"/>
-      <c r="AA5" s="283" t="n"/>
-      <c r="AB5" s="283" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="284" t="inlineStr">
+      <c r="J5" s="394" t="n"/>
+      <c r="K5" s="394" t="n"/>
+      <c r="L5" s="394" t="n"/>
+      <c r="M5" s="394" t="n"/>
+      <c r="N5" s="394" t="n"/>
+      <c r="O5" s="394" t="n"/>
+      <c r="P5" s="394" t="n"/>
+      <c r="Q5" s="394" t="n"/>
+      <c r="R5" s="394" t="n"/>
+      <c r="S5" s="394" t="n"/>
+      <c r="T5" s="394" t="n"/>
+      <c r="U5" s="394" t="n"/>
+      <c r="V5" s="394" t="n"/>
+      <c r="W5" s="394" t="n"/>
+      <c r="X5" s="394" t="n"/>
+      <c r="Y5" s="394" t="n"/>
+      <c r="Z5" s="394" t="n"/>
+      <c r="AA5" s="394" t="n"/>
+      <c r="AB5" s="394" t="n"/>
+      <c r="AC5" s="394" t="n"/>
+      <c r="AD5" s="394" t="n"/>
+      <c r="AE5" s="335" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="283" t="n"/>
-      <c r="AG5" s="283" t="n"/>
-      <c r="AH5" s="285" t="n"/>
-      <c r="AI5" s="286" t="inlineStr">
+      <c r="AF5" s="394" t="n"/>
+      <c r="AG5" s="394" t="n"/>
+      <c r="AH5" s="395" t="n"/>
+      <c r="AI5" s="338" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="283" t="n"/>
-      <c r="AK5" s="283" t="n"/>
-      <c r="AL5" s="283" t="n"/>
-      <c r="AM5" s="283" t="n"/>
-      <c r="AN5" s="287" t="n"/>
+      <c r="AJ5" s="394" t="n"/>
+      <c r="AK5" s="394" t="n"/>
+      <c r="AL5" s="394" t="n"/>
+      <c r="AM5" s="394" t="n"/>
+      <c r="AN5" s="395" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="inlineStr"/>
+      <c r="A6" s="342" t="inlineStr"/>
+      <c r="B6" s="389" t="n"/>
+      <c r="C6" s="389" t="n"/>
+      <c r="D6" s="389" t="n"/>
+      <c r="E6" s="389" t="n"/>
+      <c r="F6" s="389" t="n"/>
+      <c r="G6" s="389" t="n"/>
+      <c r="H6" s="389" t="n"/>
+      <c r="I6" s="389" t="n"/>
+      <c r="J6" s="389" t="n"/>
+      <c r="K6" s="389" t="n"/>
+      <c r="L6" s="389" t="n"/>
+      <c r="M6" s="389" t="n"/>
+      <c r="N6" s="389" t="n"/>
+      <c r="O6" s="389" t="n"/>
+      <c r="P6" s="389" t="n"/>
+      <c r="Q6" s="389" t="n"/>
+      <c r="R6" s="389" t="n"/>
+      <c r="S6" s="389" t="n"/>
+      <c r="T6" s="389" t="n"/>
+      <c r="U6" s="389" t="n"/>
+      <c r="V6" s="389" t="n"/>
+      <c r="W6" s="389" t="n"/>
+      <c r="X6" s="389" t="n"/>
+      <c r="Y6" s="389" t="n"/>
+      <c r="Z6" s="389" t="n"/>
+      <c r="AA6" s="389" t="n"/>
+      <c r="AB6" s="389" t="n"/>
+      <c r="AC6" s="389" t="n"/>
+      <c r="AD6" s="389" t="n"/>
+      <c r="AE6" s="389" t="n"/>
+      <c r="AF6" s="389" t="n"/>
+      <c r="AG6" s="389" t="n"/>
+      <c r="AH6" s="389" t="n"/>
+      <c r="AI6" s="389" t="n"/>
+      <c r="AJ6" s="389" t="n"/>
+      <c r="AK6" s="389" t="n"/>
+      <c r="AL6" s="389" t="n"/>
+      <c r="AM6" s="389" t="n"/>
+      <c r="AN6" s="389" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="288" t="inlineStr">
+      <c r="A7" s="343" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. PRINT REQUEST / CONTROL CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="289" t="n"/>
-      <c r="L7" s="289" t="n"/>
-      <c r="M7" s="289" t="n"/>
-      <c r="N7" s="289" t="n"/>
-      <c r="O7" s="289" t="n"/>
-      <c r="P7" s="289" t="n"/>
-      <c r="Q7" s="289" t="n"/>
-      <c r="R7" s="289" t="n"/>
-      <c r="S7" s="289" t="n"/>
-      <c r="T7" s="289" t="n"/>
-      <c r="U7" s="289" t="n"/>
-      <c r="V7" s="289" t="n"/>
-      <c r="W7" s="289" t="n"/>
-      <c r="X7" s="289" t="n"/>
-      <c r="Y7" s="289" t="n"/>
-      <c r="Z7" s="289" t="n"/>
-      <c r="AA7" s="289" t="n"/>
-      <c r="AB7" s="289" t="n"/>
-      <c r="AC7" s="289" t="n"/>
-      <c r="AD7" s="289" t="n"/>
-      <c r="AE7" s="289" t="n"/>
-      <c r="AF7" s="289" t="n"/>
-      <c r="AG7" s="289" t="n"/>
-      <c r="AH7" s="289" t="n"/>
-      <c r="AI7" s="289" t="n"/>
-      <c r="AJ7" s="289" t="n"/>
-      <c r="AK7" s="289" t="n"/>
-      <c r="AL7" s="289" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="290" t="n"/>
+      <c r="B7" s="391" t="n"/>
+      <c r="C7" s="391" t="n"/>
+      <c r="D7" s="391" t="n"/>
+      <c r="E7" s="391" t="n"/>
+      <c r="F7" s="391" t="n"/>
+      <c r="G7" s="391" t="n"/>
+      <c r="H7" s="391" t="n"/>
+      <c r="I7" s="391" t="n"/>
+      <c r="J7" s="391" t="n"/>
+      <c r="K7" s="391" t="n"/>
+      <c r="L7" s="391" t="n"/>
+      <c r="M7" s="391" t="n"/>
+      <c r="N7" s="391" t="n"/>
+      <c r="O7" s="391" t="n"/>
+      <c r="P7" s="391" t="n"/>
+      <c r="Q7" s="391" t="n"/>
+      <c r="R7" s="391" t="n"/>
+      <c r="S7" s="391" t="n"/>
+      <c r="T7" s="391" t="n"/>
+      <c r="U7" s="391" t="n"/>
+      <c r="V7" s="391" t="n"/>
+      <c r="W7" s="391" t="n"/>
+      <c r="X7" s="391" t="n"/>
+      <c r="Y7" s="391" t="n"/>
+      <c r="Z7" s="391" t="n"/>
+      <c r="AA7" s="391" t="n"/>
+      <c r="AB7" s="391" t="n"/>
+      <c r="AC7" s="391" t="n"/>
+      <c r="AD7" s="391" t="n"/>
+      <c r="AE7" s="391" t="n"/>
+      <c r="AF7" s="391" t="n"/>
+      <c r="AG7" s="391" t="n"/>
+      <c r="AH7" s="391" t="n"/>
+      <c r="AI7" s="391" t="n"/>
+      <c r="AJ7" s="391" t="n"/>
+      <c r="AK7" s="391" t="n"/>
+      <c r="AL7" s="391" t="n"/>
+      <c r="AM7" s="391" t="n"/>
+      <c r="AN7" s="392" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="291" t="inlineStr">
+      <c r="A8" s="344" t="inlineStr">
         <is>
           <t>WIP Tag ID</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="272" t="n"/>
-      <c r="H8" s="292">
+      <c r="B8" s="380" t="n"/>
+      <c r="C8" s="380" t="n"/>
+      <c r="D8" s="380" t="n"/>
+      <c r="E8" s="380" t="n"/>
+      <c r="F8" s="380" t="n"/>
+      <c r="G8" s="381" t="n"/>
+      <c r="H8" s="347">
         <f>IF(GENERATOR!$B$5="","",GENERATOR!$B$5)</f>
         <v/>
       </c>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="271" t="n"/>
-      <c r="K8" s="271" t="n"/>
-      <c r="L8" s="271" t="n"/>
-      <c r="M8" s="271" t="n"/>
-      <c r="N8" s="271" t="n"/>
-      <c r="O8" s="271" t="n"/>
-      <c r="P8" s="271" t="n"/>
-      <c r="Q8" s="271" t="n"/>
-      <c r="R8" s="271" t="n"/>
-      <c r="S8" s="271" t="n"/>
-      <c r="T8" s="272" t="n"/>
-      <c r="U8" s="293" t="inlineStr">
+      <c r="I8" s="380" t="n"/>
+      <c r="J8" s="380" t="n"/>
+      <c r="K8" s="380" t="n"/>
+      <c r="L8" s="380" t="n"/>
+      <c r="M8" s="380" t="n"/>
+      <c r="N8" s="380" t="n"/>
+      <c r="O8" s="380" t="n"/>
+      <c r="P8" s="380" t="n"/>
+      <c r="Q8" s="380" t="n"/>
+      <c r="R8" s="380" t="n"/>
+      <c r="S8" s="380" t="n"/>
+      <c r="T8" s="381" t="n"/>
+      <c r="U8" s="348" t="inlineStr">
         <is>
           <t>Print Status</t>
         </is>
       </c>
-      <c r="V8" s="271" t="n"/>
-      <c r="W8" s="271" t="n"/>
-      <c r="X8" s="271" t="n"/>
-      <c r="Y8" s="271" t="n"/>
-      <c r="Z8" s="271" t="n"/>
-      <c r="AA8" s="272" t="n"/>
-      <c r="AB8" s="294">
+      <c r="V8" s="380" t="n"/>
+      <c r="W8" s="380" t="n"/>
+      <c r="X8" s="380" t="n"/>
+      <c r="Y8" s="380" t="n"/>
+      <c r="Z8" s="380" t="n"/>
+      <c r="AA8" s="381" t="n"/>
+      <c r="AB8" s="347">
         <f>IF(GENERATOR!$B$12="","",GENERATOR!$B$12)</f>
         <v/>
       </c>
-      <c r="AC8" s="271" t="n"/>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="271" t="n"/>
-      <c r="AM8" s="271" t="n"/>
-      <c r="AN8" s="274" t="n"/>
+      <c r="AC8" s="380" t="n"/>
+      <c r="AD8" s="380" t="n"/>
+      <c r="AE8" s="380" t="n"/>
+      <c r="AF8" s="380" t="n"/>
+      <c r="AG8" s="380" t="n"/>
+      <c r="AH8" s="380" t="n"/>
+      <c r="AI8" s="380" t="n"/>
+      <c r="AJ8" s="380" t="n"/>
+      <c r="AK8" s="380" t="n"/>
+      <c r="AL8" s="380" t="n"/>
+      <c r="AM8" s="380" t="n"/>
+      <c r="AN8" s="381" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="295" t="inlineStr">
+      <c r="A9" s="349" t="inlineStr">
         <is>
           <t>Job / Lot / Part / Revision</t>
         </is>
       </c>
-      <c r="B9" s="277" t="n"/>
-      <c r="C9" s="277" t="n"/>
-      <c r="D9" s="277" t="n"/>
-      <c r="E9" s="277" t="n"/>
-      <c r="F9" s="277" t="n"/>
-      <c r="G9" s="278" t="n"/>
-      <c r="H9" s="296">
+      <c r="B9" s="382" t="n"/>
+      <c r="C9" s="382" t="n"/>
+      <c r="D9" s="382" t="n"/>
+      <c r="E9" s="382" t="n"/>
+      <c r="F9" s="382" t="n"/>
+      <c r="G9" s="383" t="n"/>
+      <c r="H9" s="338">
         <f>IF(GENERATOR!$B$6="","",GENERATOR!$B$6)</f>
         <v/>
       </c>
-      <c r="I9" s="277" t="n"/>
-      <c r="J9" s="277" t="n"/>
-      <c r="K9" s="277" t="n"/>
-      <c r="L9" s="277" t="n"/>
-      <c r="M9" s="277" t="n"/>
-      <c r="N9" s="277" t="n"/>
-      <c r="O9" s="277" t="n"/>
-      <c r="P9" s="277" t="n"/>
-      <c r="Q9" s="277" t="n"/>
-      <c r="R9" s="277" t="n"/>
-      <c r="S9" s="277" t="n"/>
-      <c r="T9" s="278" t="n"/>
-      <c r="U9" s="297" t="inlineStr">
+      <c r="I9" s="382" t="n"/>
+      <c r="J9" s="382" t="n"/>
+      <c r="K9" s="382" t="n"/>
+      <c r="L9" s="382" t="n"/>
+      <c r="M9" s="382" t="n"/>
+      <c r="N9" s="382" t="n"/>
+      <c r="O9" s="382" t="n"/>
+      <c r="P9" s="382" t="n"/>
+      <c r="Q9" s="382" t="n"/>
+      <c r="R9" s="382" t="n"/>
+      <c r="S9" s="382" t="n"/>
+      <c r="T9" s="383" t="n"/>
+      <c r="U9" s="352" t="inlineStr">
         <is>
           <t>Current Operation / Qty</t>
         </is>
       </c>
-      <c r="V9" s="277" t="n"/>
-      <c r="W9" s="277" t="n"/>
-      <c r="X9" s="277" t="n"/>
-      <c r="Y9" s="277" t="n"/>
-      <c r="Z9" s="277" t="n"/>
-      <c r="AA9" s="278" t="n"/>
-      <c r="AB9" s="279">
+      <c r="V9" s="382" t="n"/>
+      <c r="W9" s="382" t="n"/>
+      <c r="X9" s="382" t="n"/>
+      <c r="Y9" s="382" t="n"/>
+      <c r="Z9" s="382" t="n"/>
+      <c r="AA9" s="383" t="n"/>
+      <c r="AB9" s="338">
         <f>IF(GENERATOR!$B$13="","",GENERATOR!$B$13)</f>
         <v/>
       </c>
-      <c r="AC9" s="277" t="n"/>
-      <c r="AD9" s="277" t="n"/>
-      <c r="AE9" s="277" t="n"/>
-      <c r="AF9" s="277" t="n"/>
-      <c r="AG9" s="277" t="n"/>
-      <c r="AH9" s="277" t="n"/>
-      <c r="AI9" s="277" t="n"/>
-      <c r="AJ9" s="277" t="n"/>
-      <c r="AK9" s="277" t="n"/>
-      <c r="AL9" s="277" t="n"/>
-      <c r="AM9" s="277" t="n"/>
-      <c r="AN9" s="280" t="n"/>
+      <c r="AC9" s="382" t="n"/>
+      <c r="AD9" s="382" t="n"/>
+      <c r="AE9" s="382" t="n"/>
+      <c r="AF9" s="382" t="n"/>
+      <c r="AG9" s="382" t="n"/>
+      <c r="AH9" s="382" t="n"/>
+      <c r="AI9" s="382" t="n"/>
+      <c r="AJ9" s="382" t="n"/>
+      <c r="AK9" s="382" t="n"/>
+      <c r="AL9" s="382" t="n"/>
+      <c r="AM9" s="382" t="n"/>
+      <c r="AN9" s="383" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="295" t="inlineStr">
+      <c r="A10" s="349" t="inlineStr">
         <is>
           <t>Area / Location / Room</t>
         </is>
       </c>
-      <c r="B10" s="277" t="n"/>
-      <c r="C10" s="277" t="n"/>
-      <c r="D10" s="277" t="n"/>
-      <c r="E10" s="277" t="n"/>
-      <c r="F10" s="277" t="n"/>
-      <c r="G10" s="278" t="n"/>
-      <c r="H10" s="296">
+      <c r="B10" s="382" t="n"/>
+      <c r="C10" s="382" t="n"/>
+      <c r="D10" s="382" t="n"/>
+      <c r="E10" s="382" t="n"/>
+      <c r="F10" s="382" t="n"/>
+      <c r="G10" s="383" t="n"/>
+      <c r="H10" s="338">
         <f>IF(GENERATOR!$B$7="","",GENERATOR!$B$7)</f>
         <v/>
       </c>
-      <c r="I10" s="277" t="n"/>
-      <c r="J10" s="277" t="n"/>
-      <c r="K10" s="277" t="n"/>
-      <c r="L10" s="277" t="n"/>
-      <c r="M10" s="277" t="n"/>
-      <c r="N10" s="277" t="n"/>
-      <c r="O10" s="277" t="n"/>
-      <c r="P10" s="277" t="n"/>
-      <c r="Q10" s="277" t="n"/>
-      <c r="R10" s="277" t="n"/>
-      <c r="S10" s="277" t="n"/>
-      <c r="T10" s="278" t="n"/>
-      <c r="U10" s="297" t="inlineStr">
+      <c r="I10" s="382" t="n"/>
+      <c r="J10" s="382" t="n"/>
+      <c r="K10" s="382" t="n"/>
+      <c r="L10" s="382" t="n"/>
+      <c r="M10" s="382" t="n"/>
+      <c r="N10" s="382" t="n"/>
+      <c r="O10" s="382" t="n"/>
+      <c r="P10" s="382" t="n"/>
+      <c r="Q10" s="382" t="n"/>
+      <c r="R10" s="382" t="n"/>
+      <c r="S10" s="382" t="n"/>
+      <c r="T10" s="383" t="n"/>
+      <c r="U10" s="352" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="V10" s="277" t="n"/>
-      <c r="W10" s="277" t="n"/>
-      <c r="X10" s="277" t="n"/>
-      <c r="Y10" s="277" t="n"/>
-      <c r="Z10" s="277" t="n"/>
-      <c r="AA10" s="278" t="n"/>
-      <c r="AB10" s="279">
+      <c r="V10" s="382" t="n"/>
+      <c r="W10" s="382" t="n"/>
+      <c r="X10" s="382" t="n"/>
+      <c r="Y10" s="382" t="n"/>
+      <c r="Z10" s="382" t="n"/>
+      <c r="AA10" s="383" t="n"/>
+      <c r="AB10" s="338">
         <f>IF(GENERATOR!$B$14="","",GENERATOR!$B$14)</f>
         <v/>
       </c>
-      <c r="AC10" s="277" t="n"/>
-      <c r="AD10" s="277" t="n"/>
-      <c r="AE10" s="277" t="n"/>
-      <c r="AF10" s="277" t="n"/>
-      <c r="AG10" s="277" t="n"/>
-      <c r="AH10" s="277" t="n"/>
-      <c r="AI10" s="277" t="n"/>
-      <c r="AJ10" s="277" t="n"/>
-      <c r="AK10" s="277" t="n"/>
-      <c r="AL10" s="277" t="n"/>
-      <c r="AM10" s="277" t="n"/>
-      <c r="AN10" s="280" t="n"/>
+      <c r="AC10" s="382" t="n"/>
+      <c r="AD10" s="382" t="n"/>
+      <c r="AE10" s="382" t="n"/>
+      <c r="AF10" s="382" t="n"/>
+      <c r="AG10" s="382" t="n"/>
+      <c r="AH10" s="382" t="n"/>
+      <c r="AI10" s="382" t="n"/>
+      <c r="AJ10" s="382" t="n"/>
+      <c r="AK10" s="382" t="n"/>
+      <c r="AL10" s="382" t="n"/>
+      <c r="AM10" s="382" t="n"/>
+      <c r="AN10" s="383" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="295" t="inlineStr">
+      <c r="A11" s="349" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B11" s="277" t="n"/>
-      <c r="C11" s="277" t="n"/>
-      <c r="D11" s="277" t="n"/>
-      <c r="E11" s="277" t="n"/>
-      <c r="F11" s="277" t="n"/>
-      <c r="G11" s="278" t="n"/>
-      <c r="H11" s="296">
+      <c r="B11" s="382" t="n"/>
+      <c r="C11" s="382" t="n"/>
+      <c r="D11" s="382" t="n"/>
+      <c r="E11" s="382" t="n"/>
+      <c r="F11" s="382" t="n"/>
+      <c r="G11" s="383" t="n"/>
+      <c r="H11" s="338">
         <f>IF(GENERATOR!$B$8="","",GENERATOR!$B$8)</f>
         <v/>
       </c>
-      <c r="I11" s="277" t="n"/>
-      <c r="J11" s="277" t="n"/>
-      <c r="K11" s="277" t="n"/>
-      <c r="L11" s="277" t="n"/>
-      <c r="M11" s="277" t="n"/>
-      <c r="N11" s="277" t="n"/>
-      <c r="O11" s="277" t="n"/>
-      <c r="P11" s="277" t="n"/>
-      <c r="Q11" s="277" t="n"/>
-      <c r="R11" s="277" t="n"/>
-      <c r="S11" s="277" t="n"/>
-      <c r="T11" s="278" t="n"/>
-      <c r="U11" s="297" t="inlineStr">
+      <c r="I11" s="382" t="n"/>
+      <c r="J11" s="382" t="n"/>
+      <c r="K11" s="382" t="n"/>
+      <c r="L11" s="382" t="n"/>
+      <c r="M11" s="382" t="n"/>
+      <c r="N11" s="382" t="n"/>
+      <c r="O11" s="382" t="n"/>
+      <c r="P11" s="382" t="n"/>
+      <c r="Q11" s="382" t="n"/>
+      <c r="R11" s="382" t="n"/>
+      <c r="S11" s="382" t="n"/>
+      <c r="T11" s="383" t="n"/>
+      <c r="U11" s="352" t="inlineStr">
         <is>
           <t>Print Qty / Application Status</t>
         </is>
       </c>
-      <c r="V11" s="277" t="n"/>
-      <c r="W11" s="277" t="n"/>
-      <c r="X11" s="277" t="n"/>
-      <c r="Y11" s="277" t="n"/>
-      <c r="Z11" s="277" t="n"/>
-      <c r="AA11" s="278" t="n"/>
-      <c r="AB11" s="279">
+      <c r="V11" s="382" t="n"/>
+      <c r="W11" s="382" t="n"/>
+      <c r="X11" s="382" t="n"/>
+      <c r="Y11" s="382" t="n"/>
+      <c r="Z11" s="382" t="n"/>
+      <c r="AA11" s="383" t="n"/>
+      <c r="AB11" s="338">
         <f>IF(GENERATOR!$B$15="","",GENERATOR!$B$15)</f>
         <v/>
       </c>
-      <c r="AC11" s="277" t="n"/>
-      <c r="AD11" s="277" t="n"/>
-      <c r="AE11" s="277" t="n"/>
-      <c r="AF11" s="277" t="n"/>
-      <c r="AG11" s="277" t="n"/>
-      <c r="AH11" s="277" t="n"/>
-      <c r="AI11" s="277" t="n"/>
-      <c r="AJ11" s="277" t="n"/>
-      <c r="AK11" s="277" t="n"/>
-      <c r="AL11" s="277" t="n"/>
-      <c r="AM11" s="277" t="n"/>
-      <c r="AN11" s="280" t="n"/>
+      <c r="AC11" s="382" t="n"/>
+      <c r="AD11" s="382" t="n"/>
+      <c r="AE11" s="382" t="n"/>
+      <c r="AF11" s="382" t="n"/>
+      <c r="AG11" s="382" t="n"/>
+      <c r="AH11" s="382" t="n"/>
+      <c r="AI11" s="382" t="n"/>
+      <c r="AJ11" s="382" t="n"/>
+      <c r="AK11" s="382" t="n"/>
+      <c r="AL11" s="382" t="n"/>
+      <c r="AM11" s="382" t="n"/>
+      <c r="AN11" s="383" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="298" t="inlineStr">
+      <c r="A12" s="349" t="inlineStr">
         <is>
           <t>Encoded Data Ref</t>
         </is>
       </c>
-      <c r="B12" s="283" t="n"/>
-      <c r="C12" s="283" t="n"/>
-      <c r="D12" s="283" t="n"/>
-      <c r="E12" s="283" t="n"/>
-      <c r="F12" s="283" t="n"/>
-      <c r="G12" s="285" t="n"/>
-      <c r="H12" s="299">
+      <c r="B12" s="382" t="n"/>
+      <c r="C12" s="382" t="n"/>
+      <c r="D12" s="382" t="n"/>
+      <c r="E12" s="382" t="n"/>
+      <c r="F12" s="382" t="n"/>
+      <c r="G12" s="383" t="n"/>
+      <c r="H12" s="338">
         <f>IF(GENERATOR!$B$9="","",GENERATOR!$B$9)</f>
         <v/>
       </c>
-      <c r="I12" s="283" t="n"/>
-      <c r="J12" s="283" t="n"/>
-      <c r="K12" s="283" t="n"/>
-      <c r="L12" s="283" t="n"/>
-      <c r="M12" s="283" t="n"/>
-      <c r="N12" s="283" t="n"/>
-      <c r="O12" s="283" t="n"/>
-      <c r="P12" s="283" t="n"/>
-      <c r="Q12" s="283" t="n"/>
-      <c r="R12" s="283" t="n"/>
-      <c r="S12" s="283" t="n"/>
-      <c r="T12" s="285" t="n"/>
-      <c r="U12" s="300" t="inlineStr">
+      <c r="I12" s="382" t="n"/>
+      <c r="J12" s="382" t="n"/>
+      <c r="K12" s="382" t="n"/>
+      <c r="L12" s="382" t="n"/>
+      <c r="M12" s="382" t="n"/>
+      <c r="N12" s="382" t="n"/>
+      <c r="O12" s="382" t="n"/>
+      <c r="P12" s="382" t="n"/>
+      <c r="Q12" s="382" t="n"/>
+      <c r="R12" s="382" t="n"/>
+      <c r="S12" s="382" t="n"/>
+      <c r="T12" s="383" t="n"/>
+      <c r="U12" s="352" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="V12" s="283" t="n"/>
-      <c r="W12" s="283" t="n"/>
-      <c r="X12" s="283" t="n"/>
-      <c r="Y12" s="283" t="n"/>
-      <c r="Z12" s="283" t="n"/>
-      <c r="AA12" s="285" t="n"/>
-      <c r="AB12" s="286">
+      <c r="V12" s="382" t="n"/>
+      <c r="W12" s="382" t="n"/>
+      <c r="X12" s="382" t="n"/>
+      <c r="Y12" s="382" t="n"/>
+      <c r="Z12" s="382" t="n"/>
+      <c r="AA12" s="383" t="n"/>
+      <c r="AB12" s="338">
         <f>IF(GENERATOR!$B$16="","",GENERATOR!$B$16)</f>
         <v/>
       </c>
-      <c r="AC12" s="283" t="n"/>
-      <c r="AD12" s="283" t="n"/>
-      <c r="AE12" s="283" t="n"/>
-      <c r="AF12" s="283" t="n"/>
-      <c r="AG12" s="283" t="n"/>
-      <c r="AH12" s="283" t="n"/>
-      <c r="AI12" s="283" t="n"/>
-      <c r="AJ12" s="283" t="n"/>
-      <c r="AK12" s="283" t="n"/>
-      <c r="AL12" s="283" t="n"/>
-      <c r="AM12" s="283" t="n"/>
-      <c r="AN12" s="287" t="n"/>
+      <c r="AC12" s="382" t="n"/>
+      <c r="AD12" s="382" t="n"/>
+      <c r="AE12" s="382" t="n"/>
+      <c r="AF12" s="382" t="n"/>
+      <c r="AG12" s="382" t="n"/>
+      <c r="AH12" s="382" t="n"/>
+      <c r="AI12" s="382" t="n"/>
+      <c r="AJ12" s="382" t="n"/>
+      <c r="AK12" s="382" t="n"/>
+      <c r="AL12" s="382" t="n"/>
+      <c r="AM12" s="382" t="n"/>
+      <c r="AN12" s="383" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="288" t="inlineStr">
+      <c r="A13" s="342" t="n"/>
+      <c r="B13" s="389" t="n"/>
+      <c r="C13" s="389" t="n"/>
+      <c r="D13" s="389" t="n"/>
+      <c r="E13" s="389" t="n"/>
+      <c r="F13" s="389" t="n"/>
+      <c r="G13" s="389" t="n"/>
+      <c r="H13" s="389" t="n"/>
+      <c r="I13" s="389" t="n"/>
+      <c r="J13" s="389" t="n"/>
+      <c r="K13" s="389" t="n"/>
+      <c r="L13" s="389" t="n"/>
+      <c r="M13" s="389" t="n"/>
+      <c r="N13" s="389" t="n"/>
+      <c r="O13" s="389" t="n"/>
+      <c r="P13" s="389" t="n"/>
+      <c r="Q13" s="389" t="n"/>
+      <c r="R13" s="389" t="n"/>
+      <c r="S13" s="389" t="n"/>
+      <c r="T13" s="389" t="n"/>
+      <c r="U13" s="389" t="n"/>
+      <c r="V13" s="389" t="n"/>
+      <c r="W13" s="389" t="n"/>
+      <c r="X13" s="389" t="n"/>
+      <c r="Y13" s="389" t="n"/>
+      <c r="Z13" s="389" t="n"/>
+      <c r="AA13" s="389" t="n"/>
+      <c r="AB13" s="389" t="n"/>
+      <c r="AC13" s="389" t="n"/>
+      <c r="AD13" s="389" t="n"/>
+      <c r="AE13" s="389" t="n"/>
+      <c r="AF13" s="389" t="n"/>
+      <c r="AG13" s="389" t="n"/>
+      <c r="AH13" s="389" t="n"/>
+      <c r="AI13" s="389" t="n"/>
+      <c r="AJ13" s="389" t="n"/>
+      <c r="AK13" s="389" t="n"/>
+      <c r="AL13" s="389" t="n"/>
+      <c r="AM13" s="389" t="n"/>
+      <c r="AN13" s="389" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="343" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. PRINTED FACE / CONTROLLED IDENTITY</t>
         </is>
       </c>
-      <c r="B14" s="289" t="n"/>
-      <c r="C14" s="289" t="n"/>
-      <c r="D14" s="289" t="n"/>
-      <c r="E14" s="289" t="n"/>
-      <c r="F14" s="289" t="n"/>
-      <c r="G14" s="289" t="n"/>
-      <c r="H14" s="289" t="n"/>
-      <c r="I14" s="289" t="n"/>
-      <c r="J14" s="289" t="n"/>
-      <c r="K14" s="289" t="n"/>
-      <c r="L14" s="289" t="n"/>
-      <c r="M14" s="289" t="n"/>
-      <c r="N14" s="289" t="n"/>
-      <c r="O14" s="289" t="n"/>
-      <c r="P14" s="289" t="n"/>
-      <c r="Q14" s="289" t="n"/>
-      <c r="R14" s="289" t="n"/>
-      <c r="S14" s="289" t="n"/>
-      <c r="T14" s="289" t="n"/>
-      <c r="U14" s="289" t="n"/>
-      <c r="V14" s="289" t="n"/>
-      <c r="W14" s="289" t="n"/>
-      <c r="X14" s="289" t="n"/>
-      <c r="Y14" s="289" t="n"/>
-      <c r="Z14" s="289" t="n"/>
-      <c r="AA14" s="289" t="n"/>
-      <c r="AB14" s="289" t="n"/>
-      <c r="AC14" s="289" t="n"/>
-      <c r="AD14" s="289" t="n"/>
-      <c r="AE14" s="289" t="n"/>
-      <c r="AF14" s="289" t="n"/>
-      <c r="AG14" s="289" t="n"/>
-      <c r="AH14" s="289" t="n"/>
-      <c r="AI14" s="289" t="n"/>
-      <c r="AJ14" s="289" t="n"/>
-      <c r="AK14" s="289" t="n"/>
-      <c r="AL14" s="289" t="n"/>
-      <c r="AM14" s="289" t="n"/>
-      <c r="AN14" s="290" t="n"/>
+      <c r="B14" s="380" t="n"/>
+      <c r="C14" s="380" t="n"/>
+      <c r="D14" s="380" t="n"/>
+      <c r="E14" s="380" t="n"/>
+      <c r="F14" s="380" t="n"/>
+      <c r="G14" s="380" t="n"/>
+      <c r="H14" s="380" t="n"/>
+      <c r="I14" s="380" t="n"/>
+      <c r="J14" s="380" t="n"/>
+      <c r="K14" s="380" t="n"/>
+      <c r="L14" s="380" t="n"/>
+      <c r="M14" s="380" t="n"/>
+      <c r="N14" s="380" t="n"/>
+      <c r="O14" s="380" t="n"/>
+      <c r="P14" s="380" t="n"/>
+      <c r="Q14" s="380" t="n"/>
+      <c r="R14" s="380" t="n"/>
+      <c r="S14" s="380" t="n"/>
+      <c r="T14" s="380" t="n"/>
+      <c r="U14" s="380" t="n"/>
+      <c r="V14" s="380" t="n"/>
+      <c r="W14" s="380" t="n"/>
+      <c r="X14" s="380" t="n"/>
+      <c r="Y14" s="380" t="n"/>
+      <c r="Z14" s="380" t="n"/>
+      <c r="AA14" s="380" t="n"/>
+      <c r="AB14" s="380" t="n"/>
+      <c r="AC14" s="380" t="n"/>
+      <c r="AD14" s="380" t="n"/>
+      <c r="AE14" s="380" t="n"/>
+      <c r="AF14" s="380" t="n"/>
+      <c r="AG14" s="380" t="n"/>
+      <c r="AH14" s="380" t="n"/>
+      <c r="AI14" s="380" t="n"/>
+      <c r="AJ14" s="380" t="n"/>
+      <c r="AK14" s="380" t="n"/>
+      <c r="AL14" s="380" t="n"/>
+      <c r="AM14" s="380" t="n"/>
+      <c r="AN14" s="381" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+      <c r="A15" s="344" t="inlineStr">
         <is>
           <t>Tag Face / Status</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="271" t="n"/>
-      <c r="D15" s="271" t="n"/>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="272" t="n"/>
-      <c r="H15" s="292">
+      <c r="B15" s="380" t="n"/>
+      <c r="C15" s="380" t="n"/>
+      <c r="D15" s="380" t="n"/>
+      <c r="E15" s="380" t="n"/>
+      <c r="F15" s="380" t="n"/>
+      <c r="G15" s="381" t="n"/>
+      <c r="H15" s="347">
         <f>IF(GENERATOR!$B$19="","",GENERATOR!$B$19)</f>
         <v/>
       </c>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="271" t="n"/>
-      <c r="K15" s="271" t="n"/>
-      <c r="L15" s="271" t="n"/>
-      <c r="M15" s="271" t="n"/>
-      <c r="N15" s="271" t="n"/>
-      <c r="O15" s="271" t="n"/>
-      <c r="P15" s="271" t="n"/>
-      <c r="Q15" s="271" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="271" t="n"/>
-      <c r="T15" s="272" t="n"/>
-      <c r="U15" s="293" t="inlineStr">
+      <c r="I15" s="380" t="n"/>
+      <c r="J15" s="380" t="n"/>
+      <c r="K15" s="380" t="n"/>
+      <c r="L15" s="380" t="n"/>
+      <c r="M15" s="380" t="n"/>
+      <c r="N15" s="380" t="n"/>
+      <c r="O15" s="380" t="n"/>
+      <c r="P15" s="380" t="n"/>
+      <c r="Q15" s="380" t="n"/>
+      <c r="R15" s="380" t="n"/>
+      <c r="S15" s="380" t="n"/>
+      <c r="T15" s="381" t="n"/>
+      <c r="U15" s="348" t="inlineStr">
         <is>
           <t>Operation / Workcenter</t>
         </is>
       </c>
-      <c r="V15" s="271" t="n"/>
-      <c r="W15" s="271" t="n"/>
-      <c r="X15" s="271" t="n"/>
-      <c r="Y15" s="271" t="n"/>
-      <c r="Z15" s="271" t="n"/>
-      <c r="AA15" s="272" t="n"/>
-      <c r="AB15" s="294">
+      <c r="V15" s="380" t="n"/>
+      <c r="W15" s="380" t="n"/>
+      <c r="X15" s="380" t="n"/>
+      <c r="Y15" s="380" t="n"/>
+      <c r="Z15" s="380" t="n"/>
+      <c r="AA15" s="381" t="n"/>
+      <c r="AB15" s="347">
         <f>IF(GENERATOR!$B$20="","",GENERATOR!$B$20)</f>
         <v/>
       </c>
-      <c r="AC15" s="271" t="n"/>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="271" t="n"/>
-      <c r="AN15" s="274" t="n"/>
+      <c r="AC15" s="380" t="n"/>
+      <c r="AD15" s="380" t="n"/>
+      <c r="AE15" s="380" t="n"/>
+      <c r="AF15" s="380" t="n"/>
+      <c r="AG15" s="380" t="n"/>
+      <c r="AH15" s="380" t="n"/>
+      <c r="AI15" s="380" t="n"/>
+      <c r="AJ15" s="380" t="n"/>
+      <c r="AK15" s="380" t="n"/>
+      <c r="AL15" s="380" t="n"/>
+      <c r="AM15" s="380" t="n"/>
+      <c r="AN15" s="381" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="295" t="inlineStr">
+      <c r="A16" s="349" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B16" s="277" t="n"/>
-      <c r="C16" s="277" t="n"/>
-      <c r="D16" s="277" t="n"/>
-      <c r="E16" s="277" t="n"/>
-      <c r="F16" s="277" t="n"/>
-      <c r="G16" s="278" t="n"/>
-      <c r="H16" s="296">
+      <c r="B16" s="382" t="n"/>
+      <c r="C16" s="382" t="n"/>
+      <c r="D16" s="382" t="n"/>
+      <c r="E16" s="382" t="n"/>
+      <c r="F16" s="382" t="n"/>
+      <c r="G16" s="383" t="n"/>
+      <c r="H16" s="338">
         <f>IF(GENERATOR!$B$21="","",GENERATOR!$B$21)</f>
         <v/>
       </c>
-      <c r="I16" s="277" t="n"/>
-      <c r="J16" s="277" t="n"/>
-      <c r="K16" s="277" t="n"/>
-      <c r="L16" s="277" t="n"/>
-      <c r="M16" s="277" t="n"/>
-      <c r="N16" s="277" t="n"/>
-      <c r="O16" s="277" t="n"/>
-      <c r="P16" s="277" t="n"/>
-      <c r="Q16" s="277" t="n"/>
-      <c r="R16" s="277" t="n"/>
-      <c r="S16" s="277" t="n"/>
-      <c r="T16" s="278" t="n"/>
-      <c r="U16" s="297" t="inlineStr">
+      <c r="I16" s="382" t="n"/>
+      <c r="J16" s="382" t="n"/>
+      <c r="K16" s="382" t="n"/>
+      <c r="L16" s="382" t="n"/>
+      <c r="M16" s="382" t="n"/>
+      <c r="N16" s="382" t="n"/>
+      <c r="O16" s="382" t="n"/>
+      <c r="P16" s="382" t="n"/>
+      <c r="Q16" s="382" t="n"/>
+      <c r="R16" s="382" t="n"/>
+      <c r="S16" s="382" t="n"/>
+      <c r="T16" s="383" t="n"/>
+      <c r="U16" s="352" t="inlineStr">
         <is>
           <t>Lot / Quantity</t>
         </is>
       </c>
-      <c r="V16" s="277" t="n"/>
-      <c r="W16" s="277" t="n"/>
-      <c r="X16" s="277" t="n"/>
-      <c r="Y16" s="277" t="n"/>
-      <c r="Z16" s="277" t="n"/>
-      <c r="AA16" s="278" t="n"/>
-      <c r="AB16" s="279">
+      <c r="V16" s="382" t="n"/>
+      <c r="W16" s="382" t="n"/>
+      <c r="X16" s="382" t="n"/>
+      <c r="Y16" s="382" t="n"/>
+      <c r="Z16" s="382" t="n"/>
+      <c r="AA16" s="383" t="n"/>
+      <c r="AB16" s="338">
         <f>IF(GENERATOR!$B$22="","",GENERATOR!$B$22)</f>
         <v/>
       </c>
-      <c r="AC16" s="277" t="n"/>
-      <c r="AD16" s="277" t="n"/>
-      <c r="AE16" s="277" t="n"/>
-      <c r="AF16" s="277" t="n"/>
-      <c r="AG16" s="277" t="n"/>
-      <c r="AH16" s="277" t="n"/>
-      <c r="AI16" s="277" t="n"/>
-      <c r="AJ16" s="277" t="n"/>
-      <c r="AK16" s="277" t="n"/>
-      <c r="AL16" s="277" t="n"/>
-      <c r="AM16" s="277" t="n"/>
-      <c r="AN16" s="280" t="n"/>
+      <c r="AC16" s="382" t="n"/>
+      <c r="AD16" s="382" t="n"/>
+      <c r="AE16" s="382" t="n"/>
+      <c r="AF16" s="382" t="n"/>
+      <c r="AG16" s="382" t="n"/>
+      <c r="AH16" s="382" t="n"/>
+      <c r="AI16" s="382" t="n"/>
+      <c r="AJ16" s="382" t="n"/>
+      <c r="AK16" s="382" t="n"/>
+      <c r="AL16" s="382" t="n"/>
+      <c r="AM16" s="382" t="n"/>
+      <c r="AN16" s="383" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="295" t="inlineStr">
+      <c r="A17" s="349" t="inlineStr">
         <is>
           <t>Job / Route Step</t>
         </is>
       </c>
-      <c r="B17" s="277" t="n"/>
-      <c r="C17" s="277" t="n"/>
-      <c r="D17" s="277" t="n"/>
-      <c r="E17" s="277" t="n"/>
-      <c r="F17" s="277" t="n"/>
-      <c r="G17" s="278" t="n"/>
-      <c r="H17" s="296">
+      <c r="B17" s="382" t="n"/>
+      <c r="C17" s="382" t="n"/>
+      <c r="D17" s="382" t="n"/>
+      <c r="E17" s="382" t="n"/>
+      <c r="F17" s="382" t="n"/>
+      <c r="G17" s="383" t="n"/>
+      <c r="H17" s="338">
         <f>IF(GENERATOR!$B$23="","",GENERATOR!$B$23)</f>
         <v/>
       </c>
-      <c r="I17" s="277" t="n"/>
-      <c r="J17" s="277" t="n"/>
-      <c r="K17" s="277" t="n"/>
-      <c r="L17" s="277" t="n"/>
-      <c r="M17" s="277" t="n"/>
-      <c r="N17" s="277" t="n"/>
-      <c r="O17" s="277" t="n"/>
-      <c r="P17" s="277" t="n"/>
-      <c r="Q17" s="277" t="n"/>
-      <c r="R17" s="277" t="n"/>
-      <c r="S17" s="277" t="n"/>
-      <c r="T17" s="278" t="n"/>
-      <c r="U17" s="297" t="inlineStr">
+      <c r="I17" s="382" t="n"/>
+      <c r="J17" s="382" t="n"/>
+      <c r="K17" s="382" t="n"/>
+      <c r="L17" s="382" t="n"/>
+      <c r="M17" s="382" t="n"/>
+      <c r="N17" s="382" t="n"/>
+      <c r="O17" s="382" t="n"/>
+      <c r="P17" s="382" t="n"/>
+      <c r="Q17" s="382" t="n"/>
+      <c r="R17" s="382" t="n"/>
+      <c r="S17" s="382" t="n"/>
+      <c r="T17" s="383" t="n"/>
+      <c r="U17" s="352" t="inlineStr">
         <is>
           <t>Area / Location</t>
         </is>
       </c>
-      <c r="V17" s="277" t="n"/>
-      <c r="W17" s="277" t="n"/>
-      <c r="X17" s="277" t="n"/>
-      <c r="Y17" s="277" t="n"/>
-      <c r="Z17" s="277" t="n"/>
-      <c r="AA17" s="278" t="n"/>
-      <c r="AB17" s="279">
+      <c r="V17" s="382" t="n"/>
+      <c r="W17" s="382" t="n"/>
+      <c r="X17" s="382" t="n"/>
+      <c r="Y17" s="382" t="n"/>
+      <c r="Z17" s="382" t="n"/>
+      <c r="AA17" s="383" t="n"/>
+      <c r="AB17" s="338">
         <f>IF(GENERATOR!$B$24="","",GENERATOR!$B$24)</f>
         <v/>
       </c>
-      <c r="AC17" s="277" t="n"/>
-      <c r="AD17" s="277" t="n"/>
-      <c r="AE17" s="277" t="n"/>
-      <c r="AF17" s="277" t="n"/>
-      <c r="AG17" s="277" t="n"/>
-      <c r="AH17" s="277" t="n"/>
-      <c r="AI17" s="277" t="n"/>
-      <c r="AJ17" s="277" t="n"/>
-      <c r="AK17" s="277" t="n"/>
-      <c r="AL17" s="277" t="n"/>
-      <c r="AM17" s="277" t="n"/>
-      <c r="AN17" s="280" t="n"/>
+      <c r="AC17" s="382" t="n"/>
+      <c r="AD17" s="382" t="n"/>
+      <c r="AE17" s="382" t="n"/>
+      <c r="AF17" s="382" t="n"/>
+      <c r="AG17" s="382" t="n"/>
+      <c r="AH17" s="382" t="n"/>
+      <c r="AI17" s="382" t="n"/>
+      <c r="AJ17" s="382" t="n"/>
+      <c r="AK17" s="382" t="n"/>
+      <c r="AL17" s="382" t="n"/>
+      <c r="AM17" s="382" t="n"/>
+      <c r="AN17" s="383" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="298" t="inlineStr">
+      <c r="A18" s="349" t="inlineStr">
         <is>
           <t>Encoded String / Barcode Ref</t>
         </is>
       </c>
-      <c r="B18" s="283" t="n"/>
-      <c r="C18" s="283" t="n"/>
-      <c r="D18" s="283" t="n"/>
-      <c r="E18" s="283" t="n"/>
-      <c r="F18" s="283" t="n"/>
-      <c r="G18" s="285" t="n"/>
-      <c r="H18" s="299">
+      <c r="B18" s="382" t="n"/>
+      <c r="C18" s="382" t="n"/>
+      <c r="D18" s="382" t="n"/>
+      <c r="E18" s="382" t="n"/>
+      <c r="F18" s="382" t="n"/>
+      <c r="G18" s="383" t="n"/>
+      <c r="H18" s="338">
         <f>IF(GENERATOR!$B$25="","",GENERATOR!$B$25)</f>
         <v/>
       </c>
-      <c r="I18" s="283" t="n"/>
-      <c r="J18" s="283" t="n"/>
-      <c r="K18" s="283" t="n"/>
-      <c r="L18" s="283" t="n"/>
-      <c r="M18" s="283" t="n"/>
-      <c r="N18" s="283" t="n"/>
-      <c r="O18" s="283" t="n"/>
-      <c r="P18" s="283" t="n"/>
-      <c r="Q18" s="283" t="n"/>
-      <c r="R18" s="283" t="n"/>
-      <c r="S18" s="283" t="n"/>
-      <c r="T18" s="285" t="n"/>
-      <c r="U18" s="300" t="inlineStr">
+      <c r="I18" s="382" t="n"/>
+      <c r="J18" s="382" t="n"/>
+      <c r="K18" s="382" t="n"/>
+      <c r="L18" s="382" t="n"/>
+      <c r="M18" s="382" t="n"/>
+      <c r="N18" s="382" t="n"/>
+      <c r="O18" s="382" t="n"/>
+      <c r="P18" s="382" t="n"/>
+      <c r="Q18" s="382" t="n"/>
+      <c r="R18" s="382" t="n"/>
+      <c r="S18" s="382" t="n"/>
+      <c r="T18" s="383" t="n"/>
+      <c r="U18" s="352" t="inlineStr">
         <is>
           <t>Application Note</t>
         </is>
       </c>
-      <c r="V18" s="283" t="n"/>
-      <c r="W18" s="283" t="n"/>
-      <c r="X18" s="283" t="n"/>
-      <c r="Y18" s="283" t="n"/>
-      <c r="Z18" s="283" t="n"/>
-      <c r="AA18" s="285" t="n"/>
-      <c r="AB18" s="286">
+      <c r="V18" s="382" t="n"/>
+      <c r="W18" s="382" t="n"/>
+      <c r="X18" s="382" t="n"/>
+      <c r="Y18" s="382" t="n"/>
+      <c r="Z18" s="382" t="n"/>
+      <c r="AA18" s="383" t="n"/>
+      <c r="AB18" s="338">
         <f>IF(GENERATOR!$B$26="","",GENERATOR!$B$26)</f>
         <v/>
       </c>
-      <c r="AC18" s="283" t="n"/>
-      <c r="AD18" s="283" t="n"/>
-      <c r="AE18" s="283" t="n"/>
-      <c r="AF18" s="283" t="n"/>
-      <c r="AG18" s="283" t="n"/>
-      <c r="AH18" s="283" t="n"/>
-      <c r="AI18" s="283" t="n"/>
-      <c r="AJ18" s="283" t="n"/>
-      <c r="AK18" s="283" t="n"/>
-      <c r="AL18" s="283" t="n"/>
-      <c r="AM18" s="283" t="n"/>
-      <c r="AN18" s="287" t="n"/>
+      <c r="AC18" s="382" t="n"/>
+      <c r="AD18" s="382" t="n"/>
+      <c r="AE18" s="382" t="n"/>
+      <c r="AF18" s="382" t="n"/>
+      <c r="AG18" s="382" t="n"/>
+      <c r="AH18" s="382" t="n"/>
+      <c r="AI18" s="382" t="n"/>
+      <c r="AJ18" s="382" t="n"/>
+      <c r="AK18" s="382" t="n"/>
+      <c r="AL18" s="382" t="n"/>
+      <c r="AM18" s="382" t="n"/>
+      <c r="AN18" s="383" t="n"/>
     </row>
     <row r="19" ht="4" customHeight="1">
-      <c r="A19" s="25" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="288" t="inlineStr">
+      <c r="A19" s="342" t="n"/>
+      <c r="B19" s="389" t="n"/>
+      <c r="C19" s="389" t="n"/>
+      <c r="D19" s="389" t="n"/>
+      <c r="E19" s="389" t="n"/>
+      <c r="F19" s="389" t="n"/>
+      <c r="G19" s="389" t="n"/>
+      <c r="H19" s="389" t="n"/>
+      <c r="I19" s="389" t="n"/>
+      <c r="J19" s="389" t="n"/>
+      <c r="K19" s="389" t="n"/>
+      <c r="L19" s="389" t="n"/>
+      <c r="M19" s="389" t="n"/>
+      <c r="N19" s="389" t="n"/>
+      <c r="O19" s="389" t="n"/>
+      <c r="P19" s="389" t="n"/>
+      <c r="Q19" s="389" t="n"/>
+      <c r="R19" s="389" t="n"/>
+      <c r="S19" s="389" t="n"/>
+      <c r="T19" s="389" t="n"/>
+      <c r="U19" s="389" t="n"/>
+      <c r="V19" s="389" t="n"/>
+      <c r="W19" s="389" t="n"/>
+      <c r="X19" s="389" t="n"/>
+      <c r="Y19" s="389" t="n"/>
+      <c r="Z19" s="389" t="n"/>
+      <c r="AA19" s="389" t="n"/>
+      <c r="AB19" s="389" t="n"/>
+      <c r="AC19" s="389" t="n"/>
+      <c r="AD19" s="389" t="n"/>
+      <c r="AE19" s="389" t="n"/>
+      <c r="AF19" s="389" t="n"/>
+      <c r="AG19" s="389" t="n"/>
+      <c r="AH19" s="389" t="n"/>
+      <c r="AI19" s="389" t="n"/>
+      <c r="AJ19" s="389" t="n"/>
+      <c r="AK19" s="389" t="n"/>
+      <c r="AL19" s="389" t="n"/>
+      <c r="AM19" s="389" t="n"/>
+      <c r="AN19" s="389" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="343" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. VERIFICATION / APPLICATION CHECK</t>
         </is>
       </c>
-      <c r="B20" s="289" t="n"/>
-      <c r="C20" s="289" t="n"/>
-      <c r="D20" s="289" t="n"/>
-      <c r="E20" s="289" t="n"/>
-      <c r="F20" s="289" t="n"/>
-      <c r="G20" s="289" t="n"/>
-      <c r="H20" s="289" t="n"/>
-      <c r="I20" s="289" t="n"/>
-      <c r="J20" s="289" t="n"/>
-      <c r="K20" s="289" t="n"/>
-      <c r="L20" s="289" t="n"/>
-      <c r="M20" s="289" t="n"/>
-      <c r="N20" s="289" t="n"/>
-      <c r="O20" s="289" t="n"/>
-      <c r="P20" s="289" t="n"/>
-      <c r="Q20" s="289" t="n"/>
-      <c r="R20" s="289" t="n"/>
-      <c r="S20" s="289" t="n"/>
-      <c r="T20" s="289" t="n"/>
-      <c r="U20" s="289" t="n"/>
-      <c r="V20" s="289" t="n"/>
-      <c r="W20" s="289" t="n"/>
-      <c r="X20" s="289" t="n"/>
-      <c r="Y20" s="289" t="n"/>
-      <c r="Z20" s="289" t="n"/>
-      <c r="AA20" s="289" t="n"/>
-      <c r="AB20" s="289" t="n"/>
-      <c r="AC20" s="289" t="n"/>
-      <c r="AD20" s="289" t="n"/>
-      <c r="AE20" s="289" t="n"/>
-      <c r="AF20" s="289" t="n"/>
-      <c r="AG20" s="289" t="n"/>
-      <c r="AH20" s="289" t="n"/>
-      <c r="AI20" s="289" t="n"/>
-      <c r="AJ20" s="289" t="n"/>
-      <c r="AK20" s="289" t="n"/>
-      <c r="AL20" s="289" t="n"/>
-      <c r="AM20" s="289" t="n"/>
-      <c r="AN20" s="290" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="301" t="inlineStr">
+      <c r="B20" s="380" t="n"/>
+      <c r="C20" s="380" t="n"/>
+      <c r="D20" s="380" t="n"/>
+      <c r="E20" s="380" t="n"/>
+      <c r="F20" s="380" t="n"/>
+      <c r="G20" s="380" t="n"/>
+      <c r="H20" s="380" t="n"/>
+      <c r="I20" s="380" t="n"/>
+      <c r="J20" s="380" t="n"/>
+      <c r="K20" s="380" t="n"/>
+      <c r="L20" s="380" t="n"/>
+      <c r="M20" s="380" t="n"/>
+      <c r="N20" s="380" t="n"/>
+      <c r="O20" s="380" t="n"/>
+      <c r="P20" s="380" t="n"/>
+      <c r="Q20" s="380" t="n"/>
+      <c r="R20" s="380" t="n"/>
+      <c r="S20" s="380" t="n"/>
+      <c r="T20" s="380" t="n"/>
+      <c r="U20" s="380" t="n"/>
+      <c r="V20" s="380" t="n"/>
+      <c r="W20" s="380" t="n"/>
+      <c r="X20" s="380" t="n"/>
+      <c r="Y20" s="380" t="n"/>
+      <c r="Z20" s="380" t="n"/>
+      <c r="AA20" s="380" t="n"/>
+      <c r="AB20" s="380" t="n"/>
+      <c r="AC20" s="380" t="n"/>
+      <c r="AD20" s="380" t="n"/>
+      <c r="AE20" s="380" t="n"/>
+      <c r="AF20" s="380" t="n"/>
+      <c r="AG20" s="380" t="n"/>
+      <c r="AH20" s="380" t="n"/>
+      <c r="AI20" s="380" t="n"/>
+      <c r="AJ20" s="380" t="n"/>
+      <c r="AK20" s="380" t="n"/>
+      <c r="AL20" s="380" t="n"/>
+      <c r="AM20" s="380" t="n"/>
+      <c r="AN20" s="381" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="353" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="272" t="n"/>
-      <c r="C21" s="302" t="inlineStr">
+      <c r="B21" s="381" t="n"/>
+      <c r="C21" s="354" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="271" t="n"/>
-      <c r="E21" s="272" t="n"/>
-      <c r="F21" s="302" t="inlineStr">
+      <c r="D21" s="380" t="n"/>
+      <c r="E21" s="381" t="n"/>
+      <c r="F21" s="354" t="inlineStr">
         <is>
           <t>Verification Check</t>
         </is>
       </c>
-      <c r="G21" s="271" t="n"/>
-      <c r="H21" s="271" t="n"/>
-      <c r="I21" s="271" t="n"/>
-      <c r="J21" s="271" t="n"/>
-      <c r="K21" s="271" t="n"/>
-      <c r="L21" s="271" t="n"/>
-      <c r="M21" s="271" t="n"/>
-      <c r="N21" s="271" t="n"/>
-      <c r="O21" s="271" t="n"/>
-      <c r="P21" s="271" t="n"/>
-      <c r="Q21" s="271" t="n"/>
-      <c r="R21" s="271" t="n"/>
-      <c r="S21" s="272" t="n"/>
-      <c r="T21" s="302" t="inlineStr">
+      <c r="G21" s="380" t="n"/>
+      <c r="H21" s="380" t="n"/>
+      <c r="I21" s="380" t="n"/>
+      <c r="J21" s="380" t="n"/>
+      <c r="K21" s="380" t="n"/>
+      <c r="L21" s="380" t="n"/>
+      <c r="M21" s="380" t="n"/>
+      <c r="N21" s="380" t="n"/>
+      <c r="O21" s="380" t="n"/>
+      <c r="P21" s="380" t="n"/>
+      <c r="Q21" s="380" t="n"/>
+      <c r="R21" s="380" t="n"/>
+      <c r="S21" s="381" t="n"/>
+      <c r="T21" s="354" t="inlineStr">
         <is>
           <t>Acceptance Rule</t>
         </is>
       </c>
-      <c r="U21" s="271" t="n"/>
-      <c r="V21" s="271" t="n"/>
-      <c r="W21" s="271" t="n"/>
-      <c r="X21" s="271" t="n"/>
-      <c r="Y21" s="271" t="n"/>
-      <c r="Z21" s="271" t="n"/>
-      <c r="AA21" s="271" t="n"/>
-      <c r="AB21" s="271" t="n"/>
-      <c r="AC21" s="271" t="n"/>
-      <c r="AD21" s="271" t="n"/>
-      <c r="AE21" s="272" t="n"/>
-      <c r="AF21" s="302" t="inlineStr">
+      <c r="U21" s="380" t="n"/>
+      <c r="V21" s="380" t="n"/>
+      <c r="W21" s="380" t="n"/>
+      <c r="X21" s="380" t="n"/>
+      <c r="Y21" s="380" t="n"/>
+      <c r="Z21" s="380" t="n"/>
+      <c r="AA21" s="380" t="n"/>
+      <c r="AB21" s="380" t="n"/>
+      <c r="AC21" s="380" t="n"/>
+      <c r="AD21" s="380" t="n"/>
+      <c r="AE21" s="381" t="n"/>
+      <c r="AF21" s="354" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="271" t="n"/>
-      <c r="AH21" s="271" t="n"/>
-      <c r="AI21" s="272" t="n"/>
-      <c r="AJ21" s="302" t="inlineStr">
+      <c r="AG21" s="380" t="n"/>
+      <c r="AH21" s="380" t="n"/>
+      <c r="AI21" s="381" t="n"/>
+      <c r="AJ21" s="354" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="271" t="n"/>
-      <c r="AL21" s="272" t="n"/>
-      <c r="AM21" s="303" t="inlineStr">
+      <c r="AK21" s="380" t="n"/>
+      <c r="AL21" s="381" t="n"/>
+      <c r="AM21" s="354" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="274" t="n"/>
+      <c r="AN21" s="381" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="304">
+      <c r="A22" s="355">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="278" t="n"/>
-      <c r="C22" s="305" t="inlineStr">
+      <c r="B22" s="383" t="n"/>
+      <c r="C22" s="356" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D22" s="277" t="n"/>
-      <c r="E22" s="278" t="n"/>
-      <c r="F22" s="296" t="inlineStr">
+      <c r="D22" s="382" t="n"/>
+      <c r="E22" s="383" t="n"/>
+      <c r="F22" s="338" t="inlineStr">
         <is>
           <t>Identity match</t>
         </is>
       </c>
-      <c r="G22" s="277" t="n"/>
-      <c r="H22" s="277" t="n"/>
-      <c r="I22" s="277" t="n"/>
-      <c r="J22" s="277" t="n"/>
-      <c r="K22" s="277" t="n"/>
-      <c r="L22" s="277" t="n"/>
-      <c r="M22" s="277" t="n"/>
-      <c r="N22" s="277" t="n"/>
-      <c r="O22" s="277" t="n"/>
-      <c r="P22" s="277" t="n"/>
-      <c r="Q22" s="277" t="n"/>
-      <c r="R22" s="277" t="n"/>
-      <c r="S22" s="278" t="n"/>
-      <c r="T22" s="306" t="inlineStr">
+      <c r="G22" s="382" t="n"/>
+      <c r="H22" s="382" t="n"/>
+      <c r="I22" s="382" t="n"/>
+      <c r="J22" s="382" t="n"/>
+      <c r="K22" s="382" t="n"/>
+      <c r="L22" s="382" t="n"/>
+      <c r="M22" s="382" t="n"/>
+      <c r="N22" s="382" t="n"/>
+      <c r="O22" s="382" t="n"/>
+      <c r="P22" s="382" t="n"/>
+      <c r="Q22" s="382" t="n"/>
+      <c r="R22" s="382" t="n"/>
+      <c r="S22" s="383" t="n"/>
+      <c r="T22" s="357" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U22" s="277" t="n"/>
-      <c r="V22" s="277" t="n"/>
-      <c r="W22" s="277" t="n"/>
-      <c r="X22" s="277" t="n"/>
-      <c r="Y22" s="277" t="n"/>
-      <c r="Z22" s="277" t="n"/>
-      <c r="AA22" s="277" t="n"/>
-      <c r="AB22" s="277" t="n"/>
-      <c r="AC22" s="277" t="n"/>
-      <c r="AD22" s="277" t="n"/>
-      <c r="AE22" s="278" t="n"/>
-      <c r="AF22" s="307" t="n"/>
-      <c r="AG22" s="277" t="n"/>
-      <c r="AH22" s="277" t="n"/>
-      <c r="AI22" s="278" t="n"/>
-      <c r="AJ22" s="307" t="n"/>
-      <c r="AK22" s="277" t="n"/>
-      <c r="AL22" s="278" t="n"/>
-      <c r="AM22" s="308" t="n"/>
-      <c r="AN22" s="280" t="n"/>
+      <c r="U22" s="382" t="n"/>
+      <c r="V22" s="382" t="n"/>
+      <c r="W22" s="382" t="n"/>
+      <c r="X22" s="382" t="n"/>
+      <c r="Y22" s="382" t="n"/>
+      <c r="Z22" s="382" t="n"/>
+      <c r="AA22" s="382" t="n"/>
+      <c r="AB22" s="382" t="n"/>
+      <c r="AC22" s="382" t="n"/>
+      <c r="AD22" s="382" t="n"/>
+      <c r="AE22" s="383" t="n"/>
+      <c r="AF22" s="358" t="n"/>
+      <c r="AG22" s="382" t="n"/>
+      <c r="AH22" s="382" t="n"/>
+      <c r="AI22" s="383" t="n"/>
+      <c r="AJ22" s="358" t="n"/>
+      <c r="AK22" s="382" t="n"/>
+      <c r="AL22" s="383" t="n"/>
+      <c r="AM22" s="359" t="n"/>
+      <c r="AN22" s="383" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="304">
+      <c r="A23" s="355">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="278" t="n"/>
-      <c r="C23" s="305" t="inlineStr">
+      <c r="B23" s="383" t="n"/>
+      <c r="C23" s="356" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="D23" s="277" t="n"/>
-      <c r="E23" s="278" t="n"/>
-      <c r="F23" s="309" t="inlineStr">
+      <c r="D23" s="382" t="n"/>
+      <c r="E23" s="383" t="n"/>
+      <c r="F23" s="360" t="inlineStr">
         <is>
           <t>Readable print</t>
         </is>
       </c>
-      <c r="G23" s="277" t="n"/>
-      <c r="H23" s="277" t="n"/>
-      <c r="I23" s="277" t="n"/>
-      <c r="J23" s="277" t="n"/>
-      <c r="K23" s="277" t="n"/>
-      <c r="L23" s="277" t="n"/>
-      <c r="M23" s="277" t="n"/>
-      <c r="N23" s="277" t="n"/>
-      <c r="O23" s="277" t="n"/>
-      <c r="P23" s="277" t="n"/>
-      <c r="Q23" s="277" t="n"/>
-      <c r="R23" s="277" t="n"/>
-      <c r="S23" s="278" t="n"/>
-      <c r="T23" s="306" t="inlineStr">
+      <c r="G23" s="382" t="n"/>
+      <c r="H23" s="382" t="n"/>
+      <c r="I23" s="382" t="n"/>
+      <c r="J23" s="382" t="n"/>
+      <c r="K23" s="382" t="n"/>
+      <c r="L23" s="382" t="n"/>
+      <c r="M23" s="382" t="n"/>
+      <c r="N23" s="382" t="n"/>
+      <c r="O23" s="382" t="n"/>
+      <c r="P23" s="382" t="n"/>
+      <c r="Q23" s="382" t="n"/>
+      <c r="R23" s="382" t="n"/>
+      <c r="S23" s="383" t="n"/>
+      <c r="T23" s="357" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U23" s="277" t="n"/>
-      <c r="V23" s="277" t="n"/>
-      <c r="W23" s="277" t="n"/>
-      <c r="X23" s="277" t="n"/>
-      <c r="Y23" s="277" t="n"/>
-      <c r="Z23" s="277" t="n"/>
-      <c r="AA23" s="277" t="n"/>
-      <c r="AB23" s="277" t="n"/>
-      <c r="AC23" s="277" t="n"/>
-      <c r="AD23" s="277" t="n"/>
-      <c r="AE23" s="278" t="n"/>
-      <c r="AF23" s="307" t="n"/>
-      <c r="AG23" s="277" t="n"/>
-      <c r="AH23" s="277" t="n"/>
-      <c r="AI23" s="278" t="n"/>
-      <c r="AJ23" s="307" t="n"/>
-      <c r="AK23" s="277" t="n"/>
-      <c r="AL23" s="278" t="n"/>
-      <c r="AM23" s="308" t="n"/>
-      <c r="AN23" s="280" t="n"/>
+      <c r="U23" s="382" t="n"/>
+      <c r="V23" s="382" t="n"/>
+      <c r="W23" s="382" t="n"/>
+      <c r="X23" s="382" t="n"/>
+      <c r="Y23" s="382" t="n"/>
+      <c r="Z23" s="382" t="n"/>
+      <c r="AA23" s="382" t="n"/>
+      <c r="AB23" s="382" t="n"/>
+      <c r="AC23" s="382" t="n"/>
+      <c r="AD23" s="382" t="n"/>
+      <c r="AE23" s="383" t="n"/>
+      <c r="AF23" s="358" t="n"/>
+      <c r="AG23" s="382" t="n"/>
+      <c r="AH23" s="382" t="n"/>
+      <c r="AI23" s="383" t="n"/>
+      <c r="AJ23" s="358" t="n"/>
+      <c r="AK23" s="382" t="n"/>
+      <c r="AL23" s="383" t="n"/>
+      <c r="AM23" s="359" t="n"/>
+      <c r="AN23" s="383" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="304">
+      <c r="A24" s="355">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="278" t="n"/>
-      <c r="C24" s="305" t="inlineStr">
+      <c r="B24" s="383" t="n"/>
+      <c r="C24" s="356" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="D24" s="277" t="n"/>
-      <c r="E24" s="278" t="n"/>
-      <c r="F24" s="296" t="inlineStr">
+      <c r="D24" s="382" t="n"/>
+      <c r="E24" s="383" t="n"/>
+      <c r="F24" s="338" t="inlineStr">
         <is>
           <t>Correct quantity</t>
         </is>
       </c>
-      <c r="G24" s="277" t="n"/>
-      <c r="H24" s="277" t="n"/>
-      <c r="I24" s="277" t="n"/>
-      <c r="J24" s="277" t="n"/>
-      <c r="K24" s="277" t="n"/>
-      <c r="L24" s="277" t="n"/>
-      <c r="M24" s="277" t="n"/>
-      <c r="N24" s="277" t="n"/>
-      <c r="O24" s="277" t="n"/>
-      <c r="P24" s="277" t="n"/>
-      <c r="Q24" s="277" t="n"/>
-      <c r="R24" s="277" t="n"/>
-      <c r="S24" s="278" t="n"/>
-      <c r="T24" s="306" t="inlineStr">
+      <c r="G24" s="382" t="n"/>
+      <c r="H24" s="382" t="n"/>
+      <c r="I24" s="382" t="n"/>
+      <c r="J24" s="382" t="n"/>
+      <c r="K24" s="382" t="n"/>
+      <c r="L24" s="382" t="n"/>
+      <c r="M24" s="382" t="n"/>
+      <c r="N24" s="382" t="n"/>
+      <c r="O24" s="382" t="n"/>
+      <c r="P24" s="382" t="n"/>
+      <c r="Q24" s="382" t="n"/>
+      <c r="R24" s="382" t="n"/>
+      <c r="S24" s="383" t="n"/>
+      <c r="T24" s="357" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U24" s="277" t="n"/>
-      <c r="V24" s="277" t="n"/>
-      <c r="W24" s="277" t="n"/>
-      <c r="X24" s="277" t="n"/>
-      <c r="Y24" s="277" t="n"/>
-      <c r="Z24" s="277" t="n"/>
-      <c r="AA24" s="277" t="n"/>
-      <c r="AB24" s="277" t="n"/>
-      <c r="AC24" s="277" t="n"/>
-      <c r="AD24" s="277" t="n"/>
-      <c r="AE24" s="278" t="n"/>
-      <c r="AF24" s="307" t="n"/>
-      <c r="AG24" s="277" t="n"/>
-      <c r="AH24" s="277" t="n"/>
-      <c r="AI24" s="278" t="n"/>
-      <c r="AJ24" s="307" t="n"/>
-      <c r="AK24" s="277" t="n"/>
-      <c r="AL24" s="278" t="n"/>
-      <c r="AM24" s="308" t="n"/>
-      <c r="AN24" s="280" t="n"/>
+      <c r="U24" s="382" t="n"/>
+      <c r="V24" s="382" t="n"/>
+      <c r="W24" s="382" t="n"/>
+      <c r="X24" s="382" t="n"/>
+      <c r="Y24" s="382" t="n"/>
+      <c r="Z24" s="382" t="n"/>
+      <c r="AA24" s="382" t="n"/>
+      <c r="AB24" s="382" t="n"/>
+      <c r="AC24" s="382" t="n"/>
+      <c r="AD24" s="382" t="n"/>
+      <c r="AE24" s="383" t="n"/>
+      <c r="AF24" s="358" t="n"/>
+      <c r="AG24" s="382" t="n"/>
+      <c r="AH24" s="382" t="n"/>
+      <c r="AI24" s="383" t="n"/>
+      <c r="AJ24" s="358" t="n"/>
+      <c r="AK24" s="382" t="n"/>
+      <c r="AL24" s="383" t="n"/>
+      <c r="AM24" s="359" t="n"/>
+      <c r="AN24" s="383" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="304">
+      <c r="A25" s="355">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="278" t="n"/>
-      <c r="C25" s="305" t="inlineStr">
+      <c r="B25" s="383" t="n"/>
+      <c r="C25" s="356" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="D25" s="277" t="n"/>
-      <c r="E25" s="278" t="n"/>
-      <c r="F25" s="309" t="inlineStr">
+      <c r="D25" s="382" t="n"/>
+      <c r="E25" s="383" t="n"/>
+      <c r="F25" s="360" t="inlineStr">
         <is>
           <t>Application status</t>
         </is>
       </c>
-      <c r="G25" s="277" t="n"/>
-      <c r="H25" s="277" t="n"/>
-      <c r="I25" s="277" t="n"/>
-      <c r="J25" s="277" t="n"/>
-      <c r="K25" s="277" t="n"/>
-      <c r="L25" s="277" t="n"/>
-      <c r="M25" s="277" t="n"/>
-      <c r="N25" s="277" t="n"/>
-      <c r="O25" s="277" t="n"/>
-      <c r="P25" s="277" t="n"/>
-      <c r="Q25" s="277" t="n"/>
-      <c r="R25" s="277" t="n"/>
-      <c r="S25" s="278" t="n"/>
-      <c r="T25" s="306" t="inlineStr">
+      <c r="G25" s="382" t="n"/>
+      <c r="H25" s="382" t="n"/>
+      <c r="I25" s="382" t="n"/>
+      <c r="J25" s="382" t="n"/>
+      <c r="K25" s="382" t="n"/>
+      <c r="L25" s="382" t="n"/>
+      <c r="M25" s="382" t="n"/>
+      <c r="N25" s="382" t="n"/>
+      <c r="O25" s="382" t="n"/>
+      <c r="P25" s="382" t="n"/>
+      <c r="Q25" s="382" t="n"/>
+      <c r="R25" s="382" t="n"/>
+      <c r="S25" s="383" t="n"/>
+      <c r="T25" s="357" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U25" s="277" t="n"/>
-      <c r="V25" s="277" t="n"/>
-      <c r="W25" s="277" t="n"/>
-      <c r="X25" s="277" t="n"/>
-      <c r="Y25" s="277" t="n"/>
-      <c r="Z25" s="277" t="n"/>
-      <c r="AA25" s="277" t="n"/>
-      <c r="AB25" s="277" t="n"/>
-      <c r="AC25" s="277" t="n"/>
-      <c r="AD25" s="277" t="n"/>
-      <c r="AE25" s="278" t="n"/>
-      <c r="AF25" s="307" t="n"/>
-      <c r="AG25" s="277" t="n"/>
-      <c r="AH25" s="277" t="n"/>
-      <c r="AI25" s="278" t="n"/>
-      <c r="AJ25" s="307" t="n"/>
-      <c r="AK25" s="277" t="n"/>
-      <c r="AL25" s="278" t="n"/>
-      <c r="AM25" s="308" t="n"/>
-      <c r="AN25" s="280" t="n"/>
+      <c r="U25" s="382" t="n"/>
+      <c r="V25" s="382" t="n"/>
+      <c r="W25" s="382" t="n"/>
+      <c r="X25" s="382" t="n"/>
+      <c r="Y25" s="382" t="n"/>
+      <c r="Z25" s="382" t="n"/>
+      <c r="AA25" s="382" t="n"/>
+      <c r="AB25" s="382" t="n"/>
+      <c r="AC25" s="382" t="n"/>
+      <c r="AD25" s="382" t="n"/>
+      <c r="AE25" s="383" t="n"/>
+      <c r="AF25" s="358" t="n"/>
+      <c r="AG25" s="382" t="n"/>
+      <c r="AH25" s="382" t="n"/>
+      <c r="AI25" s="383" t="n"/>
+      <c r="AJ25" s="358" t="n"/>
+      <c r="AK25" s="382" t="n"/>
+      <c r="AL25" s="383" t="n"/>
+      <c r="AM25" s="359" t="n"/>
+      <c r="AN25" s="383" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="304">
+      <c r="A26" s="355">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="278" t="n"/>
-      <c r="C26" s="305" t="inlineStr">
+      <c r="B26" s="383" t="n"/>
+      <c r="C26" s="356" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D26" s="277" t="n"/>
-      <c r="E26" s="278" t="n"/>
-      <c r="F26" s="296" t="inlineStr">
+      <c r="D26" s="382" t="n"/>
+      <c r="E26" s="383" t="n"/>
+      <c r="F26" s="338" t="inlineStr">
         <is>
           <t>Void / scrap control</t>
         </is>
       </c>
-      <c r="G26" s="277" t="n"/>
-      <c r="H26" s="277" t="n"/>
-      <c r="I26" s="277" t="n"/>
-      <c r="J26" s="277" t="n"/>
-      <c r="K26" s="277" t="n"/>
-      <c r="L26" s="277" t="n"/>
-      <c r="M26" s="277" t="n"/>
-      <c r="N26" s="277" t="n"/>
-      <c r="O26" s="277" t="n"/>
-      <c r="P26" s="277" t="n"/>
-      <c r="Q26" s="277" t="n"/>
-      <c r="R26" s="277" t="n"/>
-      <c r="S26" s="278" t="n"/>
-      <c r="T26" s="306" t="inlineStr">
+      <c r="G26" s="382" t="n"/>
+      <c r="H26" s="382" t="n"/>
+      <c r="I26" s="382" t="n"/>
+      <c r="J26" s="382" t="n"/>
+      <c r="K26" s="382" t="n"/>
+      <c r="L26" s="382" t="n"/>
+      <c r="M26" s="382" t="n"/>
+      <c r="N26" s="382" t="n"/>
+      <c r="O26" s="382" t="n"/>
+      <c r="P26" s="382" t="n"/>
+      <c r="Q26" s="382" t="n"/>
+      <c r="R26" s="382" t="n"/>
+      <c r="S26" s="383" t="n"/>
+      <c r="T26" s="357" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U26" s="277" t="n"/>
-      <c r="V26" s="277" t="n"/>
-      <c r="W26" s="277" t="n"/>
-      <c r="X26" s="277" t="n"/>
-      <c r="Y26" s="277" t="n"/>
-      <c r="Z26" s="277" t="n"/>
-      <c r="AA26" s="277" t="n"/>
-      <c r="AB26" s="277" t="n"/>
-      <c r="AC26" s="277" t="n"/>
-      <c r="AD26" s="277" t="n"/>
-      <c r="AE26" s="278" t="n"/>
-      <c r="AF26" s="307" t="n"/>
-      <c r="AG26" s="277" t="n"/>
-      <c r="AH26" s="277" t="n"/>
-      <c r="AI26" s="278" t="n"/>
-      <c r="AJ26" s="307" t="n"/>
-      <c r="AK26" s="277" t="n"/>
-      <c r="AL26" s="278" t="n"/>
-      <c r="AM26" s="308" t="n"/>
-      <c r="AN26" s="280" t="n"/>
+      <c r="U26" s="382" t="n"/>
+      <c r="V26" s="382" t="n"/>
+      <c r="W26" s="382" t="n"/>
+      <c r="X26" s="382" t="n"/>
+      <c r="Y26" s="382" t="n"/>
+      <c r="Z26" s="382" t="n"/>
+      <c r="AA26" s="382" t="n"/>
+      <c r="AB26" s="382" t="n"/>
+      <c r="AC26" s="382" t="n"/>
+      <c r="AD26" s="382" t="n"/>
+      <c r="AE26" s="383" t="n"/>
+      <c r="AF26" s="358" t="n"/>
+      <c r="AG26" s="382" t="n"/>
+      <c r="AH26" s="382" t="n"/>
+      <c r="AI26" s="383" t="n"/>
+      <c r="AJ26" s="358" t="n"/>
+      <c r="AK26" s="382" t="n"/>
+      <c r="AL26" s="383" t="n"/>
+      <c r="AM26" s="359" t="n"/>
+      <c r="AN26" s="383" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="304" t="n"/>
-      <c r="B27" s="278" t="n"/>
-      <c r="C27" s="305" t="n"/>
-      <c r="D27" s="277" t="n"/>
-      <c r="E27" s="278" t="n"/>
-      <c r="F27" s="309" t="n"/>
-      <c r="G27" s="277" t="n"/>
-      <c r="H27" s="277" t="n"/>
-      <c r="I27" s="277" t="n"/>
-      <c r="J27" s="277" t="n"/>
-      <c r="K27" s="277" t="n"/>
-      <c r="L27" s="277" t="n"/>
-      <c r="M27" s="277" t="n"/>
-      <c r="N27" s="277" t="n"/>
-      <c r="O27" s="277" t="n"/>
-      <c r="P27" s="277" t="n"/>
-      <c r="Q27" s="277" t="n"/>
-      <c r="R27" s="277" t="n"/>
-      <c r="S27" s="278" t="n"/>
-      <c r="T27" s="306" t="n"/>
-      <c r="U27" s="277" t="n"/>
-      <c r="V27" s="277" t="n"/>
-      <c r="W27" s="277" t="n"/>
-      <c r="X27" s="277" t="n"/>
-      <c r="Y27" s="277" t="n"/>
-      <c r="Z27" s="277" t="n"/>
-      <c r="AA27" s="277" t="n"/>
-      <c r="AB27" s="277" t="n"/>
-      <c r="AC27" s="277" t="n"/>
-      <c r="AD27" s="277" t="n"/>
-      <c r="AE27" s="278" t="n"/>
-      <c r="AF27" s="307" t="n"/>
-      <c r="AG27" s="277" t="n"/>
-      <c r="AH27" s="277" t="n"/>
-      <c r="AI27" s="278" t="n"/>
-      <c r="AJ27" s="307" t="n"/>
-      <c r="AK27" s="277" t="n"/>
-      <c r="AL27" s="278" t="n"/>
-      <c r="AM27" s="308" t="n"/>
-      <c r="AN27" s="280" t="n"/>
+      <c r="A27" s="355" t="n"/>
+      <c r="B27" s="383" t="n"/>
+      <c r="C27" s="356" t="n"/>
+      <c r="D27" s="382" t="n"/>
+      <c r="E27" s="383" t="n"/>
+      <c r="F27" s="360" t="n"/>
+      <c r="G27" s="382" t="n"/>
+      <c r="H27" s="382" t="n"/>
+      <c r="I27" s="382" t="n"/>
+      <c r="J27" s="382" t="n"/>
+      <c r="K27" s="382" t="n"/>
+      <c r="L27" s="382" t="n"/>
+      <c r="M27" s="382" t="n"/>
+      <c r="N27" s="382" t="n"/>
+      <c r="O27" s="382" t="n"/>
+      <c r="P27" s="382" t="n"/>
+      <c r="Q27" s="382" t="n"/>
+      <c r="R27" s="382" t="n"/>
+      <c r="S27" s="383" t="n"/>
+      <c r="T27" s="357" t="n"/>
+      <c r="U27" s="382" t="n"/>
+      <c r="V27" s="382" t="n"/>
+      <c r="W27" s="382" t="n"/>
+      <c r="X27" s="382" t="n"/>
+      <c r="Y27" s="382" t="n"/>
+      <c r="Z27" s="382" t="n"/>
+      <c r="AA27" s="382" t="n"/>
+      <c r="AB27" s="382" t="n"/>
+      <c r="AC27" s="382" t="n"/>
+      <c r="AD27" s="382" t="n"/>
+      <c r="AE27" s="383" t="n"/>
+      <c r="AF27" s="358" t="n"/>
+      <c r="AG27" s="382" t="n"/>
+      <c r="AH27" s="382" t="n"/>
+      <c r="AI27" s="383" t="n"/>
+      <c r="AJ27" s="358" t="n"/>
+      <c r="AK27" s="382" t="n"/>
+      <c r="AL27" s="383" t="n"/>
+      <c r="AM27" s="359" t="n"/>
+      <c r="AN27" s="383" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="304" t="n"/>
-      <c r="B28" s="278" t="n"/>
-      <c r="C28" s="305" t="n"/>
-      <c r="D28" s="277" t="n"/>
-      <c r="E28" s="278" t="n"/>
-      <c r="F28" s="296" t="n"/>
-      <c r="G28" s="277" t="n"/>
-      <c r="H28" s="277" t="n"/>
-      <c r="I28" s="277" t="n"/>
-      <c r="J28" s="277" t="n"/>
-      <c r="K28" s="277" t="n"/>
-      <c r="L28" s="277" t="n"/>
-      <c r="M28" s="277" t="n"/>
-      <c r="N28" s="277" t="n"/>
-      <c r="O28" s="277" t="n"/>
-      <c r="P28" s="277" t="n"/>
-      <c r="Q28" s="277" t="n"/>
-      <c r="R28" s="277" t="n"/>
-      <c r="S28" s="278" t="n"/>
-      <c r="T28" s="306" t="n"/>
-      <c r="U28" s="277" t="n"/>
-      <c r="V28" s="277" t="n"/>
-      <c r="W28" s="277" t="n"/>
-      <c r="X28" s="277" t="n"/>
-      <c r="Y28" s="277" t="n"/>
-      <c r="Z28" s="277" t="n"/>
-      <c r="AA28" s="277" t="n"/>
-      <c r="AB28" s="277" t="n"/>
-      <c r="AC28" s="277" t="n"/>
-      <c r="AD28" s="277" t="n"/>
-      <c r="AE28" s="278" t="n"/>
-      <c r="AF28" s="307" t="n"/>
-      <c r="AG28" s="277" t="n"/>
-      <c r="AH28" s="277" t="n"/>
-      <c r="AI28" s="278" t="n"/>
-      <c r="AJ28" s="307" t="n"/>
-      <c r="AK28" s="277" t="n"/>
-      <c r="AL28" s="278" t="n"/>
-      <c r="AM28" s="308" t="n"/>
-      <c r="AN28" s="280" t="n"/>
+      <c r="A28" s="355" t="n"/>
+      <c r="B28" s="383" t="n"/>
+      <c r="C28" s="356" t="n"/>
+      <c r="D28" s="382" t="n"/>
+      <c r="E28" s="383" t="n"/>
+      <c r="F28" s="338" t="n"/>
+      <c r="G28" s="382" t="n"/>
+      <c r="H28" s="382" t="n"/>
+      <c r="I28" s="382" t="n"/>
+      <c r="J28" s="382" t="n"/>
+      <c r="K28" s="382" t="n"/>
+      <c r="L28" s="382" t="n"/>
+      <c r="M28" s="382" t="n"/>
+      <c r="N28" s="382" t="n"/>
+      <c r="O28" s="382" t="n"/>
+      <c r="P28" s="382" t="n"/>
+      <c r="Q28" s="382" t="n"/>
+      <c r="R28" s="382" t="n"/>
+      <c r="S28" s="383" t="n"/>
+      <c r="T28" s="357" t="n"/>
+      <c r="U28" s="382" t="n"/>
+      <c r="V28" s="382" t="n"/>
+      <c r="W28" s="382" t="n"/>
+      <c r="X28" s="382" t="n"/>
+      <c r="Y28" s="382" t="n"/>
+      <c r="Z28" s="382" t="n"/>
+      <c r="AA28" s="382" t="n"/>
+      <c r="AB28" s="382" t="n"/>
+      <c r="AC28" s="382" t="n"/>
+      <c r="AD28" s="382" t="n"/>
+      <c r="AE28" s="383" t="n"/>
+      <c r="AF28" s="358" t="n"/>
+      <c r="AG28" s="382" t="n"/>
+      <c r="AH28" s="382" t="n"/>
+      <c r="AI28" s="383" t="n"/>
+      <c r="AJ28" s="358" t="n"/>
+      <c r="AK28" s="382" t="n"/>
+      <c r="AL28" s="383" t="n"/>
+      <c r="AM28" s="359" t="n"/>
+      <c r="AN28" s="383" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="304" t="n"/>
-      <c r="B29" s="278" t="n"/>
-      <c r="C29" s="305" t="n"/>
-      <c r="D29" s="277" t="n"/>
-      <c r="E29" s="278" t="n"/>
-      <c r="F29" s="309" t="n"/>
-      <c r="G29" s="277" t="n"/>
-      <c r="H29" s="277" t="n"/>
-      <c r="I29" s="277" t="n"/>
-      <c r="J29" s="277" t="n"/>
-      <c r="K29" s="277" t="n"/>
-      <c r="L29" s="277" t="n"/>
-      <c r="M29" s="277" t="n"/>
-      <c r="N29" s="277" t="n"/>
-      <c r="O29" s="277" t="n"/>
-      <c r="P29" s="277" t="n"/>
-      <c r="Q29" s="277" t="n"/>
-      <c r="R29" s="277" t="n"/>
-      <c r="S29" s="278" t="n"/>
-      <c r="T29" s="306" t="n"/>
-      <c r="U29" s="277" t="n"/>
-      <c r="V29" s="277" t="n"/>
-      <c r="W29" s="277" t="n"/>
-      <c r="X29" s="277" t="n"/>
-      <c r="Y29" s="277" t="n"/>
-      <c r="Z29" s="277" t="n"/>
-      <c r="AA29" s="277" t="n"/>
-      <c r="AB29" s="277" t="n"/>
-      <c r="AC29" s="277" t="n"/>
-      <c r="AD29" s="277" t="n"/>
-      <c r="AE29" s="278" t="n"/>
-      <c r="AF29" s="307" t="n"/>
-      <c r="AG29" s="277" t="n"/>
-      <c r="AH29" s="277" t="n"/>
-      <c r="AI29" s="278" t="n"/>
-      <c r="AJ29" s="307" t="n"/>
-      <c r="AK29" s="277" t="n"/>
-      <c r="AL29" s="278" t="n"/>
-      <c r="AM29" s="308" t="n"/>
-      <c r="AN29" s="280" t="n"/>
+      <c r="A29" s="355" t="n"/>
+      <c r="B29" s="383" t="n"/>
+      <c r="C29" s="356" t="n"/>
+      <c r="D29" s="382" t="n"/>
+      <c r="E29" s="383" t="n"/>
+      <c r="F29" s="360" t="n"/>
+      <c r="G29" s="382" t="n"/>
+      <c r="H29" s="382" t="n"/>
+      <c r="I29" s="382" t="n"/>
+      <c r="J29" s="382" t="n"/>
+      <c r="K29" s="382" t="n"/>
+      <c r="L29" s="382" t="n"/>
+      <c r="M29" s="382" t="n"/>
+      <c r="N29" s="382" t="n"/>
+      <c r="O29" s="382" t="n"/>
+      <c r="P29" s="382" t="n"/>
+      <c r="Q29" s="382" t="n"/>
+      <c r="R29" s="382" t="n"/>
+      <c r="S29" s="383" t="n"/>
+      <c r="T29" s="357" t="n"/>
+      <c r="U29" s="382" t="n"/>
+      <c r="V29" s="382" t="n"/>
+      <c r="W29" s="382" t="n"/>
+      <c r="X29" s="382" t="n"/>
+      <c r="Y29" s="382" t="n"/>
+      <c r="Z29" s="382" t="n"/>
+      <c r="AA29" s="382" t="n"/>
+      <c r="AB29" s="382" t="n"/>
+      <c r="AC29" s="382" t="n"/>
+      <c r="AD29" s="382" t="n"/>
+      <c r="AE29" s="383" t="n"/>
+      <c r="AF29" s="358" t="n"/>
+      <c r="AG29" s="382" t="n"/>
+      <c r="AH29" s="382" t="n"/>
+      <c r="AI29" s="383" t="n"/>
+      <c r="AJ29" s="358" t="n"/>
+      <c r="AK29" s="382" t="n"/>
+      <c r="AL29" s="383" t="n"/>
+      <c r="AM29" s="359" t="n"/>
+      <c r="AN29" s="383" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="304" t="n"/>
-      <c r="B30" s="278" t="n"/>
-      <c r="C30" s="305" t="n"/>
-      <c r="D30" s="277" t="n"/>
-      <c r="E30" s="278" t="n"/>
-      <c r="F30" s="296" t="n"/>
-      <c r="G30" s="277" t="n"/>
-      <c r="H30" s="277" t="n"/>
-      <c r="I30" s="277" t="n"/>
-      <c r="J30" s="277" t="n"/>
-      <c r="K30" s="277" t="n"/>
-      <c r="L30" s="277" t="n"/>
-      <c r="M30" s="277" t="n"/>
-      <c r="N30" s="277" t="n"/>
-      <c r="O30" s="277" t="n"/>
-      <c r="P30" s="277" t="n"/>
-      <c r="Q30" s="277" t="n"/>
-      <c r="R30" s="277" t="n"/>
-      <c r="S30" s="278" t="n"/>
-      <c r="T30" s="306" t="n"/>
-      <c r="U30" s="277" t="n"/>
-      <c r="V30" s="277" t="n"/>
-      <c r="W30" s="277" t="n"/>
-      <c r="X30" s="277" t="n"/>
-      <c r="Y30" s="277" t="n"/>
-      <c r="Z30" s="277" t="n"/>
-      <c r="AA30" s="277" t="n"/>
-      <c r="AB30" s="277" t="n"/>
-      <c r="AC30" s="277" t="n"/>
-      <c r="AD30" s="277" t="n"/>
-      <c r="AE30" s="278" t="n"/>
-      <c r="AF30" s="307" t="n"/>
-      <c r="AG30" s="277" t="n"/>
-      <c r="AH30" s="277" t="n"/>
-      <c r="AI30" s="278" t="n"/>
-      <c r="AJ30" s="307" t="n"/>
-      <c r="AK30" s="277" t="n"/>
-      <c r="AL30" s="278" t="n"/>
-      <c r="AM30" s="308" t="n"/>
-      <c r="AN30" s="280" t="n"/>
+      <c r="A30" s="355" t="n"/>
+      <c r="B30" s="383" t="n"/>
+      <c r="C30" s="356" t="n"/>
+      <c r="D30" s="382" t="n"/>
+      <c r="E30" s="383" t="n"/>
+      <c r="F30" s="338" t="n"/>
+      <c r="G30" s="382" t="n"/>
+      <c r="H30" s="382" t="n"/>
+      <c r="I30" s="382" t="n"/>
+      <c r="J30" s="382" t="n"/>
+      <c r="K30" s="382" t="n"/>
+      <c r="L30" s="382" t="n"/>
+      <c r="M30" s="382" t="n"/>
+      <c r="N30" s="382" t="n"/>
+      <c r="O30" s="382" t="n"/>
+      <c r="P30" s="382" t="n"/>
+      <c r="Q30" s="382" t="n"/>
+      <c r="R30" s="382" t="n"/>
+      <c r="S30" s="383" t="n"/>
+      <c r="T30" s="357" t="n"/>
+      <c r="U30" s="382" t="n"/>
+      <c r="V30" s="382" t="n"/>
+      <c r="W30" s="382" t="n"/>
+      <c r="X30" s="382" t="n"/>
+      <c r="Y30" s="382" t="n"/>
+      <c r="Z30" s="382" t="n"/>
+      <c r="AA30" s="382" t="n"/>
+      <c r="AB30" s="382" t="n"/>
+      <c r="AC30" s="382" t="n"/>
+      <c r="AD30" s="382" t="n"/>
+      <c r="AE30" s="383" t="n"/>
+      <c r="AF30" s="358" t="n"/>
+      <c r="AG30" s="382" t="n"/>
+      <c r="AH30" s="382" t="n"/>
+      <c r="AI30" s="383" t="n"/>
+      <c r="AJ30" s="358" t="n"/>
+      <c r="AK30" s="382" t="n"/>
+      <c r="AL30" s="383" t="n"/>
+      <c r="AM30" s="359" t="n"/>
+      <c r="AN30" s="383" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="310" t="n"/>
-      <c r="B31" s="285" t="n"/>
-      <c r="C31" s="311" t="n"/>
-      <c r="D31" s="283" t="n"/>
-      <c r="E31" s="285" t="n"/>
-      <c r="F31" s="312" t="n"/>
-      <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
-      <c r="J31" s="283" t="n"/>
-      <c r="K31" s="283" t="n"/>
-      <c r="L31" s="283" t="n"/>
-      <c r="M31" s="283" t="n"/>
-      <c r="N31" s="283" t="n"/>
-      <c r="O31" s="283" t="n"/>
-      <c r="P31" s="283" t="n"/>
-      <c r="Q31" s="283" t="n"/>
-      <c r="R31" s="283" t="n"/>
-      <c r="S31" s="285" t="n"/>
-      <c r="T31" s="313" t="n"/>
-      <c r="U31" s="283" t="n"/>
-      <c r="V31" s="283" t="n"/>
-      <c r="W31" s="283" t="n"/>
-      <c r="X31" s="283" t="n"/>
-      <c r="Y31" s="283" t="n"/>
-      <c r="Z31" s="283" t="n"/>
-      <c r="AA31" s="283" t="n"/>
-      <c r="AB31" s="283" t="n"/>
-      <c r="AC31" s="283" t="n"/>
-      <c r="AD31" s="283" t="n"/>
-      <c r="AE31" s="285" t="n"/>
-      <c r="AF31" s="314" t="n"/>
-      <c r="AG31" s="283" t="n"/>
-      <c r="AH31" s="283" t="n"/>
-      <c r="AI31" s="285" t="n"/>
-      <c r="AJ31" s="314" t="n"/>
-      <c r="AK31" s="283" t="n"/>
-      <c r="AL31" s="285" t="n"/>
-      <c r="AM31" s="315" t="n"/>
-      <c r="AN31" s="287" t="n"/>
+      <c r="A31" s="355" t="n"/>
+      <c r="B31" s="383" t="n"/>
+      <c r="C31" s="356" t="n"/>
+      <c r="D31" s="382" t="n"/>
+      <c r="E31" s="383" t="n"/>
+      <c r="F31" s="360" t="n"/>
+      <c r="G31" s="382" t="n"/>
+      <c r="H31" s="382" t="n"/>
+      <c r="I31" s="382" t="n"/>
+      <c r="J31" s="382" t="n"/>
+      <c r="K31" s="382" t="n"/>
+      <c r="L31" s="382" t="n"/>
+      <c r="M31" s="382" t="n"/>
+      <c r="N31" s="382" t="n"/>
+      <c r="O31" s="382" t="n"/>
+      <c r="P31" s="382" t="n"/>
+      <c r="Q31" s="382" t="n"/>
+      <c r="R31" s="382" t="n"/>
+      <c r="S31" s="383" t="n"/>
+      <c r="T31" s="357" t="n"/>
+      <c r="U31" s="382" t="n"/>
+      <c r="V31" s="382" t="n"/>
+      <c r="W31" s="382" t="n"/>
+      <c r="X31" s="382" t="n"/>
+      <c r="Y31" s="382" t="n"/>
+      <c r="Z31" s="382" t="n"/>
+      <c r="AA31" s="382" t="n"/>
+      <c r="AB31" s="382" t="n"/>
+      <c r="AC31" s="382" t="n"/>
+      <c r="AD31" s="382" t="n"/>
+      <c r="AE31" s="383" t="n"/>
+      <c r="AF31" s="358" t="n"/>
+      <c r="AG31" s="382" t="n"/>
+      <c r="AH31" s="382" t="n"/>
+      <c r="AI31" s="383" t="n"/>
+      <c r="AJ31" s="358" t="n"/>
+      <c r="AK31" s="382" t="n"/>
+      <c r="AL31" s="383" t="n"/>
+      <c r="AM31" s="359" t="n"/>
+      <c r="AN31" s="383" t="n"/>
     </row>
     <row r="32" ht="4" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="288" t="inlineStr">
+      <c r="A32" s="342" t="n"/>
+      <c r="B32" s="389" t="n"/>
+      <c r="C32" s="389" t="n"/>
+      <c r="D32" s="389" t="n"/>
+      <c r="E32" s="389" t="n"/>
+      <c r="F32" s="389" t="n"/>
+      <c r="G32" s="389" t="n"/>
+      <c r="H32" s="389" t="n"/>
+      <c r="I32" s="389" t="n"/>
+      <c r="J32" s="389" t="n"/>
+      <c r="K32" s="389" t="n"/>
+      <c r="L32" s="389" t="n"/>
+      <c r="M32" s="389" t="n"/>
+      <c r="N32" s="389" t="n"/>
+      <c r="O32" s="389" t="n"/>
+      <c r="P32" s="389" t="n"/>
+      <c r="Q32" s="389" t="n"/>
+      <c r="R32" s="389" t="n"/>
+      <c r="S32" s="389" t="n"/>
+      <c r="T32" s="389" t="n"/>
+      <c r="U32" s="389" t="n"/>
+      <c r="V32" s="389" t="n"/>
+      <c r="W32" s="389" t="n"/>
+      <c r="X32" s="389" t="n"/>
+      <c r="Y32" s="389" t="n"/>
+      <c r="Z32" s="389" t="n"/>
+      <c r="AA32" s="389" t="n"/>
+      <c r="AB32" s="389" t="n"/>
+      <c r="AC32" s="389" t="n"/>
+      <c r="AD32" s="389" t="n"/>
+      <c r="AE32" s="389" t="n"/>
+      <c r="AF32" s="389" t="n"/>
+      <c r="AG32" s="389" t="n"/>
+      <c r="AH32" s="389" t="n"/>
+      <c r="AI32" s="389" t="n"/>
+      <c r="AJ32" s="389" t="n"/>
+      <c r="AK32" s="389" t="n"/>
+      <c r="AL32" s="389" t="n"/>
+      <c r="AM32" s="389" t="n"/>
+      <c r="AN32" s="389" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="343" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. PRINT CONTROL REFERENCE</t>
         </is>
       </c>
-      <c r="B33" s="289" t="n"/>
-      <c r="C33" s="289" t="n"/>
-      <c r="D33" s="289" t="n"/>
-      <c r="E33" s="289" t="n"/>
-      <c r="F33" s="289" t="n"/>
-      <c r="G33" s="289" t="n"/>
-      <c r="H33" s="289" t="n"/>
-      <c r="I33" s="289" t="n"/>
-      <c r="J33" s="289" t="n"/>
-      <c r="K33" s="289" t="n"/>
-      <c r="L33" s="289" t="n"/>
-      <c r="M33" s="289" t="n"/>
-      <c r="N33" s="289" t="n"/>
-      <c r="O33" s="289" t="n"/>
-      <c r="P33" s="289" t="n"/>
-      <c r="Q33" s="289" t="n"/>
-      <c r="R33" s="289" t="n"/>
-      <c r="S33" s="289" t="n"/>
-      <c r="T33" s="289" t="n"/>
-      <c r="U33" s="289" t="n"/>
-      <c r="V33" s="289" t="n"/>
-      <c r="W33" s="289" t="n"/>
-      <c r="X33" s="289" t="n"/>
-      <c r="Y33" s="289" t="n"/>
-      <c r="Z33" s="289" t="n"/>
-      <c r="AA33" s="289" t="n"/>
-      <c r="AB33" s="289" t="n"/>
-      <c r="AC33" s="289" t="n"/>
-      <c r="AD33" s="289" t="n"/>
-      <c r="AE33" s="289" t="n"/>
-      <c r="AF33" s="289" t="n"/>
-      <c r="AG33" s="289" t="n"/>
-      <c r="AH33" s="289" t="n"/>
-      <c r="AI33" s="289" t="n"/>
-      <c r="AJ33" s="289" t="n"/>
-      <c r="AK33" s="289" t="n"/>
-      <c r="AL33" s="289" t="n"/>
-      <c r="AM33" s="289" t="n"/>
-      <c r="AN33" s="290" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="301" t="inlineStr">
+      <c r="B33" s="380" t="n"/>
+      <c r="C33" s="380" t="n"/>
+      <c r="D33" s="380" t="n"/>
+      <c r="E33" s="380" t="n"/>
+      <c r="F33" s="380" t="n"/>
+      <c r="G33" s="380" t="n"/>
+      <c r="H33" s="380" t="n"/>
+      <c r="I33" s="380" t="n"/>
+      <c r="J33" s="380" t="n"/>
+      <c r="K33" s="380" t="n"/>
+      <c r="L33" s="380" t="n"/>
+      <c r="M33" s="380" t="n"/>
+      <c r="N33" s="380" t="n"/>
+      <c r="O33" s="380" t="n"/>
+      <c r="P33" s="380" t="n"/>
+      <c r="Q33" s="380" t="n"/>
+      <c r="R33" s="380" t="n"/>
+      <c r="S33" s="380" t="n"/>
+      <c r="T33" s="380" t="n"/>
+      <c r="U33" s="380" t="n"/>
+      <c r="V33" s="380" t="n"/>
+      <c r="W33" s="380" t="n"/>
+      <c r="X33" s="380" t="n"/>
+      <c r="Y33" s="380" t="n"/>
+      <c r="Z33" s="380" t="n"/>
+      <c r="AA33" s="380" t="n"/>
+      <c r="AB33" s="380" t="n"/>
+      <c r="AC33" s="380" t="n"/>
+      <c r="AD33" s="380" t="n"/>
+      <c r="AE33" s="380" t="n"/>
+      <c r="AF33" s="380" t="n"/>
+      <c r="AG33" s="380" t="n"/>
+      <c r="AH33" s="380" t="n"/>
+      <c r="AI33" s="380" t="n"/>
+      <c r="AJ33" s="380" t="n"/>
+      <c r="AK33" s="380" t="n"/>
+      <c r="AL33" s="380" t="n"/>
+      <c r="AM33" s="380" t="n"/>
+      <c r="AN33" s="381" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="353" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="272" t="n"/>
-      <c r="C34" s="302" t="inlineStr">
+      <c r="B34" s="381" t="n"/>
+      <c r="C34" s="354" t="inlineStr">
         <is>
           <t>Control Field</t>
         </is>
       </c>
-      <c r="D34" s="271" t="n"/>
-      <c r="E34" s="271" t="n"/>
-      <c r="F34" s="271" t="n"/>
-      <c r="G34" s="271" t="n"/>
-      <c r="H34" s="271" t="n"/>
-      <c r="I34" s="271" t="n"/>
-      <c r="J34" s="271" t="n"/>
-      <c r="K34" s="271" t="n"/>
-      <c r="L34" s="272" t="n"/>
-      <c r="M34" s="302" t="inlineStr">
+      <c r="D34" s="380" t="n"/>
+      <c r="E34" s="380" t="n"/>
+      <c r="F34" s="380" t="n"/>
+      <c r="G34" s="380" t="n"/>
+      <c r="H34" s="380" t="n"/>
+      <c r="I34" s="380" t="n"/>
+      <c r="J34" s="380" t="n"/>
+      <c r="K34" s="380" t="n"/>
+      <c r="L34" s="381" t="n"/>
+      <c r="M34" s="354" t="inlineStr">
         <is>
           <t>Required Record</t>
         </is>
       </c>
-      <c r="N34" s="271" t="n"/>
-      <c r="O34" s="271" t="n"/>
-      <c r="P34" s="271" t="n"/>
-      <c r="Q34" s="271" t="n"/>
-      <c r="R34" s="271" t="n"/>
-      <c r="S34" s="271" t="n"/>
-      <c r="T34" s="271" t="n"/>
-      <c r="U34" s="271" t="n"/>
-      <c r="V34" s="271" t="n"/>
-      <c r="W34" s="271" t="n"/>
-      <c r="X34" s="272" t="n"/>
-      <c r="Y34" s="302" t="inlineStr">
+      <c r="N34" s="380" t="n"/>
+      <c r="O34" s="380" t="n"/>
+      <c r="P34" s="380" t="n"/>
+      <c r="Q34" s="380" t="n"/>
+      <c r="R34" s="380" t="n"/>
+      <c r="S34" s="380" t="n"/>
+      <c r="T34" s="380" t="n"/>
+      <c r="U34" s="380" t="n"/>
+      <c r="V34" s="380" t="n"/>
+      <c r="W34" s="380" t="n"/>
+      <c r="X34" s="381" t="n"/>
+      <c r="Y34" s="354" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="271" t="n"/>
-      <c r="AA34" s="271" t="n"/>
-      <c r="AB34" s="271" t="n"/>
-      <c r="AC34" s="272" t="n"/>
-      <c r="AD34" s="302" t="inlineStr">
+      <c r="Z34" s="380" t="n"/>
+      <c r="AA34" s="380" t="n"/>
+      <c r="AB34" s="380" t="n"/>
+      <c r="AC34" s="381" t="n"/>
+      <c r="AD34" s="354" t="inlineStr">
         <is>
           <t>Event State</t>
         </is>
       </c>
-      <c r="AE34" s="271" t="n"/>
-      <c r="AF34" s="271" t="n"/>
-      <c r="AG34" s="271" t="n"/>
-      <c r="AH34" s="272" t="n"/>
-      <c r="AI34" s="302" t="inlineStr">
+      <c r="AE34" s="380" t="n"/>
+      <c r="AF34" s="380" t="n"/>
+      <c r="AG34" s="380" t="n"/>
+      <c r="AH34" s="381" t="n"/>
+      <c r="AI34" s="354" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AJ34" s="271" t="n"/>
-      <c r="AK34" s="272" t="n"/>
-      <c r="AL34" s="303" t="inlineStr">
+      <c r="AJ34" s="380" t="n"/>
+      <c r="AK34" s="381" t="n"/>
+      <c r="AL34" s="354" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="AM34" s="271" t="n"/>
-      <c r="AN34" s="274" t="n"/>
+      <c r="AM34" s="380" t="n"/>
+      <c r="AN34" s="381" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="304">
+      <c r="A35" s="355">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B35" s="278" t="n"/>
-      <c r="C35" s="296" t="inlineStr">
+      <c r="B35" s="383" t="n"/>
+      <c r="C35" s="338" t="inlineStr">
         <is>
           <t>Released by</t>
         </is>
       </c>
-      <c r="D35" s="277" t="n"/>
-      <c r="E35" s="277" t="n"/>
-      <c r="F35" s="277" t="n"/>
-      <c r="G35" s="277" t="n"/>
-      <c r="H35" s="277" t="n"/>
-      <c r="I35" s="277" t="n"/>
-      <c r="J35" s="277" t="n"/>
-      <c r="K35" s="277" t="n"/>
-      <c r="L35" s="278" t="n"/>
-      <c r="M35" s="296" t="n"/>
-      <c r="N35" s="277" t="n"/>
-      <c r="O35" s="277" t="n"/>
-      <c r="P35" s="277" t="n"/>
-      <c r="Q35" s="277" t="n"/>
-      <c r="R35" s="277" t="n"/>
-      <c r="S35" s="277" t="n"/>
-      <c r="T35" s="277" t="n"/>
-      <c r="U35" s="277" t="n"/>
-      <c r="V35" s="277" t="n"/>
-      <c r="W35" s="277" t="n"/>
-      <c r="X35" s="278" t="n"/>
-      <c r="Y35" s="307" t="n"/>
-      <c r="Z35" s="277" t="n"/>
-      <c r="AA35" s="277" t="n"/>
-      <c r="AB35" s="277" t="n"/>
-      <c r="AC35" s="278" t="n"/>
-      <c r="AD35" s="307" t="n"/>
-      <c r="AE35" s="277" t="n"/>
-      <c r="AF35" s="277" t="n"/>
-      <c r="AG35" s="277" t="n"/>
-      <c r="AH35" s="278" t="n"/>
-      <c r="AI35" s="307" t="n"/>
-      <c r="AJ35" s="277" t="n"/>
-      <c r="AK35" s="278" t="n"/>
-      <c r="AL35" s="316" t="n"/>
-      <c r="AM35" s="277" t="n"/>
-      <c r="AN35" s="280" t="n"/>
+      <c r="D35" s="382" t="n"/>
+      <c r="E35" s="382" t="n"/>
+      <c r="F35" s="382" t="n"/>
+      <c r="G35" s="382" t="n"/>
+      <c r="H35" s="382" t="n"/>
+      <c r="I35" s="382" t="n"/>
+      <c r="J35" s="382" t="n"/>
+      <c r="K35" s="382" t="n"/>
+      <c r="L35" s="383" t="n"/>
+      <c r="M35" s="338" t="n"/>
+      <c r="N35" s="382" t="n"/>
+      <c r="O35" s="382" t="n"/>
+      <c r="P35" s="382" t="n"/>
+      <c r="Q35" s="382" t="n"/>
+      <c r="R35" s="382" t="n"/>
+      <c r="S35" s="382" t="n"/>
+      <c r="T35" s="382" t="n"/>
+      <c r="U35" s="382" t="n"/>
+      <c r="V35" s="382" t="n"/>
+      <c r="W35" s="382" t="n"/>
+      <c r="X35" s="383" t="n"/>
+      <c r="Y35" s="358" t="n"/>
+      <c r="Z35" s="382" t="n"/>
+      <c r="AA35" s="382" t="n"/>
+      <c r="AB35" s="382" t="n"/>
+      <c r="AC35" s="383" t="n"/>
+      <c r="AD35" s="358" t="n"/>
+      <c r="AE35" s="382" t="n"/>
+      <c r="AF35" s="382" t="n"/>
+      <c r="AG35" s="382" t="n"/>
+      <c r="AH35" s="383" t="n"/>
+      <c r="AI35" s="358" t="n"/>
+      <c r="AJ35" s="382" t="n"/>
+      <c r="AK35" s="383" t="n"/>
+      <c r="AL35" s="358" t="n"/>
+      <c r="AM35" s="382" t="n"/>
+      <c r="AN35" s="383" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="304">
+      <c r="A36" s="355">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B36" s="278" t="n"/>
-      <c r="C36" s="296" t="inlineStr">
+      <c r="B36" s="383" t="n"/>
+      <c r="C36" s="338" t="inlineStr">
         <is>
           <t>Printed by</t>
         </is>
       </c>
-      <c r="D36" s="277" t="n"/>
-      <c r="E36" s="277" t="n"/>
-      <c r="F36" s="277" t="n"/>
-      <c r="G36" s="277" t="n"/>
-      <c r="H36" s="277" t="n"/>
-      <c r="I36" s="277" t="n"/>
-      <c r="J36" s="277" t="n"/>
-      <c r="K36" s="277" t="n"/>
-      <c r="L36" s="278" t="n"/>
-      <c r="M36" s="296" t="n"/>
-      <c r="N36" s="277" t="n"/>
-      <c r="O36" s="277" t="n"/>
-      <c r="P36" s="277" t="n"/>
-      <c r="Q36" s="277" t="n"/>
-      <c r="R36" s="277" t="n"/>
-      <c r="S36" s="277" t="n"/>
-      <c r="T36" s="277" t="n"/>
-      <c r="U36" s="277" t="n"/>
-      <c r="V36" s="277" t="n"/>
-      <c r="W36" s="277" t="n"/>
-      <c r="X36" s="278" t="n"/>
-      <c r="Y36" s="307" t="n"/>
-      <c r="Z36" s="277" t="n"/>
-      <c r="AA36" s="277" t="n"/>
-      <c r="AB36" s="277" t="n"/>
-      <c r="AC36" s="278" t="n"/>
-      <c r="AD36" s="307" t="n"/>
-      <c r="AE36" s="277" t="n"/>
-      <c r="AF36" s="277" t="n"/>
-      <c r="AG36" s="277" t="n"/>
-      <c r="AH36" s="278" t="n"/>
-      <c r="AI36" s="307" t="n"/>
-      <c r="AJ36" s="277" t="n"/>
-      <c r="AK36" s="278" t="n"/>
-      <c r="AL36" s="316" t="n"/>
-      <c r="AM36" s="277" t="n"/>
-      <c r="AN36" s="280" t="n"/>
+      <c r="D36" s="382" t="n"/>
+      <c r="E36" s="382" t="n"/>
+      <c r="F36" s="382" t="n"/>
+      <c r="G36" s="382" t="n"/>
+      <c r="H36" s="382" t="n"/>
+      <c r="I36" s="382" t="n"/>
+      <c r="J36" s="382" t="n"/>
+      <c r="K36" s="382" t="n"/>
+      <c r="L36" s="383" t="n"/>
+      <c r="M36" s="338" t="n"/>
+      <c r="N36" s="382" t="n"/>
+      <c r="O36" s="382" t="n"/>
+      <c r="P36" s="382" t="n"/>
+      <c r="Q36" s="382" t="n"/>
+      <c r="R36" s="382" t="n"/>
+      <c r="S36" s="382" t="n"/>
+      <c r="T36" s="382" t="n"/>
+      <c r="U36" s="382" t="n"/>
+      <c r="V36" s="382" t="n"/>
+      <c r="W36" s="382" t="n"/>
+      <c r="X36" s="383" t="n"/>
+      <c r="Y36" s="358" t="n"/>
+      <c r="Z36" s="382" t="n"/>
+      <c r="AA36" s="382" t="n"/>
+      <c r="AB36" s="382" t="n"/>
+      <c r="AC36" s="383" t="n"/>
+      <c r="AD36" s="358" t="n"/>
+      <c r="AE36" s="382" t="n"/>
+      <c r="AF36" s="382" t="n"/>
+      <c r="AG36" s="382" t="n"/>
+      <c r="AH36" s="383" t="n"/>
+      <c r="AI36" s="358" t="n"/>
+      <c r="AJ36" s="382" t="n"/>
+      <c r="AK36" s="383" t="n"/>
+      <c r="AL36" s="358" t="n"/>
+      <c r="AM36" s="382" t="n"/>
+      <c r="AN36" s="383" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="304">
+      <c r="A37" s="355">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B37" s="278" t="n"/>
-      <c r="C37" s="296" t="inlineStr">
+      <c r="B37" s="383" t="n"/>
+      <c r="C37" s="338" t="inlineStr">
         <is>
           <t>Verified application</t>
         </is>
       </c>
-      <c r="D37" s="277" t="n"/>
-      <c r="E37" s="277" t="n"/>
-      <c r="F37" s="277" t="n"/>
-      <c r="G37" s="277" t="n"/>
-      <c r="H37" s="277" t="n"/>
-      <c r="I37" s="277" t="n"/>
-      <c r="J37" s="277" t="n"/>
-      <c r="K37" s="277" t="n"/>
-      <c r="L37" s="278" t="n"/>
-      <c r="M37" s="296" t="n"/>
-      <c r="N37" s="277" t="n"/>
-      <c r="O37" s="277" t="n"/>
-      <c r="P37" s="277" t="n"/>
-      <c r="Q37" s="277" t="n"/>
-      <c r="R37" s="277" t="n"/>
-      <c r="S37" s="277" t="n"/>
-      <c r="T37" s="277" t="n"/>
-      <c r="U37" s="277" t="n"/>
-      <c r="V37" s="277" t="n"/>
-      <c r="W37" s="277" t="n"/>
-      <c r="X37" s="278" t="n"/>
-      <c r="Y37" s="307" t="n"/>
-      <c r="Z37" s="277" t="n"/>
-      <c r="AA37" s="277" t="n"/>
-      <c r="AB37" s="277" t="n"/>
-      <c r="AC37" s="278" t="n"/>
-      <c r="AD37" s="307" t="n"/>
-      <c r="AE37" s="277" t="n"/>
-      <c r="AF37" s="277" t="n"/>
-      <c r="AG37" s="277" t="n"/>
-      <c r="AH37" s="278" t="n"/>
-      <c r="AI37" s="307" t="n"/>
-      <c r="AJ37" s="277" t="n"/>
-      <c r="AK37" s="278" t="n"/>
-      <c r="AL37" s="316" t="n"/>
-      <c r="AM37" s="277" t="n"/>
-      <c r="AN37" s="280" t="n"/>
+      <c r="D37" s="382" t="n"/>
+      <c r="E37" s="382" t="n"/>
+      <c r="F37" s="382" t="n"/>
+      <c r="G37" s="382" t="n"/>
+      <c r="H37" s="382" t="n"/>
+      <c r="I37" s="382" t="n"/>
+      <c r="J37" s="382" t="n"/>
+      <c r="K37" s="382" t="n"/>
+      <c r="L37" s="383" t="n"/>
+      <c r="M37" s="338" t="n"/>
+      <c r="N37" s="382" t="n"/>
+      <c r="O37" s="382" t="n"/>
+      <c r="P37" s="382" t="n"/>
+      <c r="Q37" s="382" t="n"/>
+      <c r="R37" s="382" t="n"/>
+      <c r="S37" s="382" t="n"/>
+      <c r="T37" s="382" t="n"/>
+      <c r="U37" s="382" t="n"/>
+      <c r="V37" s="382" t="n"/>
+      <c r="W37" s="382" t="n"/>
+      <c r="X37" s="383" t="n"/>
+      <c r="Y37" s="358" t="n"/>
+      <c r="Z37" s="382" t="n"/>
+      <c r="AA37" s="382" t="n"/>
+      <c r="AB37" s="382" t="n"/>
+      <c r="AC37" s="383" t="n"/>
+      <c r="AD37" s="358" t="n"/>
+      <c r="AE37" s="382" t="n"/>
+      <c r="AF37" s="382" t="n"/>
+      <c r="AG37" s="382" t="n"/>
+      <c r="AH37" s="383" t="n"/>
+      <c r="AI37" s="358" t="n"/>
+      <c r="AJ37" s="382" t="n"/>
+      <c r="AK37" s="383" t="n"/>
+      <c r="AL37" s="358" t="n"/>
+      <c r="AM37" s="382" t="n"/>
+      <c r="AN37" s="383" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="304">
+      <c r="A38" s="355">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B38" s="278" t="n"/>
-      <c r="C38" s="296" t="inlineStr">
+      <c r="B38" s="383" t="n"/>
+      <c r="C38" s="338" t="inlineStr">
         <is>
           <t>Void / scrap</t>
         </is>
       </c>
-      <c r="D38" s="277" t="n"/>
-      <c r="E38" s="277" t="n"/>
-      <c r="F38" s="277" t="n"/>
-      <c r="G38" s="277" t="n"/>
-      <c r="H38" s="277" t="n"/>
-      <c r="I38" s="277" t="n"/>
-      <c r="J38" s="277" t="n"/>
-      <c r="K38" s="277" t="n"/>
-      <c r="L38" s="278" t="n"/>
-      <c r="M38" s="296" t="n"/>
-      <c r="N38" s="277" t="n"/>
-      <c r="O38" s="277" t="n"/>
-      <c r="P38" s="277" t="n"/>
-      <c r="Q38" s="277" t="n"/>
-      <c r="R38" s="277" t="n"/>
-      <c r="S38" s="277" t="n"/>
-      <c r="T38" s="277" t="n"/>
-      <c r="U38" s="277" t="n"/>
-      <c r="V38" s="277" t="n"/>
-      <c r="W38" s="277" t="n"/>
-      <c r="X38" s="278" t="n"/>
-      <c r="Y38" s="307" t="n"/>
-      <c r="Z38" s="277" t="n"/>
-      <c r="AA38" s="277" t="n"/>
-      <c r="AB38" s="277" t="n"/>
-      <c r="AC38" s="278" t="n"/>
-      <c r="AD38" s="307" t="n"/>
-      <c r="AE38" s="277" t="n"/>
-      <c r="AF38" s="277" t="n"/>
-      <c r="AG38" s="277" t="n"/>
-      <c r="AH38" s="278" t="n"/>
-      <c r="AI38" s="307" t="n"/>
-      <c r="AJ38" s="277" t="n"/>
-      <c r="AK38" s="278" t="n"/>
-      <c r="AL38" s="316" t="n"/>
-      <c r="AM38" s="277" t="n"/>
-      <c r="AN38" s="280" t="n"/>
+      <c r="D38" s="382" t="n"/>
+      <c r="E38" s="382" t="n"/>
+      <c r="F38" s="382" t="n"/>
+      <c r="G38" s="382" t="n"/>
+      <c r="H38" s="382" t="n"/>
+      <c r="I38" s="382" t="n"/>
+      <c r="J38" s="382" t="n"/>
+      <c r="K38" s="382" t="n"/>
+      <c r="L38" s="383" t="n"/>
+      <c r="M38" s="338" t="n"/>
+      <c r="N38" s="382" t="n"/>
+      <c r="O38" s="382" t="n"/>
+      <c r="P38" s="382" t="n"/>
+      <c r="Q38" s="382" t="n"/>
+      <c r="R38" s="382" t="n"/>
+      <c r="S38" s="382" t="n"/>
+      <c r="T38" s="382" t="n"/>
+      <c r="U38" s="382" t="n"/>
+      <c r="V38" s="382" t="n"/>
+      <c r="W38" s="382" t="n"/>
+      <c r="X38" s="383" t="n"/>
+      <c r="Y38" s="358" t="n"/>
+      <c r="Z38" s="382" t="n"/>
+      <c r="AA38" s="382" t="n"/>
+      <c r="AB38" s="382" t="n"/>
+      <c r="AC38" s="383" t="n"/>
+      <c r="AD38" s="358" t="n"/>
+      <c r="AE38" s="382" t="n"/>
+      <c r="AF38" s="382" t="n"/>
+      <c r="AG38" s="382" t="n"/>
+      <c r="AH38" s="383" t="n"/>
+      <c r="AI38" s="358" t="n"/>
+      <c r="AJ38" s="382" t="n"/>
+      <c r="AK38" s="383" t="n"/>
+      <c r="AL38" s="358" t="n"/>
+      <c r="AM38" s="382" t="n"/>
+      <c r="AN38" s="383" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="310">
+      <c r="A39" s="355">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B39" s="285" t="n"/>
-      <c r="C39" s="299" t="inlineStr">
+      <c r="B39" s="383" t="n"/>
+      <c r="C39" s="338" t="inlineStr">
         <is>
           <t>Reprint justification</t>
         </is>
       </c>
-      <c r="D39" s="283" t="n"/>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
-      <c r="J39" s="283" t="n"/>
-      <c r="K39" s="283" t="n"/>
-      <c r="L39" s="285" t="n"/>
-      <c r="M39" s="299" t="n"/>
-      <c r="N39" s="283" t="n"/>
-      <c r="O39" s="283" t="n"/>
-      <c r="P39" s="283" t="n"/>
-      <c r="Q39" s="283" t="n"/>
-      <c r="R39" s="283" t="n"/>
-      <c r="S39" s="283" t="n"/>
-      <c r="T39" s="283" t="n"/>
-      <c r="U39" s="283" t="n"/>
-      <c r="V39" s="283" t="n"/>
-      <c r="W39" s="283" t="n"/>
-      <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="314" t="n"/>
-      <c r="Z39" s="283" t="n"/>
-      <c r="AA39" s="283" t="n"/>
-      <c r="AB39" s="283" t="n"/>
-      <c r="AC39" s="285" t="n"/>
-      <c r="AD39" s="314" t="n"/>
-      <c r="AE39" s="283" t="n"/>
-      <c r="AF39" s="283" t="n"/>
-      <c r="AG39" s="283" t="n"/>
-      <c r="AH39" s="285" t="n"/>
-      <c r="AI39" s="314" t="n"/>
-      <c r="AJ39" s="283" t="n"/>
-      <c r="AK39" s="285" t="n"/>
-      <c r="AL39" s="317" t="n"/>
-      <c r="AM39" s="283" t="n"/>
-      <c r="AN39" s="287" t="n"/>
+      <c r="D39" s="382" t="n"/>
+      <c r="E39" s="382" t="n"/>
+      <c r="F39" s="382" t="n"/>
+      <c r="G39" s="382" t="n"/>
+      <c r="H39" s="382" t="n"/>
+      <c r="I39" s="382" t="n"/>
+      <c r="J39" s="382" t="n"/>
+      <c r="K39" s="382" t="n"/>
+      <c r="L39" s="383" t="n"/>
+      <c r="M39" s="338" t="n"/>
+      <c r="N39" s="382" t="n"/>
+      <c r="O39" s="382" t="n"/>
+      <c r="P39" s="382" t="n"/>
+      <c r="Q39" s="382" t="n"/>
+      <c r="R39" s="382" t="n"/>
+      <c r="S39" s="382" t="n"/>
+      <c r="T39" s="382" t="n"/>
+      <c r="U39" s="382" t="n"/>
+      <c r="V39" s="382" t="n"/>
+      <c r="W39" s="382" t="n"/>
+      <c r="X39" s="383" t="n"/>
+      <c r="Y39" s="358" t="n"/>
+      <c r="Z39" s="382" t="n"/>
+      <c r="AA39" s="382" t="n"/>
+      <c r="AB39" s="382" t="n"/>
+      <c r="AC39" s="383" t="n"/>
+      <c r="AD39" s="358" t="n"/>
+      <c r="AE39" s="382" t="n"/>
+      <c r="AF39" s="382" t="n"/>
+      <c r="AG39" s="382" t="n"/>
+      <c r="AH39" s="383" t="n"/>
+      <c r="AI39" s="358" t="n"/>
+      <c r="AJ39" s="382" t="n"/>
+      <c r="AK39" s="383" t="n"/>
+      <c r="AL39" s="358" t="n"/>
+      <c r="AM39" s="382" t="n"/>
+      <c r="AN39" s="383" t="n"/>
     </row>
     <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="25" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="288" t="inlineStr">
+      <c r="A40" s="342" t="n"/>
+      <c r="B40" s="389" t="n"/>
+      <c r="C40" s="389" t="n"/>
+      <c r="D40" s="389" t="n"/>
+      <c r="E40" s="389" t="n"/>
+      <c r="F40" s="389" t="n"/>
+      <c r="G40" s="389" t="n"/>
+      <c r="H40" s="389" t="n"/>
+      <c r="I40" s="389" t="n"/>
+      <c r="J40" s="389" t="n"/>
+      <c r="K40" s="389" t="n"/>
+      <c r="L40" s="389" t="n"/>
+      <c r="M40" s="389" t="n"/>
+      <c r="N40" s="389" t="n"/>
+      <c r="O40" s="389" t="n"/>
+      <c r="P40" s="389" t="n"/>
+      <c r="Q40" s="389" t="n"/>
+      <c r="R40" s="389" t="n"/>
+      <c r="S40" s="389" t="n"/>
+      <c r="T40" s="389" t="n"/>
+      <c r="U40" s="389" t="n"/>
+      <c r="V40" s="389" t="n"/>
+      <c r="W40" s="389" t="n"/>
+      <c r="X40" s="389" t="n"/>
+      <c r="Y40" s="389" t="n"/>
+      <c r="Z40" s="389" t="n"/>
+      <c r="AA40" s="389" t="n"/>
+      <c r="AB40" s="389" t="n"/>
+      <c r="AC40" s="389" t="n"/>
+      <c r="AD40" s="389" t="n"/>
+      <c r="AE40" s="389" t="n"/>
+      <c r="AF40" s="389" t="n"/>
+      <c r="AG40" s="389" t="n"/>
+      <c r="AH40" s="389" t="n"/>
+      <c r="AI40" s="389" t="n"/>
+      <c r="AJ40" s="389" t="n"/>
+      <c r="AK40" s="389" t="n"/>
+      <c r="AL40" s="389" t="n"/>
+      <c r="AM40" s="389" t="n"/>
+      <c r="AN40" s="389" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="343" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPLICATION STATUS / NOTES</t>
         </is>
       </c>
-      <c r="B41" s="289" t="n"/>
-      <c r="C41" s="289" t="n"/>
-      <c r="D41" s="289" t="n"/>
-      <c r="E41" s="289" t="n"/>
-      <c r="F41" s="289" t="n"/>
-      <c r="G41" s="289" t="n"/>
-      <c r="H41" s="289" t="n"/>
-      <c r="I41" s="289" t="n"/>
-      <c r="J41" s="289" t="n"/>
-      <c r="K41" s="289" t="n"/>
-      <c r="L41" s="289" t="n"/>
-      <c r="M41" s="289" t="n"/>
-      <c r="N41" s="289" t="n"/>
-      <c r="O41" s="289" t="n"/>
-      <c r="P41" s="289" t="n"/>
-      <c r="Q41" s="289" t="n"/>
-      <c r="R41" s="289" t="n"/>
-      <c r="S41" s="289" t="n"/>
-      <c r="T41" s="289" t="n"/>
-      <c r="U41" s="289" t="n"/>
-      <c r="V41" s="289" t="n"/>
-      <c r="W41" s="289" t="n"/>
-      <c r="X41" s="289" t="n"/>
-      <c r="Y41" s="289" t="n"/>
-      <c r="Z41" s="289" t="n"/>
-      <c r="AA41" s="289" t="n"/>
-      <c r="AB41" s="289" t="n"/>
-      <c r="AC41" s="289" t="n"/>
-      <c r="AD41" s="289" t="n"/>
-      <c r="AE41" s="289" t="n"/>
-      <c r="AF41" s="289" t="n"/>
-      <c r="AG41" s="289" t="n"/>
-      <c r="AH41" s="289" t="n"/>
-      <c r="AI41" s="289" t="n"/>
-      <c r="AJ41" s="289" t="n"/>
-      <c r="AK41" s="289" t="n"/>
-      <c r="AL41" s="289" t="n"/>
-      <c r="AM41" s="289" t="n"/>
-      <c r="AN41" s="290" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="B41" s="380" t="n"/>
+      <c r="C41" s="380" t="n"/>
+      <c r="D41" s="380" t="n"/>
+      <c r="E41" s="380" t="n"/>
+      <c r="F41" s="380" t="n"/>
+      <c r="G41" s="380" t="n"/>
+      <c r="H41" s="380" t="n"/>
+      <c r="I41" s="380" t="n"/>
+      <c r="J41" s="380" t="n"/>
+      <c r="K41" s="380" t="n"/>
+      <c r="L41" s="380" t="n"/>
+      <c r="M41" s="380" t="n"/>
+      <c r="N41" s="380" t="n"/>
+      <c r="O41" s="380" t="n"/>
+      <c r="P41" s="380" t="n"/>
+      <c r="Q41" s="380" t="n"/>
+      <c r="R41" s="380" t="n"/>
+      <c r="S41" s="380" t="n"/>
+      <c r="T41" s="380" t="n"/>
+      <c r="U41" s="380" t="n"/>
+      <c r="V41" s="380" t="n"/>
+      <c r="W41" s="380" t="n"/>
+      <c r="X41" s="380" t="n"/>
+      <c r="Y41" s="380" t="n"/>
+      <c r="Z41" s="380" t="n"/>
+      <c r="AA41" s="380" t="n"/>
+      <c r="AB41" s="380" t="n"/>
+      <c r="AC41" s="380" t="n"/>
+      <c r="AD41" s="380" t="n"/>
+      <c r="AE41" s="380" t="n"/>
+      <c r="AF41" s="380" t="n"/>
+      <c r="AG41" s="380" t="n"/>
+      <c r="AH41" s="380" t="n"/>
+      <c r="AI41" s="380" t="n"/>
+      <c r="AJ41" s="380" t="n"/>
+      <c r="AK41" s="380" t="n"/>
+      <c r="AL41" s="380" t="n"/>
+      <c r="AM41" s="380" t="n"/>
+      <c r="AN41" s="381" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="361" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="B42" s="289" t="n"/>
-      <c r="C42" s="289" t="n"/>
-      <c r="D42" s="289" t="n"/>
-      <c r="E42" s="289" t="n"/>
-      <c r="F42" s="289" t="n"/>
-      <c r="G42" s="289" t="n"/>
-      <c r="H42" s="289" t="n"/>
-      <c r="I42" s="289" t="n"/>
-      <c r="J42" s="289" t="n"/>
-      <c r="K42" s="289" t="n"/>
-      <c r="L42" s="289" t="n"/>
-      <c r="M42" s="289" t="n"/>
-      <c r="N42" s="51" t="inlineStr">
+      <c r="B42" s="374" t="n"/>
+      <c r="C42" s="374" t="n"/>
+      <c r="D42" s="374" t="n"/>
+      <c r="E42" s="374" t="n"/>
+      <c r="F42" s="374" t="n"/>
+      <c r="G42" s="374" t="n"/>
+      <c r="H42" s="374" t="n"/>
+      <c r="I42" s="374" t="n"/>
+      <c r="J42" s="374" t="n"/>
+      <c r="K42" s="374" t="n"/>
+      <c r="L42" s="374" t="n"/>
+      <c r="M42" s="374" t="n"/>
+      <c r="N42" s="362" t="inlineStr">
         <is>
           <t>Printed by / Date-Time</t>
         </is>
       </c>
-      <c r="O42" s="289" t="n"/>
-      <c r="P42" s="289" t="n"/>
-      <c r="Q42" s="289" t="n"/>
-      <c r="R42" s="289" t="n"/>
-      <c r="S42" s="289" t="n"/>
-      <c r="T42" s="289" t="n"/>
-      <c r="U42" s="289" t="n"/>
-      <c r="V42" s="289" t="n"/>
-      <c r="W42" s="289" t="n"/>
-      <c r="X42" s="289" t="n"/>
-      <c r="Y42" s="289" t="n"/>
-      <c r="Z42" s="289" t="n"/>
-      <c r="AA42" s="318" t="inlineStr">
+      <c r="O42" s="374" t="n"/>
+      <c r="P42" s="374" t="n"/>
+      <c r="Q42" s="374" t="n"/>
+      <c r="R42" s="374" t="n"/>
+      <c r="S42" s="374" t="n"/>
+      <c r="T42" s="374" t="n"/>
+      <c r="U42" s="374" t="n"/>
+      <c r="V42" s="374" t="n"/>
+      <c r="W42" s="374" t="n"/>
+      <c r="X42" s="374" t="n"/>
+      <c r="Y42" s="374" t="n"/>
+      <c r="Z42" s="374" t="n"/>
+      <c r="AA42" s="363" t="inlineStr">
         <is>
           <t>Print Event State</t>
         </is>
       </c>
-      <c r="AB42" s="289" t="n"/>
-      <c r="AC42" s="289" t="n"/>
-      <c r="AD42" s="289" t="n"/>
-      <c r="AE42" s="289" t="n"/>
-      <c r="AF42" s="289" t="n"/>
-      <c r="AG42" s="289" t="n"/>
-      <c r="AH42" s="289" t="n"/>
-      <c r="AI42" s="289" t="n"/>
-      <c r="AJ42" s="289" t="n"/>
-      <c r="AK42" s="289" t="n"/>
-      <c r="AL42" s="289" t="n"/>
-      <c r="AM42" s="289" t="n"/>
-      <c r="AN42" s="290" t="n"/>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="319">
+      <c r="AB42" s="374" t="n"/>
+      <c r="AC42" s="374" t="n"/>
+      <c r="AD42" s="374" t="n"/>
+      <c r="AE42" s="374" t="n"/>
+      <c r="AF42" s="374" t="n"/>
+      <c r="AG42" s="374" t="n"/>
+      <c r="AH42" s="374" t="n"/>
+      <c r="AI42" s="374" t="n"/>
+      <c r="AJ42" s="374" t="n"/>
+      <c r="AK42" s="374" t="n"/>
+      <c r="AL42" s="374" t="n"/>
+      <c r="AM42" s="374" t="n"/>
+      <c r="AN42" s="375" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="364">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="B43" s="268" t="n"/>
-      <c r="C43" s="268" t="n"/>
-      <c r="D43" s="268" t="n"/>
-      <c r="E43" s="268" t="n"/>
-      <c r="F43" s="268" t="n"/>
-      <c r="G43" s="268" t="n"/>
-      <c r="H43" s="268" t="n"/>
-      <c r="I43" s="268" t="n"/>
-      <c r="J43" s="268" t="n"/>
-      <c r="K43" s="268" t="n"/>
-      <c r="L43" s="268" t="n"/>
-      <c r="M43" s="320" t="n"/>
-      <c r="N43" s="319">
+      <c r="B43" s="384" t="n"/>
+      <c r="C43" s="384" t="n"/>
+      <c r="D43" s="384" t="n"/>
+      <c r="E43" s="384" t="n"/>
+      <c r="F43" s="384" t="n"/>
+      <c r="G43" s="384" t="n"/>
+      <c r="H43" s="384" t="n"/>
+      <c r="I43" s="384" t="n"/>
+      <c r="J43" s="384" t="n"/>
+      <c r="K43" s="384" t="n"/>
+      <c r="L43" s="384" t="n"/>
+      <c r="M43" s="385" t="n"/>
+      <c r="N43" s="364">
         <f>IF(PRINT_CONTROL!$B$6="","",PRINT_CONTROL!$B$6)</f>
         <v/>
       </c>
-      <c r="O43" s="268" t="n"/>
-      <c r="P43" s="268" t="n"/>
-      <c r="Q43" s="268" t="n"/>
-      <c r="R43" s="268" t="n"/>
-      <c r="S43" s="268" t="n"/>
-      <c r="T43" s="268" t="n"/>
-      <c r="U43" s="268" t="n"/>
-      <c r="V43" s="268" t="n"/>
-      <c r="W43" s="268" t="n"/>
-      <c r="X43" s="268" t="n"/>
-      <c r="Y43" s="268" t="n"/>
-      <c r="Z43" s="320" t="n"/>
-      <c r="AA43" s="319">
+      <c r="O43" s="384" t="n"/>
+      <c r="P43" s="384" t="n"/>
+      <c r="Q43" s="384" t="n"/>
+      <c r="R43" s="384" t="n"/>
+      <c r="S43" s="384" t="n"/>
+      <c r="T43" s="384" t="n"/>
+      <c r="U43" s="384" t="n"/>
+      <c r="V43" s="384" t="n"/>
+      <c r="W43" s="384" t="n"/>
+      <c r="X43" s="384" t="n"/>
+      <c r="Y43" s="384" t="n"/>
+      <c r="Z43" s="385" t="n"/>
+      <c r="AA43" s="364">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="AB43" s="268" t="n"/>
-      <c r="AC43" s="268" t="n"/>
-      <c r="AD43" s="268" t="n"/>
-      <c r="AE43" s="268" t="n"/>
-      <c r="AF43" s="268" t="n"/>
-      <c r="AG43" s="268" t="n"/>
-      <c r="AH43" s="268" t="n"/>
-      <c r="AI43" s="268" t="n"/>
-      <c r="AJ43" s="268" t="n"/>
-      <c r="AK43" s="268" t="n"/>
-      <c r="AL43" s="268" t="n"/>
-      <c r="AM43" s="268" t="n"/>
-      <c r="AN43" s="320" t="n"/>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="275" t="n"/>
-      <c r="M44" s="321" t="n"/>
-      <c r="N44" s="275" t="n"/>
-      <c r="Z44" s="321" t="n"/>
-      <c r="AA44" s="275" t="n"/>
-      <c r="AN44" s="321" t="n"/>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="282" t="n"/>
-      <c r="B45" s="283" t="n"/>
-      <c r="C45" s="283" t="n"/>
-      <c r="D45" s="283" t="n"/>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="283" t="n"/>
-      <c r="J45" s="283" t="n"/>
-      <c r="K45" s="283" t="n"/>
-      <c r="L45" s="283" t="n"/>
-      <c r="M45" s="287" t="n"/>
-      <c r="N45" s="282" t="n"/>
-      <c r="O45" s="283" t="n"/>
-      <c r="P45" s="283" t="n"/>
-      <c r="Q45" s="283" t="n"/>
-      <c r="R45" s="283" t="n"/>
-      <c r="S45" s="283" t="n"/>
-      <c r="T45" s="283" t="n"/>
-      <c r="U45" s="283" t="n"/>
-      <c r="V45" s="283" t="n"/>
-      <c r="W45" s="283" t="n"/>
-      <c r="X45" s="283" t="n"/>
-      <c r="Y45" s="283" t="n"/>
-      <c r="Z45" s="287" t="n"/>
-      <c r="AA45" s="282" t="n"/>
-      <c r="AB45" s="283" t="n"/>
-      <c r="AC45" s="283" t="n"/>
-      <c r="AD45" s="283" t="n"/>
-      <c r="AE45" s="283" t="n"/>
-      <c r="AF45" s="283" t="n"/>
-      <c r="AG45" s="283" t="n"/>
-      <c r="AH45" s="283" t="n"/>
-      <c r="AI45" s="283" t="n"/>
-      <c r="AJ45" s="283" t="n"/>
-      <c r="AK45" s="283" t="n"/>
-      <c r="AL45" s="283" t="n"/>
-      <c r="AM45" s="283" t="n"/>
-      <c r="AN45" s="287" t="n"/>
+      <c r="AB43" s="384" t="n"/>
+      <c r="AC43" s="384" t="n"/>
+      <c r="AD43" s="384" t="n"/>
+      <c r="AE43" s="384" t="n"/>
+      <c r="AF43" s="384" t="n"/>
+      <c r="AG43" s="384" t="n"/>
+      <c r="AH43" s="384" t="n"/>
+      <c r="AI43" s="384" t="n"/>
+      <c r="AJ43" s="384" t="n"/>
+      <c r="AK43" s="384" t="n"/>
+      <c r="AL43" s="384" t="n"/>
+      <c r="AM43" s="384" t="n"/>
+      <c r="AN43" s="385" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="386" t="n"/>
+      <c r="B44" s="368" t="n"/>
+      <c r="C44" s="368" t="n"/>
+      <c r="D44" s="368" t="n"/>
+      <c r="E44" s="368" t="n"/>
+      <c r="F44" s="368" t="n"/>
+      <c r="G44" s="368" t="n"/>
+      <c r="H44" s="368" t="n"/>
+      <c r="I44" s="368" t="n"/>
+      <c r="J44" s="368" t="n"/>
+      <c r="K44" s="368" t="n"/>
+      <c r="L44" s="368" t="n"/>
+      <c r="M44" s="387" t="n"/>
+      <c r="N44" s="386" t="n"/>
+      <c r="O44" s="368" t="n"/>
+      <c r="P44" s="368" t="n"/>
+      <c r="Q44" s="368" t="n"/>
+      <c r="R44" s="368" t="n"/>
+      <c r="S44" s="368" t="n"/>
+      <c r="T44" s="368" t="n"/>
+      <c r="U44" s="368" t="n"/>
+      <c r="V44" s="368" t="n"/>
+      <c r="W44" s="368" t="n"/>
+      <c r="X44" s="368" t="n"/>
+      <c r="Y44" s="368" t="n"/>
+      <c r="Z44" s="387" t="n"/>
+      <c r="AA44" s="386" t="n"/>
+      <c r="AB44" s="368" t="n"/>
+      <c r="AC44" s="368" t="n"/>
+      <c r="AD44" s="368" t="n"/>
+      <c r="AE44" s="368" t="n"/>
+      <c r="AF44" s="368" t="n"/>
+      <c r="AG44" s="368" t="n"/>
+      <c r="AH44" s="368" t="n"/>
+      <c r="AI44" s="368" t="n"/>
+      <c r="AJ44" s="368" t="n"/>
+      <c r="AK44" s="368" t="n"/>
+      <c r="AL44" s="368" t="n"/>
+      <c r="AM44" s="368" t="n"/>
+      <c r="AN44" s="387" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="388" t="n"/>
+      <c r="B45" s="382" t="n"/>
+      <c r="C45" s="382" t="n"/>
+      <c r="D45" s="382" t="n"/>
+      <c r="E45" s="382" t="n"/>
+      <c r="F45" s="382" t="n"/>
+      <c r="G45" s="382" t="n"/>
+      <c r="H45" s="382" t="n"/>
+      <c r="I45" s="382" t="n"/>
+      <c r="J45" s="382" t="n"/>
+      <c r="K45" s="382" t="n"/>
+      <c r="L45" s="382" t="n"/>
+      <c r="M45" s="383" t="n"/>
+      <c r="N45" s="388" t="n"/>
+      <c r="O45" s="382" t="n"/>
+      <c r="P45" s="382" t="n"/>
+      <c r="Q45" s="382" t="n"/>
+      <c r="R45" s="382" t="n"/>
+      <c r="S45" s="382" t="n"/>
+      <c r="T45" s="382" t="n"/>
+      <c r="U45" s="382" t="n"/>
+      <c r="V45" s="382" t="n"/>
+      <c r="W45" s="382" t="n"/>
+      <c r="X45" s="382" t="n"/>
+      <c r="Y45" s="382" t="n"/>
+      <c r="Z45" s="383" t="n"/>
+      <c r="AA45" s="388" t="n"/>
+      <c r="AB45" s="382" t="n"/>
+      <c r="AC45" s="382" t="n"/>
+      <c r="AD45" s="382" t="n"/>
+      <c r="AE45" s="382" t="n"/>
+      <c r="AF45" s="382" t="n"/>
+      <c r="AG45" s="382" t="n"/>
+      <c r="AH45" s="382" t="n"/>
+      <c r="AI45" s="382" t="n"/>
+      <c r="AJ45" s="382" t="n"/>
+      <c r="AK45" s="382" t="n"/>
+      <c r="AL45" s="382" t="n"/>
+      <c r="AM45" s="382" t="n"/>
+      <c r="AN45" s="383" t="n"/>
     </row>
     <row r="46" ht="4" customHeight="1">
-      <c r="A46" s="25" t="n"/>
+      <c r="A46" s="342" t="n"/>
+      <c r="B46" s="389" t="n"/>
+      <c r="C46" s="389" t="n"/>
+      <c r="D46" s="389" t="n"/>
+      <c r="E46" s="389" t="n"/>
+      <c r="F46" s="389" t="n"/>
+      <c r="G46" s="389" t="n"/>
+      <c r="H46" s="389" t="n"/>
+      <c r="I46" s="389" t="n"/>
+      <c r="J46" s="389" t="n"/>
+      <c r="K46" s="389" t="n"/>
+      <c r="L46" s="389" t="n"/>
+      <c r="M46" s="389" t="n"/>
+      <c r="N46" s="389" t="n"/>
+      <c r="O46" s="389" t="n"/>
+      <c r="P46" s="389" t="n"/>
+      <c r="Q46" s="389" t="n"/>
+      <c r="R46" s="389" t="n"/>
+      <c r="S46" s="389" t="n"/>
+      <c r="T46" s="389" t="n"/>
+      <c r="U46" s="389" t="n"/>
+      <c r="V46" s="389" t="n"/>
+      <c r="W46" s="389" t="n"/>
+      <c r="X46" s="389" t="n"/>
+      <c r="Y46" s="389" t="n"/>
+      <c r="Z46" s="389" t="n"/>
+      <c r="AA46" s="389" t="n"/>
+      <c r="AB46" s="389" t="n"/>
+      <c r="AC46" s="389" t="n"/>
+      <c r="AD46" s="389" t="n"/>
+      <c r="AE46" s="389" t="n"/>
+      <c r="AF46" s="389" t="n"/>
+      <c r="AG46" s="389" t="n"/>
+      <c r="AH46" s="389" t="n"/>
+      <c r="AI46" s="389" t="n"/>
+      <c r="AJ46" s="389" t="n"/>
+      <c r="AK46" s="389" t="n"/>
+      <c r="AL46" s="389" t="n"/>
+      <c r="AM46" s="389" t="n"/>
+      <c r="AN46" s="389" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="322" t="inlineStr">
+      <c r="A47" s="371" t="inlineStr">
         <is>
           <t>NOTICE: Printed face only. No signature on the printed face. Record release, print, verify, void or scrap event in PRINT_CONTROL and PRINT_LOG.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="289" t="n"/>
-      <c r="L47" s="289" t="n"/>
-      <c r="M47" s="289" t="n"/>
-      <c r="N47" s="289" t="n"/>
-      <c r="O47" s="289" t="n"/>
-      <c r="P47" s="289" t="n"/>
-      <c r="Q47" s="289" t="n"/>
-      <c r="R47" s="289" t="n"/>
-      <c r="S47" s="289" t="n"/>
-      <c r="T47" s="289" t="n"/>
-      <c r="U47" s="289" t="n"/>
-      <c r="V47" s="289" t="n"/>
-      <c r="W47" s="289" t="n"/>
-      <c r="X47" s="289" t="n"/>
-      <c r="Y47" s="289" t="n"/>
-      <c r="Z47" s="289" t="n"/>
-      <c r="AA47" s="289" t="n"/>
-      <c r="AB47" s="289" t="n"/>
-      <c r="AC47" s="289" t="n"/>
-      <c r="AD47" s="289" t="n"/>
-      <c r="AE47" s="289" t="n"/>
-      <c r="AF47" s="289" t="n"/>
-      <c r="AG47" s="289" t="n"/>
-      <c r="AH47" s="289" t="n"/>
-      <c r="AI47" s="289" t="n"/>
-      <c r="AJ47" s="289" t="n"/>
-      <c r="AK47" s="289" t="n"/>
-      <c r="AL47" s="289" t="n"/>
-      <c r="AM47" s="289" t="n"/>
-      <c r="AN47" s="290" t="n"/>
+      <c r="B47" s="374" t="n"/>
+      <c r="C47" s="374" t="n"/>
+      <c r="D47" s="374" t="n"/>
+      <c r="E47" s="374" t="n"/>
+      <c r="F47" s="374" t="n"/>
+      <c r="G47" s="374" t="n"/>
+      <c r="H47" s="374" t="n"/>
+      <c r="I47" s="374" t="n"/>
+      <c r="J47" s="374" t="n"/>
+      <c r="K47" s="374" t="n"/>
+      <c r="L47" s="374" t="n"/>
+      <c r="M47" s="374" t="n"/>
+      <c r="N47" s="374" t="n"/>
+      <c r="O47" s="374" t="n"/>
+      <c r="P47" s="374" t="n"/>
+      <c r="Q47" s="374" t="n"/>
+      <c r="R47" s="374" t="n"/>
+      <c r="S47" s="374" t="n"/>
+      <c r="T47" s="374" t="n"/>
+      <c r="U47" s="374" t="n"/>
+      <c r="V47" s="374" t="n"/>
+      <c r="W47" s="374" t="n"/>
+      <c r="X47" s="374" t="n"/>
+      <c r="Y47" s="374" t="n"/>
+      <c r="Z47" s="374" t="n"/>
+      <c r="AA47" s="374" t="n"/>
+      <c r="AB47" s="374" t="n"/>
+      <c r="AC47" s="374" t="n"/>
+      <c r="AD47" s="374" t="n"/>
+      <c r="AE47" s="374" t="n"/>
+      <c r="AF47" s="374" t="n"/>
+      <c r="AG47" s="374" t="n"/>
+      <c r="AH47" s="374" t="n"/>
+      <c r="AI47" s="374" t="n"/>
+      <c r="AJ47" s="374" t="n"/>
+      <c r="AK47" s="374" t="n"/>
+      <c r="AL47" s="374" t="n"/>
+      <c r="AM47" s="374" t="n"/>
+      <c r="AN47" s="375" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="187">
@@ -7005,7 +7629,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7206,12 +7829,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -7220,6 +7880,45 @@
           <t>Print Generator</t>
         </is>
       </c>
+      <c r="B1" s="334" t="n"/>
+      <c r="C1" s="334" t="n"/>
+      <c r="D1" s="334" t="n"/>
+      <c r="E1" s="334" t="n"/>
+      <c r="F1" s="334" t="n"/>
+      <c r="G1" s="334" t="n"/>
+      <c r="H1" s="334" t="n"/>
+      <c r="I1" s="334" t="n"/>
+      <c r="J1" s="334" t="n"/>
+      <c r="K1" s="334" t="n"/>
+      <c r="L1" s="334" t="n"/>
+      <c r="M1" s="334" t="n"/>
+      <c r="N1" s="334" t="n"/>
+      <c r="O1" s="334" t="n"/>
+      <c r="P1" s="334" t="n"/>
+      <c r="Q1" s="334" t="n"/>
+      <c r="R1" s="334" t="n"/>
+      <c r="S1" s="334" t="n"/>
+      <c r="T1" s="334" t="n"/>
+      <c r="U1" s="334" t="n"/>
+      <c r="V1" s="334" t="n"/>
+      <c r="W1" s="334" t="n"/>
+      <c r="X1" s="334" t="n"/>
+      <c r="Y1" s="334" t="n"/>
+      <c r="Z1" s="334" t="n"/>
+      <c r="AA1" s="334" t="n"/>
+      <c r="AB1" s="334" t="n"/>
+      <c r="AC1" s="334" t="n"/>
+      <c r="AD1" s="334" t="n"/>
+      <c r="AE1" s="334" t="n"/>
+      <c r="AF1" s="334" t="n"/>
+      <c r="AG1" s="334" t="n"/>
+      <c r="AH1" s="334" t="n"/>
+      <c r="AI1" s="334" t="n"/>
+      <c r="AJ1" s="334" t="n"/>
+      <c r="AK1" s="334" t="n"/>
+      <c r="AL1" s="334" t="n"/>
+      <c r="AM1" s="334" t="n"/>
+      <c r="AN1" s="334" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="324" t="inlineStr">
@@ -7227,240 +7926,1041 @@
           <t>Controlled generator sheet for fixed print face. Edit only approved generator fields.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
+      <c r="B2" s="334" t="n"/>
+      <c r="C2" s="334" t="n"/>
+      <c r="D2" s="334" t="n"/>
+      <c r="E2" s="334" t="n"/>
+      <c r="F2" s="334" t="n"/>
+      <c r="G2" s="334" t="n"/>
+      <c r="H2" s="334" t="n"/>
+      <c r="I2" s="334" t="n"/>
+      <c r="J2" s="334" t="n"/>
+      <c r="K2" s="334" t="n"/>
+      <c r="L2" s="334" t="n"/>
+      <c r="M2" s="334" t="n"/>
+      <c r="N2" s="334" t="n"/>
+      <c r="O2" s="334" t="n"/>
+      <c r="P2" s="334" t="n"/>
+      <c r="Q2" s="334" t="n"/>
+      <c r="R2" s="334" t="n"/>
+      <c r="S2" s="334" t="n"/>
+      <c r="T2" s="334" t="n"/>
+      <c r="U2" s="334" t="n"/>
+      <c r="V2" s="334" t="n"/>
+      <c r="W2" s="334" t="n"/>
+      <c r="X2" s="334" t="n"/>
+      <c r="Y2" s="334" t="n"/>
+      <c r="Z2" s="334" t="n"/>
+      <c r="AA2" s="334" t="n"/>
+      <c r="AB2" s="334" t="n"/>
+      <c r="AC2" s="334" t="n"/>
+      <c r="AD2" s="334" t="n"/>
+      <c r="AE2" s="334" t="n"/>
+      <c r="AF2" s="334" t="n"/>
+      <c r="AG2" s="334" t="n"/>
+      <c r="AH2" s="334" t="n"/>
+      <c r="AI2" s="334" t="n"/>
+      <c r="AJ2" s="334" t="n"/>
+      <c r="AK2" s="334" t="n"/>
+      <c r="AL2" s="334" t="n"/>
+      <c r="AM2" s="334" t="n"/>
+      <c r="AN2" s="334" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="334" t="n"/>
+      <c r="B3" s="334" t="n"/>
+      <c r="C3" s="334" t="n"/>
+      <c r="D3" s="334" t="n"/>
+      <c r="E3" s="334" t="n"/>
+      <c r="F3" s="334" t="n"/>
+      <c r="G3" s="334" t="n"/>
+      <c r="H3" s="334" t="n"/>
+      <c r="I3" s="334" t="n"/>
+      <c r="J3" s="334" t="n"/>
+      <c r="K3" s="334" t="n"/>
+      <c r="L3" s="334" t="n"/>
+      <c r="M3" s="334" t="n"/>
+      <c r="N3" s="334" t="n"/>
+      <c r="O3" s="334" t="n"/>
+      <c r="P3" s="334" t="n"/>
+      <c r="Q3" s="334" t="n"/>
+      <c r="R3" s="334" t="n"/>
+      <c r="S3" s="334" t="n"/>
+      <c r="T3" s="334" t="n"/>
+      <c r="U3" s="334" t="n"/>
+      <c r="V3" s="334" t="n"/>
+      <c r="W3" s="334" t="n"/>
+      <c r="X3" s="334" t="n"/>
+      <c r="Y3" s="334" t="n"/>
+      <c r="Z3" s="334" t="n"/>
+      <c r="AA3" s="334" t="n"/>
+      <c r="AB3" s="334" t="n"/>
+      <c r="AC3" s="334" t="n"/>
+      <c r="AD3" s="334" t="n"/>
+      <c r="AE3" s="334" t="n"/>
+      <c r="AF3" s="334" t="n"/>
+      <c r="AG3" s="334" t="n"/>
+      <c r="AH3" s="334" t="n"/>
+      <c r="AI3" s="334" t="n"/>
+      <c r="AJ3" s="334" t="n"/>
+      <c r="AK3" s="334" t="n"/>
+      <c r="AL3" s="334" t="n"/>
+      <c r="AM3" s="334" t="n"/>
+      <c r="AN3" s="334" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="325" t="inlineStr">
+      <c r="A4" s="372" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="325" t="inlineStr">
+      <c r="B4" s="372" t="inlineStr">
         <is>
           <t>Value / Source</t>
         </is>
       </c>
-      <c r="C4" s="325" t="inlineStr">
+      <c r="C4" s="372" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="334" t="n"/>
+      <c r="E4" s="334" t="n"/>
+      <c r="F4" s="334" t="n"/>
+      <c r="G4" s="334" t="n"/>
+      <c r="H4" s="334" t="n"/>
+      <c r="I4" s="334" t="n"/>
+      <c r="J4" s="334" t="n"/>
+      <c r="K4" s="334" t="n"/>
+      <c r="L4" s="334" t="n"/>
+      <c r="M4" s="334" t="n"/>
+      <c r="N4" s="334" t="n"/>
+      <c r="O4" s="334" t="n"/>
+      <c r="P4" s="334" t="n"/>
+      <c r="Q4" s="334" t="n"/>
+      <c r="R4" s="334" t="n"/>
+      <c r="S4" s="334" t="n"/>
+      <c r="T4" s="334" t="n"/>
+      <c r="U4" s="334" t="n"/>
+      <c r="V4" s="334" t="n"/>
+      <c r="W4" s="334" t="n"/>
+      <c r="X4" s="334" t="n"/>
+      <c r="Y4" s="334" t="n"/>
+      <c r="Z4" s="334" t="n"/>
+      <c r="AA4" s="334" t="n"/>
+      <c r="AB4" s="334" t="n"/>
+      <c r="AC4" s="334" t="n"/>
+      <c r="AD4" s="334" t="n"/>
+      <c r="AE4" s="334" t="n"/>
+      <c r="AF4" s="334" t="n"/>
+      <c r="AG4" s="334" t="n"/>
+      <c r="AH4" s="334" t="n"/>
+      <c r="AI4" s="334" t="n"/>
+      <c r="AJ4" s="334" t="n"/>
+      <c r="AK4" s="334" t="n"/>
+      <c r="AL4" s="334" t="n"/>
+      <c r="AM4" s="334" t="n"/>
+      <c r="AN4" s="334" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="334" t="inlineStr">
         <is>
           <t>WIP Tag ID</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="334" t="n"/>
+      <c r="C5" s="334" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D5" s="334" t="n"/>
+      <c r="E5" s="334" t="n"/>
+      <c r="F5" s="334" t="n"/>
+      <c r="G5" s="334" t="n"/>
+      <c r="H5" s="334" t="n"/>
+      <c r="I5" s="334" t="n"/>
+      <c r="J5" s="334" t="n"/>
+      <c r="K5" s="334" t="n"/>
+      <c r="L5" s="334" t="n"/>
+      <c r="M5" s="334" t="n"/>
+      <c r="N5" s="334" t="n"/>
+      <c r="O5" s="334" t="n"/>
+      <c r="P5" s="334" t="n"/>
+      <c r="Q5" s="334" t="n"/>
+      <c r="R5" s="334" t="n"/>
+      <c r="S5" s="334" t="n"/>
+      <c r="T5" s="334" t="n"/>
+      <c r="U5" s="334" t="n"/>
+      <c r="V5" s="334" t="n"/>
+      <c r="W5" s="334" t="n"/>
+      <c r="X5" s="334" t="n"/>
+      <c r="Y5" s="334" t="n"/>
+      <c r="Z5" s="334" t="n"/>
+      <c r="AA5" s="334" t="n"/>
+      <c r="AB5" s="334" t="n"/>
+      <c r="AC5" s="334" t="n"/>
+      <c r="AD5" s="334" t="n"/>
+      <c r="AE5" s="334" t="n"/>
+      <c r="AF5" s="334" t="n"/>
+      <c r="AG5" s="334" t="n"/>
+      <c r="AH5" s="334" t="n"/>
+      <c r="AI5" s="334" t="n"/>
+      <c r="AJ5" s="334" t="n"/>
+      <c r="AK5" s="334" t="n"/>
+      <c r="AL5" s="334" t="n"/>
+      <c r="AM5" s="334" t="n"/>
+      <c r="AN5" s="334" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="334" t="inlineStr">
         <is>
           <t>Job / Lot / Part / Revision</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="334" t="n"/>
+      <c r="C6" s="334" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D6" s="334" t="n"/>
+      <c r="E6" s="334" t="n"/>
+      <c r="F6" s="334" t="n"/>
+      <c r="G6" s="334" t="n"/>
+      <c r="H6" s="334" t="n"/>
+      <c r="I6" s="334" t="n"/>
+      <c r="J6" s="334" t="n"/>
+      <c r="K6" s="334" t="n"/>
+      <c r="L6" s="334" t="n"/>
+      <c r="M6" s="334" t="n"/>
+      <c r="N6" s="334" t="n"/>
+      <c r="O6" s="334" t="n"/>
+      <c r="P6" s="334" t="n"/>
+      <c r="Q6" s="334" t="n"/>
+      <c r="R6" s="334" t="n"/>
+      <c r="S6" s="334" t="n"/>
+      <c r="T6" s="334" t="n"/>
+      <c r="U6" s="334" t="n"/>
+      <c r="V6" s="334" t="n"/>
+      <c r="W6" s="334" t="n"/>
+      <c r="X6" s="334" t="n"/>
+      <c r="Y6" s="334" t="n"/>
+      <c r="Z6" s="334" t="n"/>
+      <c r="AA6" s="334" t="n"/>
+      <c r="AB6" s="334" t="n"/>
+      <c r="AC6" s="334" t="n"/>
+      <c r="AD6" s="334" t="n"/>
+      <c r="AE6" s="334" t="n"/>
+      <c r="AF6" s="334" t="n"/>
+      <c r="AG6" s="334" t="n"/>
+      <c r="AH6" s="334" t="n"/>
+      <c r="AI6" s="334" t="n"/>
+      <c r="AJ6" s="334" t="n"/>
+      <c r="AK6" s="334" t="n"/>
+      <c r="AL6" s="334" t="n"/>
+      <c r="AM6" s="334" t="n"/>
+      <c r="AN6" s="334" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="334" t="inlineStr">
         <is>
           <t>Area / Location / Room</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="334" t="n"/>
+      <c r="C7" s="334" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D7" s="334" t="n"/>
+      <c r="E7" s="334" t="n"/>
+      <c r="F7" s="334" t="n"/>
+      <c r="G7" s="334" t="n"/>
+      <c r="H7" s="334" t="n"/>
+      <c r="I7" s="334" t="n"/>
+      <c r="J7" s="334" t="n"/>
+      <c r="K7" s="334" t="n"/>
+      <c r="L7" s="334" t="n"/>
+      <c r="M7" s="334" t="n"/>
+      <c r="N7" s="334" t="n"/>
+      <c r="O7" s="334" t="n"/>
+      <c r="P7" s="334" t="n"/>
+      <c r="Q7" s="334" t="n"/>
+      <c r="R7" s="334" t="n"/>
+      <c r="S7" s="334" t="n"/>
+      <c r="T7" s="334" t="n"/>
+      <c r="U7" s="334" t="n"/>
+      <c r="V7" s="334" t="n"/>
+      <c r="W7" s="334" t="n"/>
+      <c r="X7" s="334" t="n"/>
+      <c r="Y7" s="334" t="n"/>
+      <c r="Z7" s="334" t="n"/>
+      <c r="AA7" s="334" t="n"/>
+      <c r="AB7" s="334" t="n"/>
+      <c r="AC7" s="334" t="n"/>
+      <c r="AD7" s="334" t="n"/>
+      <c r="AE7" s="334" t="n"/>
+      <c r="AF7" s="334" t="n"/>
+      <c r="AG7" s="334" t="n"/>
+      <c r="AH7" s="334" t="n"/>
+      <c r="AI7" s="334" t="n"/>
+      <c r="AJ7" s="334" t="n"/>
+      <c r="AK7" s="334" t="n"/>
+      <c r="AL7" s="334" t="n"/>
+      <c r="AM7" s="334" t="n"/>
+      <c r="AN7" s="334" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="368" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="368" t="n"/>
+      <c r="C8" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D8" s="368" t="n"/>
+      <c r="E8" s="368" t="n"/>
+      <c r="F8" s="368" t="n"/>
+      <c r="G8" s="368" t="n"/>
+      <c r="H8" s="368" t="n"/>
+      <c r="I8" s="368" t="n"/>
+      <c r="J8" s="368" t="n"/>
+      <c r="K8" s="368" t="n"/>
+      <c r="L8" s="368" t="n"/>
+      <c r="M8" s="368" t="n"/>
+      <c r="N8" s="368" t="n"/>
+      <c r="O8" s="368" t="n"/>
+      <c r="P8" s="368" t="n"/>
+      <c r="Q8" s="368" t="n"/>
+      <c r="R8" s="368" t="n"/>
+      <c r="S8" s="368" t="n"/>
+      <c r="T8" s="368" t="n"/>
+      <c r="U8" s="368" t="n"/>
+      <c r="V8" s="368" t="n"/>
+      <c r="W8" s="368" t="n"/>
+      <c r="X8" s="368" t="n"/>
+      <c r="Y8" s="368" t="n"/>
+      <c r="Z8" s="368" t="n"/>
+      <c r="AA8" s="368" t="n"/>
+      <c r="AB8" s="368" t="n"/>
+      <c r="AC8" s="368" t="n"/>
+      <c r="AD8" s="368" t="n"/>
+      <c r="AE8" s="368" t="n"/>
+      <c r="AF8" s="368" t="n"/>
+      <c r="AG8" s="368" t="n"/>
+      <c r="AH8" s="368" t="n"/>
+      <c r="AI8" s="368" t="n"/>
+      <c r="AJ8" s="368" t="n"/>
+      <c r="AK8" s="368" t="n"/>
+      <c r="AL8" s="368" t="n"/>
+      <c r="AM8" s="368" t="n"/>
+      <c r="AN8" s="368" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="368" t="inlineStr">
         <is>
           <t>Encoded Data Ref</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="368" t="n"/>
+      <c r="C9" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D9" s="368" t="n"/>
+      <c r="E9" s="368" t="n"/>
+      <c r="F9" s="368" t="n"/>
+      <c r="G9" s="368" t="n"/>
+      <c r="H9" s="368" t="n"/>
+      <c r="I9" s="368" t="n"/>
+      <c r="J9" s="368" t="n"/>
+      <c r="K9" s="368" t="n"/>
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="368" t="n"/>
+      <c r="N9" s="368" t="n"/>
+      <c r="O9" s="368" t="n"/>
+      <c r="P9" s="368" t="n"/>
+      <c r="Q9" s="368" t="n"/>
+      <c r="R9" s="368" t="n"/>
+      <c r="S9" s="368" t="n"/>
+      <c r="T9" s="368" t="n"/>
+      <c r="U9" s="368" t="n"/>
+      <c r="V9" s="368" t="n"/>
+      <c r="W9" s="368" t="n"/>
+      <c r="X9" s="368" t="n"/>
+      <c r="Y9" s="368" t="n"/>
+      <c r="Z9" s="368" t="n"/>
+      <c r="AA9" s="368" t="n"/>
+      <c r="AB9" s="368" t="n"/>
+      <c r="AC9" s="368" t="n"/>
+      <c r="AD9" s="368" t="n"/>
+      <c r="AE9" s="368" t="n"/>
+      <c r="AF9" s="368" t="n"/>
+      <c r="AG9" s="368" t="n"/>
+      <c r="AH9" s="368" t="n"/>
+      <c r="AI9" s="368" t="n"/>
+      <c r="AJ9" s="368" t="n"/>
+      <c r="AK9" s="368" t="n"/>
+      <c r="AL9" s="368" t="n"/>
+      <c r="AM9" s="368" t="n"/>
+      <c r="AN9" s="368" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="368" t="inlineStr">
         <is>
           <t>Print Status</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="368" t="n"/>
+      <c r="C10" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D10" s="368" t="n"/>
+      <c r="E10" s="368" t="n"/>
+      <c r="F10" s="368" t="n"/>
+      <c r="G10" s="368" t="n"/>
+      <c r="H10" s="368" t="n"/>
+      <c r="I10" s="368" t="n"/>
+      <c r="J10" s="368" t="n"/>
+      <c r="K10" s="368" t="n"/>
+      <c r="L10" s="368" t="n"/>
+      <c r="M10" s="368" t="n"/>
+      <c r="N10" s="368" t="n"/>
+      <c r="O10" s="368" t="n"/>
+      <c r="P10" s="368" t="n"/>
+      <c r="Q10" s="368" t="n"/>
+      <c r="R10" s="368" t="n"/>
+      <c r="S10" s="368" t="n"/>
+      <c r="T10" s="368" t="n"/>
+      <c r="U10" s="368" t="n"/>
+      <c r="V10" s="368" t="n"/>
+      <c r="W10" s="368" t="n"/>
+      <c r="X10" s="368" t="n"/>
+      <c r="Y10" s="368" t="n"/>
+      <c r="Z10" s="368" t="n"/>
+      <c r="AA10" s="368" t="n"/>
+      <c r="AB10" s="368" t="n"/>
+      <c r="AC10" s="368" t="n"/>
+      <c r="AD10" s="368" t="n"/>
+      <c r="AE10" s="368" t="n"/>
+      <c r="AF10" s="368" t="n"/>
+      <c r="AG10" s="368" t="n"/>
+      <c r="AH10" s="368" t="n"/>
+      <c r="AI10" s="368" t="n"/>
+      <c r="AJ10" s="368" t="n"/>
+      <c r="AK10" s="368" t="n"/>
+      <c r="AL10" s="368" t="n"/>
+      <c r="AM10" s="368" t="n"/>
+      <c r="AN10" s="368" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="368" t="inlineStr">
         <is>
           <t>Current Operation / Qty</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="368" t="n"/>
+      <c r="C11" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="D11" s="368" t="n"/>
+      <c r="E11" s="368" t="n"/>
+      <c r="F11" s="368" t="n"/>
+      <c r="G11" s="368" t="n"/>
+      <c r="H11" s="368" t="n"/>
+      <c r="I11" s="368" t="n"/>
+      <c r="J11" s="368" t="n"/>
+      <c r="K11" s="368" t="n"/>
+      <c r="L11" s="368" t="n"/>
+      <c r="M11" s="368" t="n"/>
+      <c r="N11" s="368" t="n"/>
+      <c r="O11" s="368" t="n"/>
+      <c r="P11" s="368" t="n"/>
+      <c r="Q11" s="368" t="n"/>
+      <c r="R11" s="368" t="n"/>
+      <c r="S11" s="368" t="n"/>
+      <c r="T11" s="368" t="n"/>
+      <c r="U11" s="368" t="n"/>
+      <c r="V11" s="368" t="n"/>
+      <c r="W11" s="368" t="n"/>
+      <c r="X11" s="368" t="n"/>
+      <c r="Y11" s="368" t="n"/>
+      <c r="Z11" s="368" t="n"/>
+      <c r="AA11" s="368" t="n"/>
+      <c r="AB11" s="368" t="n"/>
+      <c r="AC11" s="368" t="n"/>
+      <c r="AD11" s="368" t="n"/>
+      <c r="AE11" s="368" t="n"/>
+      <c r="AF11" s="368" t="n"/>
+      <c r="AG11" s="368" t="n"/>
+      <c r="AH11" s="368" t="n"/>
+      <c r="AI11" s="368" t="n"/>
+      <c r="AJ11" s="368" t="n"/>
+      <c r="AK11" s="368" t="n"/>
+      <c r="AL11" s="368" t="n"/>
+      <c r="AM11" s="368" t="n"/>
+      <c r="AN11" s="368" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="334" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="334" t="n"/>
+      <c r="C12" s="334" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D12" s="334" t="n"/>
+      <c r="E12" s="334" t="n"/>
+      <c r="F12" s="334" t="n"/>
+      <c r="G12" s="334" t="n"/>
+      <c r="H12" s="334" t="n"/>
+      <c r="I12" s="334" t="n"/>
+      <c r="J12" s="334" t="n"/>
+      <c r="K12" s="334" t="n"/>
+      <c r="L12" s="334" t="n"/>
+      <c r="M12" s="334" t="n"/>
+      <c r="N12" s="334" t="n"/>
+      <c r="O12" s="334" t="n"/>
+      <c r="P12" s="334" t="n"/>
+      <c r="Q12" s="334" t="n"/>
+      <c r="R12" s="334" t="n"/>
+      <c r="S12" s="334" t="n"/>
+      <c r="T12" s="334" t="n"/>
+      <c r="U12" s="334" t="n"/>
+      <c r="V12" s="334" t="n"/>
+      <c r="W12" s="334" t="n"/>
+      <c r="X12" s="334" t="n"/>
+      <c r="Y12" s="334" t="n"/>
+      <c r="Z12" s="334" t="n"/>
+      <c r="AA12" s="334" t="n"/>
+      <c r="AB12" s="334" t="n"/>
+      <c r="AC12" s="334" t="n"/>
+      <c r="AD12" s="334" t="n"/>
+      <c r="AE12" s="334" t="n"/>
+      <c r="AF12" s="334" t="n"/>
+      <c r="AG12" s="334" t="n"/>
+      <c r="AH12" s="334" t="n"/>
+      <c r="AI12" s="334" t="n"/>
+      <c r="AJ12" s="334" t="n"/>
+      <c r="AK12" s="334" t="n"/>
+      <c r="AL12" s="334" t="n"/>
+      <c r="AM12" s="334" t="n"/>
+      <c r="AN12" s="334" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="368" t="inlineStr">
         <is>
           <t>Print Qty / Application Status</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="368" t="n"/>
+      <c r="C13" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D13" s="368" t="n"/>
+      <c r="E13" s="368" t="n"/>
+      <c r="F13" s="368" t="n"/>
+      <c r="G13" s="368" t="n"/>
+      <c r="H13" s="368" t="n"/>
+      <c r="I13" s="368" t="n"/>
+      <c r="J13" s="368" t="n"/>
+      <c r="K13" s="368" t="n"/>
+      <c r="L13" s="368" t="n"/>
+      <c r="M13" s="368" t="n"/>
+      <c r="N13" s="368" t="n"/>
+      <c r="O13" s="368" t="n"/>
+      <c r="P13" s="368" t="n"/>
+      <c r="Q13" s="368" t="n"/>
+      <c r="R13" s="368" t="n"/>
+      <c r="S13" s="368" t="n"/>
+      <c r="T13" s="368" t="n"/>
+      <c r="U13" s="368" t="n"/>
+      <c r="V13" s="368" t="n"/>
+      <c r="W13" s="368" t="n"/>
+      <c r="X13" s="368" t="n"/>
+      <c r="Y13" s="368" t="n"/>
+      <c r="Z13" s="368" t="n"/>
+      <c r="AA13" s="368" t="n"/>
+      <c r="AB13" s="368" t="n"/>
+      <c r="AC13" s="368" t="n"/>
+      <c r="AD13" s="368" t="n"/>
+      <c r="AE13" s="368" t="n"/>
+      <c r="AF13" s="368" t="n"/>
+      <c r="AG13" s="368" t="n"/>
+      <c r="AH13" s="368" t="n"/>
+      <c r="AI13" s="368" t="n"/>
+      <c r="AJ13" s="368" t="n"/>
+      <c r="AK13" s="368" t="n"/>
+      <c r="AL13" s="368" t="n"/>
+      <c r="AM13" s="368" t="n"/>
+      <c r="AN13" s="368" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="368" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="368" t="n"/>
+      <c r="C14" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D14" s="368" t="n"/>
+      <c r="E14" s="368" t="n"/>
+      <c r="F14" s="368" t="n"/>
+      <c r="G14" s="368" t="n"/>
+      <c r="H14" s="368" t="n"/>
+      <c r="I14" s="368" t="n"/>
+      <c r="J14" s="368" t="n"/>
+      <c r="K14" s="368" t="n"/>
+      <c r="L14" s="368" t="n"/>
+      <c r="M14" s="368" t="n"/>
+      <c r="N14" s="368" t="n"/>
+      <c r="O14" s="368" t="n"/>
+      <c r="P14" s="368" t="n"/>
+      <c r="Q14" s="368" t="n"/>
+      <c r="R14" s="368" t="n"/>
+      <c r="S14" s="368" t="n"/>
+      <c r="T14" s="368" t="n"/>
+      <c r="U14" s="368" t="n"/>
+      <c r="V14" s="368" t="n"/>
+      <c r="W14" s="368" t="n"/>
+      <c r="X14" s="368" t="n"/>
+      <c r="Y14" s="368" t="n"/>
+      <c r="Z14" s="368" t="n"/>
+      <c r="AA14" s="368" t="n"/>
+      <c r="AB14" s="368" t="n"/>
+      <c r="AC14" s="368" t="n"/>
+      <c r="AD14" s="368" t="n"/>
+      <c r="AE14" s="368" t="n"/>
+      <c r="AF14" s="368" t="n"/>
+      <c r="AG14" s="368" t="n"/>
+      <c r="AH14" s="368" t="n"/>
+      <c r="AI14" s="368" t="n"/>
+      <c r="AJ14" s="368" t="n"/>
+      <c r="AK14" s="368" t="n"/>
+      <c r="AL14" s="368" t="n"/>
+      <c r="AM14" s="368" t="n"/>
+      <c r="AN14" s="368" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="368" t="inlineStr">
         <is>
           <t>Tag Face / Status</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="368" t="n"/>
+      <c r="C15" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D15" s="368" t="n"/>
+      <c r="E15" s="368" t="n"/>
+      <c r="F15" s="368" t="n"/>
+      <c r="G15" s="368" t="n"/>
+      <c r="H15" s="368" t="n"/>
+      <c r="I15" s="368" t="n"/>
+      <c r="J15" s="368" t="n"/>
+      <c r="K15" s="368" t="n"/>
+      <c r="L15" s="368" t="n"/>
+      <c r="M15" s="368" t="n"/>
+      <c r="N15" s="368" t="n"/>
+      <c r="O15" s="368" t="n"/>
+      <c r="P15" s="368" t="n"/>
+      <c r="Q15" s="368" t="n"/>
+      <c r="R15" s="368" t="n"/>
+      <c r="S15" s="368" t="n"/>
+      <c r="T15" s="368" t="n"/>
+      <c r="U15" s="368" t="n"/>
+      <c r="V15" s="368" t="n"/>
+      <c r="W15" s="368" t="n"/>
+      <c r="X15" s="368" t="n"/>
+      <c r="Y15" s="368" t="n"/>
+      <c r="Z15" s="368" t="n"/>
+      <c r="AA15" s="368" t="n"/>
+      <c r="AB15" s="368" t="n"/>
+      <c r="AC15" s="368" t="n"/>
+      <c r="AD15" s="368" t="n"/>
+      <c r="AE15" s="368" t="n"/>
+      <c r="AF15" s="368" t="n"/>
+      <c r="AG15" s="368" t="n"/>
+      <c r="AH15" s="368" t="n"/>
+      <c r="AI15" s="368" t="n"/>
+      <c r="AJ15" s="368" t="n"/>
+      <c r="AK15" s="368" t="n"/>
+      <c r="AL15" s="368" t="n"/>
+      <c r="AM15" s="368" t="n"/>
+      <c r="AN15" s="368" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="368" t="inlineStr">
         <is>
           <t>Operation / Workcenter</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="368" t="n"/>
+      <c r="C16" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D16" s="368" t="n"/>
+      <c r="E16" s="368" t="n"/>
+      <c r="F16" s="368" t="n"/>
+      <c r="G16" s="368" t="n"/>
+      <c r="H16" s="368" t="n"/>
+      <c r="I16" s="368" t="n"/>
+      <c r="J16" s="368" t="n"/>
+      <c r="K16" s="368" t="n"/>
+      <c r="L16" s="368" t="n"/>
+      <c r="M16" s="368" t="n"/>
+      <c r="N16" s="368" t="n"/>
+      <c r="O16" s="368" t="n"/>
+      <c r="P16" s="368" t="n"/>
+      <c r="Q16" s="368" t="n"/>
+      <c r="R16" s="368" t="n"/>
+      <c r="S16" s="368" t="n"/>
+      <c r="T16" s="368" t="n"/>
+      <c r="U16" s="368" t="n"/>
+      <c r="V16" s="368" t="n"/>
+      <c r="W16" s="368" t="n"/>
+      <c r="X16" s="368" t="n"/>
+      <c r="Y16" s="368" t="n"/>
+      <c r="Z16" s="368" t="n"/>
+      <c r="AA16" s="368" t="n"/>
+      <c r="AB16" s="368" t="n"/>
+      <c r="AC16" s="368" t="n"/>
+      <c r="AD16" s="368" t="n"/>
+      <c r="AE16" s="368" t="n"/>
+      <c r="AF16" s="368" t="n"/>
+      <c r="AG16" s="368" t="n"/>
+      <c r="AH16" s="368" t="n"/>
+      <c r="AI16" s="368" t="n"/>
+      <c r="AJ16" s="368" t="n"/>
+      <c r="AK16" s="368" t="n"/>
+      <c r="AL16" s="368" t="n"/>
+      <c r="AM16" s="368" t="n"/>
+      <c r="AN16" s="368" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="368" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="368" t="n"/>
+      <c r="C17" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D17" s="368" t="n"/>
+      <c r="E17" s="368" t="n"/>
+      <c r="F17" s="368" t="n"/>
+      <c r="G17" s="368" t="n"/>
+      <c r="H17" s="368" t="n"/>
+      <c r="I17" s="368" t="n"/>
+      <c r="J17" s="368" t="n"/>
+      <c r="K17" s="368" t="n"/>
+      <c r="L17" s="368" t="n"/>
+      <c r="M17" s="368" t="n"/>
+      <c r="N17" s="368" t="n"/>
+      <c r="O17" s="368" t="n"/>
+      <c r="P17" s="368" t="n"/>
+      <c r="Q17" s="368" t="n"/>
+      <c r="R17" s="368" t="n"/>
+      <c r="S17" s="368" t="n"/>
+      <c r="T17" s="368" t="n"/>
+      <c r="U17" s="368" t="n"/>
+      <c r="V17" s="368" t="n"/>
+      <c r="W17" s="368" t="n"/>
+      <c r="X17" s="368" t="n"/>
+      <c r="Y17" s="368" t="n"/>
+      <c r="Z17" s="368" t="n"/>
+      <c r="AA17" s="368" t="n"/>
+      <c r="AB17" s="368" t="n"/>
+      <c r="AC17" s="368" t="n"/>
+      <c r="AD17" s="368" t="n"/>
+      <c r="AE17" s="368" t="n"/>
+      <c r="AF17" s="368" t="n"/>
+      <c r="AG17" s="368" t="n"/>
+      <c r="AH17" s="368" t="n"/>
+      <c r="AI17" s="368" t="n"/>
+      <c r="AJ17" s="368" t="n"/>
+      <c r="AK17" s="368" t="n"/>
+      <c r="AL17" s="368" t="n"/>
+      <c r="AM17" s="368" t="n"/>
+      <c r="AN17" s="368" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="368" t="inlineStr">
         <is>
           <t>Lot / Quantity</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="368" t="n"/>
+      <c r="C18" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D18" s="368" t="n"/>
+      <c r="E18" s="368" t="n"/>
+      <c r="F18" s="368" t="n"/>
+      <c r="G18" s="368" t="n"/>
+      <c r="H18" s="368" t="n"/>
+      <c r="I18" s="368" t="n"/>
+      <c r="J18" s="368" t="n"/>
+      <c r="K18" s="368" t="n"/>
+      <c r="L18" s="368" t="n"/>
+      <c r="M18" s="368" t="n"/>
+      <c r="N18" s="368" t="n"/>
+      <c r="O18" s="368" t="n"/>
+      <c r="P18" s="368" t="n"/>
+      <c r="Q18" s="368" t="n"/>
+      <c r="R18" s="368" t="n"/>
+      <c r="S18" s="368" t="n"/>
+      <c r="T18" s="368" t="n"/>
+      <c r="U18" s="368" t="n"/>
+      <c r="V18" s="368" t="n"/>
+      <c r="W18" s="368" t="n"/>
+      <c r="X18" s="368" t="n"/>
+      <c r="Y18" s="368" t="n"/>
+      <c r="Z18" s="368" t="n"/>
+      <c r="AA18" s="368" t="n"/>
+      <c r="AB18" s="368" t="n"/>
+      <c r="AC18" s="368" t="n"/>
+      <c r="AD18" s="368" t="n"/>
+      <c r="AE18" s="368" t="n"/>
+      <c r="AF18" s="368" t="n"/>
+      <c r="AG18" s="368" t="n"/>
+      <c r="AH18" s="368" t="n"/>
+      <c r="AI18" s="368" t="n"/>
+      <c r="AJ18" s="368" t="n"/>
+      <c r="AK18" s="368" t="n"/>
+      <c r="AL18" s="368" t="n"/>
+      <c r="AM18" s="368" t="n"/>
+      <c r="AN18" s="368" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="368" t="inlineStr">
         <is>
           <t>Job / Route Step</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="368" t="n"/>
+      <c r="C19" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D19" s="368" t="n"/>
+      <c r="E19" s="368" t="n"/>
+      <c r="F19" s="368" t="n"/>
+      <c r="G19" s="368" t="n"/>
+      <c r="H19" s="368" t="n"/>
+      <c r="I19" s="368" t="n"/>
+      <c r="J19" s="368" t="n"/>
+      <c r="K19" s="368" t="n"/>
+      <c r="L19" s="368" t="n"/>
+      <c r="M19" s="368" t="n"/>
+      <c r="N19" s="368" t="n"/>
+      <c r="O19" s="368" t="n"/>
+      <c r="P19" s="368" t="n"/>
+      <c r="Q19" s="368" t="n"/>
+      <c r="R19" s="368" t="n"/>
+      <c r="S19" s="368" t="n"/>
+      <c r="T19" s="368" t="n"/>
+      <c r="U19" s="368" t="n"/>
+      <c r="V19" s="368" t="n"/>
+      <c r="W19" s="368" t="n"/>
+      <c r="X19" s="368" t="n"/>
+      <c r="Y19" s="368" t="n"/>
+      <c r="Z19" s="368" t="n"/>
+      <c r="AA19" s="368" t="n"/>
+      <c r="AB19" s="368" t="n"/>
+      <c r="AC19" s="368" t="n"/>
+      <c r="AD19" s="368" t="n"/>
+      <c r="AE19" s="368" t="n"/>
+      <c r="AF19" s="368" t="n"/>
+      <c r="AG19" s="368" t="n"/>
+      <c r="AH19" s="368" t="n"/>
+      <c r="AI19" s="368" t="n"/>
+      <c r="AJ19" s="368" t="n"/>
+      <c r="AK19" s="368" t="n"/>
+      <c r="AL19" s="368" t="n"/>
+      <c r="AM19" s="368" t="n"/>
+      <c r="AN19" s="368" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="368" t="inlineStr">
         <is>
           <t>Area / Location</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="368" t="n"/>
+      <c r="C20" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D20" s="368" t="n"/>
+      <c r="E20" s="368" t="n"/>
+      <c r="F20" s="368" t="n"/>
+      <c r="G20" s="368" t="n"/>
+      <c r="H20" s="368" t="n"/>
+      <c r="I20" s="368" t="n"/>
+      <c r="J20" s="368" t="n"/>
+      <c r="K20" s="368" t="n"/>
+      <c r="L20" s="368" t="n"/>
+      <c r="M20" s="368" t="n"/>
+      <c r="N20" s="368" t="n"/>
+      <c r="O20" s="368" t="n"/>
+      <c r="P20" s="368" t="n"/>
+      <c r="Q20" s="368" t="n"/>
+      <c r="R20" s="368" t="n"/>
+      <c r="S20" s="368" t="n"/>
+      <c r="T20" s="368" t="n"/>
+      <c r="U20" s="368" t="n"/>
+      <c r="V20" s="368" t="n"/>
+      <c r="W20" s="368" t="n"/>
+      <c r="X20" s="368" t="n"/>
+      <c r="Y20" s="368" t="n"/>
+      <c r="Z20" s="368" t="n"/>
+      <c r="AA20" s="368" t="n"/>
+      <c r="AB20" s="368" t="n"/>
+      <c r="AC20" s="368" t="n"/>
+      <c r="AD20" s="368" t="n"/>
+      <c r="AE20" s="368" t="n"/>
+      <c r="AF20" s="368" t="n"/>
+      <c r="AG20" s="368" t="n"/>
+      <c r="AH20" s="368" t="n"/>
+      <c r="AI20" s="368" t="n"/>
+      <c r="AJ20" s="368" t="n"/>
+      <c r="AK20" s="368" t="n"/>
+      <c r="AL20" s="368" t="n"/>
+      <c r="AM20" s="368" t="n"/>
+      <c r="AN20" s="368" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="368" t="inlineStr">
         <is>
           <t>Encoded String / Barcode Ref</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="368" t="n"/>
+      <c r="C21" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D21" s="368" t="n"/>
+      <c r="E21" s="368" t="n"/>
+      <c r="F21" s="368" t="n"/>
+      <c r="G21" s="368" t="n"/>
+      <c r="H21" s="368" t="n"/>
+      <c r="I21" s="368" t="n"/>
+      <c r="J21" s="368" t="n"/>
+      <c r="K21" s="368" t="n"/>
+      <c r="L21" s="368" t="n"/>
+      <c r="M21" s="368" t="n"/>
+      <c r="N21" s="368" t="n"/>
+      <c r="O21" s="368" t="n"/>
+      <c r="P21" s="368" t="n"/>
+      <c r="Q21" s="368" t="n"/>
+      <c r="R21" s="368" t="n"/>
+      <c r="S21" s="368" t="n"/>
+      <c r="T21" s="368" t="n"/>
+      <c r="U21" s="368" t="n"/>
+      <c r="V21" s="368" t="n"/>
+      <c r="W21" s="368" t="n"/>
+      <c r="X21" s="368" t="n"/>
+      <c r="Y21" s="368" t="n"/>
+      <c r="Z21" s="368" t="n"/>
+      <c r="AA21" s="368" t="n"/>
+      <c r="AB21" s="368" t="n"/>
+      <c r="AC21" s="368" t="n"/>
+      <c r="AD21" s="368" t="n"/>
+      <c r="AE21" s="368" t="n"/>
+      <c r="AF21" s="368" t="n"/>
+      <c r="AG21" s="368" t="n"/>
+      <c r="AH21" s="368" t="n"/>
+      <c r="AI21" s="368" t="n"/>
+      <c r="AJ21" s="368" t="n"/>
+      <c r="AK21" s="368" t="n"/>
+      <c r="AL21" s="368" t="n"/>
+      <c r="AM21" s="368" t="n"/>
+      <c r="AN21" s="368" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="368" t="inlineStr">
         <is>
           <t>Application Note</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="368" t="n"/>
+      <c r="C22" s="368" t="inlineStr">
         <is>
           <t>Controlled generator/source field for printed face</t>
         </is>
       </c>
+      <c r="D22" s="368" t="n"/>
+      <c r="E22" s="368" t="n"/>
+      <c r="F22" s="368" t="n"/>
+      <c r="G22" s="368" t="n"/>
+      <c r="H22" s="368" t="n"/>
+      <c r="I22" s="368" t="n"/>
+      <c r="J22" s="368" t="n"/>
+      <c r="K22" s="368" t="n"/>
+      <c r="L22" s="368" t="n"/>
+      <c r="M22" s="368" t="n"/>
+      <c r="N22" s="368" t="n"/>
+      <c r="O22" s="368" t="n"/>
+      <c r="P22" s="368" t="n"/>
+      <c r="Q22" s="368" t="n"/>
+      <c r="R22" s="368" t="n"/>
+      <c r="S22" s="368" t="n"/>
+      <c r="T22" s="368" t="n"/>
+      <c r="U22" s="368" t="n"/>
+      <c r="V22" s="368" t="n"/>
+      <c r="W22" s="368" t="n"/>
+      <c r="X22" s="368" t="n"/>
+      <c r="Y22" s="368" t="n"/>
+      <c r="Z22" s="368" t="n"/>
+      <c r="AA22" s="368" t="n"/>
+      <c r="AB22" s="368" t="n"/>
+      <c r="AC22" s="368" t="n"/>
+      <c r="AD22" s="368" t="n"/>
+      <c r="AE22" s="368" t="n"/>
+      <c r="AF22" s="368" t="n"/>
+      <c r="AG22" s="368" t="n"/>
+      <c r="AH22" s="368" t="n"/>
+      <c r="AI22" s="368" t="n"/>
+      <c r="AJ22" s="368" t="n"/>
+      <c r="AK22" s="368" t="n"/>
+      <c r="AL22" s="368" t="n"/>
+      <c r="AM22" s="368" t="n"/>
+      <c r="AN22" s="368" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -7481,7 +8981,8 @@
     <row r="39" ht="20" customHeight="1"/>
     <row r="40" ht="20" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7491,12 +8992,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -7505,92 +9043,559 @@
           <t>Print Control</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+      <c r="B1" s="334" t="n"/>
+      <c r="C1" s="334" t="n"/>
+      <c r="D1" s="334" t="n"/>
+      <c r="E1" s="334" t="n"/>
+      <c r="F1" s="334" t="n"/>
+      <c r="G1" s="334" t="n"/>
+      <c r="H1" s="334" t="n"/>
+      <c r="I1" s="334" t="n"/>
+      <c r="J1" s="334" t="n"/>
+      <c r="K1" s="334" t="n"/>
+      <c r="L1" s="334" t="n"/>
+      <c r="M1" s="334" t="n"/>
+      <c r="N1" s="334" t="n"/>
+      <c r="O1" s="334" t="n"/>
+      <c r="P1" s="334" t="n"/>
+      <c r="Q1" s="334" t="n"/>
+      <c r="R1" s="334" t="n"/>
+      <c r="S1" s="334" t="n"/>
+      <c r="T1" s="334" t="n"/>
+      <c r="U1" s="334" t="n"/>
+      <c r="V1" s="334" t="n"/>
+      <c r="W1" s="334" t="n"/>
+      <c r="X1" s="334" t="n"/>
+      <c r="Y1" s="334" t="n"/>
+      <c r="Z1" s="334" t="n"/>
+      <c r="AA1" s="334" t="n"/>
+      <c r="AB1" s="334" t="n"/>
+      <c r="AC1" s="334" t="n"/>
+      <c r="AD1" s="334" t="n"/>
+      <c r="AE1" s="334" t="n"/>
+      <c r="AF1" s="334" t="n"/>
+      <c r="AG1" s="334" t="n"/>
+      <c r="AH1" s="334" t="n"/>
+      <c r="AI1" s="334" t="n"/>
+      <c r="AJ1" s="334" t="n"/>
+      <c r="AK1" s="334" t="n"/>
+      <c r="AL1" s="334" t="n"/>
+      <c r="AM1" s="334" t="n"/>
+      <c r="AN1" s="334" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="324" t="inlineStr">
         <is>
           <t>No signature on printed face. Control release / print / verify / void here.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
+      <c r="B2" s="334" t="n"/>
+      <c r="C2" s="334" t="n"/>
+      <c r="D2" s="334" t="n"/>
+      <c r="E2" s="334" t="n"/>
+      <c r="F2" s="334" t="n"/>
+      <c r="G2" s="334" t="n"/>
+      <c r="H2" s="334" t="n"/>
+      <c r="I2" s="334" t="n"/>
+      <c r="J2" s="334" t="n"/>
+      <c r="K2" s="334" t="n"/>
+      <c r="L2" s="334" t="n"/>
+      <c r="M2" s="334" t="n"/>
+      <c r="N2" s="334" t="n"/>
+      <c r="O2" s="334" t="n"/>
+      <c r="P2" s="334" t="n"/>
+      <c r="Q2" s="334" t="n"/>
+      <c r="R2" s="334" t="n"/>
+      <c r="S2" s="334" t="n"/>
+      <c r="T2" s="334" t="n"/>
+      <c r="U2" s="334" t="n"/>
+      <c r="V2" s="334" t="n"/>
+      <c r="W2" s="334" t="n"/>
+      <c r="X2" s="334" t="n"/>
+      <c r="Y2" s="334" t="n"/>
+      <c r="Z2" s="334" t="n"/>
+      <c r="AA2" s="334" t="n"/>
+      <c r="AB2" s="334" t="n"/>
+      <c r="AC2" s="334" t="n"/>
+      <c r="AD2" s="334" t="n"/>
+      <c r="AE2" s="334" t="n"/>
+      <c r="AF2" s="334" t="n"/>
+      <c r="AG2" s="334" t="n"/>
+      <c r="AH2" s="334" t="n"/>
+      <c r="AI2" s="334" t="n"/>
+      <c r="AJ2" s="334" t="n"/>
+      <c r="AK2" s="334" t="n"/>
+      <c r="AL2" s="334" t="n"/>
+      <c r="AM2" s="334" t="n"/>
+      <c r="AN2" s="334" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="334" t="n"/>
+      <c r="B3" s="334" t="n"/>
+      <c r="C3" s="334" t="n"/>
+      <c r="D3" s="334" t="n"/>
+      <c r="E3" s="334" t="n"/>
+      <c r="F3" s="334" t="n"/>
+      <c r="G3" s="334" t="n"/>
+      <c r="H3" s="334" t="n"/>
+      <c r="I3" s="334" t="n"/>
+      <c r="J3" s="334" t="n"/>
+      <c r="K3" s="334" t="n"/>
+      <c r="L3" s="334" t="n"/>
+      <c r="M3" s="334" t="n"/>
+      <c r="N3" s="334" t="n"/>
+      <c r="O3" s="334" t="n"/>
+      <c r="P3" s="334" t="n"/>
+      <c r="Q3" s="334" t="n"/>
+      <c r="R3" s="334" t="n"/>
+      <c r="S3" s="334" t="n"/>
+      <c r="T3" s="334" t="n"/>
+      <c r="U3" s="334" t="n"/>
+      <c r="V3" s="334" t="n"/>
+      <c r="W3" s="334" t="n"/>
+      <c r="X3" s="334" t="n"/>
+      <c r="Y3" s="334" t="n"/>
+      <c r="Z3" s="334" t="n"/>
+      <c r="AA3" s="334" t="n"/>
+      <c r="AB3" s="334" t="n"/>
+      <c r="AC3" s="334" t="n"/>
+      <c r="AD3" s="334" t="n"/>
+      <c r="AE3" s="334" t="n"/>
+      <c r="AF3" s="334" t="n"/>
+      <c r="AG3" s="334" t="n"/>
+      <c r="AH3" s="334" t="n"/>
+      <c r="AI3" s="334" t="n"/>
+      <c r="AJ3" s="334" t="n"/>
+      <c r="AK3" s="334" t="n"/>
+      <c r="AL3" s="334" t="n"/>
+      <c r="AM3" s="334" t="n"/>
+      <c r="AN3" s="334" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="325" t="inlineStr">
+      <c r="A4" s="372" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="325" t="inlineStr">
+      <c r="B4" s="372" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="325" t="inlineStr">
+      <c r="C4" s="372" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="334" t="n"/>
+      <c r="E4" s="334" t="n"/>
+      <c r="F4" s="334" t="n"/>
+      <c r="G4" s="334" t="n"/>
+      <c r="H4" s="334" t="n"/>
+      <c r="I4" s="334" t="n"/>
+      <c r="J4" s="334" t="n"/>
+      <c r="K4" s="334" t="n"/>
+      <c r="L4" s="334" t="n"/>
+      <c r="M4" s="334" t="n"/>
+      <c r="N4" s="334" t="n"/>
+      <c r="O4" s="334" t="n"/>
+      <c r="P4" s="334" t="n"/>
+      <c r="Q4" s="334" t="n"/>
+      <c r="R4" s="334" t="n"/>
+      <c r="S4" s="334" t="n"/>
+      <c r="T4" s="334" t="n"/>
+      <c r="U4" s="334" t="n"/>
+      <c r="V4" s="334" t="n"/>
+      <c r="W4" s="334" t="n"/>
+      <c r="X4" s="334" t="n"/>
+      <c r="Y4" s="334" t="n"/>
+      <c r="Z4" s="334" t="n"/>
+      <c r="AA4" s="334" t="n"/>
+      <c r="AB4" s="334" t="n"/>
+      <c r="AC4" s="334" t="n"/>
+      <c r="AD4" s="334" t="n"/>
+      <c r="AE4" s="334" t="n"/>
+      <c r="AF4" s="334" t="n"/>
+      <c r="AG4" s="334" t="n"/>
+      <c r="AH4" s="334" t="n"/>
+      <c r="AI4" s="334" t="n"/>
+      <c r="AJ4" s="334" t="n"/>
+      <c r="AK4" s="334" t="n"/>
+      <c r="AL4" s="334" t="n"/>
+      <c r="AM4" s="334" t="n"/>
+      <c r="AN4" s="334" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="334" t="inlineStr">
         <is>
           <t>Print State</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="334" t="n"/>
+      <c r="C5" s="334" t="inlineStr">
         <is>
           <t>REQUESTED / PRINTED / VERIFIED / APPLIED / VOID / SCRAP / REPRINT</t>
         </is>
       </c>
+      <c r="D5" s="334" t="n"/>
+      <c r="E5" s="334" t="n"/>
+      <c r="F5" s="334" t="n"/>
+      <c r="G5" s="334" t="n"/>
+      <c r="H5" s="334" t="n"/>
+      <c r="I5" s="334" t="n"/>
+      <c r="J5" s="334" t="n"/>
+      <c r="K5" s="334" t="n"/>
+      <c r="L5" s="334" t="n"/>
+      <c r="M5" s="334" t="n"/>
+      <c r="N5" s="334" t="n"/>
+      <c r="O5" s="334" t="n"/>
+      <c r="P5" s="334" t="n"/>
+      <c r="Q5" s="334" t="n"/>
+      <c r="R5" s="334" t="n"/>
+      <c r="S5" s="334" t="n"/>
+      <c r="T5" s="334" t="n"/>
+      <c r="U5" s="334" t="n"/>
+      <c r="V5" s="334" t="n"/>
+      <c r="W5" s="334" t="n"/>
+      <c r="X5" s="334" t="n"/>
+      <c r="Y5" s="334" t="n"/>
+      <c r="Z5" s="334" t="n"/>
+      <c r="AA5" s="334" t="n"/>
+      <c r="AB5" s="334" t="n"/>
+      <c r="AC5" s="334" t="n"/>
+      <c r="AD5" s="334" t="n"/>
+      <c r="AE5" s="334" t="n"/>
+      <c r="AF5" s="334" t="n"/>
+      <c r="AG5" s="334" t="n"/>
+      <c r="AH5" s="334" t="n"/>
+      <c r="AI5" s="334" t="n"/>
+      <c r="AJ5" s="334" t="n"/>
+      <c r="AK5" s="334" t="n"/>
+      <c r="AL5" s="334" t="n"/>
+      <c r="AM5" s="334" t="n"/>
+      <c r="AN5" s="334" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="334" t="inlineStr">
         <is>
           <t>Released by</t>
         </is>
       </c>
+      <c r="B6" s="334" t="n"/>
+      <c r="C6" s="334" t="n"/>
+      <c r="D6" s="334" t="n"/>
+      <c r="E6" s="334" t="n"/>
+      <c r="F6" s="334" t="n"/>
+      <c r="G6" s="334" t="n"/>
+      <c r="H6" s="334" t="n"/>
+      <c r="I6" s="334" t="n"/>
+      <c r="J6" s="334" t="n"/>
+      <c r="K6" s="334" t="n"/>
+      <c r="L6" s="334" t="n"/>
+      <c r="M6" s="334" t="n"/>
+      <c r="N6" s="334" t="n"/>
+      <c r="O6" s="334" t="n"/>
+      <c r="P6" s="334" t="n"/>
+      <c r="Q6" s="334" t="n"/>
+      <c r="R6" s="334" t="n"/>
+      <c r="S6" s="334" t="n"/>
+      <c r="T6" s="334" t="n"/>
+      <c r="U6" s="334" t="n"/>
+      <c r="V6" s="334" t="n"/>
+      <c r="W6" s="334" t="n"/>
+      <c r="X6" s="334" t="n"/>
+      <c r="Y6" s="334" t="n"/>
+      <c r="Z6" s="334" t="n"/>
+      <c r="AA6" s="334" t="n"/>
+      <c r="AB6" s="334" t="n"/>
+      <c r="AC6" s="334" t="n"/>
+      <c r="AD6" s="334" t="n"/>
+      <c r="AE6" s="334" t="n"/>
+      <c r="AF6" s="334" t="n"/>
+      <c r="AG6" s="334" t="n"/>
+      <c r="AH6" s="334" t="n"/>
+      <c r="AI6" s="334" t="n"/>
+      <c r="AJ6" s="334" t="n"/>
+      <c r="AK6" s="334" t="n"/>
+      <c r="AL6" s="334" t="n"/>
+      <c r="AM6" s="334" t="n"/>
+      <c r="AN6" s="334" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="334" t="inlineStr">
         <is>
           <t>Printed by</t>
         </is>
       </c>
+      <c r="B7" s="334" t="n"/>
+      <c r="C7" s="334" t="n"/>
+      <c r="D7" s="334" t="n"/>
+      <c r="E7" s="334" t="n"/>
+      <c r="F7" s="334" t="n"/>
+      <c r="G7" s="334" t="n"/>
+      <c r="H7" s="334" t="n"/>
+      <c r="I7" s="334" t="n"/>
+      <c r="J7" s="334" t="n"/>
+      <c r="K7" s="334" t="n"/>
+      <c r="L7" s="334" t="n"/>
+      <c r="M7" s="334" t="n"/>
+      <c r="N7" s="334" t="n"/>
+      <c r="O7" s="334" t="n"/>
+      <c r="P7" s="334" t="n"/>
+      <c r="Q7" s="334" t="n"/>
+      <c r="R7" s="334" t="n"/>
+      <c r="S7" s="334" t="n"/>
+      <c r="T7" s="334" t="n"/>
+      <c r="U7" s="334" t="n"/>
+      <c r="V7" s="334" t="n"/>
+      <c r="W7" s="334" t="n"/>
+      <c r="X7" s="334" t="n"/>
+      <c r="Y7" s="334" t="n"/>
+      <c r="Z7" s="334" t="n"/>
+      <c r="AA7" s="334" t="n"/>
+      <c r="AB7" s="334" t="n"/>
+      <c r="AC7" s="334" t="n"/>
+      <c r="AD7" s="334" t="n"/>
+      <c r="AE7" s="334" t="n"/>
+      <c r="AF7" s="334" t="n"/>
+      <c r="AG7" s="334" t="n"/>
+      <c r="AH7" s="334" t="n"/>
+      <c r="AI7" s="334" t="n"/>
+      <c r="AJ7" s="334" t="n"/>
+      <c r="AK7" s="334" t="n"/>
+      <c r="AL7" s="334" t="n"/>
+      <c r="AM7" s="334" t="n"/>
+      <c r="AN7" s="334" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="368" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
+      <c r="B8" s="368" t="n"/>
+      <c r="C8" s="368" t="n"/>
+      <c r="D8" s="368" t="n"/>
+      <c r="E8" s="368" t="n"/>
+      <c r="F8" s="368" t="n"/>
+      <c r="G8" s="368" t="n"/>
+      <c r="H8" s="368" t="n"/>
+      <c r="I8" s="368" t="n"/>
+      <c r="J8" s="368" t="n"/>
+      <c r="K8" s="368" t="n"/>
+      <c r="L8" s="368" t="n"/>
+      <c r="M8" s="368" t="n"/>
+      <c r="N8" s="368" t="n"/>
+      <c r="O8" s="368" t="n"/>
+      <c r="P8" s="368" t="n"/>
+      <c r="Q8" s="368" t="n"/>
+      <c r="R8" s="368" t="n"/>
+      <c r="S8" s="368" t="n"/>
+      <c r="T8" s="368" t="n"/>
+      <c r="U8" s="368" t="n"/>
+      <c r="V8" s="368" t="n"/>
+      <c r="W8" s="368" t="n"/>
+      <c r="X8" s="368" t="n"/>
+      <c r="Y8" s="368" t="n"/>
+      <c r="Z8" s="368" t="n"/>
+      <c r="AA8" s="368" t="n"/>
+      <c r="AB8" s="368" t="n"/>
+      <c r="AC8" s="368" t="n"/>
+      <c r="AD8" s="368" t="n"/>
+      <c r="AE8" s="368" t="n"/>
+      <c r="AF8" s="368" t="n"/>
+      <c r="AG8" s="368" t="n"/>
+      <c r="AH8" s="368" t="n"/>
+      <c r="AI8" s="368" t="n"/>
+      <c r="AJ8" s="368" t="n"/>
+      <c r="AK8" s="368" t="n"/>
+      <c r="AL8" s="368" t="n"/>
+      <c r="AM8" s="368" t="n"/>
+      <c r="AN8" s="368" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="368" t="inlineStr">
         <is>
           <t>Void / Scrap by</t>
         </is>
       </c>
+      <c r="B9" s="368" t="n"/>
+      <c r="C9" s="368" t="n"/>
+      <c r="D9" s="368" t="n"/>
+      <c r="E9" s="368" t="n"/>
+      <c r="F9" s="368" t="n"/>
+      <c r="G9" s="368" t="n"/>
+      <c r="H9" s="368" t="n"/>
+      <c r="I9" s="368" t="n"/>
+      <c r="J9" s="368" t="n"/>
+      <c r="K9" s="368" t="n"/>
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="368" t="n"/>
+      <c r="N9" s="368" t="n"/>
+      <c r="O9" s="368" t="n"/>
+      <c r="P9" s="368" t="n"/>
+      <c r="Q9" s="368" t="n"/>
+      <c r="R9" s="368" t="n"/>
+      <c r="S9" s="368" t="n"/>
+      <c r="T9" s="368" t="n"/>
+      <c r="U9" s="368" t="n"/>
+      <c r="V9" s="368" t="n"/>
+      <c r="W9" s="368" t="n"/>
+      <c r="X9" s="368" t="n"/>
+      <c r="Y9" s="368" t="n"/>
+      <c r="Z9" s="368" t="n"/>
+      <c r="AA9" s="368" t="n"/>
+      <c r="AB9" s="368" t="n"/>
+      <c r="AC9" s="368" t="n"/>
+      <c r="AD9" s="368" t="n"/>
+      <c r="AE9" s="368" t="n"/>
+      <c r="AF9" s="368" t="n"/>
+      <c r="AG9" s="368" t="n"/>
+      <c r="AH9" s="368" t="n"/>
+      <c r="AI9" s="368" t="n"/>
+      <c r="AJ9" s="368" t="n"/>
+      <c r="AK9" s="368" t="n"/>
+      <c r="AL9" s="368" t="n"/>
+      <c r="AM9" s="368" t="n"/>
+      <c r="AN9" s="368" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="368" t="inlineStr">
         <is>
           <t>Reason / Event Ref</t>
         </is>
       </c>
+      <c r="B10" s="368" t="n"/>
+      <c r="C10" s="368" t="n"/>
+      <c r="D10" s="368" t="n"/>
+      <c r="E10" s="368" t="n"/>
+      <c r="F10" s="368" t="n"/>
+      <c r="G10" s="368" t="n"/>
+      <c r="H10" s="368" t="n"/>
+      <c r="I10" s="368" t="n"/>
+      <c r="J10" s="368" t="n"/>
+      <c r="K10" s="368" t="n"/>
+      <c r="L10" s="368" t="n"/>
+      <c r="M10" s="368" t="n"/>
+      <c r="N10" s="368" t="n"/>
+      <c r="O10" s="368" t="n"/>
+      <c r="P10" s="368" t="n"/>
+      <c r="Q10" s="368" t="n"/>
+      <c r="R10" s="368" t="n"/>
+      <c r="S10" s="368" t="n"/>
+      <c r="T10" s="368" t="n"/>
+      <c r="U10" s="368" t="n"/>
+      <c r="V10" s="368" t="n"/>
+      <c r="W10" s="368" t="n"/>
+      <c r="X10" s="368" t="n"/>
+      <c r="Y10" s="368" t="n"/>
+      <c r="Z10" s="368" t="n"/>
+      <c r="AA10" s="368" t="n"/>
+      <c r="AB10" s="368" t="n"/>
+      <c r="AC10" s="368" t="n"/>
+      <c r="AD10" s="368" t="n"/>
+      <c r="AE10" s="368" t="n"/>
+      <c r="AF10" s="368" t="n"/>
+      <c r="AG10" s="368" t="n"/>
+      <c r="AH10" s="368" t="n"/>
+      <c r="AI10" s="368" t="n"/>
+      <c r="AJ10" s="368" t="n"/>
+      <c r="AK10" s="368" t="n"/>
+      <c r="AL10" s="368" t="n"/>
+      <c r="AM10" s="368" t="n"/>
+      <c r="AN10" s="368" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="368" t="inlineStr">
         <is>
           <t>Application Location / Lot</t>
         </is>
       </c>
+      <c r="B11" s="368" t="n"/>
+      <c r="C11" s="368" t="n"/>
+      <c r="D11" s="368" t="n"/>
+      <c r="E11" s="368" t="n"/>
+      <c r="F11" s="368" t="n"/>
+      <c r="G11" s="368" t="n"/>
+      <c r="H11" s="368" t="n"/>
+      <c r="I11" s="368" t="n"/>
+      <c r="J11" s="368" t="n"/>
+      <c r="K11" s="368" t="n"/>
+      <c r="L11" s="368" t="n"/>
+      <c r="M11" s="368" t="n"/>
+      <c r="N11" s="368" t="n"/>
+      <c r="O11" s="368" t="n"/>
+      <c r="P11" s="368" t="n"/>
+      <c r="Q11" s="368" t="n"/>
+      <c r="R11" s="368" t="n"/>
+      <c r="S11" s="368" t="n"/>
+      <c r="T11" s="368" t="n"/>
+      <c r="U11" s="368" t="n"/>
+      <c r="V11" s="368" t="n"/>
+      <c r="W11" s="368" t="n"/>
+      <c r="X11" s="368" t="n"/>
+      <c r="Y11" s="368" t="n"/>
+      <c r="Z11" s="368" t="n"/>
+      <c r="AA11" s="368" t="n"/>
+      <c r="AB11" s="368" t="n"/>
+      <c r="AC11" s="368" t="n"/>
+      <c r="AD11" s="368" t="n"/>
+      <c r="AE11" s="368" t="n"/>
+      <c r="AF11" s="368" t="n"/>
+      <c r="AG11" s="368" t="n"/>
+      <c r="AH11" s="368" t="n"/>
+      <c r="AI11" s="368" t="n"/>
+      <c r="AJ11" s="368" t="n"/>
+      <c r="AK11" s="368" t="n"/>
+      <c r="AL11" s="368" t="n"/>
+      <c r="AM11" s="368" t="n"/>
+      <c r="AN11" s="368" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="368" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="B12" s="368" t="n"/>
+      <c r="C12" s="368" t="n"/>
+      <c r="D12" s="368" t="n"/>
+      <c r="E12" s="368" t="n"/>
+      <c r="F12" s="368" t="n"/>
+      <c r="G12" s="368" t="n"/>
+      <c r="H12" s="368" t="n"/>
+      <c r="I12" s="368" t="n"/>
+      <c r="J12" s="368" t="n"/>
+      <c r="K12" s="368" t="n"/>
+      <c r="L12" s="368" t="n"/>
+      <c r="M12" s="368" t="n"/>
+      <c r="N12" s="368" t="n"/>
+      <c r="O12" s="368" t="n"/>
+      <c r="P12" s="368" t="n"/>
+      <c r="Q12" s="368" t="n"/>
+      <c r="R12" s="368" t="n"/>
+      <c r="S12" s="368" t="n"/>
+      <c r="T12" s="368" t="n"/>
+      <c r="U12" s="368" t="n"/>
+      <c r="V12" s="368" t="n"/>
+      <c r="W12" s="368" t="n"/>
+      <c r="X12" s="368" t="n"/>
+      <c r="Y12" s="368" t="n"/>
+      <c r="Z12" s="368" t="n"/>
+      <c r="AA12" s="368" t="n"/>
+      <c r="AB12" s="368" t="n"/>
+      <c r="AC12" s="368" t="n"/>
+      <c r="AD12" s="368" t="n"/>
+      <c r="AE12" s="368" t="n"/>
+      <c r="AF12" s="368" t="n"/>
+      <c r="AG12" s="368" t="n"/>
+      <c r="AH12" s="368" t="n"/>
+      <c r="AI12" s="368" t="n"/>
+      <c r="AJ12" s="368" t="n"/>
+      <c r="AK12" s="368" t="n"/>
+      <c r="AL12" s="368" t="n"/>
+      <c r="AM12" s="368" t="n"/>
+      <c r="AN12" s="368" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1"/>
     <row r="14" ht="20" customHeight="1"/>
@@ -7616,7 +9621,8 @@
       <formula1>=LISTS!$A$2:$A$8</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7626,17 +9632,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -7645,6 +9683,45 @@
           <t>Print Event Log</t>
         </is>
       </c>
+      <c r="B1" s="334" t="n"/>
+      <c r="C1" s="334" t="n"/>
+      <c r="D1" s="334" t="n"/>
+      <c r="E1" s="334" t="n"/>
+      <c r="F1" s="334" t="n"/>
+      <c r="G1" s="334" t="n"/>
+      <c r="H1" s="334" t="n"/>
+      <c r="I1" s="334" t="n"/>
+      <c r="J1" s="334" t="n"/>
+      <c r="K1" s="334" t="n"/>
+      <c r="L1" s="334" t="n"/>
+      <c r="M1" s="334" t="n"/>
+      <c r="N1" s="334" t="n"/>
+      <c r="O1" s="334" t="n"/>
+      <c r="P1" s="334" t="n"/>
+      <c r="Q1" s="334" t="n"/>
+      <c r="R1" s="334" t="n"/>
+      <c r="S1" s="334" t="n"/>
+      <c r="T1" s="334" t="n"/>
+      <c r="U1" s="334" t="n"/>
+      <c r="V1" s="334" t="n"/>
+      <c r="W1" s="334" t="n"/>
+      <c r="X1" s="334" t="n"/>
+      <c r="Y1" s="334" t="n"/>
+      <c r="Z1" s="334" t="n"/>
+      <c r="AA1" s="334" t="n"/>
+      <c r="AB1" s="334" t="n"/>
+      <c r="AC1" s="334" t="n"/>
+      <c r="AD1" s="334" t="n"/>
+      <c r="AE1" s="334" t="n"/>
+      <c r="AF1" s="334" t="n"/>
+      <c r="AG1" s="334" t="n"/>
+      <c r="AH1" s="334" t="n"/>
+      <c r="AI1" s="334" t="n"/>
+      <c r="AJ1" s="334" t="n"/>
+      <c r="AK1" s="334" t="n"/>
+      <c r="AL1" s="334" t="n"/>
+      <c r="AM1" s="334" t="n"/>
+      <c r="AN1" s="334" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="324" t="inlineStr">
@@ -7652,109 +9729,611 @@
           <t>Controlled WIP tag print object. Keep printed face limited to approved identity and status only.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
+      <c r="B2" s="334" t="n"/>
+      <c r="C2" s="334" t="n"/>
+      <c r="D2" s="334" t="n"/>
+      <c r="E2" s="334" t="n"/>
+      <c r="F2" s="334" t="n"/>
+      <c r="G2" s="334" t="n"/>
+      <c r="H2" s="334" t="n"/>
+      <c r="I2" s="334" t="n"/>
+      <c r="J2" s="334" t="n"/>
+      <c r="K2" s="334" t="n"/>
+      <c r="L2" s="334" t="n"/>
+      <c r="M2" s="334" t="n"/>
+      <c r="N2" s="334" t="n"/>
+      <c r="O2" s="334" t="n"/>
+      <c r="P2" s="334" t="n"/>
+      <c r="Q2" s="334" t="n"/>
+      <c r="R2" s="334" t="n"/>
+      <c r="S2" s="334" t="n"/>
+      <c r="T2" s="334" t="n"/>
+      <c r="U2" s="334" t="n"/>
+      <c r="V2" s="334" t="n"/>
+      <c r="W2" s="334" t="n"/>
+      <c r="X2" s="334" t="n"/>
+      <c r="Y2" s="334" t="n"/>
+      <c r="Z2" s="334" t="n"/>
+      <c r="AA2" s="334" t="n"/>
+      <c r="AB2" s="334" t="n"/>
+      <c r="AC2" s="334" t="n"/>
+      <c r="AD2" s="334" t="n"/>
+      <c r="AE2" s="334" t="n"/>
+      <c r="AF2" s="334" t="n"/>
+      <c r="AG2" s="334" t="n"/>
+      <c r="AH2" s="334" t="n"/>
+      <c r="AI2" s="334" t="n"/>
+      <c r="AJ2" s="334" t="n"/>
+      <c r="AK2" s="334" t="n"/>
+      <c r="AL2" s="334" t="n"/>
+      <c r="AM2" s="334" t="n"/>
+      <c r="AN2" s="334" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="334" t="n"/>
+      <c r="B3" s="334" t="n"/>
+      <c r="C3" s="334" t="n"/>
+      <c r="D3" s="334" t="n"/>
+      <c r="E3" s="334" t="n"/>
+      <c r="F3" s="334" t="n"/>
+      <c r="G3" s="334" t="n"/>
+      <c r="H3" s="334" t="n"/>
+      <c r="I3" s="334" t="n"/>
+      <c r="J3" s="334" t="n"/>
+      <c r="K3" s="334" t="n"/>
+      <c r="L3" s="334" t="n"/>
+      <c r="M3" s="334" t="n"/>
+      <c r="N3" s="334" t="n"/>
+      <c r="O3" s="334" t="n"/>
+      <c r="P3" s="334" t="n"/>
+      <c r="Q3" s="334" t="n"/>
+      <c r="R3" s="334" t="n"/>
+      <c r="S3" s="334" t="n"/>
+      <c r="T3" s="334" t="n"/>
+      <c r="U3" s="334" t="n"/>
+      <c r="V3" s="334" t="n"/>
+      <c r="W3" s="334" t="n"/>
+      <c r="X3" s="334" t="n"/>
+      <c r="Y3" s="334" t="n"/>
+      <c r="Z3" s="334" t="n"/>
+      <c r="AA3" s="334" t="n"/>
+      <c r="AB3" s="334" t="n"/>
+      <c r="AC3" s="334" t="n"/>
+      <c r="AD3" s="334" t="n"/>
+      <c r="AE3" s="334" t="n"/>
+      <c r="AF3" s="334" t="n"/>
+      <c r="AG3" s="334" t="n"/>
+      <c r="AH3" s="334" t="n"/>
+      <c r="AI3" s="334" t="n"/>
+      <c r="AJ3" s="334" t="n"/>
+      <c r="AK3" s="334" t="n"/>
+      <c r="AL3" s="334" t="n"/>
+      <c r="AM3" s="334" t="n"/>
+      <c r="AN3" s="334" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="325" t="inlineStr">
+      <c r="A4" s="372" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="325" t="inlineStr">
+      <c r="B4" s="372" t="inlineStr">
         <is>
           <t>Date-Time</t>
         </is>
       </c>
-      <c r="C4" s="325" t="inlineStr">
+      <c r="C4" s="372" t="inlineStr">
         <is>
           <t>Event State</t>
         </is>
       </c>
-      <c r="D4" s="325" t="inlineStr">
+      <c r="D4" s="372" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E4" s="325" t="inlineStr">
+      <c r="E4" s="372" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F4" s="325" t="inlineStr">
+      <c r="F4" s="372" t="inlineStr">
         <is>
           <t>Reason / Event Ref</t>
         </is>
       </c>
-      <c r="G4" s="325" t="inlineStr">
+      <c r="G4" s="372" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="H4" s="325" t="inlineStr">
+      <c r="H4" s="372" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="I4" s="334" t="n"/>
+      <c r="J4" s="334" t="n"/>
+      <c r="K4" s="334" t="n"/>
+      <c r="L4" s="334" t="n"/>
+      <c r="M4" s="334" t="n"/>
+      <c r="N4" s="334" t="n"/>
+      <c r="O4" s="334" t="n"/>
+      <c r="P4" s="334" t="n"/>
+      <c r="Q4" s="334" t="n"/>
+      <c r="R4" s="334" t="n"/>
+      <c r="S4" s="334" t="n"/>
+      <c r="T4" s="334" t="n"/>
+      <c r="U4" s="334" t="n"/>
+      <c r="V4" s="334" t="n"/>
+      <c r="W4" s="334" t="n"/>
+      <c r="X4" s="334" t="n"/>
+      <c r="Y4" s="334" t="n"/>
+      <c r="Z4" s="334" t="n"/>
+      <c r="AA4" s="334" t="n"/>
+      <c r="AB4" s="334" t="n"/>
+      <c r="AC4" s="334" t="n"/>
+      <c r="AD4" s="334" t="n"/>
+      <c r="AE4" s="334" t="n"/>
+      <c r="AF4" s="334" t="n"/>
+      <c r="AG4" s="334" t="n"/>
+      <c r="AH4" s="334" t="n"/>
+      <c r="AI4" s="334" t="n"/>
+      <c r="AJ4" s="334" t="n"/>
+      <c r="AK4" s="334" t="n"/>
+      <c r="AL4" s="334" t="n"/>
+      <c r="AM4" s="334" t="n"/>
+      <c r="AN4" s="334" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5">
+      <c r="A5" s="334">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B5" s="334" t="n"/>
+      <c r="C5" s="334" t="n"/>
+      <c r="D5" s="334" t="n"/>
+      <c r="E5" s="334" t="n"/>
+      <c r="F5" s="334" t="n"/>
+      <c r="G5" s="334" t="n"/>
+      <c r="H5" s="334" t="n"/>
+      <c r="I5" s="334" t="n"/>
+      <c r="J5" s="334" t="n"/>
+      <c r="K5" s="334" t="n"/>
+      <c r="L5" s="334" t="n"/>
+      <c r="M5" s="334" t="n"/>
+      <c r="N5" s="334" t="n"/>
+      <c r="O5" s="334" t="n"/>
+      <c r="P5" s="334" t="n"/>
+      <c r="Q5" s="334" t="n"/>
+      <c r="R5" s="334" t="n"/>
+      <c r="S5" s="334" t="n"/>
+      <c r="T5" s="334" t="n"/>
+      <c r="U5" s="334" t="n"/>
+      <c r="V5" s="334" t="n"/>
+      <c r="W5" s="334" t="n"/>
+      <c r="X5" s="334" t="n"/>
+      <c r="Y5" s="334" t="n"/>
+      <c r="Z5" s="334" t="n"/>
+      <c r="AA5" s="334" t="n"/>
+      <c r="AB5" s="334" t="n"/>
+      <c r="AC5" s="334" t="n"/>
+      <c r="AD5" s="334" t="n"/>
+      <c r="AE5" s="334" t="n"/>
+      <c r="AF5" s="334" t="n"/>
+      <c r="AG5" s="334" t="n"/>
+      <c r="AH5" s="334" t="n"/>
+      <c r="AI5" s="334" t="n"/>
+      <c r="AJ5" s="334" t="n"/>
+      <c r="AK5" s="334" t="n"/>
+      <c r="AL5" s="334" t="n"/>
+      <c r="AM5" s="334" t="n"/>
+      <c r="AN5" s="334" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6">
+      <c r="A6" s="334">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B6" s="334" t="n"/>
+      <c r="C6" s="334" t="n"/>
+      <c r="D6" s="334" t="n"/>
+      <c r="E6" s="334" t="n"/>
+      <c r="F6" s="334" t="n"/>
+      <c r="G6" s="334" t="n"/>
+      <c r="H6" s="334" t="n"/>
+      <c r="I6" s="334" t="n"/>
+      <c r="J6" s="334" t="n"/>
+      <c r="K6" s="334" t="n"/>
+      <c r="L6" s="334" t="n"/>
+      <c r="M6" s="334" t="n"/>
+      <c r="N6" s="334" t="n"/>
+      <c r="O6" s="334" t="n"/>
+      <c r="P6" s="334" t="n"/>
+      <c r="Q6" s="334" t="n"/>
+      <c r="R6" s="334" t="n"/>
+      <c r="S6" s="334" t="n"/>
+      <c r="T6" s="334" t="n"/>
+      <c r="U6" s="334" t="n"/>
+      <c r="V6" s="334" t="n"/>
+      <c r="W6" s="334" t="n"/>
+      <c r="X6" s="334" t="n"/>
+      <c r="Y6" s="334" t="n"/>
+      <c r="Z6" s="334" t="n"/>
+      <c r="AA6" s="334" t="n"/>
+      <c r="AB6" s="334" t="n"/>
+      <c r="AC6" s="334" t="n"/>
+      <c r="AD6" s="334" t="n"/>
+      <c r="AE6" s="334" t="n"/>
+      <c r="AF6" s="334" t="n"/>
+      <c r="AG6" s="334" t="n"/>
+      <c r="AH6" s="334" t="n"/>
+      <c r="AI6" s="334" t="n"/>
+      <c r="AJ6" s="334" t="n"/>
+      <c r="AK6" s="334" t="n"/>
+      <c r="AL6" s="334" t="n"/>
+      <c r="AM6" s="334" t="n"/>
+      <c r="AN6" s="334" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7">
+      <c r="A7" s="334">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B7" s="334" t="n"/>
+      <c r="C7" s="334" t="n"/>
+      <c r="D7" s="334" t="n"/>
+      <c r="E7" s="334" t="n"/>
+      <c r="F7" s="334" t="n"/>
+      <c r="G7" s="334" t="n"/>
+      <c r="H7" s="334" t="n"/>
+      <c r="I7" s="334" t="n"/>
+      <c r="J7" s="334" t="n"/>
+      <c r="K7" s="334" t="n"/>
+      <c r="L7" s="334" t="n"/>
+      <c r="M7" s="334" t="n"/>
+      <c r="N7" s="334" t="n"/>
+      <c r="O7" s="334" t="n"/>
+      <c r="P7" s="334" t="n"/>
+      <c r="Q7" s="334" t="n"/>
+      <c r="R7" s="334" t="n"/>
+      <c r="S7" s="334" t="n"/>
+      <c r="T7" s="334" t="n"/>
+      <c r="U7" s="334" t="n"/>
+      <c r="V7" s="334" t="n"/>
+      <c r="W7" s="334" t="n"/>
+      <c r="X7" s="334" t="n"/>
+      <c r="Y7" s="334" t="n"/>
+      <c r="Z7" s="334" t="n"/>
+      <c r="AA7" s="334" t="n"/>
+      <c r="AB7" s="334" t="n"/>
+      <c r="AC7" s="334" t="n"/>
+      <c r="AD7" s="334" t="n"/>
+      <c r="AE7" s="334" t="n"/>
+      <c r="AF7" s="334" t="n"/>
+      <c r="AG7" s="334" t="n"/>
+      <c r="AH7" s="334" t="n"/>
+      <c r="AI7" s="334" t="n"/>
+      <c r="AJ7" s="334" t="n"/>
+      <c r="AK7" s="334" t="n"/>
+      <c r="AL7" s="334" t="n"/>
+      <c r="AM7" s="334" t="n"/>
+      <c r="AN7" s="334" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8">
+      <c r="A8" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B8" s="368" t="n"/>
+      <c r="C8" s="368" t="n"/>
+      <c r="D8" s="368" t="n"/>
+      <c r="E8" s="368" t="n"/>
+      <c r="F8" s="368" t="n"/>
+      <c r="G8" s="368" t="n"/>
+      <c r="H8" s="368" t="n"/>
+      <c r="I8" s="368" t="n"/>
+      <c r="J8" s="368" t="n"/>
+      <c r="K8" s="368" t="n"/>
+      <c r="L8" s="368" t="n"/>
+      <c r="M8" s="368" t="n"/>
+      <c r="N8" s="368" t="n"/>
+      <c r="O8" s="368" t="n"/>
+      <c r="P8" s="368" t="n"/>
+      <c r="Q8" s="368" t="n"/>
+      <c r="R8" s="368" t="n"/>
+      <c r="S8" s="368" t="n"/>
+      <c r="T8" s="368" t="n"/>
+      <c r="U8" s="368" t="n"/>
+      <c r="V8" s="368" t="n"/>
+      <c r="W8" s="368" t="n"/>
+      <c r="X8" s="368" t="n"/>
+      <c r="Y8" s="368" t="n"/>
+      <c r="Z8" s="368" t="n"/>
+      <c r="AA8" s="368" t="n"/>
+      <c r="AB8" s="368" t="n"/>
+      <c r="AC8" s="368" t="n"/>
+      <c r="AD8" s="368" t="n"/>
+      <c r="AE8" s="368" t="n"/>
+      <c r="AF8" s="368" t="n"/>
+      <c r="AG8" s="368" t="n"/>
+      <c r="AH8" s="368" t="n"/>
+      <c r="AI8" s="368" t="n"/>
+      <c r="AJ8" s="368" t="n"/>
+      <c r="AK8" s="368" t="n"/>
+      <c r="AL8" s="368" t="n"/>
+      <c r="AM8" s="368" t="n"/>
+      <c r="AN8" s="368" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9">
+      <c r="A9" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B9" s="368" t="n"/>
+      <c r="C9" s="368" t="n"/>
+      <c r="D9" s="368" t="n"/>
+      <c r="E9" s="368" t="n"/>
+      <c r="F9" s="368" t="n"/>
+      <c r="G9" s="368" t="n"/>
+      <c r="H9" s="368" t="n"/>
+      <c r="I9" s="368" t="n"/>
+      <c r="J9" s="368" t="n"/>
+      <c r="K9" s="368" t="n"/>
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="368" t="n"/>
+      <c r="N9" s="368" t="n"/>
+      <c r="O9" s="368" t="n"/>
+      <c r="P9" s="368" t="n"/>
+      <c r="Q9" s="368" t="n"/>
+      <c r="R9" s="368" t="n"/>
+      <c r="S9" s="368" t="n"/>
+      <c r="T9" s="368" t="n"/>
+      <c r="U9" s="368" t="n"/>
+      <c r="V9" s="368" t="n"/>
+      <c r="W9" s="368" t="n"/>
+      <c r="X9" s="368" t="n"/>
+      <c r="Y9" s="368" t="n"/>
+      <c r="Z9" s="368" t="n"/>
+      <c r="AA9" s="368" t="n"/>
+      <c r="AB9" s="368" t="n"/>
+      <c r="AC9" s="368" t="n"/>
+      <c r="AD9" s="368" t="n"/>
+      <c r="AE9" s="368" t="n"/>
+      <c r="AF9" s="368" t="n"/>
+      <c r="AG9" s="368" t="n"/>
+      <c r="AH9" s="368" t="n"/>
+      <c r="AI9" s="368" t="n"/>
+      <c r="AJ9" s="368" t="n"/>
+      <c r="AK9" s="368" t="n"/>
+      <c r="AL9" s="368" t="n"/>
+      <c r="AM9" s="368" t="n"/>
+      <c r="AN9" s="368" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10">
+      <c r="A10" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B10" s="368" t="n"/>
+      <c r="C10" s="368" t="n"/>
+      <c r="D10" s="368" t="n"/>
+      <c r="E10" s="368" t="n"/>
+      <c r="F10" s="368" t="n"/>
+      <c r="G10" s="368" t="n"/>
+      <c r="H10" s="368" t="n"/>
+      <c r="I10" s="368" t="n"/>
+      <c r="J10" s="368" t="n"/>
+      <c r="K10" s="368" t="n"/>
+      <c r="L10" s="368" t="n"/>
+      <c r="M10" s="368" t="n"/>
+      <c r="N10" s="368" t="n"/>
+      <c r="O10" s="368" t="n"/>
+      <c r="P10" s="368" t="n"/>
+      <c r="Q10" s="368" t="n"/>
+      <c r="R10" s="368" t="n"/>
+      <c r="S10" s="368" t="n"/>
+      <c r="T10" s="368" t="n"/>
+      <c r="U10" s="368" t="n"/>
+      <c r="V10" s="368" t="n"/>
+      <c r="W10" s="368" t="n"/>
+      <c r="X10" s="368" t="n"/>
+      <c r="Y10" s="368" t="n"/>
+      <c r="Z10" s="368" t="n"/>
+      <c r="AA10" s="368" t="n"/>
+      <c r="AB10" s="368" t="n"/>
+      <c r="AC10" s="368" t="n"/>
+      <c r="AD10" s="368" t="n"/>
+      <c r="AE10" s="368" t="n"/>
+      <c r="AF10" s="368" t="n"/>
+      <c r="AG10" s="368" t="n"/>
+      <c r="AH10" s="368" t="n"/>
+      <c r="AI10" s="368" t="n"/>
+      <c r="AJ10" s="368" t="n"/>
+      <c r="AK10" s="368" t="n"/>
+      <c r="AL10" s="368" t="n"/>
+      <c r="AM10" s="368" t="n"/>
+      <c r="AN10" s="368" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11">
+      <c r="A11" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B11" s="368" t="n"/>
+      <c r="C11" s="368" t="n"/>
+      <c r="D11" s="368" t="n"/>
+      <c r="E11" s="368" t="n"/>
+      <c r="F11" s="368" t="n"/>
+      <c r="G11" s="368" t="n"/>
+      <c r="H11" s="368" t="n"/>
+      <c r="I11" s="368" t="n"/>
+      <c r="J11" s="368" t="n"/>
+      <c r="K11" s="368" t="n"/>
+      <c r="L11" s="368" t="n"/>
+      <c r="M11" s="368" t="n"/>
+      <c r="N11" s="368" t="n"/>
+      <c r="O11" s="368" t="n"/>
+      <c r="P11" s="368" t="n"/>
+      <c r="Q11" s="368" t="n"/>
+      <c r="R11" s="368" t="n"/>
+      <c r="S11" s="368" t="n"/>
+      <c r="T11" s="368" t="n"/>
+      <c r="U11" s="368" t="n"/>
+      <c r="V11" s="368" t="n"/>
+      <c r="W11" s="368" t="n"/>
+      <c r="X11" s="368" t="n"/>
+      <c r="Y11" s="368" t="n"/>
+      <c r="Z11" s="368" t="n"/>
+      <c r="AA11" s="368" t="n"/>
+      <c r="AB11" s="368" t="n"/>
+      <c r="AC11" s="368" t="n"/>
+      <c r="AD11" s="368" t="n"/>
+      <c r="AE11" s="368" t="n"/>
+      <c r="AF11" s="368" t="n"/>
+      <c r="AG11" s="368" t="n"/>
+      <c r="AH11" s="368" t="n"/>
+      <c r="AI11" s="368" t="n"/>
+      <c r="AJ11" s="368" t="n"/>
+      <c r="AK11" s="368" t="n"/>
+      <c r="AL11" s="368" t="n"/>
+      <c r="AM11" s="368" t="n"/>
+      <c r="AN11" s="368" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12">
+      <c r="A12" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B12" s="368" t="n"/>
+      <c r="C12" s="368" t="n"/>
+      <c r="D12" s="368" t="n"/>
+      <c r="E12" s="368" t="n"/>
+      <c r="F12" s="368" t="n"/>
+      <c r="G12" s="368" t="n"/>
+      <c r="H12" s="368" t="n"/>
+      <c r="I12" s="368" t="n"/>
+      <c r="J12" s="368" t="n"/>
+      <c r="K12" s="368" t="n"/>
+      <c r="L12" s="368" t="n"/>
+      <c r="M12" s="368" t="n"/>
+      <c r="N12" s="368" t="n"/>
+      <c r="O12" s="368" t="n"/>
+      <c r="P12" s="368" t="n"/>
+      <c r="Q12" s="368" t="n"/>
+      <c r="R12" s="368" t="n"/>
+      <c r="S12" s="368" t="n"/>
+      <c r="T12" s="368" t="n"/>
+      <c r="U12" s="368" t="n"/>
+      <c r="V12" s="368" t="n"/>
+      <c r="W12" s="368" t="n"/>
+      <c r="X12" s="368" t="n"/>
+      <c r="Y12" s="368" t="n"/>
+      <c r="Z12" s="368" t="n"/>
+      <c r="AA12" s="368" t="n"/>
+      <c r="AB12" s="368" t="n"/>
+      <c r="AC12" s="368" t="n"/>
+      <c r="AD12" s="368" t="n"/>
+      <c r="AE12" s="368" t="n"/>
+      <c r="AF12" s="368" t="n"/>
+      <c r="AG12" s="368" t="n"/>
+      <c r="AH12" s="368" t="n"/>
+      <c r="AI12" s="368" t="n"/>
+      <c r="AJ12" s="368" t="n"/>
+      <c r="AK12" s="368" t="n"/>
+      <c r="AL12" s="368" t="n"/>
+      <c r="AM12" s="368" t="n"/>
+      <c r="AN12" s="368" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13">
+      <c r="A13" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B13" s="368" t="n"/>
+      <c r="C13" s="368" t="n"/>
+      <c r="D13" s="368" t="n"/>
+      <c r="E13" s="368" t="n"/>
+      <c r="F13" s="368" t="n"/>
+      <c r="G13" s="368" t="n"/>
+      <c r="H13" s="368" t="n"/>
+      <c r="I13" s="368" t="n"/>
+      <c r="J13" s="368" t="n"/>
+      <c r="K13" s="368" t="n"/>
+      <c r="L13" s="368" t="n"/>
+      <c r="M13" s="368" t="n"/>
+      <c r="N13" s="368" t="n"/>
+      <c r="O13" s="368" t="n"/>
+      <c r="P13" s="368" t="n"/>
+      <c r="Q13" s="368" t="n"/>
+      <c r="R13" s="368" t="n"/>
+      <c r="S13" s="368" t="n"/>
+      <c r="T13" s="368" t="n"/>
+      <c r="U13" s="368" t="n"/>
+      <c r="V13" s="368" t="n"/>
+      <c r="W13" s="368" t="n"/>
+      <c r="X13" s="368" t="n"/>
+      <c r="Y13" s="368" t="n"/>
+      <c r="Z13" s="368" t="n"/>
+      <c r="AA13" s="368" t="n"/>
+      <c r="AB13" s="368" t="n"/>
+      <c r="AC13" s="368" t="n"/>
+      <c r="AD13" s="368" t="n"/>
+      <c r="AE13" s="368" t="n"/>
+      <c r="AF13" s="368" t="n"/>
+      <c r="AG13" s="368" t="n"/>
+      <c r="AH13" s="368" t="n"/>
+      <c r="AI13" s="368" t="n"/>
+      <c r="AJ13" s="368" t="n"/>
+      <c r="AK13" s="368" t="n"/>
+      <c r="AL13" s="368" t="n"/>
+      <c r="AM13" s="368" t="n"/>
+      <c r="AN13" s="368" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14">
+      <c r="A14" s="368">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
+      <c r="B14" s="368" t="n"/>
+      <c r="C14" s="368" t="n"/>
+      <c r="D14" s="368" t="n"/>
+      <c r="E14" s="368" t="n"/>
+      <c r="F14" s="368" t="n"/>
+      <c r="G14" s="368" t="n"/>
+      <c r="H14" s="368" t="n"/>
+      <c r="I14" s="368" t="n"/>
+      <c r="J14" s="368" t="n"/>
+      <c r="K14" s="368" t="n"/>
+      <c r="L14" s="368" t="n"/>
+      <c r="M14" s="368" t="n"/>
+      <c r="N14" s="368" t="n"/>
+      <c r="O14" s="368" t="n"/>
+      <c r="P14" s="368" t="n"/>
+      <c r="Q14" s="368" t="n"/>
+      <c r="R14" s="368" t="n"/>
+      <c r="S14" s="368" t="n"/>
+      <c r="T14" s="368" t="n"/>
+      <c r="U14" s="368" t="n"/>
+      <c r="V14" s="368" t="n"/>
+      <c r="W14" s="368" t="n"/>
+      <c r="X14" s="368" t="n"/>
+      <c r="Y14" s="368" t="n"/>
+      <c r="Z14" s="368" t="n"/>
+      <c r="AA14" s="368" t="n"/>
+      <c r="AB14" s="368" t="n"/>
+      <c r="AC14" s="368" t="n"/>
+      <c r="AD14" s="368" t="n"/>
+      <c r="AE14" s="368" t="n"/>
+      <c r="AF14" s="368" t="n"/>
+      <c r="AG14" s="368" t="n"/>
+      <c r="AH14" s="368" t="n"/>
+      <c r="AI14" s="368" t="n"/>
+      <c r="AJ14" s="368" t="n"/>
+      <c r="AK14" s="368" t="n"/>
+      <c r="AL14" s="368" t="n"/>
+      <c r="AM14" s="368" t="n"/>
+      <c r="AN14" s="368" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1"/>
     <row r="16" ht="20" customHeight="1"/>
@@ -7791,7 +10370,8 @@
       <formula1>=LISTS!$C$2:$C$11</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7804,12 +10384,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -7818,6 +10435,45 @@
           <t>Source / Boundary Guidance</t>
         </is>
       </c>
+      <c r="B1" s="334" t="n"/>
+      <c r="C1" s="334" t="n"/>
+      <c r="D1" s="334" t="n"/>
+      <c r="E1" s="334" t="n"/>
+      <c r="F1" s="334" t="n"/>
+      <c r="G1" s="334" t="n"/>
+      <c r="H1" s="334" t="n"/>
+      <c r="I1" s="334" t="n"/>
+      <c r="J1" s="334" t="n"/>
+      <c r="K1" s="334" t="n"/>
+      <c r="L1" s="334" t="n"/>
+      <c r="M1" s="334" t="n"/>
+      <c r="N1" s="334" t="n"/>
+      <c r="O1" s="334" t="n"/>
+      <c r="P1" s="334" t="n"/>
+      <c r="Q1" s="334" t="n"/>
+      <c r="R1" s="334" t="n"/>
+      <c r="S1" s="334" t="n"/>
+      <c r="T1" s="334" t="n"/>
+      <c r="U1" s="334" t="n"/>
+      <c r="V1" s="334" t="n"/>
+      <c r="W1" s="334" t="n"/>
+      <c r="X1" s="334" t="n"/>
+      <c r="Y1" s="334" t="n"/>
+      <c r="Z1" s="334" t="n"/>
+      <c r="AA1" s="334" t="n"/>
+      <c r="AB1" s="334" t="n"/>
+      <c r="AC1" s="334" t="n"/>
+      <c r="AD1" s="334" t="n"/>
+      <c r="AE1" s="334" t="n"/>
+      <c r="AF1" s="334" t="n"/>
+      <c r="AG1" s="334" t="n"/>
+      <c r="AH1" s="334" t="n"/>
+      <c r="AI1" s="334" t="n"/>
+      <c r="AJ1" s="334" t="n"/>
+      <c r="AK1" s="334" t="n"/>
+      <c r="AL1" s="334" t="n"/>
+      <c r="AM1" s="334" t="n"/>
+      <c r="AN1" s="334" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="324" t="inlineStr">
@@ -7825,49 +10481,203 @@
           <t>Controlled WIP tag print object. Keep printed face limited to approved identity and status only.</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
+      <c r="B2" s="334" t="n"/>
+      <c r="C2" s="334" t="n"/>
+      <c r="D2" s="334" t="n"/>
+      <c r="E2" s="334" t="n"/>
+      <c r="F2" s="334" t="n"/>
+      <c r="G2" s="334" t="n"/>
+      <c r="H2" s="334" t="n"/>
+      <c r="I2" s="334" t="n"/>
+      <c r="J2" s="334" t="n"/>
+      <c r="K2" s="334" t="n"/>
+      <c r="L2" s="334" t="n"/>
+      <c r="M2" s="334" t="n"/>
+      <c r="N2" s="334" t="n"/>
+      <c r="O2" s="334" t="n"/>
+      <c r="P2" s="334" t="n"/>
+      <c r="Q2" s="334" t="n"/>
+      <c r="R2" s="334" t="n"/>
+      <c r="S2" s="334" t="n"/>
+      <c r="T2" s="334" t="n"/>
+      <c r="U2" s="334" t="n"/>
+      <c r="V2" s="334" t="n"/>
+      <c r="W2" s="334" t="n"/>
+      <c r="X2" s="334" t="n"/>
+      <c r="Y2" s="334" t="n"/>
+      <c r="Z2" s="334" t="n"/>
+      <c r="AA2" s="334" t="n"/>
+      <c r="AB2" s="334" t="n"/>
+      <c r="AC2" s="334" t="n"/>
+      <c r="AD2" s="334" t="n"/>
+      <c r="AE2" s="334" t="n"/>
+      <c r="AF2" s="334" t="n"/>
+      <c r="AG2" s="334" t="n"/>
+      <c r="AH2" s="334" t="n"/>
+      <c r="AI2" s="334" t="n"/>
+      <c r="AJ2" s="334" t="n"/>
+      <c r="AK2" s="334" t="n"/>
+      <c r="AL2" s="334" t="n"/>
+      <c r="AM2" s="334" t="n"/>
+      <c r="AN2" s="334" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="334" t="n"/>
+      <c r="B3" s="334" t="n"/>
+      <c r="C3" s="334" t="n"/>
+      <c r="D3" s="334" t="n"/>
+      <c r="E3" s="334" t="n"/>
+      <c r="F3" s="334" t="n"/>
+      <c r="G3" s="334" t="n"/>
+      <c r="H3" s="334" t="n"/>
+      <c r="I3" s="334" t="n"/>
+      <c r="J3" s="334" t="n"/>
+      <c r="K3" s="334" t="n"/>
+      <c r="L3" s="334" t="n"/>
+      <c r="M3" s="334" t="n"/>
+      <c r="N3" s="334" t="n"/>
+      <c r="O3" s="334" t="n"/>
+      <c r="P3" s="334" t="n"/>
+      <c r="Q3" s="334" t="n"/>
+      <c r="R3" s="334" t="n"/>
+      <c r="S3" s="334" t="n"/>
+      <c r="T3" s="334" t="n"/>
+      <c r="U3" s="334" t="n"/>
+      <c r="V3" s="334" t="n"/>
+      <c r="W3" s="334" t="n"/>
+      <c r="X3" s="334" t="n"/>
+      <c r="Y3" s="334" t="n"/>
+      <c r="Z3" s="334" t="n"/>
+      <c r="AA3" s="334" t="n"/>
+      <c r="AB3" s="334" t="n"/>
+      <c r="AC3" s="334" t="n"/>
+      <c r="AD3" s="334" t="n"/>
+      <c r="AE3" s="334" t="n"/>
+      <c r="AF3" s="334" t="n"/>
+      <c r="AG3" s="334" t="n"/>
+      <c r="AH3" s="334" t="n"/>
+      <c r="AI3" s="334" t="n"/>
+      <c r="AJ3" s="334" t="n"/>
+      <c r="AK3" s="334" t="n"/>
+      <c r="AL3" s="334" t="n"/>
+      <c r="AM3" s="334" t="n"/>
+      <c r="AN3" s="334" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="325" t="inlineStr">
+      <c r="A4" s="372" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="325" t="inlineStr">
+      <c r="B4" s="372" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="325" t="inlineStr">
+      <c r="C4" s="372" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="334" t="n"/>
+      <c r="E4" s="334" t="n"/>
+      <c r="F4" s="334" t="n"/>
+      <c r="G4" s="334" t="n"/>
+      <c r="H4" s="334" t="n"/>
+      <c r="I4" s="334" t="n"/>
+      <c r="J4" s="334" t="n"/>
+      <c r="K4" s="334" t="n"/>
+      <c r="L4" s="334" t="n"/>
+      <c r="M4" s="334" t="n"/>
+      <c r="N4" s="334" t="n"/>
+      <c r="O4" s="334" t="n"/>
+      <c r="P4" s="334" t="n"/>
+      <c r="Q4" s="334" t="n"/>
+      <c r="R4" s="334" t="n"/>
+      <c r="S4" s="334" t="n"/>
+      <c r="T4" s="334" t="n"/>
+      <c r="U4" s="334" t="n"/>
+      <c r="V4" s="334" t="n"/>
+      <c r="W4" s="334" t="n"/>
+      <c r="X4" s="334" t="n"/>
+      <c r="Y4" s="334" t="n"/>
+      <c r="Z4" s="334" t="n"/>
+      <c r="AA4" s="334" t="n"/>
+      <c r="AB4" s="334" t="n"/>
+      <c r="AC4" s="334" t="n"/>
+      <c r="AD4" s="334" t="n"/>
+      <c r="AE4" s="334" t="n"/>
+      <c r="AF4" s="334" t="n"/>
+      <c r="AG4" s="334" t="n"/>
+      <c r="AH4" s="334" t="n"/>
+      <c r="AI4" s="334" t="n"/>
+      <c r="AJ4" s="334" t="n"/>
+      <c r="AK4" s="334" t="n"/>
+      <c r="AL4" s="334" t="n"/>
+      <c r="AM4" s="334" t="n"/>
+      <c r="AN4" s="334" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="334" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="334" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="334" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="334" t="n"/>
+      <c r="E5" s="334" t="n"/>
+      <c r="F5" s="334" t="n"/>
+      <c r="G5" s="334" t="n"/>
+      <c r="H5" s="334" t="n"/>
+      <c r="I5" s="334" t="n"/>
+      <c r="J5" s="334" t="n"/>
+      <c r="K5" s="334" t="n"/>
+      <c r="L5" s="334" t="n"/>
+      <c r="M5" s="334" t="n"/>
+      <c r="N5" s="334" t="n"/>
+      <c r="O5" s="334" t="n"/>
+      <c r="P5" s="334" t="n"/>
+      <c r="Q5" s="334" t="n"/>
+      <c r="R5" s="334" t="n"/>
+      <c r="S5" s="334" t="n"/>
+      <c r="T5" s="334" t="n"/>
+      <c r="U5" s="334" t="n"/>
+      <c r="V5" s="334" t="n"/>
+      <c r="W5" s="334" t="n"/>
+      <c r="X5" s="334" t="n"/>
+      <c r="Y5" s="334" t="n"/>
+      <c r="Z5" s="334" t="n"/>
+      <c r="AA5" s="334" t="n"/>
+      <c r="AB5" s="334" t="n"/>
+      <c r="AC5" s="334" t="n"/>
+      <c r="AD5" s="334" t="n"/>
+      <c r="AE5" s="334" t="n"/>
+      <c r="AF5" s="334" t="n"/>
+      <c r="AG5" s="334" t="n"/>
+      <c r="AH5" s="334" t="n"/>
+      <c r="AI5" s="334" t="n"/>
+      <c r="AJ5" s="334" t="n"/>
+      <c r="AK5" s="334" t="n"/>
+      <c r="AL5" s="334" t="n"/>
+      <c r="AM5" s="334" t="n"/>
+      <c r="AN5" s="334" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="334" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="334" t="inlineStr">
         <is>
           <t>This form does not replace SOP-701; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-702; this form captures results, checks, decisions or exceptions only.
@@ -7875,7 +10685,7 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="334" t="inlineStr">
         <is>
           <t>This form does not replace SOP-701; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-702; this form captures results, checks, decisions or exceptions only.
@@ -7883,159 +10693,529 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="334" t="n"/>
+      <c r="E6" s="334" t="n"/>
+      <c r="F6" s="334" t="n"/>
+      <c r="G6" s="334" t="n"/>
+      <c r="H6" s="334" t="n"/>
+      <c r="I6" s="334" t="n"/>
+      <c r="J6" s="334" t="n"/>
+      <c r="K6" s="334" t="n"/>
+      <c r="L6" s="334" t="n"/>
+      <c r="M6" s="334" t="n"/>
+      <c r="N6" s="334" t="n"/>
+      <c r="O6" s="334" t="n"/>
+      <c r="P6" s="334" t="n"/>
+      <c r="Q6" s="334" t="n"/>
+      <c r="R6" s="334" t="n"/>
+      <c r="S6" s="334" t="n"/>
+      <c r="T6" s="334" t="n"/>
+      <c r="U6" s="334" t="n"/>
+      <c r="V6" s="334" t="n"/>
+      <c r="W6" s="334" t="n"/>
+      <c r="X6" s="334" t="n"/>
+      <c r="Y6" s="334" t="n"/>
+      <c r="Z6" s="334" t="n"/>
+      <c r="AA6" s="334" t="n"/>
+      <c r="AB6" s="334" t="n"/>
+      <c r="AC6" s="334" t="n"/>
+      <c r="AD6" s="334" t="n"/>
+      <c r="AE6" s="334" t="n"/>
+      <c r="AF6" s="334" t="n"/>
+      <c r="AG6" s="334" t="n"/>
+      <c r="AH6" s="334" t="n"/>
+      <c r="AI6" s="334" t="n"/>
+      <c r="AJ6" s="334" t="n"/>
+      <c r="AK6" s="334" t="n"/>
+      <c r="AL6" s="334" t="n"/>
+      <c r="AM6" s="334" t="n"/>
+      <c r="AN6" s="334" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="334" t="inlineStr">
         <is>
           <t>SOP-701</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="334" t="inlineStr">
         <is>
           <t>SOP-701 — Tiếp nhận, kho, đóng gói, thao tác và bảo quản | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="334" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-701-receiving-packaging-handling-and-storage.html</t>
         </is>
       </c>
+      <c r="D7" s="334" t="n"/>
+      <c r="E7" s="334" t="n"/>
+      <c r="F7" s="334" t="n"/>
+      <c r="G7" s="334" t="n"/>
+      <c r="H7" s="334" t="n"/>
+      <c r="I7" s="334" t="n"/>
+      <c r="J7" s="334" t="n"/>
+      <c r="K7" s="334" t="n"/>
+      <c r="L7" s="334" t="n"/>
+      <c r="M7" s="334" t="n"/>
+      <c r="N7" s="334" t="n"/>
+      <c r="O7" s="334" t="n"/>
+      <c r="P7" s="334" t="n"/>
+      <c r="Q7" s="334" t="n"/>
+      <c r="R7" s="334" t="n"/>
+      <c r="S7" s="334" t="n"/>
+      <c r="T7" s="334" t="n"/>
+      <c r="U7" s="334" t="n"/>
+      <c r="V7" s="334" t="n"/>
+      <c r="W7" s="334" t="n"/>
+      <c r="X7" s="334" t="n"/>
+      <c r="Y7" s="334" t="n"/>
+      <c r="Z7" s="334" t="n"/>
+      <c r="AA7" s="334" t="n"/>
+      <c r="AB7" s="334" t="n"/>
+      <c r="AC7" s="334" t="n"/>
+      <c r="AD7" s="334" t="n"/>
+      <c r="AE7" s="334" t="n"/>
+      <c r="AF7" s="334" t="n"/>
+      <c r="AG7" s="334" t="n"/>
+      <c r="AH7" s="334" t="n"/>
+      <c r="AI7" s="334" t="n"/>
+      <c r="AJ7" s="334" t="n"/>
+      <c r="AK7" s="334" t="n"/>
+      <c r="AL7" s="334" t="n"/>
+      <c r="AM7" s="334" t="n"/>
+      <c r="AN7" s="334" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="368" t="inlineStr">
         <is>
           <t>WI-702</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="368" t="inlineStr">
         <is>
           <t>WI-702 — Bảo quản, môi trường kho/xưởng, vị trí, FIFO/FEFO và kiểm soát chạm hỏng</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-702-storage-environment-location-and-fifo-control.html</t>
         </is>
       </c>
+      <c r="D8" s="368" t="n"/>
+      <c r="E8" s="368" t="n"/>
+      <c r="F8" s="368" t="n"/>
+      <c r="G8" s="368" t="n"/>
+      <c r="H8" s="368" t="n"/>
+      <c r="I8" s="368" t="n"/>
+      <c r="J8" s="368" t="n"/>
+      <c r="K8" s="368" t="n"/>
+      <c r="L8" s="368" t="n"/>
+      <c r="M8" s="368" t="n"/>
+      <c r="N8" s="368" t="n"/>
+      <c r="O8" s="368" t="n"/>
+      <c r="P8" s="368" t="n"/>
+      <c r="Q8" s="368" t="n"/>
+      <c r="R8" s="368" t="n"/>
+      <c r="S8" s="368" t="n"/>
+      <c r="T8" s="368" t="n"/>
+      <c r="U8" s="368" t="n"/>
+      <c r="V8" s="368" t="n"/>
+      <c r="W8" s="368" t="n"/>
+      <c r="X8" s="368" t="n"/>
+      <c r="Y8" s="368" t="n"/>
+      <c r="Z8" s="368" t="n"/>
+      <c r="AA8" s="368" t="n"/>
+      <c r="AB8" s="368" t="n"/>
+      <c r="AC8" s="368" t="n"/>
+      <c r="AD8" s="368" t="n"/>
+      <c r="AE8" s="368" t="n"/>
+      <c r="AF8" s="368" t="n"/>
+      <c r="AG8" s="368" t="n"/>
+      <c r="AH8" s="368" t="n"/>
+      <c r="AI8" s="368" t="n"/>
+      <c r="AJ8" s="368" t="n"/>
+      <c r="AK8" s="368" t="n"/>
+      <c r="AL8" s="368" t="n"/>
+      <c r="AM8" s="368" t="n"/>
+      <c r="AN8" s="368" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="368" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="368" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
         </is>
       </c>
+      <c r="D9" s="368" t="n"/>
+      <c r="E9" s="368" t="n"/>
+      <c r="F9" s="368" t="n"/>
+      <c r="G9" s="368" t="n"/>
+      <c r="H9" s="368" t="n"/>
+      <c r="I9" s="368" t="n"/>
+      <c r="J9" s="368" t="n"/>
+      <c r="K9" s="368" t="n"/>
+      <c r="L9" s="368" t="n"/>
+      <c r="M9" s="368" t="n"/>
+      <c r="N9" s="368" t="n"/>
+      <c r="O9" s="368" t="n"/>
+      <c r="P9" s="368" t="n"/>
+      <c r="Q9" s="368" t="n"/>
+      <c r="R9" s="368" t="n"/>
+      <c r="S9" s="368" t="n"/>
+      <c r="T9" s="368" t="n"/>
+      <c r="U9" s="368" t="n"/>
+      <c r="V9" s="368" t="n"/>
+      <c r="W9" s="368" t="n"/>
+      <c r="X9" s="368" t="n"/>
+      <c r="Y9" s="368" t="n"/>
+      <c r="Z9" s="368" t="n"/>
+      <c r="AA9" s="368" t="n"/>
+      <c r="AB9" s="368" t="n"/>
+      <c r="AC9" s="368" t="n"/>
+      <c r="AD9" s="368" t="n"/>
+      <c r="AE9" s="368" t="n"/>
+      <c r="AF9" s="368" t="n"/>
+      <c r="AG9" s="368" t="n"/>
+      <c r="AH9" s="368" t="n"/>
+      <c r="AI9" s="368" t="n"/>
+      <c r="AJ9" s="368" t="n"/>
+      <c r="AK9" s="368" t="n"/>
+      <c r="AL9" s="368" t="n"/>
+      <c r="AM9" s="368" t="n"/>
+      <c r="AN9" s="368" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="368" t="inlineStr">
         <is>
           <t>ANNEX-WHS-002</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="368" t="inlineStr">
         <is>
           <t>ANNEX-WHS-002 — Quy tắc vị trí kho, zoning, FIFO/FEFO, staging và cycle count</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-002-warehouse-location-fifo-rules.html</t>
         </is>
       </c>
+      <c r="D10" s="368" t="n"/>
+      <c r="E10" s="368" t="n"/>
+      <c r="F10" s="368" t="n"/>
+      <c r="G10" s="368" t="n"/>
+      <c r="H10" s="368" t="n"/>
+      <c r="I10" s="368" t="n"/>
+      <c r="J10" s="368" t="n"/>
+      <c r="K10" s="368" t="n"/>
+      <c r="L10" s="368" t="n"/>
+      <c r="M10" s="368" t="n"/>
+      <c r="N10" s="368" t="n"/>
+      <c r="O10" s="368" t="n"/>
+      <c r="P10" s="368" t="n"/>
+      <c r="Q10" s="368" t="n"/>
+      <c r="R10" s="368" t="n"/>
+      <c r="S10" s="368" t="n"/>
+      <c r="T10" s="368" t="n"/>
+      <c r="U10" s="368" t="n"/>
+      <c r="V10" s="368" t="n"/>
+      <c r="W10" s="368" t="n"/>
+      <c r="X10" s="368" t="n"/>
+      <c r="Y10" s="368" t="n"/>
+      <c r="Z10" s="368" t="n"/>
+      <c r="AA10" s="368" t="n"/>
+      <c r="AB10" s="368" t="n"/>
+      <c r="AC10" s="368" t="n"/>
+      <c r="AD10" s="368" t="n"/>
+      <c r="AE10" s="368" t="n"/>
+      <c r="AF10" s="368" t="n"/>
+      <c r="AG10" s="368" t="n"/>
+      <c r="AH10" s="368" t="n"/>
+      <c r="AI10" s="368" t="n"/>
+      <c r="AJ10" s="368" t="n"/>
+      <c r="AK10" s="368" t="n"/>
+      <c r="AL10" s="368" t="n"/>
+      <c r="AM10" s="368" t="n"/>
+      <c r="AN10" s="368" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-007</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-007 — Từ điển dữ liệu GS1/SSCC, quy tắc cấp mã và đối soát kiện hàng</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-007-gs1-sscc-data-dictionary-and-pack-reconciliation.html</t>
         </is>
       </c>
+      <c r="D11" s="368" t="n"/>
+      <c r="E11" s="368" t="n"/>
+      <c r="F11" s="368" t="n"/>
+      <c r="G11" s="368" t="n"/>
+      <c r="H11" s="368" t="n"/>
+      <c r="I11" s="368" t="n"/>
+      <c r="J11" s="368" t="n"/>
+      <c r="K11" s="368" t="n"/>
+      <c r="L11" s="368" t="n"/>
+      <c r="M11" s="368" t="n"/>
+      <c r="N11" s="368" t="n"/>
+      <c r="O11" s="368" t="n"/>
+      <c r="P11" s="368" t="n"/>
+      <c r="Q11" s="368" t="n"/>
+      <c r="R11" s="368" t="n"/>
+      <c r="S11" s="368" t="n"/>
+      <c r="T11" s="368" t="n"/>
+      <c r="U11" s="368" t="n"/>
+      <c r="V11" s="368" t="n"/>
+      <c r="W11" s="368" t="n"/>
+      <c r="X11" s="368" t="n"/>
+      <c r="Y11" s="368" t="n"/>
+      <c r="Z11" s="368" t="n"/>
+      <c r="AA11" s="368" t="n"/>
+      <c r="AB11" s="368" t="n"/>
+      <c r="AC11" s="368" t="n"/>
+      <c r="AD11" s="368" t="n"/>
+      <c r="AE11" s="368" t="n"/>
+      <c r="AF11" s="368" t="n"/>
+      <c r="AG11" s="368" t="n"/>
+      <c r="AH11" s="368" t="n"/>
+      <c r="AI11" s="368" t="n"/>
+      <c r="AJ11" s="368" t="n"/>
+      <c r="AK11" s="368" t="n"/>
+      <c r="AL11" s="368" t="n"/>
+      <c r="AM11" s="368" t="n"/>
+      <c r="AN11" s="368" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-014</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-014 — Chỉ mục put-thru / pass-through / tuyến đặc biệt và yêu cầu hồ sơ đi kèm</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-014-put-thru-index.html</t>
         </is>
       </c>
+      <c r="D12" s="368" t="n"/>
+      <c r="E12" s="368" t="n"/>
+      <c r="F12" s="368" t="n"/>
+      <c r="G12" s="368" t="n"/>
+      <c r="H12" s="368" t="n"/>
+      <c r="I12" s="368" t="n"/>
+      <c r="J12" s="368" t="n"/>
+      <c r="K12" s="368" t="n"/>
+      <c r="L12" s="368" t="n"/>
+      <c r="M12" s="368" t="n"/>
+      <c r="N12" s="368" t="n"/>
+      <c r="O12" s="368" t="n"/>
+      <c r="P12" s="368" t="n"/>
+      <c r="Q12" s="368" t="n"/>
+      <c r="R12" s="368" t="n"/>
+      <c r="S12" s="368" t="n"/>
+      <c r="T12" s="368" t="n"/>
+      <c r="U12" s="368" t="n"/>
+      <c r="V12" s="368" t="n"/>
+      <c r="W12" s="368" t="n"/>
+      <c r="X12" s="368" t="n"/>
+      <c r="Y12" s="368" t="n"/>
+      <c r="Z12" s="368" t="n"/>
+      <c r="AA12" s="368" t="n"/>
+      <c r="AB12" s="368" t="n"/>
+      <c r="AC12" s="368" t="n"/>
+      <c r="AD12" s="368" t="n"/>
+      <c r="AE12" s="368" t="n"/>
+      <c r="AF12" s="368" t="n"/>
+      <c r="AG12" s="368" t="n"/>
+      <c r="AH12" s="368" t="n"/>
+      <c r="AI12" s="368" t="n"/>
+      <c r="AJ12" s="368" t="n"/>
+      <c r="AK12" s="368" t="n"/>
+      <c r="AL12" s="368" t="n"/>
+      <c r="AM12" s="368" t="n"/>
+      <c r="AN12" s="368" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-017</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="368" t="inlineStr">
         <is>
           <t>ANNEX-QMS-017 — Chương trình phòng ngừa FOD</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="368" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-017-fod-prevention-program.html</t>
         </is>
       </c>
+      <c r="D13" s="368" t="n"/>
+      <c r="E13" s="368" t="n"/>
+      <c r="F13" s="368" t="n"/>
+      <c r="G13" s="368" t="n"/>
+      <c r="H13" s="368" t="n"/>
+      <c r="I13" s="368" t="n"/>
+      <c r="J13" s="368" t="n"/>
+      <c r="K13" s="368" t="n"/>
+      <c r="L13" s="368" t="n"/>
+      <c r="M13" s="368" t="n"/>
+      <c r="N13" s="368" t="n"/>
+      <c r="O13" s="368" t="n"/>
+      <c r="P13" s="368" t="n"/>
+      <c r="Q13" s="368" t="n"/>
+      <c r="R13" s="368" t="n"/>
+      <c r="S13" s="368" t="n"/>
+      <c r="T13" s="368" t="n"/>
+      <c r="U13" s="368" t="n"/>
+      <c r="V13" s="368" t="n"/>
+      <c r="W13" s="368" t="n"/>
+      <c r="X13" s="368" t="n"/>
+      <c r="Y13" s="368" t="n"/>
+      <c r="Z13" s="368" t="n"/>
+      <c r="AA13" s="368" t="n"/>
+      <c r="AB13" s="368" t="n"/>
+      <c r="AC13" s="368" t="n"/>
+      <c r="AD13" s="368" t="n"/>
+      <c r="AE13" s="368" t="n"/>
+      <c r="AF13" s="368" t="n"/>
+      <c r="AG13" s="368" t="n"/>
+      <c r="AH13" s="368" t="n"/>
+      <c r="AI13" s="368" t="n"/>
+      <c r="AJ13" s="368" t="n"/>
+      <c r="AK13" s="368" t="n"/>
+      <c r="AL13" s="368" t="n"/>
+      <c r="AM13" s="368" t="n"/>
+      <c r="AN13" s="368" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="368" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="368" t="inlineStr">
         <is>
           <t>Open only from the approved print trigger or parent release transaction; do not open ad hoc for uncontrolled printing.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="368" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D14" s="368" t="n"/>
+      <c r="E14" s="368" t="n"/>
+      <c r="F14" s="368" t="n"/>
+      <c r="G14" s="368" t="n"/>
+      <c r="H14" s="368" t="n"/>
+      <c r="I14" s="368" t="n"/>
+      <c r="J14" s="368" t="n"/>
+      <c r="K14" s="368" t="n"/>
+      <c r="L14" s="368" t="n"/>
+      <c r="M14" s="368" t="n"/>
+      <c r="N14" s="368" t="n"/>
+      <c r="O14" s="368" t="n"/>
+      <c r="P14" s="368" t="n"/>
+      <c r="Q14" s="368" t="n"/>
+      <c r="R14" s="368" t="n"/>
+      <c r="S14" s="368" t="n"/>
+      <c r="T14" s="368" t="n"/>
+      <c r="U14" s="368" t="n"/>
+      <c r="V14" s="368" t="n"/>
+      <c r="W14" s="368" t="n"/>
+      <c r="X14" s="368" t="n"/>
+      <c r="Y14" s="368" t="n"/>
+      <c r="Z14" s="368" t="n"/>
+      <c r="AA14" s="368" t="n"/>
+      <c r="AB14" s="368" t="n"/>
+      <c r="AC14" s="368" t="n"/>
+      <c r="AD14" s="368" t="n"/>
+      <c r="AE14" s="368" t="n"/>
+      <c r="AF14" s="368" t="n"/>
+      <c r="AG14" s="368" t="n"/>
+      <c r="AH14" s="368" t="n"/>
+      <c r="AI14" s="368" t="n"/>
+      <c r="AJ14" s="368" t="n"/>
+      <c r="AK14" s="368" t="n"/>
+      <c r="AL14" s="368" t="n"/>
+      <c r="AM14" s="368" t="n"/>
+      <c r="AN14" s="368" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="368" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="368" t="inlineStr">
         <is>
           <t>Close after the label / card is printed, verified, applied or voided, with reprint and scrap events controlled.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="368" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D15" s="368" t="n"/>
+      <c r="E15" s="368" t="n"/>
+      <c r="F15" s="368" t="n"/>
+      <c r="G15" s="368" t="n"/>
+      <c r="H15" s="368" t="n"/>
+      <c r="I15" s="368" t="n"/>
+      <c r="J15" s="368" t="n"/>
+      <c r="K15" s="368" t="n"/>
+      <c r="L15" s="368" t="n"/>
+      <c r="M15" s="368" t="n"/>
+      <c r="N15" s="368" t="n"/>
+      <c r="O15" s="368" t="n"/>
+      <c r="P15" s="368" t="n"/>
+      <c r="Q15" s="368" t="n"/>
+      <c r="R15" s="368" t="n"/>
+      <c r="S15" s="368" t="n"/>
+      <c r="T15" s="368" t="n"/>
+      <c r="U15" s="368" t="n"/>
+      <c r="V15" s="368" t="n"/>
+      <c r="W15" s="368" t="n"/>
+      <c r="X15" s="368" t="n"/>
+      <c r="Y15" s="368" t="n"/>
+      <c r="Z15" s="368" t="n"/>
+      <c r="AA15" s="368" t="n"/>
+      <c r="AB15" s="368" t="n"/>
+      <c r="AC15" s="368" t="n"/>
+      <c r="AD15" s="368" t="n"/>
+      <c r="AE15" s="368" t="n"/>
+      <c r="AF15" s="368" t="n"/>
+      <c r="AG15" s="368" t="n"/>
+      <c r="AH15" s="368" t="n"/>
+      <c r="AI15" s="368" t="n"/>
+      <c r="AJ15" s="368" t="n"/>
+      <c r="AK15" s="368" t="n"/>
+      <c r="AL15" s="368" t="n"/>
+      <c r="AM15" s="368" t="n"/>
+      <c r="AN15" s="368" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1"/>
     <row r="17" ht="20" customHeight="1"/>
@@ -8053,6 +11233,7 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -510,6 +510,12 @@
       <color rgb="000C2D48"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="52">
     <fill>
@@ -769,7 +775,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="318">
+  <borders count="359">
     <border>
       <left/>
       <right/>
@@ -4157,13 +4163,484 @@
       </top>
       <bottom style="medium">
         <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="489">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5288,6 +5765,91 @@
     </xf>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5370,11 +5932,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>253512</colOff>
+      <row>0</row>
+      <rowOff>340740</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="941616" cy="271620"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5747,2367 +6309,2367 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="397" t="inlineStr"/>
-      <c r="B1" s="398" t="n"/>
-      <c r="C1" s="398" t="n"/>
-      <c r="D1" s="398" t="n"/>
-      <c r="E1" s="398" t="n"/>
-      <c r="F1" s="398" t="n"/>
-      <c r="G1" s="398" t="n"/>
-      <c r="H1" s="399" t="n"/>
-      <c r="I1" s="400" t="inlineStr">
+      <c r="A1" s="489" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="53" t="n"/>
+      <c r="I1" s="490" t="inlineStr">
         <is>
           <t>WIP Tag</t>
         </is>
       </c>
-      <c r="J1" s="401" t="n"/>
-      <c r="K1" s="401" t="n"/>
-      <c r="L1" s="401" t="n"/>
-      <c r="M1" s="401" t="n"/>
-      <c r="N1" s="401" t="n"/>
-      <c r="O1" s="401" t="n"/>
-      <c r="P1" s="401" t="n"/>
-      <c r="Q1" s="401" t="n"/>
-      <c r="R1" s="401" t="n"/>
-      <c r="S1" s="401" t="n"/>
-      <c r="T1" s="401" t="n"/>
-      <c r="U1" s="401" t="n"/>
-      <c r="V1" s="401" t="n"/>
-      <c r="W1" s="401" t="n"/>
-      <c r="X1" s="401" t="n"/>
-      <c r="Y1" s="401" t="n"/>
-      <c r="Z1" s="401" t="n"/>
-      <c r="AA1" s="401" t="n"/>
-      <c r="AB1" s="401" t="n"/>
-      <c r="AC1" s="401" t="n"/>
-      <c r="AD1" s="402" t="n"/>
-      <c r="AE1" s="403" t="inlineStr">
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="491" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="404" t="n"/>
-      <c r="AG1" s="404" t="n"/>
-      <c r="AH1" s="405" t="n"/>
-      <c r="AI1" s="406" t="inlineStr">
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="492" t="n"/>
+      <c r="AI1" s="493" t="inlineStr">
         <is>
           <t>FRM-703</t>
         </is>
       </c>
-      <c r="AJ1" s="407" t="n"/>
-      <c r="AK1" s="407" t="n"/>
-      <c r="AL1" s="407" t="n"/>
-      <c r="AM1" s="407" t="n"/>
-      <c r="AN1" s="408" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="53" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="409" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="410" t="n"/>
-      <c r="I2" s="411" t="n"/>
-      <c r="J2" s="412" t="n"/>
-      <c r="K2" s="412" t="n"/>
-      <c r="L2" s="412" t="n"/>
-      <c r="M2" s="412" t="n"/>
-      <c r="N2" s="412" t="n"/>
-      <c r="O2" s="412" t="n"/>
-      <c r="P2" s="412" t="n"/>
-      <c r="Q2" s="412" t="n"/>
-      <c r="R2" s="412" t="n"/>
-      <c r="S2" s="412" t="n"/>
-      <c r="T2" s="412" t="n"/>
-      <c r="U2" s="412" t="n"/>
-      <c r="V2" s="412" t="n"/>
-      <c r="W2" s="412" t="n"/>
-      <c r="X2" s="412" t="n"/>
-      <c r="Y2" s="412" t="n"/>
-      <c r="Z2" s="412" t="n"/>
-      <c r="AA2" s="412" t="n"/>
-      <c r="AB2" s="412" t="n"/>
-      <c r="AC2" s="412" t="n"/>
-      <c r="AD2" s="413" t="n"/>
-      <c r="AE2" s="414" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="494" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="415" t="n"/>
-      <c r="AG2" s="415" t="n"/>
-      <c r="AH2" s="416" t="n"/>
-      <c r="AI2" s="417" t="inlineStr">
+      <c r="AF2" s="495" t="n"/>
+      <c r="AG2" s="495" t="n"/>
+      <c r="AH2" s="496" t="n"/>
+      <c r="AI2" s="497" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="418" t="n"/>
-      <c r="AK2" s="418" t="n"/>
-      <c r="AL2" s="418" t="n"/>
-      <c r="AM2" s="418" t="n"/>
-      <c r="AN2" s="419" t="n"/>
+      <c r="AJ2" s="495" t="n"/>
+      <c r="AK2" s="495" t="n"/>
+      <c r="AL2" s="495" t="n"/>
+      <c r="AM2" s="495" t="n"/>
+      <c r="AN2" s="498" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="409" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="410" t="n"/>
-      <c r="I3" s="411" t="n"/>
-      <c r="J3" s="412" t="n"/>
-      <c r="K3" s="412" t="n"/>
-      <c r="L3" s="412" t="n"/>
-      <c r="M3" s="412" t="n"/>
-      <c r="N3" s="412" t="n"/>
-      <c r="O3" s="412" t="n"/>
-      <c r="P3" s="412" t="n"/>
-      <c r="Q3" s="412" t="n"/>
-      <c r="R3" s="412" t="n"/>
-      <c r="S3" s="412" t="n"/>
-      <c r="T3" s="412" t="n"/>
-      <c r="U3" s="412" t="n"/>
-      <c r="V3" s="412" t="n"/>
-      <c r="W3" s="412" t="n"/>
-      <c r="X3" s="412" t="n"/>
-      <c r="Y3" s="412" t="n"/>
-      <c r="Z3" s="412" t="n"/>
-      <c r="AA3" s="412" t="n"/>
-      <c r="AB3" s="412" t="n"/>
-      <c r="AC3" s="412" t="n"/>
-      <c r="AD3" s="413" t="n"/>
-      <c r="AE3" s="414" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="494" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="415" t="n"/>
-      <c r="AG3" s="415" t="n"/>
-      <c r="AH3" s="416" t="n"/>
-      <c r="AI3" s="417" t="inlineStr">
+      <c r="AF3" s="495" t="n"/>
+      <c r="AG3" s="495" t="n"/>
+      <c r="AH3" s="496" t="n"/>
+      <c r="AI3" s="497" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="418" t="n"/>
-      <c r="AK3" s="418" t="n"/>
-      <c r="AL3" s="418" t="n"/>
-      <c r="AM3" s="418" t="n"/>
-      <c r="AN3" s="419" t="n"/>
+      <c r="AJ3" s="495" t="n"/>
+      <c r="AK3" s="495" t="n"/>
+      <c r="AL3" s="495" t="n"/>
+      <c r="AM3" s="495" t="n"/>
+      <c r="AN3" s="498" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="409" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="410" t="n"/>
-      <c r="I4" s="420" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="499" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="421" t="n"/>
-      <c r="K4" s="421" t="n"/>
-      <c r="L4" s="421" t="n"/>
-      <c r="M4" s="421" t="n"/>
-      <c r="N4" s="421" t="n"/>
-      <c r="O4" s="421" t="n"/>
-      <c r="P4" s="421" t="n"/>
-      <c r="Q4" s="421" t="n"/>
-      <c r="R4" s="421" t="n"/>
-      <c r="S4" s="421" t="n"/>
-      <c r="T4" s="421" t="n"/>
-      <c r="U4" s="421" t="n"/>
-      <c r="V4" s="421" t="n"/>
-      <c r="W4" s="421" t="n"/>
-      <c r="X4" s="421" t="n"/>
-      <c r="Y4" s="421" t="n"/>
-      <c r="Z4" s="421" t="n"/>
-      <c r="AA4" s="421" t="n"/>
-      <c r="AB4" s="421" t="n"/>
-      <c r="AC4" s="421" t="n"/>
-      <c r="AD4" s="422" t="n"/>
-      <c r="AE4" s="414" t="inlineStr">
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="494" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="415" t="n"/>
-      <c r="AG4" s="415" t="n"/>
-      <c r="AH4" s="416" t="n"/>
-      <c r="AI4" s="417" t="inlineStr">
+      <c r="AF4" s="495" t="n"/>
+      <c r="AG4" s="495" t="n"/>
+      <c r="AH4" s="496" t="n"/>
+      <c r="AI4" s="497" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="418" t="n"/>
-      <c r="AK4" s="418" t="n"/>
-      <c r="AL4" s="418" t="n"/>
-      <c r="AM4" s="418" t="n"/>
-      <c r="AN4" s="419" t="n"/>
+      <c r="AJ4" s="495" t="n"/>
+      <c r="AK4" s="495" t="n"/>
+      <c r="AL4" s="495" t="n"/>
+      <c r="AM4" s="495" t="n"/>
+      <c r="AN4" s="498" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="423" t="n"/>
-      <c r="B5" s="424" t="n"/>
-      <c r="C5" s="424" t="n"/>
-      <c r="D5" s="424" t="n"/>
-      <c r="E5" s="424" t="n"/>
-      <c r="F5" s="424" t="n"/>
-      <c r="G5" s="424" t="n"/>
-      <c r="H5" s="425" t="n"/>
-      <c r="I5" s="426" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="427" t="n"/>
-      <c r="K5" s="427" t="n"/>
-      <c r="L5" s="427" t="n"/>
-      <c r="M5" s="427" t="n"/>
-      <c r="N5" s="427" t="n"/>
-      <c r="O5" s="427" t="n"/>
-      <c r="P5" s="427" t="n"/>
-      <c r="Q5" s="427" t="n"/>
-      <c r="R5" s="427" t="n"/>
-      <c r="S5" s="427" t="n"/>
-      <c r="T5" s="427" t="n"/>
-      <c r="U5" s="427" t="n"/>
-      <c r="V5" s="427" t="n"/>
-      <c r="W5" s="427" t="n"/>
-      <c r="X5" s="427" t="n"/>
-      <c r="Y5" s="427" t="n"/>
-      <c r="Z5" s="427" t="n"/>
-      <c r="AA5" s="427" t="n"/>
-      <c r="AB5" s="427" t="n"/>
-      <c r="AC5" s="427" t="n"/>
-      <c r="AD5" s="428" t="n"/>
-      <c r="AE5" s="429" t="inlineStr">
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="500" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="430" t="n"/>
-      <c r="AG5" s="430" t="n"/>
-      <c r="AH5" s="431" t="n"/>
-      <c r="AI5" s="432" t="inlineStr">
+      <c r="AF5" s="501" t="n"/>
+      <c r="AG5" s="501" t="n"/>
+      <c r="AH5" s="502" t="n"/>
+      <c r="AI5" s="503" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="433" t="n"/>
-      <c r="AK5" s="433" t="n"/>
-      <c r="AL5" s="433" t="n"/>
-      <c r="AM5" s="433" t="n"/>
-      <c r="AN5" s="434" t="n"/>
+      <c r="AJ5" s="501" t="n"/>
+      <c r="AK5" s="501" t="n"/>
+      <c r="AL5" s="501" t="n"/>
+      <c r="AM5" s="501" t="n"/>
+      <c r="AN5" s="504" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="435" t="n"/>
-      <c r="B6" s="435" t="n"/>
-      <c r="C6" s="435" t="n"/>
-      <c r="D6" s="435" t="n"/>
-      <c r="E6" s="435" t="n"/>
-      <c r="F6" s="435" t="n"/>
-      <c r="G6" s="435" t="n"/>
-      <c r="H6" s="435" t="n"/>
-      <c r="I6" s="435" t="n"/>
-      <c r="J6" s="435" t="n"/>
-      <c r="K6" s="435" t="n"/>
-      <c r="L6" s="435" t="n"/>
-      <c r="M6" s="435" t="n"/>
-      <c r="N6" s="435" t="n"/>
-      <c r="O6" s="435" t="n"/>
-      <c r="P6" s="435" t="n"/>
-      <c r="Q6" s="435" t="n"/>
-      <c r="R6" s="435" t="n"/>
-      <c r="S6" s="435" t="n"/>
-      <c r="T6" s="435" t="n"/>
-      <c r="U6" s="435" t="n"/>
-      <c r="V6" s="435" t="n"/>
-      <c r="W6" s="435" t="n"/>
-      <c r="X6" s="435" t="n"/>
-      <c r="Y6" s="435" t="n"/>
-      <c r="Z6" s="435" t="n"/>
-      <c r="AA6" s="435" t="n"/>
-      <c r="AB6" s="435" t="n"/>
-      <c r="AC6" s="435" t="n"/>
-      <c r="AD6" s="435" t="n"/>
-      <c r="AE6" s="435" t="n"/>
-      <c r="AF6" s="435" t="n"/>
-      <c r="AG6" s="435" t="n"/>
-      <c r="AH6" s="435" t="n"/>
-      <c r="AI6" s="435" t="n"/>
-      <c r="AJ6" s="435" t="n"/>
-      <c r="AK6" s="435" t="n"/>
-      <c r="AL6" s="435" t="n"/>
-      <c r="AM6" s="435" t="n"/>
-      <c r="AN6" s="435" t="n"/>
+      <c r="A6" s="505" t="n"/>
+      <c r="B6" s="505" t="n"/>
+      <c r="C6" s="505" t="n"/>
+      <c r="D6" s="505" t="n"/>
+      <c r="E6" s="505" t="n"/>
+      <c r="F6" s="505" t="n"/>
+      <c r="G6" s="505" t="n"/>
+      <c r="H6" s="505" t="n"/>
+      <c r="I6" s="505" t="n"/>
+      <c r="J6" s="505" t="n"/>
+      <c r="K6" s="505" t="n"/>
+      <c r="L6" s="505" t="n"/>
+      <c r="M6" s="505" t="n"/>
+      <c r="N6" s="505" t="n"/>
+      <c r="O6" s="505" t="n"/>
+      <c r="P6" s="505" t="n"/>
+      <c r="Q6" s="505" t="n"/>
+      <c r="R6" s="505" t="n"/>
+      <c r="S6" s="505" t="n"/>
+      <c r="T6" s="505" t="n"/>
+      <c r="U6" s="505" t="n"/>
+      <c r="V6" s="505" t="n"/>
+      <c r="W6" s="505" t="n"/>
+      <c r="X6" s="505" t="n"/>
+      <c r="Y6" s="505" t="n"/>
+      <c r="Z6" s="505" t="n"/>
+      <c r="AA6" s="505" t="n"/>
+      <c r="AB6" s="505" t="n"/>
+      <c r="AC6" s="505" t="n"/>
+      <c r="AD6" s="505" t="n"/>
+      <c r="AE6" s="505" t="n"/>
+      <c r="AF6" s="505" t="n"/>
+      <c r="AG6" s="505" t="n"/>
+      <c r="AH6" s="505" t="n"/>
+      <c r="AI6" s="505" t="n"/>
+      <c r="AJ6" s="505" t="n"/>
+      <c r="AK6" s="505" t="n"/>
+      <c r="AL6" s="505" t="n"/>
+      <c r="AM6" s="505" t="n"/>
+      <c r="AN6" s="505" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="436" t="inlineStr">
+      <c r="A7" s="506" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. PRINT REQUEST / CONTROL CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="437" t="n"/>
-      <c r="C7" s="437" t="n"/>
-      <c r="D7" s="437" t="n"/>
-      <c r="E7" s="437" t="n"/>
-      <c r="F7" s="437" t="n"/>
-      <c r="G7" s="437" t="n"/>
-      <c r="H7" s="437" t="n"/>
-      <c r="I7" s="437" t="n"/>
-      <c r="J7" s="437" t="n"/>
-      <c r="K7" s="437" t="n"/>
-      <c r="L7" s="437" t="n"/>
-      <c r="M7" s="437" t="n"/>
-      <c r="N7" s="437" t="n"/>
-      <c r="O7" s="437" t="n"/>
-      <c r="P7" s="437" t="n"/>
-      <c r="Q7" s="437" t="n"/>
-      <c r="R7" s="437" t="n"/>
-      <c r="S7" s="437" t="n"/>
-      <c r="T7" s="437" t="n"/>
-      <c r="U7" s="437" t="n"/>
-      <c r="V7" s="437" t="n"/>
-      <c r="W7" s="437" t="n"/>
-      <c r="X7" s="437" t="n"/>
-      <c r="Y7" s="437" t="n"/>
-      <c r="Z7" s="437" t="n"/>
-      <c r="AA7" s="437" t="n"/>
-      <c r="AB7" s="437" t="n"/>
-      <c r="AC7" s="437" t="n"/>
-      <c r="AD7" s="437" t="n"/>
-      <c r="AE7" s="437" t="n"/>
-      <c r="AF7" s="437" t="n"/>
-      <c r="AG7" s="437" t="n"/>
-      <c r="AH7" s="437" t="n"/>
-      <c r="AI7" s="437" t="n"/>
-      <c r="AJ7" s="437" t="n"/>
-      <c r="AK7" s="437" t="n"/>
-      <c r="AL7" s="437" t="n"/>
-      <c r="AM7" s="437" t="n"/>
-      <c r="AN7" s="438" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="439" t="inlineStr">
+      <c r="A8" s="507" t="inlineStr">
         <is>
           <t>WIP Tag ID</t>
         </is>
       </c>
-      <c r="B8" s="440" t="n"/>
-      <c r="C8" s="440" t="n"/>
-      <c r="D8" s="440" t="n"/>
-      <c r="E8" s="440" t="n"/>
-      <c r="F8" s="440" t="n"/>
-      <c r="G8" s="440" t="n"/>
-      <c r="H8" s="441">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="30">
         <f>IF(GENERATOR!$B$5="","",GENERATOR!$B$5)</f>
         <v/>
       </c>
-      <c r="I8" s="440" t="n"/>
-      <c r="J8" s="440" t="n"/>
-      <c r="K8" s="440" t="n"/>
-      <c r="L8" s="440" t="n"/>
-      <c r="M8" s="440" t="n"/>
-      <c r="N8" s="440" t="n"/>
-      <c r="O8" s="440" t="n"/>
-      <c r="P8" s="440" t="n"/>
-      <c r="Q8" s="440" t="n"/>
-      <c r="R8" s="440" t="n"/>
-      <c r="S8" s="440" t="n"/>
-      <c r="T8" s="440" t="n"/>
-      <c r="U8" s="442" t="inlineStr">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="508" t="inlineStr">
         <is>
           <t>Print Status</t>
         </is>
       </c>
-      <c r="V8" s="440" t="n"/>
-      <c r="W8" s="440" t="n"/>
-      <c r="X8" s="440" t="n"/>
-      <c r="Y8" s="440" t="n"/>
-      <c r="Z8" s="440" t="n"/>
-      <c r="AA8" s="440" t="n"/>
-      <c r="AB8" s="441">
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+      <c r="Y8" s="5" t="n"/>
+      <c r="Z8" s="5" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="30">
         <f>IF(GENERATOR!$B$12="","",GENERATOR!$B$12)</f>
         <v/>
       </c>
-      <c r="AC8" s="440" t="n"/>
-      <c r="AD8" s="440" t="n"/>
-      <c r="AE8" s="440" t="n"/>
-      <c r="AF8" s="440" t="n"/>
-      <c r="AG8" s="440" t="n"/>
-      <c r="AH8" s="440" t="n"/>
-      <c r="AI8" s="440" t="n"/>
-      <c r="AJ8" s="440" t="n"/>
-      <c r="AK8" s="440" t="n"/>
-      <c r="AL8" s="440" t="n"/>
-      <c r="AM8" s="440" t="n"/>
-      <c r="AN8" s="443" t="n"/>
+      <c r="AC8" s="5" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="5" t="n"/>
+      <c r="AM8" s="5" t="n"/>
+      <c r="AN8" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="444" t="inlineStr">
+      <c r="A9" s="509" t="inlineStr">
         <is>
           <t>Job / Lot / Part / Revision</t>
         </is>
       </c>
-      <c r="B9" s="330" t="n"/>
-      <c r="C9" s="330" t="n"/>
-      <c r="D9" s="330" t="n"/>
-      <c r="E9" s="330" t="n"/>
-      <c r="F9" s="330" t="n"/>
-      <c r="G9" s="330" t="n"/>
-      <c r="H9" s="445">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="14">
         <f>IF(GENERATOR!$B$6="","",GENERATOR!$B$6)</f>
         <v/>
       </c>
-      <c r="I9" s="330" t="n"/>
-      <c r="J9" s="330" t="n"/>
-      <c r="K9" s="330" t="n"/>
-      <c r="L9" s="330" t="n"/>
-      <c r="M9" s="330" t="n"/>
-      <c r="N9" s="330" t="n"/>
-      <c r="O9" s="330" t="n"/>
-      <c r="P9" s="330" t="n"/>
-      <c r="Q9" s="330" t="n"/>
-      <c r="R9" s="330" t="n"/>
-      <c r="S9" s="330" t="n"/>
-      <c r="T9" s="330" t="n"/>
-      <c r="U9" s="446" t="inlineStr">
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="510" t="inlineStr">
         <is>
           <t>Current Operation / Qty</t>
         </is>
       </c>
-      <c r="V9" s="330" t="n"/>
-      <c r="W9" s="330" t="n"/>
-      <c r="X9" s="330" t="n"/>
-      <c r="Y9" s="330" t="n"/>
-      <c r="Z9" s="330" t="n"/>
-      <c r="AA9" s="330" t="n"/>
-      <c r="AB9" s="445">
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="12" t="n"/>
+      <c r="Y9" s="12" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="14">
         <f>IF(GENERATOR!$B$13="","",GENERATOR!$B$13)</f>
         <v/>
       </c>
-      <c r="AC9" s="330" t="n"/>
-      <c r="AD9" s="330" t="n"/>
-      <c r="AE9" s="330" t="n"/>
-      <c r="AF9" s="330" t="n"/>
-      <c r="AG9" s="330" t="n"/>
-      <c r="AH9" s="330" t="n"/>
-      <c r="AI9" s="330" t="n"/>
-      <c r="AJ9" s="330" t="n"/>
-      <c r="AK9" s="330" t="n"/>
-      <c r="AL9" s="330" t="n"/>
-      <c r="AM9" s="330" t="n"/>
-      <c r="AN9" s="447" t="n"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n"/>
+      <c r="AK9" s="12" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="12" t="n"/>
+      <c r="AN9" s="15" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="444" t="inlineStr">
+      <c r="A10" s="509" t="inlineStr">
         <is>
           <t>Area / Location / Room</t>
         </is>
       </c>
-      <c r="B10" s="330" t="n"/>
-      <c r="C10" s="330" t="n"/>
-      <c r="D10" s="330" t="n"/>
-      <c r="E10" s="330" t="n"/>
-      <c r="F10" s="330" t="n"/>
-      <c r="G10" s="330" t="n"/>
-      <c r="H10" s="445">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="14">
         <f>IF(GENERATOR!$B$7="","",GENERATOR!$B$7)</f>
         <v/>
       </c>
-      <c r="I10" s="330" t="n"/>
-      <c r="J10" s="330" t="n"/>
-      <c r="K10" s="330" t="n"/>
-      <c r="L10" s="330" t="n"/>
-      <c r="M10" s="330" t="n"/>
-      <c r="N10" s="330" t="n"/>
-      <c r="O10" s="330" t="n"/>
-      <c r="P10" s="330" t="n"/>
-      <c r="Q10" s="330" t="n"/>
-      <c r="R10" s="330" t="n"/>
-      <c r="S10" s="330" t="n"/>
-      <c r="T10" s="330" t="n"/>
-      <c r="U10" s="446" t="inlineStr">
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="510" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="V10" s="330" t="n"/>
-      <c r="W10" s="330" t="n"/>
-      <c r="X10" s="330" t="n"/>
-      <c r="Y10" s="330" t="n"/>
-      <c r="Z10" s="330" t="n"/>
-      <c r="AA10" s="330" t="n"/>
-      <c r="AB10" s="445">
+      <c r="V10" s="12" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="12" t="n"/>
+      <c r="Y10" s="12" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="14">
         <f>IF(GENERATOR!$B$14="","",GENERATOR!$B$14)</f>
         <v/>
       </c>
-      <c r="AC10" s="330" t="n"/>
-      <c r="AD10" s="330" t="n"/>
-      <c r="AE10" s="330" t="n"/>
-      <c r="AF10" s="330" t="n"/>
-      <c r="AG10" s="330" t="n"/>
-      <c r="AH10" s="330" t="n"/>
-      <c r="AI10" s="330" t="n"/>
-      <c r="AJ10" s="330" t="n"/>
-      <c r="AK10" s="330" t="n"/>
-      <c r="AL10" s="330" t="n"/>
-      <c r="AM10" s="330" t="n"/>
-      <c r="AN10" s="447" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="12" t="n"/>
+      <c r="AN10" s="15" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="444" t="inlineStr">
+      <c r="A11" s="509" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B11" s="330" t="n"/>
-      <c r="C11" s="330" t="n"/>
-      <c r="D11" s="330" t="n"/>
-      <c r="E11" s="330" t="n"/>
-      <c r="F11" s="330" t="n"/>
-      <c r="G11" s="330" t="n"/>
-      <c r="H11" s="445">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="14">
         <f>IF(GENERATOR!$B$8="","",GENERATOR!$B$8)</f>
         <v/>
       </c>
-      <c r="I11" s="330" t="n"/>
-      <c r="J11" s="330" t="n"/>
-      <c r="K11" s="330" t="n"/>
-      <c r="L11" s="330" t="n"/>
-      <c r="M11" s="330" t="n"/>
-      <c r="N11" s="330" t="n"/>
-      <c r="O11" s="330" t="n"/>
-      <c r="P11" s="330" t="n"/>
-      <c r="Q11" s="330" t="n"/>
-      <c r="R11" s="330" t="n"/>
-      <c r="S11" s="330" t="n"/>
-      <c r="T11" s="330" t="n"/>
-      <c r="U11" s="446" t="inlineStr">
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="510" t="inlineStr">
         <is>
           <t>Print Qty / Application Status</t>
         </is>
       </c>
-      <c r="V11" s="330" t="n"/>
-      <c r="W11" s="330" t="n"/>
-      <c r="X11" s="330" t="n"/>
-      <c r="Y11" s="330" t="n"/>
-      <c r="Z11" s="330" t="n"/>
-      <c r="AA11" s="330" t="n"/>
-      <c r="AB11" s="445">
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="12" t="n"/>
+      <c r="Y11" s="12" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="14">
         <f>IF(GENERATOR!$B$15="","",GENERATOR!$B$15)</f>
         <v/>
       </c>
-      <c r="AC11" s="330" t="n"/>
-      <c r="AD11" s="330" t="n"/>
-      <c r="AE11" s="330" t="n"/>
-      <c r="AF11" s="330" t="n"/>
-      <c r="AG11" s="330" t="n"/>
-      <c r="AH11" s="330" t="n"/>
-      <c r="AI11" s="330" t="n"/>
-      <c r="AJ11" s="330" t="n"/>
-      <c r="AK11" s="330" t="n"/>
-      <c r="AL11" s="330" t="n"/>
-      <c r="AM11" s="330" t="n"/>
-      <c r="AN11" s="447" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n"/>
+      <c r="AK11" s="12" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="12" t="n"/>
+      <c r="AN11" s="15" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="448" t="inlineStr">
+      <c r="A12" s="511" t="inlineStr">
         <is>
           <t>Encoded Data Ref</t>
         </is>
       </c>
-      <c r="B12" s="449" t="n"/>
-      <c r="C12" s="449" t="n"/>
-      <c r="D12" s="449" t="n"/>
-      <c r="E12" s="449" t="n"/>
-      <c r="F12" s="449" t="n"/>
-      <c r="G12" s="449" t="n"/>
-      <c r="H12" s="450">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="23">
         <f>IF(GENERATOR!$B$9="","",GENERATOR!$B$9)</f>
         <v/>
       </c>
-      <c r="I12" s="449" t="n"/>
-      <c r="J12" s="449" t="n"/>
-      <c r="K12" s="449" t="n"/>
-      <c r="L12" s="449" t="n"/>
-      <c r="M12" s="449" t="n"/>
-      <c r="N12" s="449" t="n"/>
-      <c r="O12" s="449" t="n"/>
-      <c r="P12" s="449" t="n"/>
-      <c r="Q12" s="449" t="n"/>
-      <c r="R12" s="449" t="n"/>
-      <c r="S12" s="449" t="n"/>
-      <c r="T12" s="449" t="n"/>
-      <c r="U12" s="451" t="inlineStr">
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="19" t="n"/>
+      <c r="Q12" s="19" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="19" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="512" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="V12" s="449" t="n"/>
-      <c r="W12" s="449" t="n"/>
-      <c r="X12" s="449" t="n"/>
-      <c r="Y12" s="449" t="n"/>
-      <c r="Z12" s="449" t="n"/>
-      <c r="AA12" s="449" t="n"/>
-      <c r="AB12" s="450">
+      <c r="V12" s="19" t="n"/>
+      <c r="W12" s="19" t="n"/>
+      <c r="X12" s="19" t="n"/>
+      <c r="Y12" s="19" t="n"/>
+      <c r="Z12" s="19" t="n"/>
+      <c r="AA12" s="22" t="n"/>
+      <c r="AB12" s="23">
         <f>IF(GENERATOR!$B$16="","",GENERATOR!$B$16)</f>
         <v/>
       </c>
-      <c r="AC12" s="449" t="n"/>
-      <c r="AD12" s="449" t="n"/>
-      <c r="AE12" s="449" t="n"/>
-      <c r="AF12" s="449" t="n"/>
-      <c r="AG12" s="449" t="n"/>
-      <c r="AH12" s="449" t="n"/>
-      <c r="AI12" s="449" t="n"/>
-      <c r="AJ12" s="449" t="n"/>
-      <c r="AK12" s="449" t="n"/>
-      <c r="AL12" s="449" t="n"/>
-      <c r="AM12" s="449" t="n"/>
-      <c r="AN12" s="452" t="n"/>
+      <c r="AC12" s="19" t="n"/>
+      <c r="AD12" s="19" t="n"/>
+      <c r="AE12" s="19" t="n"/>
+      <c r="AF12" s="19" t="n"/>
+      <c r="AG12" s="19" t="n"/>
+      <c r="AH12" s="19" t="n"/>
+      <c r="AI12" s="19" t="n"/>
+      <c r="AJ12" s="19" t="n"/>
+      <c r="AK12" s="19" t="n"/>
+      <c r="AL12" s="19" t="n"/>
+      <c r="AM12" s="19" t="n"/>
+      <c r="AN12" s="24" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="342" t="n"/>
-      <c r="B13" s="389" t="n"/>
-      <c r="C13" s="389" t="n"/>
-      <c r="D13" s="389" t="n"/>
-      <c r="E13" s="389" t="n"/>
-      <c r="F13" s="389" t="n"/>
-      <c r="G13" s="389" t="n"/>
-      <c r="H13" s="389" t="n"/>
-      <c r="I13" s="389" t="n"/>
-      <c r="J13" s="389" t="n"/>
-      <c r="K13" s="389" t="n"/>
-      <c r="L13" s="389" t="n"/>
-      <c r="M13" s="389" t="n"/>
-      <c r="N13" s="389" t="n"/>
-      <c r="O13" s="389" t="n"/>
-      <c r="P13" s="389" t="n"/>
-      <c r="Q13" s="389" t="n"/>
-      <c r="R13" s="389" t="n"/>
-      <c r="S13" s="389" t="n"/>
-      <c r="T13" s="389" t="n"/>
-      <c r="U13" s="389" t="n"/>
-      <c r="V13" s="389" t="n"/>
-      <c r="W13" s="389" t="n"/>
-      <c r="X13" s="389" t="n"/>
-      <c r="Y13" s="389" t="n"/>
-      <c r="Z13" s="389" t="n"/>
-      <c r="AA13" s="389" t="n"/>
-      <c r="AB13" s="389" t="n"/>
-      <c r="AC13" s="389" t="n"/>
-      <c r="AD13" s="389" t="n"/>
-      <c r="AE13" s="389" t="n"/>
-      <c r="AF13" s="389" t="n"/>
-      <c r="AG13" s="389" t="n"/>
-      <c r="AH13" s="389" t="n"/>
-      <c r="AI13" s="389" t="n"/>
-      <c r="AJ13" s="389" t="n"/>
-      <c r="AK13" s="389" t="n"/>
-      <c r="AL13" s="389" t="n"/>
-      <c r="AM13" s="389" t="n"/>
-      <c r="AN13" s="389" t="n"/>
+      <c r="A13" s="513" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="10" t="n"/>
+      <c r="AL13" s="10" t="n"/>
+      <c r="AM13" s="10" t="n"/>
+      <c r="AN13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="436" t="inlineStr">
+      <c r="A14" s="506" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. PRINTED FACE / CONTROLLED IDENTITY</t>
         </is>
       </c>
-      <c r="B14" s="437" t="n"/>
-      <c r="C14" s="437" t="n"/>
-      <c r="D14" s="437" t="n"/>
-      <c r="E14" s="437" t="n"/>
-      <c r="F14" s="437" t="n"/>
-      <c r="G14" s="437" t="n"/>
-      <c r="H14" s="437" t="n"/>
-      <c r="I14" s="437" t="n"/>
-      <c r="J14" s="437" t="n"/>
-      <c r="K14" s="437" t="n"/>
-      <c r="L14" s="437" t="n"/>
-      <c r="M14" s="437" t="n"/>
-      <c r="N14" s="437" t="n"/>
-      <c r="O14" s="437" t="n"/>
-      <c r="P14" s="437" t="n"/>
-      <c r="Q14" s="437" t="n"/>
-      <c r="R14" s="437" t="n"/>
-      <c r="S14" s="437" t="n"/>
-      <c r="T14" s="437" t="n"/>
-      <c r="U14" s="437" t="n"/>
-      <c r="V14" s="437" t="n"/>
-      <c r="W14" s="437" t="n"/>
-      <c r="X14" s="437" t="n"/>
-      <c r="Y14" s="437" t="n"/>
-      <c r="Z14" s="437" t="n"/>
-      <c r="AA14" s="437" t="n"/>
-      <c r="AB14" s="437" t="n"/>
-      <c r="AC14" s="437" t="n"/>
-      <c r="AD14" s="437" t="n"/>
-      <c r="AE14" s="437" t="n"/>
-      <c r="AF14" s="437" t="n"/>
-      <c r="AG14" s="437" t="n"/>
-      <c r="AH14" s="437" t="n"/>
-      <c r="AI14" s="437" t="n"/>
-      <c r="AJ14" s="437" t="n"/>
-      <c r="AK14" s="437" t="n"/>
-      <c r="AL14" s="437" t="n"/>
-      <c r="AM14" s="437" t="n"/>
-      <c r="AN14" s="438" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="27" t="n"/>
+      <c r="Z14" s="27" t="n"/>
+      <c r="AA14" s="27" t="n"/>
+      <c r="AB14" s="27" t="n"/>
+      <c r="AC14" s="27" t="n"/>
+      <c r="AD14" s="27" t="n"/>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="27" t="n"/>
+      <c r="AI14" s="27" t="n"/>
+      <c r="AJ14" s="27" t="n"/>
+      <c r="AK14" s="27" t="n"/>
+      <c r="AL14" s="27" t="n"/>
+      <c r="AM14" s="27" t="n"/>
+      <c r="AN14" s="28" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="439" t="inlineStr">
+      <c r="A15" s="507" t="inlineStr">
         <is>
           <t>Tag Face / Status</t>
         </is>
       </c>
-      <c r="B15" s="440" t="n"/>
-      <c r="C15" s="440" t="n"/>
-      <c r="D15" s="440" t="n"/>
-      <c r="E15" s="440" t="n"/>
-      <c r="F15" s="440" t="n"/>
-      <c r="G15" s="440" t="n"/>
-      <c r="H15" s="441">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="30">
         <f>IF(GENERATOR!$B$19="","",GENERATOR!$B$19)</f>
         <v/>
       </c>
-      <c r="I15" s="440" t="n"/>
-      <c r="J15" s="440" t="n"/>
-      <c r="K15" s="440" t="n"/>
-      <c r="L15" s="440" t="n"/>
-      <c r="M15" s="440" t="n"/>
-      <c r="N15" s="440" t="n"/>
-      <c r="O15" s="440" t="n"/>
-      <c r="P15" s="440" t="n"/>
-      <c r="Q15" s="440" t="n"/>
-      <c r="R15" s="440" t="n"/>
-      <c r="S15" s="440" t="n"/>
-      <c r="T15" s="440" t="n"/>
-      <c r="U15" s="442" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="508" t="inlineStr">
         <is>
           <t>Operation / Workcenter</t>
         </is>
       </c>
-      <c r="V15" s="440" t="n"/>
-      <c r="W15" s="440" t="n"/>
-      <c r="X15" s="440" t="n"/>
-      <c r="Y15" s="440" t="n"/>
-      <c r="Z15" s="440" t="n"/>
-      <c r="AA15" s="440" t="n"/>
-      <c r="AB15" s="441">
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="5" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="30">
         <f>IF(GENERATOR!$B$20="","",GENERATOR!$B$20)</f>
         <v/>
       </c>
-      <c r="AC15" s="440" t="n"/>
-      <c r="AD15" s="440" t="n"/>
-      <c r="AE15" s="440" t="n"/>
-      <c r="AF15" s="440" t="n"/>
-      <c r="AG15" s="440" t="n"/>
-      <c r="AH15" s="440" t="n"/>
-      <c r="AI15" s="440" t="n"/>
-      <c r="AJ15" s="440" t="n"/>
-      <c r="AK15" s="440" t="n"/>
-      <c r="AL15" s="440" t="n"/>
-      <c r="AM15" s="440" t="n"/>
-      <c r="AN15" s="443" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
+      <c r="AL15" s="5" t="n"/>
+      <c r="AM15" s="5" t="n"/>
+      <c r="AN15" s="8" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="444" t="inlineStr">
+      <c r="A16" s="509" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B16" s="330" t="n"/>
-      <c r="C16" s="330" t="n"/>
-      <c r="D16" s="330" t="n"/>
-      <c r="E16" s="330" t="n"/>
-      <c r="F16" s="330" t="n"/>
-      <c r="G16" s="330" t="n"/>
-      <c r="H16" s="445">
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14">
         <f>IF(GENERATOR!$B$21="","",GENERATOR!$B$21)</f>
         <v/>
       </c>
-      <c r="I16" s="330" t="n"/>
-      <c r="J16" s="330" t="n"/>
-      <c r="K16" s="330" t="n"/>
-      <c r="L16" s="330" t="n"/>
-      <c r="M16" s="330" t="n"/>
-      <c r="N16" s="330" t="n"/>
-      <c r="O16" s="330" t="n"/>
-      <c r="P16" s="330" t="n"/>
-      <c r="Q16" s="330" t="n"/>
-      <c r="R16" s="330" t="n"/>
-      <c r="S16" s="330" t="n"/>
-      <c r="T16" s="330" t="n"/>
-      <c r="U16" s="446" t="inlineStr">
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="510" t="inlineStr">
         <is>
           <t>Lot / Quantity</t>
         </is>
       </c>
-      <c r="V16" s="330" t="n"/>
-      <c r="W16" s="330" t="n"/>
-      <c r="X16" s="330" t="n"/>
-      <c r="Y16" s="330" t="n"/>
-      <c r="Z16" s="330" t="n"/>
-      <c r="AA16" s="330" t="n"/>
-      <c r="AB16" s="445">
+      <c r="V16" s="12" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="12" t="n"/>
+      <c r="Y16" s="12" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="14">
         <f>IF(GENERATOR!$B$22="","",GENERATOR!$B$22)</f>
         <v/>
       </c>
-      <c r="AC16" s="330" t="n"/>
-      <c r="AD16" s="330" t="n"/>
-      <c r="AE16" s="330" t="n"/>
-      <c r="AF16" s="330" t="n"/>
-      <c r="AG16" s="330" t="n"/>
-      <c r="AH16" s="330" t="n"/>
-      <c r="AI16" s="330" t="n"/>
-      <c r="AJ16" s="330" t="n"/>
-      <c r="AK16" s="330" t="n"/>
-      <c r="AL16" s="330" t="n"/>
-      <c r="AM16" s="330" t="n"/>
-      <c r="AN16" s="447" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="12" t="n"/>
+      <c r="AE16" s="12" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="12" t="n"/>
+      <c r="AK16" s="12" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="12" t="n"/>
+      <c r="AN16" s="15" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="444" t="inlineStr">
+      <c r="A17" s="509" t="inlineStr">
         <is>
           <t>Job / Route Step</t>
         </is>
       </c>
-      <c r="B17" s="330" t="n"/>
-      <c r="C17" s="330" t="n"/>
-      <c r="D17" s="330" t="n"/>
-      <c r="E17" s="330" t="n"/>
-      <c r="F17" s="330" t="n"/>
-      <c r="G17" s="330" t="n"/>
-      <c r="H17" s="445">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14">
         <f>IF(GENERATOR!$B$23="","",GENERATOR!$B$23)</f>
         <v/>
       </c>
-      <c r="I17" s="330" t="n"/>
-      <c r="J17" s="330" t="n"/>
-      <c r="K17" s="330" t="n"/>
-      <c r="L17" s="330" t="n"/>
-      <c r="M17" s="330" t="n"/>
-      <c r="N17" s="330" t="n"/>
-      <c r="O17" s="330" t="n"/>
-      <c r="P17" s="330" t="n"/>
-      <c r="Q17" s="330" t="n"/>
-      <c r="R17" s="330" t="n"/>
-      <c r="S17" s="330" t="n"/>
-      <c r="T17" s="330" t="n"/>
-      <c r="U17" s="446" t="inlineStr">
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="510" t="inlineStr">
         <is>
           <t>Area / Location</t>
         </is>
       </c>
-      <c r="V17" s="330" t="n"/>
-      <c r="W17" s="330" t="n"/>
-      <c r="X17" s="330" t="n"/>
-      <c r="Y17" s="330" t="n"/>
-      <c r="Z17" s="330" t="n"/>
-      <c r="AA17" s="330" t="n"/>
-      <c r="AB17" s="445">
+      <c r="V17" s="12" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="12" t="n"/>
+      <c r="Y17" s="12" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="14">
         <f>IF(GENERATOR!$B$24="","",GENERATOR!$B$24)</f>
         <v/>
       </c>
-      <c r="AC17" s="330" t="n"/>
-      <c r="AD17" s="330" t="n"/>
-      <c r="AE17" s="330" t="n"/>
-      <c r="AF17" s="330" t="n"/>
-      <c r="AG17" s="330" t="n"/>
-      <c r="AH17" s="330" t="n"/>
-      <c r="AI17" s="330" t="n"/>
-      <c r="AJ17" s="330" t="n"/>
-      <c r="AK17" s="330" t="n"/>
-      <c r="AL17" s="330" t="n"/>
-      <c r="AM17" s="330" t="n"/>
-      <c r="AN17" s="447" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="12" t="n"/>
+      <c r="AE17" s="12" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n"/>
+      <c r="AH17" s="12" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="12" t="n"/>
+      <c r="AK17" s="12" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="12" t="n"/>
+      <c r="AN17" s="15" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="448" t="inlineStr">
+      <c r="A18" s="511" t="inlineStr">
         <is>
           <t>Encoded String / Barcode Ref</t>
         </is>
       </c>
-      <c r="B18" s="449" t="n"/>
-      <c r="C18" s="449" t="n"/>
-      <c r="D18" s="449" t="n"/>
-      <c r="E18" s="449" t="n"/>
-      <c r="F18" s="449" t="n"/>
-      <c r="G18" s="449" t="n"/>
-      <c r="H18" s="450">
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="23">
         <f>IF(GENERATOR!$B$25="","",GENERATOR!$B$25)</f>
         <v/>
       </c>
-      <c r="I18" s="449" t="n"/>
-      <c r="J18" s="449" t="n"/>
-      <c r="K18" s="449" t="n"/>
-      <c r="L18" s="449" t="n"/>
-      <c r="M18" s="449" t="n"/>
-      <c r="N18" s="449" t="n"/>
-      <c r="O18" s="449" t="n"/>
-      <c r="P18" s="449" t="n"/>
-      <c r="Q18" s="449" t="n"/>
-      <c r="R18" s="449" t="n"/>
-      <c r="S18" s="449" t="n"/>
-      <c r="T18" s="449" t="n"/>
-      <c r="U18" s="451" t="inlineStr">
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="19" t="n"/>
+      <c r="Q18" s="19" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="19" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="512" t="inlineStr">
         <is>
           <t>Application Note</t>
         </is>
       </c>
-      <c r="V18" s="449" t="n"/>
-      <c r="W18" s="449" t="n"/>
-      <c r="X18" s="449" t="n"/>
-      <c r="Y18" s="449" t="n"/>
-      <c r="Z18" s="449" t="n"/>
-      <c r="AA18" s="449" t="n"/>
-      <c r="AB18" s="450">
+      <c r="V18" s="19" t="n"/>
+      <c r="W18" s="19" t="n"/>
+      <c r="X18" s="19" t="n"/>
+      <c r="Y18" s="19" t="n"/>
+      <c r="Z18" s="19" t="n"/>
+      <c r="AA18" s="22" t="n"/>
+      <c r="AB18" s="23">
         <f>IF(GENERATOR!$B$26="","",GENERATOR!$B$26)</f>
         <v/>
       </c>
-      <c r="AC18" s="449" t="n"/>
-      <c r="AD18" s="449" t="n"/>
-      <c r="AE18" s="449" t="n"/>
-      <c r="AF18" s="449" t="n"/>
-      <c r="AG18" s="449" t="n"/>
-      <c r="AH18" s="449" t="n"/>
-      <c r="AI18" s="449" t="n"/>
-      <c r="AJ18" s="449" t="n"/>
-      <c r="AK18" s="449" t="n"/>
-      <c r="AL18" s="449" t="n"/>
-      <c r="AM18" s="449" t="n"/>
-      <c r="AN18" s="452" t="n"/>
+      <c r="AC18" s="19" t="n"/>
+      <c r="AD18" s="19" t="n"/>
+      <c r="AE18" s="19" t="n"/>
+      <c r="AF18" s="19" t="n"/>
+      <c r="AG18" s="19" t="n"/>
+      <c r="AH18" s="19" t="n"/>
+      <c r="AI18" s="19" t="n"/>
+      <c r="AJ18" s="19" t="n"/>
+      <c r="AK18" s="19" t="n"/>
+      <c r="AL18" s="19" t="n"/>
+      <c r="AM18" s="19" t="n"/>
+      <c r="AN18" s="24" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
-      <c r="A19" s="342" t="n"/>
-      <c r="B19" s="389" t="n"/>
-      <c r="C19" s="389" t="n"/>
-      <c r="D19" s="389" t="n"/>
-      <c r="E19" s="389" t="n"/>
-      <c r="F19" s="389" t="n"/>
-      <c r="G19" s="389" t="n"/>
-      <c r="H19" s="389" t="n"/>
-      <c r="I19" s="389" t="n"/>
-      <c r="J19" s="389" t="n"/>
-      <c r="K19" s="389" t="n"/>
-      <c r="L19" s="389" t="n"/>
-      <c r="M19" s="389" t="n"/>
-      <c r="N19" s="389" t="n"/>
-      <c r="O19" s="389" t="n"/>
-      <c r="P19" s="389" t="n"/>
-      <c r="Q19" s="389" t="n"/>
-      <c r="R19" s="389" t="n"/>
-      <c r="S19" s="389" t="n"/>
-      <c r="T19" s="389" t="n"/>
-      <c r="U19" s="389" t="n"/>
-      <c r="V19" s="389" t="n"/>
-      <c r="W19" s="389" t="n"/>
-      <c r="X19" s="389" t="n"/>
-      <c r="Y19" s="389" t="n"/>
-      <c r="Z19" s="389" t="n"/>
-      <c r="AA19" s="389" t="n"/>
-      <c r="AB19" s="389" t="n"/>
-      <c r="AC19" s="389" t="n"/>
-      <c r="AD19" s="389" t="n"/>
-      <c r="AE19" s="389" t="n"/>
-      <c r="AF19" s="389" t="n"/>
-      <c r="AG19" s="389" t="n"/>
-      <c r="AH19" s="389" t="n"/>
-      <c r="AI19" s="389" t="n"/>
-      <c r="AJ19" s="389" t="n"/>
-      <c r="AK19" s="389" t="n"/>
-      <c r="AL19" s="389" t="n"/>
-      <c r="AM19" s="389" t="n"/>
-      <c r="AN19" s="389" t="n"/>
+      <c r="A19" s="513" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="10" t="n"/>
+      <c r="Z19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n"/>
+      <c r="AB19" s="10" t="n"/>
+      <c r="AC19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
+      <c r="AK19" s="10" t="n"/>
+      <c r="AL19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n"/>
+      <c r="AN19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="436" t="inlineStr">
+      <c r="A20" s="506" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. VERIFICATION / APPLICATION CHECK</t>
         </is>
       </c>
-      <c r="B20" s="437" t="n"/>
-      <c r="C20" s="437" t="n"/>
-      <c r="D20" s="437" t="n"/>
-      <c r="E20" s="437" t="n"/>
-      <c r="F20" s="437" t="n"/>
-      <c r="G20" s="437" t="n"/>
-      <c r="H20" s="437" t="n"/>
-      <c r="I20" s="437" t="n"/>
-      <c r="J20" s="437" t="n"/>
-      <c r="K20" s="437" t="n"/>
-      <c r="L20" s="437" t="n"/>
-      <c r="M20" s="437" t="n"/>
-      <c r="N20" s="437" t="n"/>
-      <c r="O20" s="437" t="n"/>
-      <c r="P20" s="437" t="n"/>
-      <c r="Q20" s="437" t="n"/>
-      <c r="R20" s="437" t="n"/>
-      <c r="S20" s="437" t="n"/>
-      <c r="T20" s="437" t="n"/>
-      <c r="U20" s="437" t="n"/>
-      <c r="V20" s="437" t="n"/>
-      <c r="W20" s="437" t="n"/>
-      <c r="X20" s="437" t="n"/>
-      <c r="Y20" s="437" t="n"/>
-      <c r="Z20" s="437" t="n"/>
-      <c r="AA20" s="437" t="n"/>
-      <c r="AB20" s="437" t="n"/>
-      <c r="AC20" s="437" t="n"/>
-      <c r="AD20" s="437" t="n"/>
-      <c r="AE20" s="437" t="n"/>
-      <c r="AF20" s="437" t="n"/>
-      <c r="AG20" s="437" t="n"/>
-      <c r="AH20" s="437" t="n"/>
-      <c r="AI20" s="437" t="n"/>
-      <c r="AJ20" s="437" t="n"/>
-      <c r="AK20" s="437" t="n"/>
-      <c r="AL20" s="437" t="n"/>
-      <c r="AM20" s="437" t="n"/>
-      <c r="AN20" s="438" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="27" t="n"/>
+      <c r="L20" s="27" t="n"/>
+      <c r="M20" s="27" t="n"/>
+      <c r="N20" s="27" t="n"/>
+      <c r="O20" s="27" t="n"/>
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="27" t="n"/>
+      <c r="R20" s="27" t="n"/>
+      <c r="S20" s="27" t="n"/>
+      <c r="T20" s="27" t="n"/>
+      <c r="U20" s="27" t="n"/>
+      <c r="V20" s="27" t="n"/>
+      <c r="W20" s="27" t="n"/>
+      <c r="X20" s="27" t="n"/>
+      <c r="Y20" s="27" t="n"/>
+      <c r="Z20" s="27" t="n"/>
+      <c r="AA20" s="27" t="n"/>
+      <c r="AB20" s="27" t="n"/>
+      <c r="AC20" s="27" t="n"/>
+      <c r="AD20" s="27" t="n"/>
+      <c r="AE20" s="27" t="n"/>
+      <c r="AF20" s="27" t="n"/>
+      <c r="AG20" s="27" t="n"/>
+      <c r="AH20" s="27" t="n"/>
+      <c r="AI20" s="27" t="n"/>
+      <c r="AJ20" s="27" t="n"/>
+      <c r="AK20" s="27" t="n"/>
+      <c r="AL20" s="27" t="n"/>
+      <c r="AM20" s="27" t="n"/>
+      <c r="AN20" s="28" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="453" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="454" t="n"/>
-      <c r="C21" s="455" t="inlineStr">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="454" t="n"/>
-      <c r="E21" s="454" t="n"/>
-      <c r="F21" s="455" t="inlineStr">
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Verification Check</t>
         </is>
       </c>
-      <c r="G21" s="454" t="n"/>
-      <c r="H21" s="454" t="n"/>
-      <c r="I21" s="454" t="n"/>
-      <c r="J21" s="454" t="n"/>
-      <c r="K21" s="454" t="n"/>
-      <c r="L21" s="454" t="n"/>
-      <c r="M21" s="454" t="n"/>
-      <c r="N21" s="454" t="n"/>
-      <c r="O21" s="454" t="n"/>
-      <c r="P21" s="454" t="n"/>
-      <c r="Q21" s="454" t="n"/>
-      <c r="R21" s="454" t="n"/>
-      <c r="S21" s="454" t="n"/>
-      <c r="T21" s="455" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="37" t="inlineStr">
         <is>
           <t>Acceptance Rule</t>
         </is>
       </c>
-      <c r="U21" s="454" t="n"/>
-      <c r="V21" s="454" t="n"/>
-      <c r="W21" s="454" t="n"/>
-      <c r="X21" s="454" t="n"/>
-      <c r="Y21" s="454" t="n"/>
-      <c r="Z21" s="454" t="n"/>
-      <c r="AA21" s="454" t="n"/>
-      <c r="AB21" s="454" t="n"/>
-      <c r="AC21" s="454" t="n"/>
-      <c r="AD21" s="454" t="n"/>
-      <c r="AE21" s="454" t="n"/>
-      <c r="AF21" s="455" t="inlineStr">
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="6" t="n"/>
+      <c r="AF21" s="37" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="454" t="n"/>
-      <c r="AH21" s="454" t="n"/>
-      <c r="AI21" s="454" t="n"/>
-      <c r="AJ21" s="455" t="inlineStr">
+      <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="6" t="n"/>
+      <c r="AJ21" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="454" t="n"/>
-      <c r="AL21" s="454" t="n"/>
-      <c r="AM21" s="455" t="inlineStr">
+      <c r="AK21" s="5" t="n"/>
+      <c r="AL21" s="6" t="n"/>
+      <c r="AM21" s="37" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="456" t="n"/>
+      <c r="AN21" s="8" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="457">
+      <c r="A22" s="514">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="440" t="n"/>
-      <c r="C22" s="458" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="515" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D22" s="440" t="n"/>
-      <c r="E22" s="440" t="n"/>
-      <c r="F22" s="441" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="30" t="inlineStr">
         <is>
           <t>Identity match</t>
         </is>
       </c>
-      <c r="G22" s="440" t="n"/>
-      <c r="H22" s="440" t="n"/>
-      <c r="I22" s="440" t="n"/>
-      <c r="J22" s="440" t="n"/>
-      <c r="K22" s="440" t="n"/>
-      <c r="L22" s="440" t="n"/>
-      <c r="M22" s="440" t="n"/>
-      <c r="N22" s="440" t="n"/>
-      <c r="O22" s="440" t="n"/>
-      <c r="P22" s="440" t="n"/>
-      <c r="Q22" s="440" t="n"/>
-      <c r="R22" s="440" t="n"/>
-      <c r="S22" s="440" t="n"/>
-      <c r="T22" s="459" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="516" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U22" s="440" t="n"/>
-      <c r="V22" s="440" t="n"/>
-      <c r="W22" s="440" t="n"/>
-      <c r="X22" s="440" t="n"/>
-      <c r="Y22" s="440" t="n"/>
-      <c r="Z22" s="440" t="n"/>
-      <c r="AA22" s="440" t="n"/>
-      <c r="AB22" s="440" t="n"/>
-      <c r="AC22" s="440" t="n"/>
-      <c r="AD22" s="440" t="n"/>
-      <c r="AE22" s="440" t="n"/>
-      <c r="AF22" s="460" t="n"/>
-      <c r="AG22" s="440" t="n"/>
-      <c r="AH22" s="440" t="n"/>
-      <c r="AI22" s="440" t="n"/>
-      <c r="AJ22" s="460" t="n"/>
-      <c r="AK22" s="440" t="n"/>
-      <c r="AL22" s="440" t="n"/>
-      <c r="AM22" s="461" t="n"/>
-      <c r="AN22" s="443" t="n"/>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="517" t="n"/>
+      <c r="AG22" s="5" t="n"/>
+      <c r="AH22" s="5" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="517" t="n"/>
+      <c r="AK22" s="5" t="n"/>
+      <c r="AL22" s="6" t="n"/>
+      <c r="AM22" s="518" t="n"/>
+      <c r="AN22" s="8" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="462">
+      <c r="A23" s="519">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="330" t="n"/>
-      <c r="C23" s="463" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="39" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="D23" s="330" t="n"/>
-      <c r="E23" s="330" t="n"/>
-      <c r="F23" s="464" t="inlineStr">
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="43" t="inlineStr">
         <is>
           <t>Readable print</t>
         </is>
       </c>
-      <c r="G23" s="330" t="n"/>
-      <c r="H23" s="330" t="n"/>
-      <c r="I23" s="330" t="n"/>
-      <c r="J23" s="330" t="n"/>
-      <c r="K23" s="330" t="n"/>
-      <c r="L23" s="330" t="n"/>
-      <c r="M23" s="330" t="n"/>
-      <c r="N23" s="330" t="n"/>
-      <c r="O23" s="330" t="n"/>
-      <c r="P23" s="330" t="n"/>
-      <c r="Q23" s="330" t="n"/>
-      <c r="R23" s="330" t="n"/>
-      <c r="S23" s="330" t="n"/>
-      <c r="T23" s="465" t="inlineStr">
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="12" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="40" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U23" s="330" t="n"/>
-      <c r="V23" s="330" t="n"/>
-      <c r="W23" s="330" t="n"/>
-      <c r="X23" s="330" t="n"/>
-      <c r="Y23" s="330" t="n"/>
-      <c r="Z23" s="330" t="n"/>
-      <c r="AA23" s="330" t="n"/>
-      <c r="AB23" s="330" t="n"/>
-      <c r="AC23" s="330" t="n"/>
-      <c r="AD23" s="330" t="n"/>
-      <c r="AE23" s="330" t="n"/>
-      <c r="AF23" s="466" t="n"/>
-      <c r="AG23" s="330" t="n"/>
-      <c r="AH23" s="330" t="n"/>
-      <c r="AI23" s="330" t="n"/>
-      <c r="AJ23" s="466" t="n"/>
-      <c r="AK23" s="330" t="n"/>
-      <c r="AL23" s="330" t="n"/>
-      <c r="AM23" s="467" t="n"/>
-      <c r="AN23" s="447" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="12" t="n"/>
+      <c r="Y23" s="12" t="n"/>
+      <c r="Z23" s="12" t="n"/>
+      <c r="AA23" s="12" t="n"/>
+      <c r="AB23" s="12" t="n"/>
+      <c r="AC23" s="12" t="n"/>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="13" t="n"/>
+      <c r="AF23" s="41" t="n"/>
+      <c r="AG23" s="12" t="n"/>
+      <c r="AH23" s="12" t="n"/>
+      <c r="AI23" s="13" t="n"/>
+      <c r="AJ23" s="41" t="n"/>
+      <c r="AK23" s="12" t="n"/>
+      <c r="AL23" s="13" t="n"/>
+      <c r="AM23" s="42" t="n"/>
+      <c r="AN23" s="15" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="462">
+      <c r="A24" s="519">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="330" t="n"/>
-      <c r="C24" s="463" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="39" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="D24" s="330" t="n"/>
-      <c r="E24" s="330" t="n"/>
-      <c r="F24" s="445" t="inlineStr">
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Correct quantity</t>
         </is>
       </c>
-      <c r="G24" s="330" t="n"/>
-      <c r="H24" s="330" t="n"/>
-      <c r="I24" s="330" t="n"/>
-      <c r="J24" s="330" t="n"/>
-      <c r="K24" s="330" t="n"/>
-      <c r="L24" s="330" t="n"/>
-      <c r="M24" s="330" t="n"/>
-      <c r="N24" s="330" t="n"/>
-      <c r="O24" s="330" t="n"/>
-      <c r="P24" s="330" t="n"/>
-      <c r="Q24" s="330" t="n"/>
-      <c r="R24" s="330" t="n"/>
-      <c r="S24" s="330" t="n"/>
-      <c r="T24" s="465" t="inlineStr">
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="12" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="40" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U24" s="330" t="n"/>
-      <c r="V24" s="330" t="n"/>
-      <c r="W24" s="330" t="n"/>
-      <c r="X24" s="330" t="n"/>
-      <c r="Y24" s="330" t="n"/>
-      <c r="Z24" s="330" t="n"/>
-      <c r="AA24" s="330" t="n"/>
-      <c r="AB24" s="330" t="n"/>
-      <c r="AC24" s="330" t="n"/>
-      <c r="AD24" s="330" t="n"/>
-      <c r="AE24" s="330" t="n"/>
-      <c r="AF24" s="466" t="n"/>
-      <c r="AG24" s="330" t="n"/>
-      <c r="AH24" s="330" t="n"/>
-      <c r="AI24" s="330" t="n"/>
-      <c r="AJ24" s="466" t="n"/>
-      <c r="AK24" s="330" t="n"/>
-      <c r="AL24" s="330" t="n"/>
-      <c r="AM24" s="467" t="n"/>
-      <c r="AN24" s="447" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="12" t="n"/>
+      <c r="W24" s="12" t="n"/>
+      <c r="X24" s="12" t="n"/>
+      <c r="Y24" s="12" t="n"/>
+      <c r="Z24" s="12" t="n"/>
+      <c r="AA24" s="12" t="n"/>
+      <c r="AB24" s="12" t="n"/>
+      <c r="AC24" s="12" t="n"/>
+      <c r="AD24" s="12" t="n"/>
+      <c r="AE24" s="13" t="n"/>
+      <c r="AF24" s="41" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="12" t="n"/>
+      <c r="AI24" s="13" t="n"/>
+      <c r="AJ24" s="41" t="n"/>
+      <c r="AK24" s="12" t="n"/>
+      <c r="AL24" s="13" t="n"/>
+      <c r="AM24" s="42" t="n"/>
+      <c r="AN24" s="15" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="462">
+      <c r="A25" s="519">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="330" t="n"/>
-      <c r="C25" s="463" t="inlineStr">
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="D25" s="330" t="n"/>
-      <c r="E25" s="330" t="n"/>
-      <c r="F25" s="464" t="inlineStr">
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="43" t="inlineStr">
         <is>
           <t>Application status</t>
         </is>
       </c>
-      <c r="G25" s="330" t="n"/>
-      <c r="H25" s="330" t="n"/>
-      <c r="I25" s="330" t="n"/>
-      <c r="J25" s="330" t="n"/>
-      <c r="K25" s="330" t="n"/>
-      <c r="L25" s="330" t="n"/>
-      <c r="M25" s="330" t="n"/>
-      <c r="N25" s="330" t="n"/>
-      <c r="O25" s="330" t="n"/>
-      <c r="P25" s="330" t="n"/>
-      <c r="Q25" s="330" t="n"/>
-      <c r="R25" s="330" t="n"/>
-      <c r="S25" s="330" t="n"/>
-      <c r="T25" s="465" t="inlineStr">
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="12" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="40" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U25" s="330" t="n"/>
-      <c r="V25" s="330" t="n"/>
-      <c r="W25" s="330" t="n"/>
-      <c r="X25" s="330" t="n"/>
-      <c r="Y25" s="330" t="n"/>
-      <c r="Z25" s="330" t="n"/>
-      <c r="AA25" s="330" t="n"/>
-      <c r="AB25" s="330" t="n"/>
-      <c r="AC25" s="330" t="n"/>
-      <c r="AD25" s="330" t="n"/>
-      <c r="AE25" s="330" t="n"/>
-      <c r="AF25" s="466" t="n"/>
-      <c r="AG25" s="330" t="n"/>
-      <c r="AH25" s="330" t="n"/>
-      <c r="AI25" s="330" t="n"/>
-      <c r="AJ25" s="466" t="n"/>
-      <c r="AK25" s="330" t="n"/>
-      <c r="AL25" s="330" t="n"/>
-      <c r="AM25" s="467" t="n"/>
-      <c r="AN25" s="447" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="12" t="n"/>
+      <c r="W25" s="12" t="n"/>
+      <c r="X25" s="12" t="n"/>
+      <c r="Y25" s="12" t="n"/>
+      <c r="Z25" s="12" t="n"/>
+      <c r="AA25" s="12" t="n"/>
+      <c r="AB25" s="12" t="n"/>
+      <c r="AC25" s="12" t="n"/>
+      <c r="AD25" s="12" t="n"/>
+      <c r="AE25" s="13" t="n"/>
+      <c r="AF25" s="41" t="n"/>
+      <c r="AG25" s="12" t="n"/>
+      <c r="AH25" s="12" t="n"/>
+      <c r="AI25" s="13" t="n"/>
+      <c r="AJ25" s="41" t="n"/>
+      <c r="AK25" s="12" t="n"/>
+      <c r="AL25" s="13" t="n"/>
+      <c r="AM25" s="42" t="n"/>
+      <c r="AN25" s="15" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="462">
+      <c r="A26" s="519">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="330" t="n"/>
-      <c r="C26" s="463" t="inlineStr">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D26" s="330" t="n"/>
-      <c r="E26" s="330" t="n"/>
-      <c r="F26" s="445" t="inlineStr">
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Void / scrap control</t>
         </is>
       </c>
-      <c r="G26" s="330" t="n"/>
-      <c r="H26" s="330" t="n"/>
-      <c r="I26" s="330" t="n"/>
-      <c r="J26" s="330" t="n"/>
-      <c r="K26" s="330" t="n"/>
-      <c r="L26" s="330" t="n"/>
-      <c r="M26" s="330" t="n"/>
-      <c r="N26" s="330" t="n"/>
-      <c r="O26" s="330" t="n"/>
-      <c r="P26" s="330" t="n"/>
-      <c r="Q26" s="330" t="n"/>
-      <c r="R26" s="330" t="n"/>
-      <c r="S26" s="330" t="n"/>
-      <c r="T26" s="465" t="inlineStr">
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="12" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="40" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U26" s="330" t="n"/>
-      <c r="V26" s="330" t="n"/>
-      <c r="W26" s="330" t="n"/>
-      <c r="X26" s="330" t="n"/>
-      <c r="Y26" s="330" t="n"/>
-      <c r="Z26" s="330" t="n"/>
-      <c r="AA26" s="330" t="n"/>
-      <c r="AB26" s="330" t="n"/>
-      <c r="AC26" s="330" t="n"/>
-      <c r="AD26" s="330" t="n"/>
-      <c r="AE26" s="330" t="n"/>
-      <c r="AF26" s="466" t="n"/>
-      <c r="AG26" s="330" t="n"/>
-      <c r="AH26" s="330" t="n"/>
-      <c r="AI26" s="330" t="n"/>
-      <c r="AJ26" s="466" t="n"/>
-      <c r="AK26" s="330" t="n"/>
-      <c r="AL26" s="330" t="n"/>
-      <c r="AM26" s="467" t="n"/>
-      <c r="AN26" s="447" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="12" t="n"/>
+      <c r="Y26" s="12" t="n"/>
+      <c r="Z26" s="12" t="n"/>
+      <c r="AA26" s="12" t="n"/>
+      <c r="AB26" s="12" t="n"/>
+      <c r="AC26" s="12" t="n"/>
+      <c r="AD26" s="12" t="n"/>
+      <c r="AE26" s="13" t="n"/>
+      <c r="AF26" s="41" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="13" t="n"/>
+      <c r="AJ26" s="41" t="n"/>
+      <c r="AK26" s="12" t="n"/>
+      <c r="AL26" s="13" t="n"/>
+      <c r="AM26" s="42" t="n"/>
+      <c r="AN26" s="15" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="462" t="n"/>
-      <c r="B27" s="330" t="n"/>
-      <c r="C27" s="463" t="n"/>
-      <c r="D27" s="330" t="n"/>
-      <c r="E27" s="330" t="n"/>
-      <c r="F27" s="464" t="n"/>
-      <c r="G27" s="330" t="n"/>
-      <c r="H27" s="330" t="n"/>
-      <c r="I27" s="330" t="n"/>
-      <c r="J27" s="330" t="n"/>
-      <c r="K27" s="330" t="n"/>
-      <c r="L27" s="330" t="n"/>
-      <c r="M27" s="330" t="n"/>
-      <c r="N27" s="330" t="n"/>
-      <c r="O27" s="330" t="n"/>
-      <c r="P27" s="330" t="n"/>
-      <c r="Q27" s="330" t="n"/>
-      <c r="R27" s="330" t="n"/>
-      <c r="S27" s="330" t="n"/>
-      <c r="T27" s="465" t="n"/>
-      <c r="U27" s="330" t="n"/>
-      <c r="V27" s="330" t="n"/>
-      <c r="W27" s="330" t="n"/>
-      <c r="X27" s="330" t="n"/>
-      <c r="Y27" s="330" t="n"/>
-      <c r="Z27" s="330" t="n"/>
-      <c r="AA27" s="330" t="n"/>
-      <c r="AB27" s="330" t="n"/>
-      <c r="AC27" s="330" t="n"/>
-      <c r="AD27" s="330" t="n"/>
-      <c r="AE27" s="330" t="n"/>
-      <c r="AF27" s="466" t="n"/>
-      <c r="AG27" s="330" t="n"/>
-      <c r="AH27" s="330" t="n"/>
-      <c r="AI27" s="330" t="n"/>
-      <c r="AJ27" s="466" t="n"/>
-      <c r="AK27" s="330" t="n"/>
-      <c r="AL27" s="330" t="n"/>
-      <c r="AM27" s="467" t="n"/>
-      <c r="AN27" s="447" t="n"/>
+      <c r="A27" s="519" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="12" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="40" t="n"/>
+      <c r="U27" s="12" t="n"/>
+      <c r="V27" s="12" t="n"/>
+      <c r="W27" s="12" t="n"/>
+      <c r="X27" s="12" t="n"/>
+      <c r="Y27" s="12" t="n"/>
+      <c r="Z27" s="12" t="n"/>
+      <c r="AA27" s="12" t="n"/>
+      <c r="AB27" s="12" t="n"/>
+      <c r="AC27" s="12" t="n"/>
+      <c r="AD27" s="12" t="n"/>
+      <c r="AE27" s="13" t="n"/>
+      <c r="AF27" s="41" t="n"/>
+      <c r="AG27" s="12" t="n"/>
+      <c r="AH27" s="12" t="n"/>
+      <c r="AI27" s="13" t="n"/>
+      <c r="AJ27" s="41" t="n"/>
+      <c r="AK27" s="12" t="n"/>
+      <c r="AL27" s="13" t="n"/>
+      <c r="AM27" s="42" t="n"/>
+      <c r="AN27" s="15" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="462" t="n"/>
-      <c r="B28" s="330" t="n"/>
-      <c r="C28" s="463" t="n"/>
-      <c r="D28" s="330" t="n"/>
-      <c r="E28" s="330" t="n"/>
-      <c r="F28" s="445" t="n"/>
-      <c r="G28" s="330" t="n"/>
-      <c r="H28" s="330" t="n"/>
-      <c r="I28" s="330" t="n"/>
-      <c r="J28" s="330" t="n"/>
-      <c r="K28" s="330" t="n"/>
-      <c r="L28" s="330" t="n"/>
-      <c r="M28" s="330" t="n"/>
-      <c r="N28" s="330" t="n"/>
-      <c r="O28" s="330" t="n"/>
-      <c r="P28" s="330" t="n"/>
-      <c r="Q28" s="330" t="n"/>
-      <c r="R28" s="330" t="n"/>
-      <c r="S28" s="330" t="n"/>
-      <c r="T28" s="465" t="n"/>
-      <c r="U28" s="330" t="n"/>
-      <c r="V28" s="330" t="n"/>
-      <c r="W28" s="330" t="n"/>
-      <c r="X28" s="330" t="n"/>
-      <c r="Y28" s="330" t="n"/>
-      <c r="Z28" s="330" t="n"/>
-      <c r="AA28" s="330" t="n"/>
-      <c r="AB28" s="330" t="n"/>
-      <c r="AC28" s="330" t="n"/>
-      <c r="AD28" s="330" t="n"/>
-      <c r="AE28" s="330" t="n"/>
-      <c r="AF28" s="466" t="n"/>
-      <c r="AG28" s="330" t="n"/>
-      <c r="AH28" s="330" t="n"/>
-      <c r="AI28" s="330" t="n"/>
-      <c r="AJ28" s="466" t="n"/>
-      <c r="AK28" s="330" t="n"/>
-      <c r="AL28" s="330" t="n"/>
-      <c r="AM28" s="467" t="n"/>
-      <c r="AN28" s="447" t="n"/>
+      <c r="A28" s="519" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="12" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="40" t="n"/>
+      <c r="U28" s="12" t="n"/>
+      <c r="V28" s="12" t="n"/>
+      <c r="W28" s="12" t="n"/>
+      <c r="X28" s="12" t="n"/>
+      <c r="Y28" s="12" t="n"/>
+      <c r="Z28" s="12" t="n"/>
+      <c r="AA28" s="12" t="n"/>
+      <c r="AB28" s="12" t="n"/>
+      <c r="AC28" s="12" t="n"/>
+      <c r="AD28" s="12" t="n"/>
+      <c r="AE28" s="13" t="n"/>
+      <c r="AF28" s="41" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="12" t="n"/>
+      <c r="AI28" s="13" t="n"/>
+      <c r="AJ28" s="41" t="n"/>
+      <c r="AK28" s="12" t="n"/>
+      <c r="AL28" s="13" t="n"/>
+      <c r="AM28" s="42" t="n"/>
+      <c r="AN28" s="15" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="462" t="n"/>
-      <c r="B29" s="330" t="n"/>
-      <c r="C29" s="463" t="n"/>
-      <c r="D29" s="330" t="n"/>
-      <c r="E29" s="330" t="n"/>
-      <c r="F29" s="464" t="n"/>
-      <c r="G29" s="330" t="n"/>
-      <c r="H29" s="330" t="n"/>
-      <c r="I29" s="330" t="n"/>
-      <c r="J29" s="330" t="n"/>
-      <c r="K29" s="330" t="n"/>
-      <c r="L29" s="330" t="n"/>
-      <c r="M29" s="330" t="n"/>
-      <c r="N29" s="330" t="n"/>
-      <c r="O29" s="330" t="n"/>
-      <c r="P29" s="330" t="n"/>
-      <c r="Q29" s="330" t="n"/>
-      <c r="R29" s="330" t="n"/>
-      <c r="S29" s="330" t="n"/>
-      <c r="T29" s="465" t="n"/>
-      <c r="U29" s="330" t="n"/>
-      <c r="V29" s="330" t="n"/>
-      <c r="W29" s="330" t="n"/>
-      <c r="X29" s="330" t="n"/>
-      <c r="Y29" s="330" t="n"/>
-      <c r="Z29" s="330" t="n"/>
-      <c r="AA29" s="330" t="n"/>
-      <c r="AB29" s="330" t="n"/>
-      <c r="AC29" s="330" t="n"/>
-      <c r="AD29" s="330" t="n"/>
-      <c r="AE29" s="330" t="n"/>
-      <c r="AF29" s="466" t="n"/>
-      <c r="AG29" s="330" t="n"/>
-      <c r="AH29" s="330" t="n"/>
-      <c r="AI29" s="330" t="n"/>
-      <c r="AJ29" s="466" t="n"/>
-      <c r="AK29" s="330" t="n"/>
-      <c r="AL29" s="330" t="n"/>
-      <c r="AM29" s="467" t="n"/>
-      <c r="AN29" s="447" t="n"/>
+      <c r="A29" s="519" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="39" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="12" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="40" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="12" t="n"/>
+      <c r="W29" s="12" t="n"/>
+      <c r="X29" s="12" t="n"/>
+      <c r="Y29" s="12" t="n"/>
+      <c r="Z29" s="12" t="n"/>
+      <c r="AA29" s="12" t="n"/>
+      <c r="AB29" s="12" t="n"/>
+      <c r="AC29" s="12" t="n"/>
+      <c r="AD29" s="12" t="n"/>
+      <c r="AE29" s="13" t="n"/>
+      <c r="AF29" s="41" t="n"/>
+      <c r="AG29" s="12" t="n"/>
+      <c r="AH29" s="12" t="n"/>
+      <c r="AI29" s="13" t="n"/>
+      <c r="AJ29" s="41" t="n"/>
+      <c r="AK29" s="12" t="n"/>
+      <c r="AL29" s="13" t="n"/>
+      <c r="AM29" s="42" t="n"/>
+      <c r="AN29" s="15" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="462" t="n"/>
-      <c r="B30" s="330" t="n"/>
-      <c r="C30" s="463" t="n"/>
-      <c r="D30" s="330" t="n"/>
-      <c r="E30" s="330" t="n"/>
-      <c r="F30" s="445" t="n"/>
-      <c r="G30" s="330" t="n"/>
-      <c r="H30" s="330" t="n"/>
-      <c r="I30" s="330" t="n"/>
-      <c r="J30" s="330" t="n"/>
-      <c r="K30" s="330" t="n"/>
-      <c r="L30" s="330" t="n"/>
-      <c r="M30" s="330" t="n"/>
-      <c r="N30" s="330" t="n"/>
-      <c r="O30" s="330" t="n"/>
-      <c r="P30" s="330" t="n"/>
-      <c r="Q30" s="330" t="n"/>
-      <c r="R30" s="330" t="n"/>
-      <c r="S30" s="330" t="n"/>
-      <c r="T30" s="465" t="n"/>
-      <c r="U30" s="330" t="n"/>
-      <c r="V30" s="330" t="n"/>
-      <c r="W30" s="330" t="n"/>
-      <c r="X30" s="330" t="n"/>
-      <c r="Y30" s="330" t="n"/>
-      <c r="Z30" s="330" t="n"/>
-      <c r="AA30" s="330" t="n"/>
-      <c r="AB30" s="330" t="n"/>
-      <c r="AC30" s="330" t="n"/>
-      <c r="AD30" s="330" t="n"/>
-      <c r="AE30" s="330" t="n"/>
-      <c r="AF30" s="466" t="n"/>
-      <c r="AG30" s="330" t="n"/>
-      <c r="AH30" s="330" t="n"/>
-      <c r="AI30" s="330" t="n"/>
-      <c r="AJ30" s="466" t="n"/>
-      <c r="AK30" s="330" t="n"/>
-      <c r="AL30" s="330" t="n"/>
-      <c r="AM30" s="467" t="n"/>
-      <c r="AN30" s="447" t="n"/>
+      <c r="A30" s="519" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="12" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="40" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="12" t="n"/>
+      <c r="W30" s="12" t="n"/>
+      <c r="X30" s="12" t="n"/>
+      <c r="Y30" s="12" t="n"/>
+      <c r="Z30" s="12" t="n"/>
+      <c r="AA30" s="12" t="n"/>
+      <c r="AB30" s="12" t="n"/>
+      <c r="AC30" s="12" t="n"/>
+      <c r="AD30" s="12" t="n"/>
+      <c r="AE30" s="13" t="n"/>
+      <c r="AF30" s="41" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="12" t="n"/>
+      <c r="AI30" s="13" t="n"/>
+      <c r="AJ30" s="41" t="n"/>
+      <c r="AK30" s="12" t="n"/>
+      <c r="AL30" s="13" t="n"/>
+      <c r="AM30" s="42" t="n"/>
+      <c r="AN30" s="15" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="468" t="n"/>
-      <c r="B31" s="449" t="n"/>
-      <c r="C31" s="469" t="n"/>
-      <c r="D31" s="449" t="n"/>
-      <c r="E31" s="449" t="n"/>
-      <c r="F31" s="470" t="n"/>
-      <c r="G31" s="449" t="n"/>
-      <c r="H31" s="449" t="n"/>
-      <c r="I31" s="449" t="n"/>
-      <c r="J31" s="449" t="n"/>
-      <c r="K31" s="449" t="n"/>
-      <c r="L31" s="449" t="n"/>
-      <c r="M31" s="449" t="n"/>
-      <c r="N31" s="449" t="n"/>
-      <c r="O31" s="449" t="n"/>
-      <c r="P31" s="449" t="n"/>
-      <c r="Q31" s="449" t="n"/>
-      <c r="R31" s="449" t="n"/>
-      <c r="S31" s="449" t="n"/>
-      <c r="T31" s="471" t="n"/>
-      <c r="U31" s="449" t="n"/>
-      <c r="V31" s="449" t="n"/>
-      <c r="W31" s="449" t="n"/>
-      <c r="X31" s="449" t="n"/>
-      <c r="Y31" s="449" t="n"/>
-      <c r="Z31" s="449" t="n"/>
-      <c r="AA31" s="449" t="n"/>
-      <c r="AB31" s="449" t="n"/>
-      <c r="AC31" s="449" t="n"/>
-      <c r="AD31" s="449" t="n"/>
-      <c r="AE31" s="449" t="n"/>
-      <c r="AF31" s="472" t="n"/>
-      <c r="AG31" s="449" t="n"/>
-      <c r="AH31" s="449" t="n"/>
-      <c r="AI31" s="449" t="n"/>
-      <c r="AJ31" s="472" t="n"/>
-      <c r="AK31" s="449" t="n"/>
-      <c r="AL31" s="449" t="n"/>
-      <c r="AM31" s="473" t="n"/>
-      <c r="AN31" s="452" t="n"/>
+      <c r="A31" s="520" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="45" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="46" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="19" t="n"/>
+      <c r="R31" s="19" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="47" t="n"/>
+      <c r="U31" s="19" t="n"/>
+      <c r="V31" s="19" t="n"/>
+      <c r="W31" s="19" t="n"/>
+      <c r="X31" s="19" t="n"/>
+      <c r="Y31" s="19" t="n"/>
+      <c r="Z31" s="19" t="n"/>
+      <c r="AA31" s="19" t="n"/>
+      <c r="AB31" s="19" t="n"/>
+      <c r="AC31" s="19" t="n"/>
+      <c r="AD31" s="19" t="n"/>
+      <c r="AE31" s="22" t="n"/>
+      <c r="AF31" s="48" t="n"/>
+      <c r="AG31" s="19" t="n"/>
+      <c r="AH31" s="19" t="n"/>
+      <c r="AI31" s="22" t="n"/>
+      <c r="AJ31" s="48" t="n"/>
+      <c r="AK31" s="19" t="n"/>
+      <c r="AL31" s="22" t="n"/>
+      <c r="AM31" s="49" t="n"/>
+      <c r="AN31" s="24" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
-      <c r="A32" s="342" t="n"/>
-      <c r="B32" s="389" t="n"/>
-      <c r="C32" s="389" t="n"/>
-      <c r="D32" s="389" t="n"/>
-      <c r="E32" s="389" t="n"/>
-      <c r="F32" s="389" t="n"/>
-      <c r="G32" s="389" t="n"/>
-      <c r="H32" s="389" t="n"/>
-      <c r="I32" s="389" t="n"/>
-      <c r="J32" s="389" t="n"/>
-      <c r="K32" s="389" t="n"/>
-      <c r="L32" s="389" t="n"/>
-      <c r="M32" s="389" t="n"/>
-      <c r="N32" s="389" t="n"/>
-      <c r="O32" s="389" t="n"/>
-      <c r="P32" s="389" t="n"/>
-      <c r="Q32" s="389" t="n"/>
-      <c r="R32" s="389" t="n"/>
-      <c r="S32" s="389" t="n"/>
-      <c r="T32" s="389" t="n"/>
-      <c r="U32" s="389" t="n"/>
-      <c r="V32" s="389" t="n"/>
-      <c r="W32" s="389" t="n"/>
-      <c r="X32" s="389" t="n"/>
-      <c r="Y32" s="389" t="n"/>
-      <c r="Z32" s="389" t="n"/>
-      <c r="AA32" s="389" t="n"/>
-      <c r="AB32" s="389" t="n"/>
-      <c r="AC32" s="389" t="n"/>
-      <c r="AD32" s="389" t="n"/>
-      <c r="AE32" s="389" t="n"/>
-      <c r="AF32" s="389" t="n"/>
-      <c r="AG32" s="389" t="n"/>
-      <c r="AH32" s="389" t="n"/>
-      <c r="AI32" s="389" t="n"/>
-      <c r="AJ32" s="389" t="n"/>
-      <c r="AK32" s="389" t="n"/>
-      <c r="AL32" s="389" t="n"/>
-      <c r="AM32" s="389" t="n"/>
-      <c r="AN32" s="389" t="n"/>
+      <c r="A32" s="513" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="10" t="n"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n"/>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="10" t="n"/>
+      <c r="AL32" s="10" t="n"/>
+      <c r="AM32" s="10" t="n"/>
+      <c r="AN32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="436" t="inlineStr">
+      <c r="A33" s="506" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. PRINT CONTROL REFERENCE</t>
         </is>
       </c>
-      <c r="B33" s="437" t="n"/>
-      <c r="C33" s="437" t="n"/>
-      <c r="D33" s="437" t="n"/>
-      <c r="E33" s="437" t="n"/>
-      <c r="F33" s="437" t="n"/>
-      <c r="G33" s="437" t="n"/>
-      <c r="H33" s="437" t="n"/>
-      <c r="I33" s="437" t="n"/>
-      <c r="J33" s="437" t="n"/>
-      <c r="K33" s="437" t="n"/>
-      <c r="L33" s="437" t="n"/>
-      <c r="M33" s="437" t="n"/>
-      <c r="N33" s="437" t="n"/>
-      <c r="O33" s="437" t="n"/>
-      <c r="P33" s="437" t="n"/>
-      <c r="Q33" s="437" t="n"/>
-      <c r="R33" s="437" t="n"/>
-      <c r="S33" s="437" t="n"/>
-      <c r="T33" s="437" t="n"/>
-      <c r="U33" s="437" t="n"/>
-      <c r="V33" s="437" t="n"/>
-      <c r="W33" s="437" t="n"/>
-      <c r="X33" s="437" t="n"/>
-      <c r="Y33" s="437" t="n"/>
-      <c r="Z33" s="437" t="n"/>
-      <c r="AA33" s="437" t="n"/>
-      <c r="AB33" s="437" t="n"/>
-      <c r="AC33" s="437" t="n"/>
-      <c r="AD33" s="437" t="n"/>
-      <c r="AE33" s="437" t="n"/>
-      <c r="AF33" s="437" t="n"/>
-      <c r="AG33" s="437" t="n"/>
-      <c r="AH33" s="437" t="n"/>
-      <c r="AI33" s="437" t="n"/>
-      <c r="AJ33" s="437" t="n"/>
-      <c r="AK33" s="437" t="n"/>
-      <c r="AL33" s="437" t="n"/>
-      <c r="AM33" s="437" t="n"/>
-      <c r="AN33" s="438" t="n"/>
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="27" t="n"/>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
+      <c r="Y33" s="27" t="n"/>
+      <c r="Z33" s="27" t="n"/>
+      <c r="AA33" s="27" t="n"/>
+      <c r="AB33" s="27" t="n"/>
+      <c r="AC33" s="27" t="n"/>
+      <c r="AD33" s="27" t="n"/>
+      <c r="AE33" s="27" t="n"/>
+      <c r="AF33" s="27" t="n"/>
+      <c r="AG33" s="27" t="n"/>
+      <c r="AH33" s="27" t="n"/>
+      <c r="AI33" s="27" t="n"/>
+      <c r="AJ33" s="27" t="n"/>
+      <c r="AK33" s="27" t="n"/>
+      <c r="AL33" s="27" t="n"/>
+      <c r="AM33" s="27" t="n"/>
+      <c r="AN33" s="28" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="453" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="454" t="n"/>
-      <c r="C34" s="455" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Control Field</t>
         </is>
       </c>
-      <c r="D34" s="454" t="n"/>
-      <c r="E34" s="454" t="n"/>
-      <c r="F34" s="454" t="n"/>
-      <c r="G34" s="454" t="n"/>
-      <c r="H34" s="454" t="n"/>
-      <c r="I34" s="454" t="n"/>
-      <c r="J34" s="454" t="n"/>
-      <c r="K34" s="454" t="n"/>
-      <c r="L34" s="454" t="n"/>
-      <c r="M34" s="455" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="37" t="inlineStr">
         <is>
           <t>Required Record</t>
         </is>
       </c>
-      <c r="N34" s="454" t="n"/>
-      <c r="O34" s="454" t="n"/>
-      <c r="P34" s="454" t="n"/>
-      <c r="Q34" s="454" t="n"/>
-      <c r="R34" s="454" t="n"/>
-      <c r="S34" s="454" t="n"/>
-      <c r="T34" s="454" t="n"/>
-      <c r="U34" s="454" t="n"/>
-      <c r="V34" s="454" t="n"/>
-      <c r="W34" s="454" t="n"/>
-      <c r="X34" s="454" t="n"/>
-      <c r="Y34" s="455" t="inlineStr">
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="6" t="n"/>
+      <c r="Y34" s="37" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="454" t="n"/>
-      <c r="AA34" s="454" t="n"/>
-      <c r="AB34" s="454" t="n"/>
-      <c r="AC34" s="454" t="n"/>
-      <c r="AD34" s="455" t="inlineStr">
+      <c r="Z34" s="5" t="n"/>
+      <c r="AA34" s="5" t="n"/>
+      <c r="AB34" s="5" t="n"/>
+      <c r="AC34" s="6" t="n"/>
+      <c r="AD34" s="37" t="inlineStr">
         <is>
           <t>Event State</t>
         </is>
       </c>
-      <c r="AE34" s="454" t="n"/>
-      <c r="AF34" s="454" t="n"/>
-      <c r="AG34" s="454" t="n"/>
-      <c r="AH34" s="454" t="n"/>
-      <c r="AI34" s="455" t="inlineStr">
+      <c r="AE34" s="5" t="n"/>
+      <c r="AF34" s="5" t="n"/>
+      <c r="AG34" s="5" t="n"/>
+      <c r="AH34" s="6" t="n"/>
+      <c r="AI34" s="37" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AJ34" s="454" t="n"/>
-      <c r="AK34" s="454" t="n"/>
-      <c r="AL34" s="455" t="inlineStr">
+      <c r="AJ34" s="5" t="n"/>
+      <c r="AK34" s="6" t="n"/>
+      <c r="AL34" s="37" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="AM34" s="454" t="n"/>
-      <c r="AN34" s="456" t="n"/>
+      <c r="AM34" s="5" t="n"/>
+      <c r="AN34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="457">
+      <c r="A35" s="514">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B35" s="440" t="n"/>
-      <c r="C35" s="441" t="inlineStr">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>Released by</t>
         </is>
       </c>
-      <c r="D35" s="440" t="n"/>
-      <c r="E35" s="440" t="n"/>
-      <c r="F35" s="440" t="n"/>
-      <c r="G35" s="440" t="n"/>
-      <c r="H35" s="440" t="n"/>
-      <c r="I35" s="440" t="n"/>
-      <c r="J35" s="440" t="n"/>
-      <c r="K35" s="440" t="n"/>
-      <c r="L35" s="440" t="n"/>
-      <c r="M35" s="441" t="n"/>
-      <c r="N35" s="440" t="n"/>
-      <c r="O35" s="440" t="n"/>
-      <c r="P35" s="440" t="n"/>
-      <c r="Q35" s="440" t="n"/>
-      <c r="R35" s="440" t="n"/>
-      <c r="S35" s="440" t="n"/>
-      <c r="T35" s="440" t="n"/>
-      <c r="U35" s="440" t="n"/>
-      <c r="V35" s="440" t="n"/>
-      <c r="W35" s="440" t="n"/>
-      <c r="X35" s="440" t="n"/>
-      <c r="Y35" s="460" t="n"/>
-      <c r="Z35" s="440" t="n"/>
-      <c r="AA35" s="440" t="n"/>
-      <c r="AB35" s="440" t="n"/>
-      <c r="AC35" s="440" t="n"/>
-      <c r="AD35" s="460" t="n"/>
-      <c r="AE35" s="440" t="n"/>
-      <c r="AF35" s="440" t="n"/>
-      <c r="AG35" s="440" t="n"/>
-      <c r="AH35" s="440" t="n"/>
-      <c r="AI35" s="460" t="n"/>
-      <c r="AJ35" s="440" t="n"/>
-      <c r="AK35" s="440" t="n"/>
-      <c r="AL35" s="460" t="n"/>
-      <c r="AM35" s="440" t="n"/>
-      <c r="AN35" s="443" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="30" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="5" t="n"/>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="6" t="n"/>
+      <c r="Y35" s="517" t="n"/>
+      <c r="Z35" s="5" t="n"/>
+      <c r="AA35" s="5" t="n"/>
+      <c r="AB35" s="5" t="n"/>
+      <c r="AC35" s="6" t="n"/>
+      <c r="AD35" s="517" t="n"/>
+      <c r="AE35" s="5" t="n"/>
+      <c r="AF35" s="5" t="n"/>
+      <c r="AG35" s="5" t="n"/>
+      <c r="AH35" s="6" t="n"/>
+      <c r="AI35" s="517" t="n"/>
+      <c r="AJ35" s="5" t="n"/>
+      <c r="AK35" s="6" t="n"/>
+      <c r="AL35" s="517" t="n"/>
+      <c r="AM35" s="5" t="n"/>
+      <c r="AN35" s="8" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="462">
+      <c r="A36" s="519">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B36" s="330" t="n"/>
-      <c r="C36" s="445" t="inlineStr">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Printed by</t>
         </is>
       </c>
-      <c r="D36" s="330" t="n"/>
-      <c r="E36" s="330" t="n"/>
-      <c r="F36" s="330" t="n"/>
-      <c r="G36" s="330" t="n"/>
-      <c r="H36" s="330" t="n"/>
-      <c r="I36" s="330" t="n"/>
-      <c r="J36" s="330" t="n"/>
-      <c r="K36" s="330" t="n"/>
-      <c r="L36" s="330" t="n"/>
-      <c r="M36" s="445" t="n"/>
-      <c r="N36" s="330" t="n"/>
-      <c r="O36" s="330" t="n"/>
-      <c r="P36" s="330" t="n"/>
-      <c r="Q36" s="330" t="n"/>
-      <c r="R36" s="330" t="n"/>
-      <c r="S36" s="330" t="n"/>
-      <c r="T36" s="330" t="n"/>
-      <c r="U36" s="330" t="n"/>
-      <c r="V36" s="330" t="n"/>
-      <c r="W36" s="330" t="n"/>
-      <c r="X36" s="330" t="n"/>
-      <c r="Y36" s="466" t="n"/>
-      <c r="Z36" s="330" t="n"/>
-      <c r="AA36" s="330" t="n"/>
-      <c r="AB36" s="330" t="n"/>
-      <c r="AC36" s="330" t="n"/>
-      <c r="AD36" s="466" t="n"/>
-      <c r="AE36" s="330" t="n"/>
-      <c r="AF36" s="330" t="n"/>
-      <c r="AG36" s="330" t="n"/>
-      <c r="AH36" s="330" t="n"/>
-      <c r="AI36" s="466" t="n"/>
-      <c r="AJ36" s="330" t="n"/>
-      <c r="AK36" s="330" t="n"/>
-      <c r="AL36" s="466" t="n"/>
-      <c r="AM36" s="330" t="n"/>
-      <c r="AN36" s="447" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+      <c r="P36" s="12" t="n"/>
+      <c r="Q36" s="12" t="n"/>
+      <c r="R36" s="12" t="n"/>
+      <c r="S36" s="12" t="n"/>
+      <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="12" t="n"/>
+      <c r="W36" s="12" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="41" t="n"/>
+      <c r="Z36" s="12" t="n"/>
+      <c r="AA36" s="12" t="n"/>
+      <c r="AB36" s="12" t="n"/>
+      <c r="AC36" s="13" t="n"/>
+      <c r="AD36" s="41" t="n"/>
+      <c r="AE36" s="12" t="n"/>
+      <c r="AF36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n"/>
+      <c r="AH36" s="13" t="n"/>
+      <c r="AI36" s="41" t="n"/>
+      <c r="AJ36" s="12" t="n"/>
+      <c r="AK36" s="13" t="n"/>
+      <c r="AL36" s="41" t="n"/>
+      <c r="AM36" s="12" t="n"/>
+      <c r="AN36" s="15" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="462">
+      <c r="A37" s="519">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B37" s="330" t="n"/>
-      <c r="C37" s="445" t="inlineStr">
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>Verified application</t>
         </is>
       </c>
-      <c r="D37" s="330" t="n"/>
-      <c r="E37" s="330" t="n"/>
-      <c r="F37" s="330" t="n"/>
-      <c r="G37" s="330" t="n"/>
-      <c r="H37" s="330" t="n"/>
-      <c r="I37" s="330" t="n"/>
-      <c r="J37" s="330" t="n"/>
-      <c r="K37" s="330" t="n"/>
-      <c r="L37" s="330" t="n"/>
-      <c r="M37" s="445" t="n"/>
-      <c r="N37" s="330" t="n"/>
-      <c r="O37" s="330" t="n"/>
-      <c r="P37" s="330" t="n"/>
-      <c r="Q37" s="330" t="n"/>
-      <c r="R37" s="330" t="n"/>
-      <c r="S37" s="330" t="n"/>
-      <c r="T37" s="330" t="n"/>
-      <c r="U37" s="330" t="n"/>
-      <c r="V37" s="330" t="n"/>
-      <c r="W37" s="330" t="n"/>
-      <c r="X37" s="330" t="n"/>
-      <c r="Y37" s="466" t="n"/>
-      <c r="Z37" s="330" t="n"/>
-      <c r="AA37" s="330" t="n"/>
-      <c r="AB37" s="330" t="n"/>
-      <c r="AC37" s="330" t="n"/>
-      <c r="AD37" s="466" t="n"/>
-      <c r="AE37" s="330" t="n"/>
-      <c r="AF37" s="330" t="n"/>
-      <c r="AG37" s="330" t="n"/>
-      <c r="AH37" s="330" t="n"/>
-      <c r="AI37" s="466" t="n"/>
-      <c r="AJ37" s="330" t="n"/>
-      <c r="AK37" s="330" t="n"/>
-      <c r="AL37" s="466" t="n"/>
-      <c r="AM37" s="330" t="n"/>
-      <c r="AN37" s="447" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="12" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12" t="n"/>
+      <c r="U37" s="12" t="n"/>
+      <c r="V37" s="12" t="n"/>
+      <c r="W37" s="12" t="n"/>
+      <c r="X37" s="13" t="n"/>
+      <c r="Y37" s="41" t="n"/>
+      <c r="Z37" s="12" t="n"/>
+      <c r="AA37" s="12" t="n"/>
+      <c r="AB37" s="12" t="n"/>
+      <c r="AC37" s="13" t="n"/>
+      <c r="AD37" s="41" t="n"/>
+      <c r="AE37" s="12" t="n"/>
+      <c r="AF37" s="12" t="n"/>
+      <c r="AG37" s="12" t="n"/>
+      <c r="AH37" s="13" t="n"/>
+      <c r="AI37" s="41" t="n"/>
+      <c r="AJ37" s="12" t="n"/>
+      <c r="AK37" s="13" t="n"/>
+      <c r="AL37" s="41" t="n"/>
+      <c r="AM37" s="12" t="n"/>
+      <c r="AN37" s="15" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="462">
+      <c r="A38" s="519">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B38" s="330" t="n"/>
-      <c r="C38" s="445" t="inlineStr">
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>Void / scrap</t>
         </is>
       </c>
-      <c r="D38" s="330" t="n"/>
-      <c r="E38" s="330" t="n"/>
-      <c r="F38" s="330" t="n"/>
-      <c r="G38" s="330" t="n"/>
-      <c r="H38" s="330" t="n"/>
-      <c r="I38" s="330" t="n"/>
-      <c r="J38" s="330" t="n"/>
-      <c r="K38" s="330" t="n"/>
-      <c r="L38" s="330" t="n"/>
-      <c r="M38" s="445" t="n"/>
-      <c r="N38" s="330" t="n"/>
-      <c r="O38" s="330" t="n"/>
-      <c r="P38" s="330" t="n"/>
-      <c r="Q38" s="330" t="n"/>
-      <c r="R38" s="330" t="n"/>
-      <c r="S38" s="330" t="n"/>
-      <c r="T38" s="330" t="n"/>
-      <c r="U38" s="330" t="n"/>
-      <c r="V38" s="330" t="n"/>
-      <c r="W38" s="330" t="n"/>
-      <c r="X38" s="330" t="n"/>
-      <c r="Y38" s="466" t="n"/>
-      <c r="Z38" s="330" t="n"/>
-      <c r="AA38" s="330" t="n"/>
-      <c r="AB38" s="330" t="n"/>
-      <c r="AC38" s="330" t="n"/>
-      <c r="AD38" s="466" t="n"/>
-      <c r="AE38" s="330" t="n"/>
-      <c r="AF38" s="330" t="n"/>
-      <c r="AG38" s="330" t="n"/>
-      <c r="AH38" s="330" t="n"/>
-      <c r="AI38" s="466" t="n"/>
-      <c r="AJ38" s="330" t="n"/>
-      <c r="AK38" s="330" t="n"/>
-      <c r="AL38" s="466" t="n"/>
-      <c r="AM38" s="330" t="n"/>
-      <c r="AN38" s="447" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+      <c r="P38" s="12" t="n"/>
+      <c r="Q38" s="12" t="n"/>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n"/>
+      <c r="V38" s="12" t="n"/>
+      <c r="W38" s="12" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="41" t="n"/>
+      <c r="Z38" s="12" t="n"/>
+      <c r="AA38" s="12" t="n"/>
+      <c r="AB38" s="12" t="n"/>
+      <c r="AC38" s="13" t="n"/>
+      <c r="AD38" s="41" t="n"/>
+      <c r="AE38" s="12" t="n"/>
+      <c r="AF38" s="12" t="n"/>
+      <c r="AG38" s="12" t="n"/>
+      <c r="AH38" s="13" t="n"/>
+      <c r="AI38" s="41" t="n"/>
+      <c r="AJ38" s="12" t="n"/>
+      <c r="AK38" s="13" t="n"/>
+      <c r="AL38" s="41" t="n"/>
+      <c r="AM38" s="12" t="n"/>
+      <c r="AN38" s="15" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="468">
+      <c r="A39" s="520">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B39" s="449" t="n"/>
-      <c r="C39" s="450" t="inlineStr">
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>Reprint justification</t>
         </is>
       </c>
-      <c r="D39" s="449" t="n"/>
-      <c r="E39" s="449" t="n"/>
-      <c r="F39" s="449" t="n"/>
-      <c r="G39" s="449" t="n"/>
-      <c r="H39" s="449" t="n"/>
-      <c r="I39" s="449" t="n"/>
-      <c r="J39" s="449" t="n"/>
-      <c r="K39" s="449" t="n"/>
-      <c r="L39" s="449" t="n"/>
-      <c r="M39" s="450" t="n"/>
-      <c r="N39" s="449" t="n"/>
-      <c r="O39" s="449" t="n"/>
-      <c r="P39" s="449" t="n"/>
-      <c r="Q39" s="449" t="n"/>
-      <c r="R39" s="449" t="n"/>
-      <c r="S39" s="449" t="n"/>
-      <c r="T39" s="449" t="n"/>
-      <c r="U39" s="449" t="n"/>
-      <c r="V39" s="449" t="n"/>
-      <c r="W39" s="449" t="n"/>
-      <c r="X39" s="449" t="n"/>
-      <c r="Y39" s="472" t="n"/>
-      <c r="Z39" s="449" t="n"/>
-      <c r="AA39" s="449" t="n"/>
-      <c r="AB39" s="449" t="n"/>
-      <c r="AC39" s="449" t="n"/>
-      <c r="AD39" s="472" t="n"/>
-      <c r="AE39" s="449" t="n"/>
-      <c r="AF39" s="449" t="n"/>
-      <c r="AG39" s="449" t="n"/>
-      <c r="AH39" s="449" t="n"/>
-      <c r="AI39" s="472" t="n"/>
-      <c r="AJ39" s="449" t="n"/>
-      <c r="AK39" s="449" t="n"/>
-      <c r="AL39" s="472" t="n"/>
-      <c r="AM39" s="449" t="n"/>
-      <c r="AN39" s="452" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="23" t="n"/>
+      <c r="N39" s="19" t="n"/>
+      <c r="O39" s="19" t="n"/>
+      <c r="P39" s="19" t="n"/>
+      <c r="Q39" s="19" t="n"/>
+      <c r="R39" s="19" t="n"/>
+      <c r="S39" s="19" t="n"/>
+      <c r="T39" s="19" t="n"/>
+      <c r="U39" s="19" t="n"/>
+      <c r="V39" s="19" t="n"/>
+      <c r="W39" s="19" t="n"/>
+      <c r="X39" s="22" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="19" t="n"/>
+      <c r="AA39" s="19" t="n"/>
+      <c r="AB39" s="19" t="n"/>
+      <c r="AC39" s="22" t="n"/>
+      <c r="AD39" s="48" t="n"/>
+      <c r="AE39" s="19" t="n"/>
+      <c r="AF39" s="19" t="n"/>
+      <c r="AG39" s="19" t="n"/>
+      <c r="AH39" s="22" t="n"/>
+      <c r="AI39" s="48" t="n"/>
+      <c r="AJ39" s="19" t="n"/>
+      <c r="AK39" s="22" t="n"/>
+      <c r="AL39" s="48" t="n"/>
+      <c r="AM39" s="19" t="n"/>
+      <c r="AN39" s="24" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
-      <c r="A40" s="342" t="n"/>
-      <c r="B40" s="389" t="n"/>
-      <c r="C40" s="389" t="n"/>
-      <c r="D40" s="389" t="n"/>
-      <c r="E40" s="389" t="n"/>
-      <c r="F40" s="389" t="n"/>
-      <c r="G40" s="389" t="n"/>
-      <c r="H40" s="389" t="n"/>
-      <c r="I40" s="389" t="n"/>
-      <c r="J40" s="389" t="n"/>
-      <c r="K40" s="389" t="n"/>
-      <c r="L40" s="389" t="n"/>
-      <c r="M40" s="389" t="n"/>
-      <c r="N40" s="389" t="n"/>
-      <c r="O40" s="389" t="n"/>
-      <c r="P40" s="389" t="n"/>
-      <c r="Q40" s="389" t="n"/>
-      <c r="R40" s="389" t="n"/>
-      <c r="S40" s="389" t="n"/>
-      <c r="T40" s="389" t="n"/>
-      <c r="U40" s="389" t="n"/>
-      <c r="V40" s="389" t="n"/>
-      <c r="W40" s="389" t="n"/>
-      <c r="X40" s="389" t="n"/>
-      <c r="Y40" s="389" t="n"/>
-      <c r="Z40" s="389" t="n"/>
-      <c r="AA40" s="389" t="n"/>
-      <c r="AB40" s="389" t="n"/>
-      <c r="AC40" s="389" t="n"/>
-      <c r="AD40" s="389" t="n"/>
-      <c r="AE40" s="389" t="n"/>
-      <c r="AF40" s="389" t="n"/>
-      <c r="AG40" s="389" t="n"/>
-      <c r="AH40" s="389" t="n"/>
-      <c r="AI40" s="389" t="n"/>
-      <c r="AJ40" s="389" t="n"/>
-      <c r="AK40" s="389" t="n"/>
-      <c r="AL40" s="389" t="n"/>
-      <c r="AM40" s="389" t="n"/>
-      <c r="AN40" s="389" t="n"/>
+      <c r="A40" s="513" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="10" t="n"/>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="10" t="n"/>
+      <c r="AF40" s="10" t="n"/>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="10" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="10" t="n"/>
+      <c r="AN40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="436" t="inlineStr">
+      <c r="A41" s="506" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPLICATION STATUS / NOTES</t>
         </is>
       </c>
-      <c r="B41" s="437" t="n"/>
-      <c r="C41" s="437" t="n"/>
-      <c r="D41" s="437" t="n"/>
-      <c r="E41" s="437" t="n"/>
-      <c r="F41" s="437" t="n"/>
-      <c r="G41" s="437" t="n"/>
-      <c r="H41" s="437" t="n"/>
-      <c r="I41" s="437" t="n"/>
-      <c r="J41" s="437" t="n"/>
-      <c r="K41" s="437" t="n"/>
-      <c r="L41" s="437" t="n"/>
-      <c r="M41" s="437" t="n"/>
-      <c r="N41" s="437" t="n"/>
-      <c r="O41" s="437" t="n"/>
-      <c r="P41" s="437" t="n"/>
-      <c r="Q41" s="437" t="n"/>
-      <c r="R41" s="437" t="n"/>
-      <c r="S41" s="437" t="n"/>
-      <c r="T41" s="437" t="n"/>
-      <c r="U41" s="437" t="n"/>
-      <c r="V41" s="437" t="n"/>
-      <c r="W41" s="437" t="n"/>
-      <c r="X41" s="437" t="n"/>
-      <c r="Y41" s="437" t="n"/>
-      <c r="Z41" s="437" t="n"/>
-      <c r="AA41" s="437" t="n"/>
-      <c r="AB41" s="437" t="n"/>
-      <c r="AC41" s="437" t="n"/>
-      <c r="AD41" s="437" t="n"/>
-      <c r="AE41" s="437" t="n"/>
-      <c r="AF41" s="437" t="n"/>
-      <c r="AG41" s="437" t="n"/>
-      <c r="AH41" s="437" t="n"/>
-      <c r="AI41" s="437" t="n"/>
-      <c r="AJ41" s="437" t="n"/>
-      <c r="AK41" s="437" t="n"/>
-      <c r="AL41" s="437" t="n"/>
-      <c r="AM41" s="437" t="n"/>
-      <c r="AN41" s="438" t="n"/>
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="27" t="n"/>
+      <c r="L41" s="27" t="n"/>
+      <c r="M41" s="27" t="n"/>
+      <c r="N41" s="27" t="n"/>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="27" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="27" t="n"/>
+      <c r="T41" s="27" t="n"/>
+      <c r="U41" s="27" t="n"/>
+      <c r="V41" s="27" t="n"/>
+      <c r="W41" s="27" t="n"/>
+      <c r="X41" s="27" t="n"/>
+      <c r="Y41" s="27" t="n"/>
+      <c r="Z41" s="27" t="n"/>
+      <c r="AA41" s="27" t="n"/>
+      <c r="AB41" s="27" t="n"/>
+      <c r="AC41" s="27" t="n"/>
+      <c r="AD41" s="27" t="n"/>
+      <c r="AE41" s="27" t="n"/>
+      <c r="AF41" s="27" t="n"/>
+      <c r="AG41" s="27" t="n"/>
+      <c r="AH41" s="27" t="n"/>
+      <c r="AI41" s="27" t="n"/>
+      <c r="AJ41" s="27" t="n"/>
+      <c r="AK41" s="27" t="n"/>
+      <c r="AL41" s="27" t="n"/>
+      <c r="AM41" s="27" t="n"/>
+      <c r="AN41" s="28" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="457" t="inlineStr">
+      <c r="A42" s="514" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="B42" s="440" t="n"/>
-      <c r="C42" s="440" t="n"/>
-      <c r="D42" s="440" t="n"/>
-      <c r="E42" s="440" t="n"/>
-      <c r="F42" s="440" t="n"/>
-      <c r="G42" s="440" t="n"/>
-      <c r="H42" s="440" t="n"/>
-      <c r="I42" s="440" t="n"/>
-      <c r="J42" s="440" t="n"/>
-      <c r="K42" s="440" t="n"/>
-      <c r="L42" s="440" t="n"/>
-      <c r="M42" s="440" t="n"/>
-      <c r="N42" s="474" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="521" t="inlineStr">
         <is>
           <t>Printed by / Date-Time</t>
         </is>
       </c>
-      <c r="O42" s="440" t="n"/>
-      <c r="P42" s="440" t="n"/>
-      <c r="Q42" s="440" t="n"/>
-      <c r="R42" s="440" t="n"/>
-      <c r="S42" s="440" t="n"/>
-      <c r="T42" s="440" t="n"/>
-      <c r="U42" s="440" t="n"/>
-      <c r="V42" s="440" t="n"/>
-      <c r="W42" s="440" t="n"/>
-      <c r="X42" s="440" t="n"/>
-      <c r="Y42" s="440" t="n"/>
-      <c r="Z42" s="440" t="n"/>
-      <c r="AA42" s="474" t="inlineStr">
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="5" t="n"/>
+      <c r="V42" s="5" t="n"/>
+      <c r="W42" s="5" t="n"/>
+      <c r="X42" s="5" t="n"/>
+      <c r="Y42" s="5" t="n"/>
+      <c r="Z42" s="6" t="n"/>
+      <c r="AA42" s="521" t="inlineStr">
         <is>
           <t>Print Event State</t>
         </is>
       </c>
-      <c r="AB42" s="440" t="n"/>
-      <c r="AC42" s="440" t="n"/>
-      <c r="AD42" s="440" t="n"/>
-      <c r="AE42" s="440" t="n"/>
-      <c r="AF42" s="440" t="n"/>
-      <c r="AG42" s="440" t="n"/>
-      <c r="AH42" s="440" t="n"/>
-      <c r="AI42" s="440" t="n"/>
-      <c r="AJ42" s="440" t="n"/>
-      <c r="AK42" s="440" t="n"/>
-      <c r="AL42" s="440" t="n"/>
-      <c r="AM42" s="440" t="n"/>
-      <c r="AN42" s="443" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="5" t="n"/>
+      <c r="AD42" s="5" t="n"/>
+      <c r="AE42" s="5" t="n"/>
+      <c r="AF42" s="5" t="n"/>
+      <c r="AG42" s="5" t="n"/>
+      <c r="AH42" s="5" t="n"/>
+      <c r="AI42" s="5" t="n"/>
+      <c r="AJ42" s="5" t="n"/>
+      <c r="AK42" s="5" t="n"/>
+      <c r="AL42" s="5" t="n"/>
+      <c r="AM42" s="5" t="n"/>
+      <c r="AN42" s="8" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="475">
+      <c r="A43" s="522">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="B43" s="330" t="n"/>
-      <c r="C43" s="330" t="n"/>
-      <c r="D43" s="330" t="n"/>
-      <c r="E43" s="330" t="n"/>
-      <c r="F43" s="330" t="n"/>
-      <c r="G43" s="330" t="n"/>
-      <c r="H43" s="330" t="n"/>
-      <c r="I43" s="330" t="n"/>
-      <c r="J43" s="330" t="n"/>
-      <c r="K43" s="330" t="n"/>
-      <c r="L43" s="330" t="n"/>
-      <c r="M43" s="330" t="n"/>
-      <c r="N43" s="476">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="13" t="n"/>
+      <c r="N43" s="523">
         <f>IF(PRINT_CONTROL!$B$6="","",PRINT_CONTROL!$B$6)</f>
         <v/>
       </c>
-      <c r="O43" s="330" t="n"/>
-      <c r="P43" s="330" t="n"/>
-      <c r="Q43" s="330" t="n"/>
-      <c r="R43" s="330" t="n"/>
-      <c r="S43" s="330" t="n"/>
-      <c r="T43" s="330" t="n"/>
-      <c r="U43" s="330" t="n"/>
-      <c r="V43" s="330" t="n"/>
-      <c r="W43" s="330" t="n"/>
-      <c r="X43" s="330" t="n"/>
-      <c r="Y43" s="330" t="n"/>
-      <c r="Z43" s="330" t="n"/>
-      <c r="AA43" s="476">
+      <c r="O43" s="12" t="n"/>
+      <c r="P43" s="12" t="n"/>
+      <c r="Q43" s="12" t="n"/>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="12" t="n"/>
+      <c r="U43" s="12" t="n"/>
+      <c r="V43" s="12" t="n"/>
+      <c r="W43" s="12" t="n"/>
+      <c r="X43" s="12" t="n"/>
+      <c r="Y43" s="12" t="n"/>
+      <c r="Z43" s="13" t="n"/>
+      <c r="AA43" s="523">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="AB43" s="330" t="n"/>
-      <c r="AC43" s="330" t="n"/>
-      <c r="AD43" s="330" t="n"/>
-      <c r="AE43" s="330" t="n"/>
-      <c r="AF43" s="330" t="n"/>
-      <c r="AG43" s="330" t="n"/>
-      <c r="AH43" s="330" t="n"/>
-      <c r="AI43" s="330" t="n"/>
-      <c r="AJ43" s="330" t="n"/>
-      <c r="AK43" s="330" t="n"/>
-      <c r="AL43" s="330" t="n"/>
-      <c r="AM43" s="330" t="n"/>
-      <c r="AN43" s="447" t="n"/>
+      <c r="AB43" s="12" t="n"/>
+      <c r="AC43" s="12" t="n"/>
+      <c r="AD43" s="12" t="n"/>
+      <c r="AE43" s="12" t="n"/>
+      <c r="AF43" s="12" t="n"/>
+      <c r="AG43" s="12" t="n"/>
+      <c r="AH43" s="12" t="n"/>
+      <c r="AI43" s="12" t="n"/>
+      <c r="AJ43" s="12" t="n"/>
+      <c r="AK43" s="12" t="n"/>
+      <c r="AL43" s="12" t="n"/>
+      <c r="AM43" s="12" t="n"/>
+      <c r="AN43" s="15" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="477" t="n"/>
-      <c r="B44" s="330" t="n"/>
-      <c r="C44" s="330" t="n"/>
-      <c r="D44" s="330" t="n"/>
-      <c r="E44" s="330" t="n"/>
-      <c r="F44" s="330" t="n"/>
-      <c r="G44" s="330" t="n"/>
-      <c r="H44" s="330" t="n"/>
-      <c r="I44" s="330" t="n"/>
-      <c r="J44" s="330" t="n"/>
-      <c r="K44" s="330" t="n"/>
-      <c r="L44" s="330" t="n"/>
-      <c r="M44" s="330" t="n"/>
-      <c r="N44" s="478" t="n"/>
-      <c r="O44" s="330" t="n"/>
-      <c r="P44" s="330" t="n"/>
-      <c r="Q44" s="330" t="n"/>
-      <c r="R44" s="330" t="n"/>
-      <c r="S44" s="330" t="n"/>
-      <c r="T44" s="330" t="n"/>
-      <c r="U44" s="330" t="n"/>
-      <c r="V44" s="330" t="n"/>
-      <c r="W44" s="330" t="n"/>
-      <c r="X44" s="330" t="n"/>
-      <c r="Y44" s="330" t="n"/>
-      <c r="Z44" s="330" t="n"/>
-      <c r="AA44" s="478" t="n"/>
-      <c r="AB44" s="330" t="n"/>
-      <c r="AC44" s="330" t="n"/>
-      <c r="AD44" s="330" t="n"/>
-      <c r="AE44" s="330" t="n"/>
-      <c r="AF44" s="330" t="n"/>
-      <c r="AG44" s="330" t="n"/>
-      <c r="AH44" s="330" t="n"/>
-      <c r="AI44" s="330" t="n"/>
-      <c r="AJ44" s="330" t="n"/>
-      <c r="AK44" s="330" t="n"/>
-      <c r="AL44" s="330" t="n"/>
-      <c r="AM44" s="330" t="n"/>
-      <c r="AN44" s="447" t="n"/>
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="12" t="n"/>
+      <c r="P44" s="12" t="n"/>
+      <c r="Q44" s="12" t="n"/>
+      <c r="R44" s="12" t="n"/>
+      <c r="S44" s="12" t="n"/>
+      <c r="T44" s="12" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="12" t="n"/>
+      <c r="W44" s="12" t="n"/>
+      <c r="X44" s="12" t="n"/>
+      <c r="Y44" s="12" t="n"/>
+      <c r="Z44" s="13" t="n"/>
+      <c r="AA44" s="12" t="n"/>
+      <c r="AB44" s="12" t="n"/>
+      <c r="AC44" s="12" t="n"/>
+      <c r="AD44" s="12" t="n"/>
+      <c r="AE44" s="12" t="n"/>
+      <c r="AF44" s="12" t="n"/>
+      <c r="AG44" s="12" t="n"/>
+      <c r="AH44" s="12" t="n"/>
+      <c r="AI44" s="12" t="n"/>
+      <c r="AJ44" s="12" t="n"/>
+      <c r="AK44" s="12" t="n"/>
+      <c r="AL44" s="12" t="n"/>
+      <c r="AM44" s="12" t="n"/>
+      <c r="AN44" s="15" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="479" t="n"/>
-      <c r="B45" s="449" t="n"/>
-      <c r="C45" s="449" t="n"/>
-      <c r="D45" s="449" t="n"/>
-      <c r="E45" s="449" t="n"/>
-      <c r="F45" s="449" t="n"/>
-      <c r="G45" s="449" t="n"/>
-      <c r="H45" s="449" t="n"/>
-      <c r="I45" s="449" t="n"/>
-      <c r="J45" s="449" t="n"/>
-      <c r="K45" s="449" t="n"/>
-      <c r="L45" s="449" t="n"/>
-      <c r="M45" s="449" t="n"/>
-      <c r="N45" s="480" t="n"/>
-      <c r="O45" s="449" t="n"/>
-      <c r="P45" s="449" t="n"/>
-      <c r="Q45" s="449" t="n"/>
-      <c r="R45" s="449" t="n"/>
-      <c r="S45" s="449" t="n"/>
-      <c r="T45" s="449" t="n"/>
-      <c r="U45" s="449" t="n"/>
-      <c r="V45" s="449" t="n"/>
-      <c r="W45" s="449" t="n"/>
-      <c r="X45" s="449" t="n"/>
-      <c r="Y45" s="449" t="n"/>
-      <c r="Z45" s="449" t="n"/>
-      <c r="AA45" s="480" t="n"/>
-      <c r="AB45" s="449" t="n"/>
-      <c r="AC45" s="449" t="n"/>
-      <c r="AD45" s="449" t="n"/>
-      <c r="AE45" s="449" t="n"/>
-      <c r="AF45" s="449" t="n"/>
-      <c r="AG45" s="449" t="n"/>
-      <c r="AH45" s="449" t="n"/>
-      <c r="AI45" s="449" t="n"/>
-      <c r="AJ45" s="449" t="n"/>
-      <c r="AK45" s="449" t="n"/>
-      <c r="AL45" s="449" t="n"/>
-      <c r="AM45" s="449" t="n"/>
-      <c r="AN45" s="452" t="n"/>
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
+      <c r="J45" s="19" t="n"/>
+      <c r="K45" s="19" t="n"/>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="19" t="n"/>
+      <c r="O45" s="19" t="n"/>
+      <c r="P45" s="19" t="n"/>
+      <c r="Q45" s="19" t="n"/>
+      <c r="R45" s="19" t="n"/>
+      <c r="S45" s="19" t="n"/>
+      <c r="T45" s="19" t="n"/>
+      <c r="U45" s="19" t="n"/>
+      <c r="V45" s="19" t="n"/>
+      <c r="W45" s="19" t="n"/>
+      <c r="X45" s="19" t="n"/>
+      <c r="Y45" s="19" t="n"/>
+      <c r="Z45" s="22" t="n"/>
+      <c r="AA45" s="19" t="n"/>
+      <c r="AB45" s="19" t="n"/>
+      <c r="AC45" s="19" t="n"/>
+      <c r="AD45" s="19" t="n"/>
+      <c r="AE45" s="19" t="n"/>
+      <c r="AF45" s="19" t="n"/>
+      <c r="AG45" s="19" t="n"/>
+      <c r="AH45" s="19" t="n"/>
+      <c r="AI45" s="19" t="n"/>
+      <c r="AJ45" s="19" t="n"/>
+      <c r="AK45" s="19" t="n"/>
+      <c r="AL45" s="19" t="n"/>
+      <c r="AM45" s="19" t="n"/>
+      <c r="AN45" s="24" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
-      <c r="A46" s="342" t="n"/>
-      <c r="B46" s="389" t="n"/>
-      <c r="C46" s="389" t="n"/>
-      <c r="D46" s="389" t="n"/>
-      <c r="E46" s="389" t="n"/>
-      <c r="F46" s="389" t="n"/>
-      <c r="G46" s="389" t="n"/>
-      <c r="H46" s="389" t="n"/>
-      <c r="I46" s="389" t="n"/>
-      <c r="J46" s="389" t="n"/>
-      <c r="K46" s="389" t="n"/>
-      <c r="L46" s="389" t="n"/>
-      <c r="M46" s="389" t="n"/>
-      <c r="N46" s="389" t="n"/>
-      <c r="O46" s="389" t="n"/>
-      <c r="P46" s="389" t="n"/>
-      <c r="Q46" s="389" t="n"/>
-      <c r="R46" s="389" t="n"/>
-      <c r="S46" s="389" t="n"/>
-      <c r="T46" s="389" t="n"/>
-      <c r="U46" s="389" t="n"/>
-      <c r="V46" s="389" t="n"/>
-      <c r="W46" s="389" t="n"/>
-      <c r="X46" s="389" t="n"/>
-      <c r="Y46" s="389" t="n"/>
-      <c r="Z46" s="389" t="n"/>
-      <c r="AA46" s="389" t="n"/>
-      <c r="AB46" s="389" t="n"/>
-      <c r="AC46" s="389" t="n"/>
-      <c r="AD46" s="389" t="n"/>
-      <c r="AE46" s="389" t="n"/>
-      <c r="AF46" s="389" t="n"/>
-      <c r="AG46" s="389" t="n"/>
-      <c r="AH46" s="389" t="n"/>
-      <c r="AI46" s="389" t="n"/>
-      <c r="AJ46" s="389" t="n"/>
-      <c r="AK46" s="389" t="n"/>
-      <c r="AL46" s="389" t="n"/>
-      <c r="AM46" s="389" t="n"/>
-      <c r="AN46" s="389" t="n"/>
+      <c r="A46" s="513" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="10" t="n"/>
+      <c r="AL46" s="10" t="n"/>
+      <c r="AM46" s="10" t="n"/>
+      <c r="AN46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="436" t="inlineStr">
+      <c r="A47" s="506" t="inlineStr">
         <is>
           <t>NOTICE: Printed face only. No signature on the printed face. Record release, print, verify, void or scrap event in PRINT_CONTROL and PRINT_LOG.</t>
         </is>
       </c>
-      <c r="B47" s="437" t="n"/>
-      <c r="C47" s="437" t="n"/>
-      <c r="D47" s="437" t="n"/>
-      <c r="E47" s="437" t="n"/>
-      <c r="F47" s="437" t="n"/>
-      <c r="G47" s="437" t="n"/>
-      <c r="H47" s="437" t="n"/>
-      <c r="I47" s="437" t="n"/>
-      <c r="J47" s="437" t="n"/>
-      <c r="K47" s="437" t="n"/>
-      <c r="L47" s="437" t="n"/>
-      <c r="M47" s="437" t="n"/>
-      <c r="N47" s="437" t="n"/>
-      <c r="O47" s="437" t="n"/>
-      <c r="P47" s="437" t="n"/>
-      <c r="Q47" s="437" t="n"/>
-      <c r="R47" s="437" t="n"/>
-      <c r="S47" s="437" t="n"/>
-      <c r="T47" s="437" t="n"/>
-      <c r="U47" s="437" t="n"/>
-      <c r="V47" s="437" t="n"/>
-      <c r="W47" s="437" t="n"/>
-      <c r="X47" s="437" t="n"/>
-      <c r="Y47" s="437" t="n"/>
-      <c r="Z47" s="437" t="n"/>
-      <c r="AA47" s="437" t="n"/>
-      <c r="AB47" s="437" t="n"/>
-      <c r="AC47" s="437" t="n"/>
-      <c r="AD47" s="437" t="n"/>
-      <c r="AE47" s="437" t="n"/>
-      <c r="AF47" s="437" t="n"/>
-      <c r="AG47" s="437" t="n"/>
-      <c r="AH47" s="437" t="n"/>
-      <c r="AI47" s="437" t="n"/>
-      <c r="AJ47" s="437" t="n"/>
-      <c r="AK47" s="437" t="n"/>
-      <c r="AL47" s="437" t="n"/>
-      <c r="AM47" s="437" t="n"/>
-      <c r="AN47" s="438" t="n"/>
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
+      <c r="H47" s="27" t="n"/>
+      <c r="I47" s="27" t="n"/>
+      <c r="J47" s="27" t="n"/>
+      <c r="K47" s="27" t="n"/>
+      <c r="L47" s="27" t="n"/>
+      <c r="M47" s="27" t="n"/>
+      <c r="N47" s="27" t="n"/>
+      <c r="O47" s="27" t="n"/>
+      <c r="P47" s="27" t="n"/>
+      <c r="Q47" s="27" t="n"/>
+      <c r="R47" s="27" t="n"/>
+      <c r="S47" s="27" t="n"/>
+      <c r="T47" s="27" t="n"/>
+      <c r="U47" s="27" t="n"/>
+      <c r="V47" s="27" t="n"/>
+      <c r="W47" s="27" t="n"/>
+      <c r="X47" s="27" t="n"/>
+      <c r="Y47" s="27" t="n"/>
+      <c r="Z47" s="27" t="n"/>
+      <c r="AA47" s="27" t="n"/>
+      <c r="AB47" s="27" t="n"/>
+      <c r="AC47" s="27" t="n"/>
+      <c r="AD47" s="27" t="n"/>
+      <c r="AE47" s="27" t="n"/>
+      <c r="AF47" s="27" t="n"/>
+      <c r="AG47" s="27" t="n"/>
+      <c r="AH47" s="27" t="n"/>
+      <c r="AI47" s="27" t="n"/>
+      <c r="AJ47" s="27" t="n"/>
+      <c r="AK47" s="27" t="n"/>
+      <c r="AL47" s="27" t="n"/>
+      <c r="AM47" s="27" t="n"/>
+      <c r="AN47" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="181">
@@ -8297,7 +8859,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"-,Regular"&amp;7 FRM-703  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-703  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8313,7 +8875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8504,7 +9066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:CU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9667,7 +10229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:CU12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10307,7 +10869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:CU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11059,7 +11621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:CU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_FACE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PRINT_FACE'!$A$1:$AN$47</definedName>
@@ -775,7 +775,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="359">
+  <borders count="368">
     <border>
       <left/>
       <right/>
@@ -4636,11 +4636,117 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="559">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5849,6 +5955,93 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5950,6 +6143,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6309,266 +6505,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="489" t="inlineStr"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="53" t="n"/>
+      <c r="A1" s="524" t="inlineStr"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="320" t="n"/>
       <c r="I1" s="490" t="inlineStr">
         <is>
           <t>WIP Tag</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="491" t="inlineStr">
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="268" t="n"/>
+      <c r="L1" s="268" t="n"/>
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="268" t="n"/>
+      <c r="Q1" s="268" t="n"/>
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="525" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="492" t="n"/>
-      <c r="AI1" s="493" t="inlineStr">
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="526" t="n"/>
+      <c r="AI1" s="527" t="inlineStr">
         <is>
           <t>FRM-703</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="53" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="320" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="54" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="494" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="H2" s="321" t="n"/>
+      <c r="I2" s="275" t="n"/>
+      <c r="AE2" s="528" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="495" t="n"/>
-      <c r="AG2" s="495" t="n"/>
-      <c r="AH2" s="496" t="n"/>
-      <c r="AI2" s="497" t="inlineStr">
+      <c r="AF2" s="529" t="n"/>
+      <c r="AG2" s="529" t="n"/>
+      <c r="AH2" s="530" t="n"/>
+      <c r="AI2" s="531" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="495" t="n"/>
-      <c r="AK2" s="495" t="n"/>
-      <c r="AL2" s="495" t="n"/>
-      <c r="AM2" s="495" t="n"/>
-      <c r="AN2" s="498" t="n"/>
+      <c r="AJ2" s="529" t="n"/>
+      <c r="AK2" s="529" t="n"/>
+      <c r="AL2" s="529" t="n"/>
+      <c r="AM2" s="529" t="n"/>
+      <c r="AN2" s="532" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="54" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="494" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="H3" s="321" t="n"/>
+      <c r="I3" s="275" t="n"/>
+      <c r="AE3" s="528" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="495" t="n"/>
-      <c r="AG3" s="495" t="n"/>
-      <c r="AH3" s="496" t="n"/>
-      <c r="AI3" s="497" t="inlineStr">
+      <c r="AF3" s="529" t="n"/>
+      <c r="AG3" s="529" t="n"/>
+      <c r="AH3" s="530" t="n"/>
+      <c r="AI3" s="531" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="495" t="n"/>
-      <c r="AK3" s="495" t="n"/>
-      <c r="AL3" s="495" t="n"/>
-      <c r="AM3" s="495" t="n"/>
-      <c r="AN3" s="498" t="n"/>
+      <c r="AJ3" s="529" t="n"/>
+      <c r="AK3" s="529" t="n"/>
+      <c r="AL3" s="529" t="n"/>
+      <c r="AM3" s="529" t="n"/>
+      <c r="AN3" s="532" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="H4" s="321" t="n"/>
       <c r="I4" s="499" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="494" t="inlineStr">
+      <c r="AE4" s="528" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="495" t="n"/>
-      <c r="AG4" s="495" t="n"/>
-      <c r="AH4" s="496" t="n"/>
-      <c r="AI4" s="497" t="inlineStr">
+      <c r="AF4" s="529" t="n"/>
+      <c r="AG4" s="529" t="n"/>
+      <c r="AH4" s="530" t="n"/>
+      <c r="AI4" s="531" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="495" t="n"/>
-      <c r="AK4" s="495" t="n"/>
-      <c r="AL4" s="495" t="n"/>
-      <c r="AM4" s="495" t="n"/>
-      <c r="AN4" s="498" t="n"/>
+      <c r="AJ4" s="529" t="n"/>
+      <c r="AK4" s="529" t="n"/>
+      <c r="AL4" s="529" t="n"/>
+      <c r="AM4" s="529" t="n"/>
+      <c r="AN4" s="532" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="24" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="283" t="n"/>
+      <c r="C5" s="283" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="287" t="n"/>
       <c r="I5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="19" t="n"/>
-      <c r="L5" s="19" t="n"/>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="500" t="inlineStr">
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="283" t="n"/>
+      <c r="L5" s="283" t="n"/>
+      <c r="M5" s="283" t="n"/>
+      <c r="N5" s="283" t="n"/>
+      <c r="O5" s="283" t="n"/>
+      <c r="P5" s="283" t="n"/>
+      <c r="Q5" s="283" t="n"/>
+      <c r="R5" s="283" t="n"/>
+      <c r="S5" s="283" t="n"/>
+      <c r="T5" s="283" t="n"/>
+      <c r="U5" s="283" t="n"/>
+      <c r="V5" s="283" t="n"/>
+      <c r="W5" s="283" t="n"/>
+      <c r="X5" s="283" t="n"/>
+      <c r="Y5" s="283" t="n"/>
+      <c r="Z5" s="283" t="n"/>
+      <c r="AA5" s="283" t="n"/>
+      <c r="AB5" s="283" t="n"/>
+      <c r="AC5" s="283" t="n"/>
+      <c r="AD5" s="283" t="n"/>
+      <c r="AE5" s="533" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="501" t="n"/>
-      <c r="AG5" s="501" t="n"/>
-      <c r="AH5" s="502" t="n"/>
-      <c r="AI5" s="503" t="inlineStr">
+      <c r="AF5" s="534" t="n"/>
+      <c r="AG5" s="534" t="n"/>
+      <c r="AH5" s="535" t="n"/>
+      <c r="AI5" s="536" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="501" t="n"/>
-      <c r="AK5" s="501" t="n"/>
-      <c r="AL5" s="501" t="n"/>
-      <c r="AM5" s="501" t="n"/>
-      <c r="AN5" s="504" t="n"/>
+      <c r="AJ5" s="534" t="n"/>
+      <c r="AK5" s="534" t="n"/>
+      <c r="AL5" s="534" t="n"/>
+      <c r="AM5" s="534" t="n"/>
+      <c r="AN5" s="537" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="505" t="n"/>
@@ -6613,330 +6728,330 @@
       <c r="AN6" s="505" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="506" t="inlineStr">
+      <c r="A7" s="538" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. PRINT REQUEST / CONTROL CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="28" t="n"/>
+      <c r="B7" s="289" t="n"/>
+      <c r="C7" s="289" t="n"/>
+      <c r="D7" s="289" t="n"/>
+      <c r="E7" s="289" t="n"/>
+      <c r="F7" s="289" t="n"/>
+      <c r="G7" s="289" t="n"/>
+      <c r="H7" s="289" t="n"/>
+      <c r="I7" s="289" t="n"/>
+      <c r="J7" s="289" t="n"/>
+      <c r="K7" s="289" t="n"/>
+      <c r="L7" s="289" t="n"/>
+      <c r="M7" s="289" t="n"/>
+      <c r="N7" s="289" t="n"/>
+      <c r="O7" s="289" t="n"/>
+      <c r="P7" s="289" t="n"/>
+      <c r="Q7" s="289" t="n"/>
+      <c r="R7" s="289" t="n"/>
+      <c r="S7" s="289" t="n"/>
+      <c r="T7" s="289" t="n"/>
+      <c r="U7" s="289" t="n"/>
+      <c r="V7" s="289" t="n"/>
+      <c r="W7" s="289" t="n"/>
+      <c r="X7" s="289" t="n"/>
+      <c r="Y7" s="289" t="n"/>
+      <c r="Z7" s="289" t="n"/>
+      <c r="AA7" s="289" t="n"/>
+      <c r="AB7" s="289" t="n"/>
+      <c r="AC7" s="289" t="n"/>
+      <c r="AD7" s="289" t="n"/>
+      <c r="AE7" s="289" t="n"/>
+      <c r="AF7" s="289" t="n"/>
+      <c r="AG7" s="289" t="n"/>
+      <c r="AH7" s="289" t="n"/>
+      <c r="AI7" s="289" t="n"/>
+      <c r="AJ7" s="289" t="n"/>
+      <c r="AK7" s="289" t="n"/>
+      <c r="AL7" s="289" t="n"/>
+      <c r="AM7" s="289" t="n"/>
+      <c r="AN7" s="290" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="507" t="inlineStr">
+      <c r="A8" s="539" t="inlineStr">
         <is>
           <t>WIP Tag ID</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="30">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="272" t="n"/>
+      <c r="H8" s="292">
         <f>IF(GENERATOR!$B$5="","",GENERATOR!$B$5)</f>
         <v/>
       </c>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="508" t="inlineStr">
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="271" t="n"/>
+      <c r="K8" s="271" t="n"/>
+      <c r="L8" s="271" t="n"/>
+      <c r="M8" s="271" t="n"/>
+      <c r="N8" s="271" t="n"/>
+      <c r="O8" s="271" t="n"/>
+      <c r="P8" s="271" t="n"/>
+      <c r="Q8" s="271" t="n"/>
+      <c r="R8" s="271" t="n"/>
+      <c r="S8" s="271" t="n"/>
+      <c r="T8" s="272" t="n"/>
+      <c r="U8" s="540" t="inlineStr">
         <is>
           <t>Print Status</t>
         </is>
       </c>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="30">
+      <c r="V8" s="271" t="n"/>
+      <c r="W8" s="271" t="n"/>
+      <c r="X8" s="271" t="n"/>
+      <c r="Y8" s="271" t="n"/>
+      <c r="Z8" s="271" t="n"/>
+      <c r="AA8" s="272" t="n"/>
+      <c r="AB8" s="294">
         <f>IF(GENERATOR!$B$12="","",GENERATOR!$B$12)</f>
         <v/>
       </c>
-      <c r="AC8" s="5" t="n"/>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="5" t="n"/>
-      <c r="AN8" s="8" t="n"/>
+      <c r="AC8" s="271" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="271" t="n"/>
+      <c r="AM8" s="271" t="n"/>
+      <c r="AN8" s="274" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="509" t="inlineStr">
+      <c r="A9" s="541" t="inlineStr">
         <is>
           <t>Job / Lot / Part / Revision</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="14">
+      <c r="B9" s="277" t="n"/>
+      <c r="C9" s="277" t="n"/>
+      <c r="D9" s="277" t="n"/>
+      <c r="E9" s="277" t="n"/>
+      <c r="F9" s="277" t="n"/>
+      <c r="G9" s="278" t="n"/>
+      <c r="H9" s="296">
         <f>IF(GENERATOR!$B$6="","",GENERATOR!$B$6)</f>
         <v/>
       </c>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="510" t="inlineStr">
+      <c r="I9" s="277" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="277" t="n"/>
+      <c r="L9" s="277" t="n"/>
+      <c r="M9" s="277" t="n"/>
+      <c r="N9" s="277" t="n"/>
+      <c r="O9" s="277" t="n"/>
+      <c r="P9" s="277" t="n"/>
+      <c r="Q9" s="277" t="n"/>
+      <c r="R9" s="277" t="n"/>
+      <c r="S9" s="277" t="n"/>
+      <c r="T9" s="278" t="n"/>
+      <c r="U9" s="542" t="inlineStr">
         <is>
           <t>Current Operation / Qty</t>
         </is>
       </c>
-      <c r="V9" s="12" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="12" t="n"/>
-      <c r="Y9" s="12" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="14">
+      <c r="V9" s="277" t="n"/>
+      <c r="W9" s="277" t="n"/>
+      <c r="X9" s="277" t="n"/>
+      <c r="Y9" s="277" t="n"/>
+      <c r="Z9" s="277" t="n"/>
+      <c r="AA9" s="278" t="n"/>
+      <c r="AB9" s="279">
         <f>IF(GENERATOR!$B$13="","",GENERATOR!$B$13)</f>
         <v/>
       </c>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="12" t="n"/>
-      <c r="AN9" s="15" t="n"/>
+      <c r="AC9" s="277" t="n"/>
+      <c r="AD9" s="277" t="n"/>
+      <c r="AE9" s="277" t="n"/>
+      <c r="AF9" s="277" t="n"/>
+      <c r="AG9" s="277" t="n"/>
+      <c r="AH9" s="277" t="n"/>
+      <c r="AI9" s="277" t="n"/>
+      <c r="AJ9" s="277" t="n"/>
+      <c r="AK9" s="277" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="277" t="n"/>
+      <c r="AN9" s="280" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="509" t="inlineStr">
+      <c r="A10" s="541" t="inlineStr">
         <is>
           <t>Area / Location / Room</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="14">
+      <c r="B10" s="277" t="n"/>
+      <c r="C10" s="277" t="n"/>
+      <c r="D10" s="277" t="n"/>
+      <c r="E10" s="277" t="n"/>
+      <c r="F10" s="277" t="n"/>
+      <c r="G10" s="278" t="n"/>
+      <c r="H10" s="296">
         <f>IF(GENERATOR!$B$7="","",GENERATOR!$B$7)</f>
         <v/>
       </c>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="510" t="inlineStr">
+      <c r="I10" s="277" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="277" t="n"/>
+      <c r="L10" s="277" t="n"/>
+      <c r="M10" s="277" t="n"/>
+      <c r="N10" s="277" t="n"/>
+      <c r="O10" s="277" t="n"/>
+      <c r="P10" s="277" t="n"/>
+      <c r="Q10" s="277" t="n"/>
+      <c r="R10" s="277" t="n"/>
+      <c r="S10" s="277" t="n"/>
+      <c r="T10" s="278" t="n"/>
+      <c r="U10" s="542" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="V10" s="12" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="12" t="n"/>
-      <c r="Y10" s="12" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="14">
+      <c r="V10" s="277" t="n"/>
+      <c r="W10" s="277" t="n"/>
+      <c r="X10" s="277" t="n"/>
+      <c r="Y10" s="277" t="n"/>
+      <c r="Z10" s="277" t="n"/>
+      <c r="AA10" s="278" t="n"/>
+      <c r="AB10" s="279">
         <f>IF(GENERATOR!$B$14="","",GENERATOR!$B$14)</f>
         <v/>
       </c>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="12" t="n"/>
-      <c r="AN10" s="15" t="n"/>
+      <c r="AC10" s="277" t="n"/>
+      <c r="AD10" s="277" t="n"/>
+      <c r="AE10" s="277" t="n"/>
+      <c r="AF10" s="277" t="n"/>
+      <c r="AG10" s="277" t="n"/>
+      <c r="AH10" s="277" t="n"/>
+      <c r="AI10" s="277" t="n"/>
+      <c r="AJ10" s="277" t="n"/>
+      <c r="AK10" s="277" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="277" t="n"/>
+      <c r="AN10" s="280" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="509" t="inlineStr">
+      <c r="A11" s="541" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="14">
+      <c r="B11" s="277" t="n"/>
+      <c r="C11" s="277" t="n"/>
+      <c r="D11" s="277" t="n"/>
+      <c r="E11" s="277" t="n"/>
+      <c r="F11" s="277" t="n"/>
+      <c r="G11" s="278" t="n"/>
+      <c r="H11" s="296">
         <f>IF(GENERATOR!$B$8="","",GENERATOR!$B$8)</f>
         <v/>
       </c>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="510" t="inlineStr">
+      <c r="I11" s="277" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="277" t="n"/>
+      <c r="L11" s="277" t="n"/>
+      <c r="M11" s="277" t="n"/>
+      <c r="N11" s="277" t="n"/>
+      <c r="O11" s="277" t="n"/>
+      <c r="P11" s="277" t="n"/>
+      <c r="Q11" s="277" t="n"/>
+      <c r="R11" s="277" t="n"/>
+      <c r="S11" s="277" t="n"/>
+      <c r="T11" s="278" t="n"/>
+      <c r="U11" s="542" t="inlineStr">
         <is>
           <t>Print Qty / Application Status</t>
         </is>
       </c>
-      <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="12" t="n"/>
-      <c r="Y11" s="12" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="13" t="n"/>
-      <c r="AB11" s="14">
+      <c r="V11" s="277" t="n"/>
+      <c r="W11" s="277" t="n"/>
+      <c r="X11" s="277" t="n"/>
+      <c r="Y11" s="277" t="n"/>
+      <c r="Z11" s="277" t="n"/>
+      <c r="AA11" s="278" t="n"/>
+      <c r="AB11" s="279">
         <f>IF(GENERATOR!$B$15="","",GENERATOR!$B$15)</f>
         <v/>
       </c>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="12" t="n"/>
-      <c r="AN11" s="15" t="n"/>
+      <c r="AC11" s="277" t="n"/>
+      <c r="AD11" s="277" t="n"/>
+      <c r="AE11" s="277" t="n"/>
+      <c r="AF11" s="277" t="n"/>
+      <c r="AG11" s="277" t="n"/>
+      <c r="AH11" s="277" t="n"/>
+      <c r="AI11" s="277" t="n"/>
+      <c r="AJ11" s="277" t="n"/>
+      <c r="AK11" s="277" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="277" t="n"/>
+      <c r="AN11" s="280" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="511" t="inlineStr">
+      <c r="A12" s="543" t="inlineStr">
         <is>
           <t>Encoded Data Ref</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="23">
+      <c r="B12" s="283" t="n"/>
+      <c r="C12" s="283" t="n"/>
+      <c r="D12" s="283" t="n"/>
+      <c r="E12" s="283" t="n"/>
+      <c r="F12" s="283" t="n"/>
+      <c r="G12" s="285" t="n"/>
+      <c r="H12" s="299">
         <f>IF(GENERATOR!$B$9="","",GENERATOR!$B$9)</f>
         <v/>
       </c>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="19" t="n"/>
-      <c r="R12" s="19" t="n"/>
-      <c r="S12" s="19" t="n"/>
-      <c r="T12" s="22" t="n"/>
-      <c r="U12" s="512" t="inlineStr">
+      <c r="I12" s="283" t="n"/>
+      <c r="J12" s="283" t="n"/>
+      <c r="K12" s="283" t="n"/>
+      <c r="L12" s="283" t="n"/>
+      <c r="M12" s="283" t="n"/>
+      <c r="N12" s="283" t="n"/>
+      <c r="O12" s="283" t="n"/>
+      <c r="P12" s="283" t="n"/>
+      <c r="Q12" s="283" t="n"/>
+      <c r="R12" s="283" t="n"/>
+      <c r="S12" s="283" t="n"/>
+      <c r="T12" s="285" t="n"/>
+      <c r="U12" s="544" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="V12" s="19" t="n"/>
-      <c r="W12" s="19" t="n"/>
-      <c r="X12" s="19" t="n"/>
-      <c r="Y12" s="19" t="n"/>
-      <c r="Z12" s="19" t="n"/>
-      <c r="AA12" s="22" t="n"/>
-      <c r="AB12" s="23">
+      <c r="V12" s="283" t="n"/>
+      <c r="W12" s="283" t="n"/>
+      <c r="X12" s="283" t="n"/>
+      <c r="Y12" s="283" t="n"/>
+      <c r="Z12" s="283" t="n"/>
+      <c r="AA12" s="285" t="n"/>
+      <c r="AB12" s="286">
         <f>IF(GENERATOR!$B$16="","",GENERATOR!$B$16)</f>
         <v/>
       </c>
-      <c r="AC12" s="19" t="n"/>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
-      <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="19" t="n"/>
-      <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="19" t="n"/>
-      <c r="AM12" s="19" t="n"/>
-      <c r="AN12" s="24" t="n"/>
+      <c r="AC12" s="283" t="n"/>
+      <c r="AD12" s="283" t="n"/>
+      <c r="AE12" s="283" t="n"/>
+      <c r="AF12" s="283" t="n"/>
+      <c r="AG12" s="283" t="n"/>
+      <c r="AH12" s="283" t="n"/>
+      <c r="AI12" s="283" t="n"/>
+      <c r="AJ12" s="283" t="n"/>
+      <c r="AK12" s="283" t="n"/>
+      <c r="AL12" s="283" t="n"/>
+      <c r="AM12" s="283" t="n"/>
+      <c r="AN12" s="287" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="513" t="n"/>
@@ -6981,274 +7096,274 @@
       <c r="AN13" s="10" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="506" t="inlineStr">
+      <c r="A14" s="538" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. PRINTED FACE / CONTROLLED IDENTITY</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="27" t="n"/>
-      <c r="U14" s="27" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="27" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="27" t="n"/>
-      <c r="Z14" s="27" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="27" t="n"/>
-      <c r="AC14" s="27" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="27" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="27" t="n"/>
-      <c r="AH14" s="27" t="n"/>
-      <c r="AI14" s="27" t="n"/>
-      <c r="AJ14" s="27" t="n"/>
-      <c r="AK14" s="27" t="n"/>
-      <c r="AL14" s="27" t="n"/>
-      <c r="AM14" s="27" t="n"/>
-      <c r="AN14" s="28" t="n"/>
+      <c r="B14" s="289" t="n"/>
+      <c r="C14" s="289" t="n"/>
+      <c r="D14" s="289" t="n"/>
+      <c r="E14" s="289" t="n"/>
+      <c r="F14" s="289" t="n"/>
+      <c r="G14" s="289" t="n"/>
+      <c r="H14" s="289" t="n"/>
+      <c r="I14" s="289" t="n"/>
+      <c r="J14" s="289" t="n"/>
+      <c r="K14" s="289" t="n"/>
+      <c r="L14" s="289" t="n"/>
+      <c r="M14" s="289" t="n"/>
+      <c r="N14" s="289" t="n"/>
+      <c r="O14" s="289" t="n"/>
+      <c r="P14" s="289" t="n"/>
+      <c r="Q14" s="289" t="n"/>
+      <c r="R14" s="289" t="n"/>
+      <c r="S14" s="289" t="n"/>
+      <c r="T14" s="289" t="n"/>
+      <c r="U14" s="289" t="n"/>
+      <c r="V14" s="289" t="n"/>
+      <c r="W14" s="289" t="n"/>
+      <c r="X14" s="289" t="n"/>
+      <c r="Y14" s="289" t="n"/>
+      <c r="Z14" s="289" t="n"/>
+      <c r="AA14" s="289" t="n"/>
+      <c r="AB14" s="289" t="n"/>
+      <c r="AC14" s="289" t="n"/>
+      <c r="AD14" s="289" t="n"/>
+      <c r="AE14" s="289" t="n"/>
+      <c r="AF14" s="289" t="n"/>
+      <c r="AG14" s="289" t="n"/>
+      <c r="AH14" s="289" t="n"/>
+      <c r="AI14" s="289" t="n"/>
+      <c r="AJ14" s="289" t="n"/>
+      <c r="AK14" s="289" t="n"/>
+      <c r="AL14" s="289" t="n"/>
+      <c r="AM14" s="289" t="n"/>
+      <c r="AN14" s="290" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="507" t="inlineStr">
+      <c r="A15" s="539" t="inlineStr">
         <is>
           <t>Tag Face / Status</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="30">
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="271" t="n"/>
+      <c r="D15" s="271" t="n"/>
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="272" t="n"/>
+      <c r="H15" s="292">
         <f>IF(GENERATOR!$B$19="","",GENERATOR!$B$19)</f>
         <v/>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="6" t="n"/>
-      <c r="U15" s="508" t="inlineStr">
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="271" t="n"/>
+      <c r="N15" s="271" t="n"/>
+      <c r="O15" s="271" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="272" t="n"/>
+      <c r="U15" s="540" t="inlineStr">
         <is>
           <t>Operation / Workcenter</t>
         </is>
       </c>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="5" t="n"/>
-      <c r="AA15" s="6" t="n"/>
-      <c r="AB15" s="30">
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="271" t="n"/>
+      <c r="AA15" s="272" t="n"/>
+      <c r="AB15" s="294">
         <f>IF(GENERATOR!$B$20="","",GENERATOR!$B$20)</f>
         <v/>
       </c>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="5" t="n"/>
-      <c r="AH15" s="5" t="n"/>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="8" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="271" t="n"/>
+      <c r="AH15" s="271" t="n"/>
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="271" t="n"/>
+      <c r="AL15" s="271" t="n"/>
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="509" t="inlineStr">
+      <c r="A16" s="541" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14">
+      <c r="B16" s="277" t="n"/>
+      <c r="C16" s="277" t="n"/>
+      <c r="D16" s="277" t="n"/>
+      <c r="E16" s="277" t="n"/>
+      <c r="F16" s="277" t="n"/>
+      <c r="G16" s="278" t="n"/>
+      <c r="H16" s="296">
         <f>IF(GENERATOR!$B$21="","",GENERATOR!$B$21)</f>
         <v/>
       </c>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="510" t="inlineStr">
+      <c r="I16" s="277" t="n"/>
+      <c r="J16" s="277" t="n"/>
+      <c r="K16" s="277" t="n"/>
+      <c r="L16" s="277" t="n"/>
+      <c r="M16" s="277" t="n"/>
+      <c r="N16" s="277" t="n"/>
+      <c r="O16" s="277" t="n"/>
+      <c r="P16" s="277" t="n"/>
+      <c r="Q16" s="277" t="n"/>
+      <c r="R16" s="277" t="n"/>
+      <c r="S16" s="277" t="n"/>
+      <c r="T16" s="278" t="n"/>
+      <c r="U16" s="542" t="inlineStr">
         <is>
           <t>Lot / Quantity</t>
         </is>
       </c>
-      <c r="V16" s="12" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="12" t="n"/>
-      <c r="Y16" s="12" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="13" t="n"/>
-      <c r="AB16" s="14">
+      <c r="V16" s="277" t="n"/>
+      <c r="W16" s="277" t="n"/>
+      <c r="X16" s="277" t="n"/>
+      <c r="Y16" s="277" t="n"/>
+      <c r="Z16" s="277" t="n"/>
+      <c r="AA16" s="278" t="n"/>
+      <c r="AB16" s="279">
         <f>IF(GENERATOR!$B$22="","",GENERATOR!$B$22)</f>
         <v/>
       </c>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="12" t="n"/>
-      <c r="AE16" s="12" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="12" t="n"/>
-      <c r="AH16" s="12" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="12" t="n"/>
-      <c r="AK16" s="12" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="12" t="n"/>
-      <c r="AN16" s="15" t="n"/>
+      <c r="AC16" s="277" t="n"/>
+      <c r="AD16" s="277" t="n"/>
+      <c r="AE16" s="277" t="n"/>
+      <c r="AF16" s="277" t="n"/>
+      <c r="AG16" s="277" t="n"/>
+      <c r="AH16" s="277" t="n"/>
+      <c r="AI16" s="277" t="n"/>
+      <c r="AJ16" s="277" t="n"/>
+      <c r="AK16" s="277" t="n"/>
+      <c r="AL16" s="277" t="n"/>
+      <c r="AM16" s="277" t="n"/>
+      <c r="AN16" s="280" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="509" t="inlineStr">
+      <c r="A17" s="541" t="inlineStr">
         <is>
           <t>Job / Route Step</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="14">
+      <c r="B17" s="277" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="277" t="n"/>
+      <c r="E17" s="277" t="n"/>
+      <c r="F17" s="277" t="n"/>
+      <c r="G17" s="278" t="n"/>
+      <c r="H17" s="296">
         <f>IF(GENERATOR!$B$23="","",GENERATOR!$B$23)</f>
         <v/>
       </c>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="510" t="inlineStr">
+      <c r="I17" s="277" t="n"/>
+      <c r="J17" s="277" t="n"/>
+      <c r="K17" s="277" t="n"/>
+      <c r="L17" s="277" t="n"/>
+      <c r="M17" s="277" t="n"/>
+      <c r="N17" s="277" t="n"/>
+      <c r="O17" s="277" t="n"/>
+      <c r="P17" s="277" t="n"/>
+      <c r="Q17" s="277" t="n"/>
+      <c r="R17" s="277" t="n"/>
+      <c r="S17" s="277" t="n"/>
+      <c r="T17" s="278" t="n"/>
+      <c r="U17" s="542" t="inlineStr">
         <is>
           <t>Area / Location</t>
         </is>
       </c>
-      <c r="V17" s="12" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="12" t="n"/>
-      <c r="Y17" s="12" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="13" t="n"/>
-      <c r="AB17" s="14">
+      <c r="V17" s="277" t="n"/>
+      <c r="W17" s="277" t="n"/>
+      <c r="X17" s="277" t="n"/>
+      <c r="Y17" s="277" t="n"/>
+      <c r="Z17" s="277" t="n"/>
+      <c r="AA17" s="278" t="n"/>
+      <c r="AB17" s="279">
         <f>IF(GENERATOR!$B$24="","",GENERATOR!$B$24)</f>
         <v/>
       </c>
-      <c r="AC17" s="12" t="n"/>
-      <c r="AD17" s="12" t="n"/>
-      <c r="AE17" s="12" t="n"/>
-      <c r="AF17" s="12" t="n"/>
-      <c r="AG17" s="12" t="n"/>
-      <c r="AH17" s="12" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="12" t="n"/>
-      <c r="AK17" s="12" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="12" t="n"/>
-      <c r="AN17" s="15" t="n"/>
+      <c r="AC17" s="277" t="n"/>
+      <c r="AD17" s="277" t="n"/>
+      <c r="AE17" s="277" t="n"/>
+      <c r="AF17" s="277" t="n"/>
+      <c r="AG17" s="277" t="n"/>
+      <c r="AH17" s="277" t="n"/>
+      <c r="AI17" s="277" t="n"/>
+      <c r="AJ17" s="277" t="n"/>
+      <c r="AK17" s="277" t="n"/>
+      <c r="AL17" s="277" t="n"/>
+      <c r="AM17" s="277" t="n"/>
+      <c r="AN17" s="280" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="511" t="inlineStr">
+      <c r="A18" s="543" t="inlineStr">
         <is>
           <t>Encoded String / Barcode Ref</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="23">
+      <c r="B18" s="283" t="n"/>
+      <c r="C18" s="283" t="n"/>
+      <c r="D18" s="283" t="n"/>
+      <c r="E18" s="283" t="n"/>
+      <c r="F18" s="283" t="n"/>
+      <c r="G18" s="285" t="n"/>
+      <c r="H18" s="299">
         <f>IF(GENERATOR!$B$25="","",GENERATOR!$B$25)</f>
         <v/>
       </c>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="19" t="n"/>
-      <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
-      <c r="N18" s="19" t="n"/>
-      <c r="O18" s="19" t="n"/>
-      <c r="P18" s="19" t="n"/>
-      <c r="Q18" s="19" t="n"/>
-      <c r="R18" s="19" t="n"/>
-      <c r="S18" s="19" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="512" t="inlineStr">
+      <c r="I18" s="283" t="n"/>
+      <c r="J18" s="283" t="n"/>
+      <c r="K18" s="283" t="n"/>
+      <c r="L18" s="283" t="n"/>
+      <c r="M18" s="283" t="n"/>
+      <c r="N18" s="283" t="n"/>
+      <c r="O18" s="283" t="n"/>
+      <c r="P18" s="283" t="n"/>
+      <c r="Q18" s="283" t="n"/>
+      <c r="R18" s="283" t="n"/>
+      <c r="S18" s="283" t="n"/>
+      <c r="T18" s="285" t="n"/>
+      <c r="U18" s="544" t="inlineStr">
         <is>
           <t>Application Note</t>
         </is>
       </c>
-      <c r="V18" s="19" t="n"/>
-      <c r="W18" s="19" t="n"/>
-      <c r="X18" s="19" t="n"/>
-      <c r="Y18" s="19" t="n"/>
-      <c r="Z18" s="19" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="23">
+      <c r="V18" s="283" t="n"/>
+      <c r="W18" s="283" t="n"/>
+      <c r="X18" s="283" t="n"/>
+      <c r="Y18" s="283" t="n"/>
+      <c r="Z18" s="283" t="n"/>
+      <c r="AA18" s="285" t="n"/>
+      <c r="AB18" s="286">
         <f>IF(GENERATOR!$B$26="","",GENERATOR!$B$26)</f>
         <v/>
       </c>
-      <c r="AC18" s="19" t="n"/>
-      <c r="AD18" s="19" t="n"/>
-      <c r="AE18" s="19" t="n"/>
-      <c r="AF18" s="19" t="n"/>
-      <c r="AG18" s="19" t="n"/>
-      <c r="AH18" s="19" t="n"/>
-      <c r="AI18" s="19" t="n"/>
-      <c r="AJ18" s="19" t="n"/>
-      <c r="AK18" s="19" t="n"/>
-      <c r="AL18" s="19" t="n"/>
-      <c r="AM18" s="19" t="n"/>
-      <c r="AN18" s="24" t="n"/>
+      <c r="AC18" s="283" t="n"/>
+      <c r="AD18" s="283" t="n"/>
+      <c r="AE18" s="283" t="n"/>
+      <c r="AF18" s="283" t="n"/>
+      <c r="AG18" s="283" t="n"/>
+      <c r="AH18" s="283" t="n"/>
+      <c r="AI18" s="283" t="n"/>
+      <c r="AJ18" s="283" t="n"/>
+      <c r="AK18" s="283" t="n"/>
+      <c r="AL18" s="283" t="n"/>
+      <c r="AM18" s="283" t="n"/>
+      <c r="AN18" s="287" t="n"/>
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="513" t="n"/>
@@ -7293,615 +7408,615 @@
       <c r="AN19" s="10" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="506" t="inlineStr">
+      <c r="A20" s="538" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. VERIFICATION / APPLICATION CHECK</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="27" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="27" t="n"/>
-      <c r="T20" s="27" t="n"/>
-      <c r="U20" s="27" t="n"/>
-      <c r="V20" s="27" t="n"/>
-      <c r="W20" s="27" t="n"/>
-      <c r="X20" s="27" t="n"/>
-      <c r="Y20" s="27" t="n"/>
-      <c r="Z20" s="27" t="n"/>
-      <c r="AA20" s="27" t="n"/>
-      <c r="AB20" s="27" t="n"/>
-      <c r="AC20" s="27" t="n"/>
-      <c r="AD20" s="27" t="n"/>
-      <c r="AE20" s="27" t="n"/>
-      <c r="AF20" s="27" t="n"/>
-      <c r="AG20" s="27" t="n"/>
-      <c r="AH20" s="27" t="n"/>
-      <c r="AI20" s="27" t="n"/>
-      <c r="AJ20" s="27" t="n"/>
-      <c r="AK20" s="27" t="n"/>
-      <c r="AL20" s="27" t="n"/>
-      <c r="AM20" s="27" t="n"/>
-      <c r="AN20" s="28" t="n"/>
+      <c r="B20" s="289" t="n"/>
+      <c r="C20" s="289" t="n"/>
+      <c r="D20" s="289" t="n"/>
+      <c r="E20" s="289" t="n"/>
+      <c r="F20" s="289" t="n"/>
+      <c r="G20" s="289" t="n"/>
+      <c r="H20" s="289" t="n"/>
+      <c r="I20" s="289" t="n"/>
+      <c r="J20" s="289" t="n"/>
+      <c r="K20" s="289" t="n"/>
+      <c r="L20" s="289" t="n"/>
+      <c r="M20" s="289" t="n"/>
+      <c r="N20" s="289" t="n"/>
+      <c r="O20" s="289" t="n"/>
+      <c r="P20" s="289" t="n"/>
+      <c r="Q20" s="289" t="n"/>
+      <c r="R20" s="289" t="n"/>
+      <c r="S20" s="289" t="n"/>
+      <c r="T20" s="289" t="n"/>
+      <c r="U20" s="289" t="n"/>
+      <c r="V20" s="289" t="n"/>
+      <c r="W20" s="289" t="n"/>
+      <c r="X20" s="289" t="n"/>
+      <c r="Y20" s="289" t="n"/>
+      <c r="Z20" s="289" t="n"/>
+      <c r="AA20" s="289" t="n"/>
+      <c r="AB20" s="289" t="n"/>
+      <c r="AC20" s="289" t="n"/>
+      <c r="AD20" s="289" t="n"/>
+      <c r="AE20" s="289" t="n"/>
+      <c r="AF20" s="289" t="n"/>
+      <c r="AG20" s="289" t="n"/>
+      <c r="AH20" s="289" t="n"/>
+      <c r="AI20" s="289" t="n"/>
+      <c r="AJ20" s="289" t="n"/>
+      <c r="AK20" s="289" t="n"/>
+      <c r="AL20" s="289" t="n"/>
+      <c r="AM20" s="289" t="n"/>
+      <c r="AN20" s="290" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="B21" s="272" t="n"/>
+      <c r="C21" s="302" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="37" t="inlineStr">
+      <c r="D21" s="271" t="n"/>
+      <c r="E21" s="272" t="n"/>
+      <c r="F21" s="302" t="inlineStr">
         <is>
           <t>Verification Check</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="6" t="n"/>
-      <c r="T21" s="37" t="inlineStr">
+      <c r="G21" s="271" t="n"/>
+      <c r="H21" s="271" t="n"/>
+      <c r="I21" s="271" t="n"/>
+      <c r="J21" s="271" t="n"/>
+      <c r="K21" s="271" t="n"/>
+      <c r="L21" s="271" t="n"/>
+      <c r="M21" s="271" t="n"/>
+      <c r="N21" s="271" t="n"/>
+      <c r="O21" s="271" t="n"/>
+      <c r="P21" s="271" t="n"/>
+      <c r="Q21" s="271" t="n"/>
+      <c r="R21" s="271" t="n"/>
+      <c r="S21" s="272" t="n"/>
+      <c r="T21" s="302" t="inlineStr">
         <is>
           <t>Acceptance Rule</t>
         </is>
       </c>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-      <c r="Y21" s="5" t="n"/>
-      <c r="Z21" s="5" t="n"/>
-      <c r="AA21" s="5" t="n"/>
-      <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="5" t="n"/>
-      <c r="AD21" s="5" t="n"/>
-      <c r="AE21" s="6" t="n"/>
-      <c r="AF21" s="37" t="inlineStr">
+      <c r="U21" s="271" t="n"/>
+      <c r="V21" s="271" t="n"/>
+      <c r="W21" s="271" t="n"/>
+      <c r="X21" s="271" t="n"/>
+      <c r="Y21" s="271" t="n"/>
+      <c r="Z21" s="271" t="n"/>
+      <c r="AA21" s="271" t="n"/>
+      <c r="AB21" s="271" t="n"/>
+      <c r="AC21" s="271" t="n"/>
+      <c r="AD21" s="271" t="n"/>
+      <c r="AE21" s="272" t="n"/>
+      <c r="AF21" s="302" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG21" s="5" t="n"/>
-      <c r="AH21" s="5" t="n"/>
-      <c r="AI21" s="6" t="n"/>
-      <c r="AJ21" s="37" t="inlineStr">
+      <c r="AG21" s="271" t="n"/>
+      <c r="AH21" s="271" t="n"/>
+      <c r="AI21" s="272" t="n"/>
+      <c r="AJ21" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK21" s="5" t="n"/>
-      <c r="AL21" s="6" t="n"/>
-      <c r="AM21" s="37" t="inlineStr">
+      <c r="AK21" s="271" t="n"/>
+      <c r="AL21" s="272" t="n"/>
+      <c r="AM21" s="303" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="n"/>
+      <c r="AN21" s="274" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="514">
+      <c r="A22" s="545">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="515" t="inlineStr">
+      <c r="B22" s="272" t="n"/>
+      <c r="C22" s="546" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="D22" s="271" t="n"/>
+      <c r="E22" s="272" t="n"/>
+      <c r="F22" s="292" t="inlineStr">
         <is>
           <t>Identity match</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="516" t="inlineStr">
+      <c r="G22" s="271" t="n"/>
+      <c r="H22" s="271" t="n"/>
+      <c r="I22" s="271" t="n"/>
+      <c r="J22" s="271" t="n"/>
+      <c r="K22" s="271" t="n"/>
+      <c r="L22" s="271" t="n"/>
+      <c r="M22" s="271" t="n"/>
+      <c r="N22" s="271" t="n"/>
+      <c r="O22" s="271" t="n"/>
+      <c r="P22" s="271" t="n"/>
+      <c r="Q22" s="271" t="n"/>
+      <c r="R22" s="271" t="n"/>
+      <c r="S22" s="272" t="n"/>
+      <c r="T22" s="547" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-      <c r="Y22" s="5" t="n"/>
-      <c r="Z22" s="5" t="n"/>
-      <c r="AA22" s="5" t="n"/>
-      <c r="AB22" s="5" t="n"/>
-      <c r="AC22" s="5" t="n"/>
-      <c r="AD22" s="5" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="517" t="n"/>
-      <c r="AG22" s="5" t="n"/>
-      <c r="AH22" s="5" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="517" t="n"/>
-      <c r="AK22" s="5" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="518" t="n"/>
-      <c r="AN22" s="8" t="n"/>
+      <c r="U22" s="271" t="n"/>
+      <c r="V22" s="271" t="n"/>
+      <c r="W22" s="271" t="n"/>
+      <c r="X22" s="271" t="n"/>
+      <c r="Y22" s="271" t="n"/>
+      <c r="Z22" s="271" t="n"/>
+      <c r="AA22" s="271" t="n"/>
+      <c r="AB22" s="271" t="n"/>
+      <c r="AC22" s="271" t="n"/>
+      <c r="AD22" s="271" t="n"/>
+      <c r="AE22" s="272" t="n"/>
+      <c r="AF22" s="548" t="n"/>
+      <c r="AG22" s="271" t="n"/>
+      <c r="AH22" s="271" t="n"/>
+      <c r="AI22" s="272" t="n"/>
+      <c r="AJ22" s="548" t="n"/>
+      <c r="AK22" s="271" t="n"/>
+      <c r="AL22" s="272" t="n"/>
+      <c r="AM22" s="549" t="n"/>
+      <c r="AN22" s="274" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="519">
+      <c r="A23" s="550">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="B23" s="278" t="n"/>
+      <c r="C23" s="305" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="D23" s="277" t="n"/>
+      <c r="E23" s="278" t="n"/>
+      <c r="F23" s="309" t="inlineStr">
         <is>
           <t>Readable print</t>
         </is>
       </c>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="12" t="n"/>
-      <c r="R23" s="12" t="n"/>
-      <c r="S23" s="13" t="n"/>
-      <c r="T23" s="40" t="inlineStr">
+      <c r="G23" s="277" t="n"/>
+      <c r="H23" s="277" t="n"/>
+      <c r="I23" s="277" t="n"/>
+      <c r="J23" s="277" t="n"/>
+      <c r="K23" s="277" t="n"/>
+      <c r="L23" s="277" t="n"/>
+      <c r="M23" s="277" t="n"/>
+      <c r="N23" s="277" t="n"/>
+      <c r="O23" s="277" t="n"/>
+      <c r="P23" s="277" t="n"/>
+      <c r="Q23" s="277" t="n"/>
+      <c r="R23" s="277" t="n"/>
+      <c r="S23" s="278" t="n"/>
+      <c r="T23" s="306" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="12" t="n"/>
-      <c r="W23" s="12" t="n"/>
-      <c r="X23" s="12" t="n"/>
-      <c r="Y23" s="12" t="n"/>
-      <c r="Z23" s="12" t="n"/>
-      <c r="AA23" s="12" t="n"/>
-      <c r="AB23" s="12" t="n"/>
-      <c r="AC23" s="12" t="n"/>
-      <c r="AD23" s="12" t="n"/>
-      <c r="AE23" s="13" t="n"/>
-      <c r="AF23" s="41" t="n"/>
-      <c r="AG23" s="12" t="n"/>
-      <c r="AH23" s="12" t="n"/>
-      <c r="AI23" s="13" t="n"/>
-      <c r="AJ23" s="41" t="n"/>
-      <c r="AK23" s="12" t="n"/>
-      <c r="AL23" s="13" t="n"/>
-      <c r="AM23" s="42" t="n"/>
-      <c r="AN23" s="15" t="n"/>
+      <c r="U23" s="277" t="n"/>
+      <c r="V23" s="277" t="n"/>
+      <c r="W23" s="277" t="n"/>
+      <c r="X23" s="277" t="n"/>
+      <c r="Y23" s="277" t="n"/>
+      <c r="Z23" s="277" t="n"/>
+      <c r="AA23" s="277" t="n"/>
+      <c r="AB23" s="277" t="n"/>
+      <c r="AC23" s="277" t="n"/>
+      <c r="AD23" s="277" t="n"/>
+      <c r="AE23" s="278" t="n"/>
+      <c r="AF23" s="307" t="n"/>
+      <c r="AG23" s="277" t="n"/>
+      <c r="AH23" s="277" t="n"/>
+      <c r="AI23" s="278" t="n"/>
+      <c r="AJ23" s="307" t="n"/>
+      <c r="AK23" s="277" t="n"/>
+      <c r="AL23" s="278" t="n"/>
+      <c r="AM23" s="308" t="n"/>
+      <c r="AN23" s="280" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="519">
+      <c r="A24" s="550">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="B24" s="278" t="n"/>
+      <c r="C24" s="305" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="D24" s="277" t="n"/>
+      <c r="E24" s="278" t="n"/>
+      <c r="F24" s="296" t="inlineStr">
         <is>
           <t>Correct quantity</t>
         </is>
       </c>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="40" t="inlineStr">
+      <c r="G24" s="277" t="n"/>
+      <c r="H24" s="277" t="n"/>
+      <c r="I24" s="277" t="n"/>
+      <c r="J24" s="277" t="n"/>
+      <c r="K24" s="277" t="n"/>
+      <c r="L24" s="277" t="n"/>
+      <c r="M24" s="277" t="n"/>
+      <c r="N24" s="277" t="n"/>
+      <c r="O24" s="277" t="n"/>
+      <c r="P24" s="277" t="n"/>
+      <c r="Q24" s="277" t="n"/>
+      <c r="R24" s="277" t="n"/>
+      <c r="S24" s="278" t="n"/>
+      <c r="T24" s="306" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="12" t="n"/>
-      <c r="W24" s="12" t="n"/>
-      <c r="X24" s="12" t="n"/>
-      <c r="Y24" s="12" t="n"/>
-      <c r="Z24" s="12" t="n"/>
-      <c r="AA24" s="12" t="n"/>
-      <c r="AB24" s="12" t="n"/>
-      <c r="AC24" s="12" t="n"/>
-      <c r="AD24" s="12" t="n"/>
-      <c r="AE24" s="13" t="n"/>
-      <c r="AF24" s="41" t="n"/>
-      <c r="AG24" s="12" t="n"/>
-      <c r="AH24" s="12" t="n"/>
-      <c r="AI24" s="13" t="n"/>
-      <c r="AJ24" s="41" t="n"/>
-      <c r="AK24" s="12" t="n"/>
-      <c r="AL24" s="13" t="n"/>
-      <c r="AM24" s="42" t="n"/>
-      <c r="AN24" s="15" t="n"/>
+      <c r="U24" s="277" t="n"/>
+      <c r="V24" s="277" t="n"/>
+      <c r="W24" s="277" t="n"/>
+      <c r="X24" s="277" t="n"/>
+      <c r="Y24" s="277" t="n"/>
+      <c r="Z24" s="277" t="n"/>
+      <c r="AA24" s="277" t="n"/>
+      <c r="AB24" s="277" t="n"/>
+      <c r="AC24" s="277" t="n"/>
+      <c r="AD24" s="277" t="n"/>
+      <c r="AE24" s="278" t="n"/>
+      <c r="AF24" s="307" t="n"/>
+      <c r="AG24" s="277" t="n"/>
+      <c r="AH24" s="277" t="n"/>
+      <c r="AI24" s="278" t="n"/>
+      <c r="AJ24" s="307" t="n"/>
+      <c r="AK24" s="277" t="n"/>
+      <c r="AL24" s="278" t="n"/>
+      <c r="AM24" s="308" t="n"/>
+      <c r="AN24" s="280" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="519">
+      <c r="A25" s="550">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="B25" s="278" t="n"/>
+      <c r="C25" s="305" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="43" t="inlineStr">
+      <c r="D25" s="277" t="n"/>
+      <c r="E25" s="278" t="n"/>
+      <c r="F25" s="309" t="inlineStr">
         <is>
           <t>Application status</t>
         </is>
       </c>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="12" t="n"/>
-      <c r="R25" s="12" t="n"/>
-      <c r="S25" s="13" t="n"/>
-      <c r="T25" s="40" t="inlineStr">
+      <c r="G25" s="277" t="n"/>
+      <c r="H25" s="277" t="n"/>
+      <c r="I25" s="277" t="n"/>
+      <c r="J25" s="277" t="n"/>
+      <c r="K25" s="277" t="n"/>
+      <c r="L25" s="277" t="n"/>
+      <c r="M25" s="277" t="n"/>
+      <c r="N25" s="277" t="n"/>
+      <c r="O25" s="277" t="n"/>
+      <c r="P25" s="277" t="n"/>
+      <c r="Q25" s="277" t="n"/>
+      <c r="R25" s="277" t="n"/>
+      <c r="S25" s="278" t="n"/>
+      <c r="T25" s="306" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="12" t="n"/>
-      <c r="W25" s="12" t="n"/>
-      <c r="X25" s="12" t="n"/>
-      <c r="Y25" s="12" t="n"/>
-      <c r="Z25" s="12" t="n"/>
-      <c r="AA25" s="12" t="n"/>
-      <c r="AB25" s="12" t="n"/>
-      <c r="AC25" s="12" t="n"/>
-      <c r="AD25" s="12" t="n"/>
-      <c r="AE25" s="13" t="n"/>
-      <c r="AF25" s="41" t="n"/>
-      <c r="AG25" s="12" t="n"/>
-      <c r="AH25" s="12" t="n"/>
-      <c r="AI25" s="13" t="n"/>
-      <c r="AJ25" s="41" t="n"/>
-      <c r="AK25" s="12" t="n"/>
-      <c r="AL25" s="13" t="n"/>
-      <c r="AM25" s="42" t="n"/>
-      <c r="AN25" s="15" t="n"/>
+      <c r="U25" s="277" t="n"/>
+      <c r="V25" s="277" t="n"/>
+      <c r="W25" s="277" t="n"/>
+      <c r="X25" s="277" t="n"/>
+      <c r="Y25" s="277" t="n"/>
+      <c r="Z25" s="277" t="n"/>
+      <c r="AA25" s="277" t="n"/>
+      <c r="AB25" s="277" t="n"/>
+      <c r="AC25" s="277" t="n"/>
+      <c r="AD25" s="277" t="n"/>
+      <c r="AE25" s="278" t="n"/>
+      <c r="AF25" s="307" t="n"/>
+      <c r="AG25" s="277" t="n"/>
+      <c r="AH25" s="277" t="n"/>
+      <c r="AI25" s="278" t="n"/>
+      <c r="AJ25" s="307" t="n"/>
+      <c r="AK25" s="277" t="n"/>
+      <c r="AL25" s="278" t="n"/>
+      <c r="AM25" s="308" t="n"/>
+      <c r="AN25" s="280" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="519">
+      <c r="A26" s="550">
         <f>ROW()-ROW($A$22)+1</f>
         <v/>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="B26" s="278" t="n"/>
+      <c r="C26" s="305" t="inlineStr">
         <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="D26" s="277" t="n"/>
+      <c r="E26" s="278" t="n"/>
+      <c r="F26" s="296" t="inlineStr">
         <is>
           <t>Void / scrap control</t>
         </is>
       </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
-      <c r="R26" s="12" t="n"/>
-      <c r="S26" s="13" t="n"/>
-      <c r="T26" s="40" t="inlineStr">
+      <c r="G26" s="277" t="n"/>
+      <c r="H26" s="277" t="n"/>
+      <c r="I26" s="277" t="n"/>
+      <c r="J26" s="277" t="n"/>
+      <c r="K26" s="277" t="n"/>
+      <c r="L26" s="277" t="n"/>
+      <c r="M26" s="277" t="n"/>
+      <c r="N26" s="277" t="n"/>
+      <c r="O26" s="277" t="n"/>
+      <c r="P26" s="277" t="n"/>
+      <c r="Q26" s="277" t="n"/>
+      <c r="R26" s="277" t="n"/>
+      <c r="S26" s="278" t="n"/>
+      <c r="T26" s="306" t="inlineStr">
         <is>
           <t>Controlled print record and application evidence</t>
         </is>
       </c>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="12" t="n"/>
-      <c r="W26" s="12" t="n"/>
-      <c r="X26" s="12" t="n"/>
-      <c r="Y26" s="12" t="n"/>
-      <c r="Z26" s="12" t="n"/>
-      <c r="AA26" s="12" t="n"/>
-      <c r="AB26" s="12" t="n"/>
-      <c r="AC26" s="12" t="n"/>
-      <c r="AD26" s="12" t="n"/>
-      <c r="AE26" s="13" t="n"/>
-      <c r="AF26" s="41" t="n"/>
-      <c r="AG26" s="12" t="n"/>
-      <c r="AH26" s="12" t="n"/>
-      <c r="AI26" s="13" t="n"/>
-      <c r="AJ26" s="41" t="n"/>
-      <c r="AK26" s="12" t="n"/>
-      <c r="AL26" s="13" t="n"/>
-      <c r="AM26" s="42" t="n"/>
-      <c r="AN26" s="15" t="n"/>
+      <c r="U26" s="277" t="n"/>
+      <c r="V26" s="277" t="n"/>
+      <c r="W26" s="277" t="n"/>
+      <c r="X26" s="277" t="n"/>
+      <c r="Y26" s="277" t="n"/>
+      <c r="Z26" s="277" t="n"/>
+      <c r="AA26" s="277" t="n"/>
+      <c r="AB26" s="277" t="n"/>
+      <c r="AC26" s="277" t="n"/>
+      <c r="AD26" s="277" t="n"/>
+      <c r="AE26" s="278" t="n"/>
+      <c r="AF26" s="307" t="n"/>
+      <c r="AG26" s="277" t="n"/>
+      <c r="AH26" s="277" t="n"/>
+      <c r="AI26" s="278" t="n"/>
+      <c r="AJ26" s="307" t="n"/>
+      <c r="AK26" s="277" t="n"/>
+      <c r="AL26" s="278" t="n"/>
+      <c r="AM26" s="308" t="n"/>
+      <c r="AN26" s="280" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="519" t="n"/>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="39" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="12" t="n"/>
-      <c r="R27" s="12" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="40" t="n"/>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="12" t="n"/>
-      <c r="W27" s="12" t="n"/>
-      <c r="X27" s="12" t="n"/>
-      <c r="Y27" s="12" t="n"/>
-      <c r="Z27" s="12" t="n"/>
-      <c r="AA27" s="12" t="n"/>
-      <c r="AB27" s="12" t="n"/>
-      <c r="AC27" s="12" t="n"/>
-      <c r="AD27" s="12" t="n"/>
-      <c r="AE27" s="13" t="n"/>
-      <c r="AF27" s="41" t="n"/>
-      <c r="AG27" s="12" t="n"/>
-      <c r="AH27" s="12" t="n"/>
-      <c r="AI27" s="13" t="n"/>
-      <c r="AJ27" s="41" t="n"/>
-      <c r="AK27" s="12" t="n"/>
-      <c r="AL27" s="13" t="n"/>
-      <c r="AM27" s="42" t="n"/>
-      <c r="AN27" s="15" t="n"/>
+      <c r="A27" s="550" t="n"/>
+      <c r="B27" s="278" t="n"/>
+      <c r="C27" s="305" t="n"/>
+      <c r="D27" s="277" t="n"/>
+      <c r="E27" s="278" t="n"/>
+      <c r="F27" s="309" t="n"/>
+      <c r="G27" s="277" t="n"/>
+      <c r="H27" s="277" t="n"/>
+      <c r="I27" s="277" t="n"/>
+      <c r="J27" s="277" t="n"/>
+      <c r="K27" s="277" t="n"/>
+      <c r="L27" s="277" t="n"/>
+      <c r="M27" s="277" t="n"/>
+      <c r="N27" s="277" t="n"/>
+      <c r="O27" s="277" t="n"/>
+      <c r="P27" s="277" t="n"/>
+      <c r="Q27" s="277" t="n"/>
+      <c r="R27" s="277" t="n"/>
+      <c r="S27" s="278" t="n"/>
+      <c r="T27" s="306" t="n"/>
+      <c r="U27" s="277" t="n"/>
+      <c r="V27" s="277" t="n"/>
+      <c r="W27" s="277" t="n"/>
+      <c r="X27" s="277" t="n"/>
+      <c r="Y27" s="277" t="n"/>
+      <c r="Z27" s="277" t="n"/>
+      <c r="AA27" s="277" t="n"/>
+      <c r="AB27" s="277" t="n"/>
+      <c r="AC27" s="277" t="n"/>
+      <c r="AD27" s="277" t="n"/>
+      <c r="AE27" s="278" t="n"/>
+      <c r="AF27" s="307" t="n"/>
+      <c r="AG27" s="277" t="n"/>
+      <c r="AH27" s="277" t="n"/>
+      <c r="AI27" s="278" t="n"/>
+      <c r="AJ27" s="307" t="n"/>
+      <c r="AK27" s="277" t="n"/>
+      <c r="AL27" s="278" t="n"/>
+      <c r="AM27" s="308" t="n"/>
+      <c r="AN27" s="280" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="519" t="n"/>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="39" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="12" t="n"/>
-      <c r="R28" s="12" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="40" t="n"/>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="12" t="n"/>
-      <c r="W28" s="12" t="n"/>
-      <c r="X28" s="12" t="n"/>
-      <c r="Y28" s="12" t="n"/>
-      <c r="Z28" s="12" t="n"/>
-      <c r="AA28" s="12" t="n"/>
-      <c r="AB28" s="12" t="n"/>
-      <c r="AC28" s="12" t="n"/>
-      <c r="AD28" s="12" t="n"/>
-      <c r="AE28" s="13" t="n"/>
-      <c r="AF28" s="41" t="n"/>
-      <c r="AG28" s="12" t="n"/>
-      <c r="AH28" s="12" t="n"/>
-      <c r="AI28" s="13" t="n"/>
-      <c r="AJ28" s="41" t="n"/>
-      <c r="AK28" s="12" t="n"/>
-      <c r="AL28" s="13" t="n"/>
-      <c r="AM28" s="42" t="n"/>
-      <c r="AN28" s="15" t="n"/>
+      <c r="A28" s="550" t="n"/>
+      <c r="B28" s="278" t="n"/>
+      <c r="C28" s="305" t="n"/>
+      <c r="D28" s="277" t="n"/>
+      <c r="E28" s="278" t="n"/>
+      <c r="F28" s="296" t="n"/>
+      <c r="G28" s="277" t="n"/>
+      <c r="H28" s="277" t="n"/>
+      <c r="I28" s="277" t="n"/>
+      <c r="J28" s="277" t="n"/>
+      <c r="K28" s="277" t="n"/>
+      <c r="L28" s="277" t="n"/>
+      <c r="M28" s="277" t="n"/>
+      <c r="N28" s="277" t="n"/>
+      <c r="O28" s="277" t="n"/>
+      <c r="P28" s="277" t="n"/>
+      <c r="Q28" s="277" t="n"/>
+      <c r="R28" s="277" t="n"/>
+      <c r="S28" s="278" t="n"/>
+      <c r="T28" s="306" t="n"/>
+      <c r="U28" s="277" t="n"/>
+      <c r="V28" s="277" t="n"/>
+      <c r="W28" s="277" t="n"/>
+      <c r="X28" s="277" t="n"/>
+      <c r="Y28" s="277" t="n"/>
+      <c r="Z28" s="277" t="n"/>
+      <c r="AA28" s="277" t="n"/>
+      <c r="AB28" s="277" t="n"/>
+      <c r="AC28" s="277" t="n"/>
+      <c r="AD28" s="277" t="n"/>
+      <c r="AE28" s="278" t="n"/>
+      <c r="AF28" s="307" t="n"/>
+      <c r="AG28" s="277" t="n"/>
+      <c r="AH28" s="277" t="n"/>
+      <c r="AI28" s="278" t="n"/>
+      <c r="AJ28" s="307" t="n"/>
+      <c r="AK28" s="277" t="n"/>
+      <c r="AL28" s="278" t="n"/>
+      <c r="AM28" s="308" t="n"/>
+      <c r="AN28" s="280" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="519" t="n"/>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="39" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="43" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="12" t="n"/>
-      <c r="R29" s="12" t="n"/>
-      <c r="S29" s="13" t="n"/>
-      <c r="T29" s="40" t="n"/>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="12" t="n"/>
-      <c r="W29" s="12" t="n"/>
-      <c r="X29" s="12" t="n"/>
-      <c r="Y29" s="12" t="n"/>
-      <c r="Z29" s="12" t="n"/>
-      <c r="AA29" s="12" t="n"/>
-      <c r="AB29" s="12" t="n"/>
-      <c r="AC29" s="12" t="n"/>
-      <c r="AD29" s="12" t="n"/>
-      <c r="AE29" s="13" t="n"/>
-      <c r="AF29" s="41" t="n"/>
-      <c r="AG29" s="12" t="n"/>
-      <c r="AH29" s="12" t="n"/>
-      <c r="AI29" s="13" t="n"/>
-      <c r="AJ29" s="41" t="n"/>
-      <c r="AK29" s="12" t="n"/>
-      <c r="AL29" s="13" t="n"/>
-      <c r="AM29" s="42" t="n"/>
-      <c r="AN29" s="15" t="n"/>
+      <c r="A29" s="550" t="n"/>
+      <c r="B29" s="278" t="n"/>
+      <c r="C29" s="305" t="n"/>
+      <c r="D29" s="277" t="n"/>
+      <c r="E29" s="278" t="n"/>
+      <c r="F29" s="309" t="n"/>
+      <c r="G29" s="277" t="n"/>
+      <c r="H29" s="277" t="n"/>
+      <c r="I29" s="277" t="n"/>
+      <c r="J29" s="277" t="n"/>
+      <c r="K29" s="277" t="n"/>
+      <c r="L29" s="277" t="n"/>
+      <c r="M29" s="277" t="n"/>
+      <c r="N29" s="277" t="n"/>
+      <c r="O29" s="277" t="n"/>
+      <c r="P29" s="277" t="n"/>
+      <c r="Q29" s="277" t="n"/>
+      <c r="R29" s="277" t="n"/>
+      <c r="S29" s="278" t="n"/>
+      <c r="T29" s="306" t="n"/>
+      <c r="U29" s="277" t="n"/>
+      <c r="V29" s="277" t="n"/>
+      <c r="W29" s="277" t="n"/>
+      <c r="X29" s="277" t="n"/>
+      <c r="Y29" s="277" t="n"/>
+      <c r="Z29" s="277" t="n"/>
+      <c r="AA29" s="277" t="n"/>
+      <c r="AB29" s="277" t="n"/>
+      <c r="AC29" s="277" t="n"/>
+      <c r="AD29" s="277" t="n"/>
+      <c r="AE29" s="278" t="n"/>
+      <c r="AF29" s="307" t="n"/>
+      <c r="AG29" s="277" t="n"/>
+      <c r="AH29" s="277" t="n"/>
+      <c r="AI29" s="278" t="n"/>
+      <c r="AJ29" s="307" t="n"/>
+      <c r="AK29" s="277" t="n"/>
+      <c r="AL29" s="278" t="n"/>
+      <c r="AM29" s="308" t="n"/>
+      <c r="AN29" s="280" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="519" t="n"/>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="39" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="40" t="n"/>
-      <c r="U30" s="12" t="n"/>
-      <c r="V30" s="12" t="n"/>
-      <c r="W30" s="12" t="n"/>
-      <c r="X30" s="12" t="n"/>
-      <c r="Y30" s="12" t="n"/>
-      <c r="Z30" s="12" t="n"/>
-      <c r="AA30" s="12" t="n"/>
-      <c r="AB30" s="12" t="n"/>
-      <c r="AC30" s="12" t="n"/>
-      <c r="AD30" s="12" t="n"/>
-      <c r="AE30" s="13" t="n"/>
-      <c r="AF30" s="41" t="n"/>
-      <c r="AG30" s="12" t="n"/>
-      <c r="AH30" s="12" t="n"/>
-      <c r="AI30" s="13" t="n"/>
-      <c r="AJ30" s="41" t="n"/>
-      <c r="AK30" s="12" t="n"/>
-      <c r="AL30" s="13" t="n"/>
-      <c r="AM30" s="42" t="n"/>
-      <c r="AN30" s="15" t="n"/>
+      <c r="A30" s="550" t="n"/>
+      <c r="B30" s="278" t="n"/>
+      <c r="C30" s="305" t="n"/>
+      <c r="D30" s="277" t="n"/>
+      <c r="E30" s="278" t="n"/>
+      <c r="F30" s="296" t="n"/>
+      <c r="G30" s="277" t="n"/>
+      <c r="H30" s="277" t="n"/>
+      <c r="I30" s="277" t="n"/>
+      <c r="J30" s="277" t="n"/>
+      <c r="K30" s="277" t="n"/>
+      <c r="L30" s="277" t="n"/>
+      <c r="M30" s="277" t="n"/>
+      <c r="N30" s="277" t="n"/>
+      <c r="O30" s="277" t="n"/>
+      <c r="P30" s="277" t="n"/>
+      <c r="Q30" s="277" t="n"/>
+      <c r="R30" s="277" t="n"/>
+      <c r="S30" s="278" t="n"/>
+      <c r="T30" s="306" t="n"/>
+      <c r="U30" s="277" t="n"/>
+      <c r="V30" s="277" t="n"/>
+      <c r="W30" s="277" t="n"/>
+      <c r="X30" s="277" t="n"/>
+      <c r="Y30" s="277" t="n"/>
+      <c r="Z30" s="277" t="n"/>
+      <c r="AA30" s="277" t="n"/>
+      <c r="AB30" s="277" t="n"/>
+      <c r="AC30" s="277" t="n"/>
+      <c r="AD30" s="277" t="n"/>
+      <c r="AE30" s="278" t="n"/>
+      <c r="AF30" s="307" t="n"/>
+      <c r="AG30" s="277" t="n"/>
+      <c r="AH30" s="277" t="n"/>
+      <c r="AI30" s="278" t="n"/>
+      <c r="AJ30" s="307" t="n"/>
+      <c r="AK30" s="277" t="n"/>
+      <c r="AL30" s="278" t="n"/>
+      <c r="AM30" s="308" t="n"/>
+      <c r="AN30" s="280" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="520" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="19" t="n"/>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="19" t="n"/>
-      <c r="R31" s="19" t="n"/>
-      <c r="S31" s="22" t="n"/>
-      <c r="T31" s="47" t="n"/>
-      <c r="U31" s="19" t="n"/>
-      <c r="V31" s="19" t="n"/>
-      <c r="W31" s="19" t="n"/>
-      <c r="X31" s="19" t="n"/>
-      <c r="Y31" s="19" t="n"/>
-      <c r="Z31" s="19" t="n"/>
-      <c r="AA31" s="19" t="n"/>
-      <c r="AB31" s="19" t="n"/>
-      <c r="AC31" s="19" t="n"/>
-      <c r="AD31" s="19" t="n"/>
-      <c r="AE31" s="22" t="n"/>
-      <c r="AF31" s="48" t="n"/>
-      <c r="AG31" s="19" t="n"/>
-      <c r="AH31" s="19" t="n"/>
-      <c r="AI31" s="22" t="n"/>
-      <c r="AJ31" s="48" t="n"/>
-      <c r="AK31" s="19" t="n"/>
-      <c r="AL31" s="22" t="n"/>
-      <c r="AM31" s="49" t="n"/>
-      <c r="AN31" s="24" t="n"/>
+      <c r="A31" s="551" t="n"/>
+      <c r="B31" s="285" t="n"/>
+      <c r="C31" s="311" t="n"/>
+      <c r="D31" s="283" t="n"/>
+      <c r="E31" s="285" t="n"/>
+      <c r="F31" s="312" t="n"/>
+      <c r="G31" s="283" t="n"/>
+      <c r="H31" s="283" t="n"/>
+      <c r="I31" s="283" t="n"/>
+      <c r="J31" s="283" t="n"/>
+      <c r="K31" s="283" t="n"/>
+      <c r="L31" s="283" t="n"/>
+      <c r="M31" s="283" t="n"/>
+      <c r="N31" s="283" t="n"/>
+      <c r="O31" s="283" t="n"/>
+      <c r="P31" s="283" t="n"/>
+      <c r="Q31" s="283" t="n"/>
+      <c r="R31" s="283" t="n"/>
+      <c r="S31" s="285" t="n"/>
+      <c r="T31" s="313" t="n"/>
+      <c r="U31" s="283" t="n"/>
+      <c r="V31" s="283" t="n"/>
+      <c r="W31" s="283" t="n"/>
+      <c r="X31" s="283" t="n"/>
+      <c r="Y31" s="283" t="n"/>
+      <c r="Z31" s="283" t="n"/>
+      <c r="AA31" s="283" t="n"/>
+      <c r="AB31" s="283" t="n"/>
+      <c r="AC31" s="283" t="n"/>
+      <c r="AD31" s="283" t="n"/>
+      <c r="AE31" s="285" t="n"/>
+      <c r="AF31" s="314" t="n"/>
+      <c r="AG31" s="283" t="n"/>
+      <c r="AH31" s="283" t="n"/>
+      <c r="AI31" s="285" t="n"/>
+      <c r="AJ31" s="314" t="n"/>
+      <c r="AK31" s="283" t="n"/>
+      <c r="AL31" s="285" t="n"/>
+      <c r="AM31" s="315" t="n"/>
+      <c r="AN31" s="287" t="n"/>
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="513" t="n"/>
@@ -7946,365 +8061,365 @@
       <c r="AN32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="506" t="inlineStr">
+      <c r="A33" s="538" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. PRINT CONTROL REFERENCE</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-      <c r="Q33" s="27" t="n"/>
-      <c r="R33" s="27" t="n"/>
-      <c r="S33" s="27" t="n"/>
-      <c r="T33" s="27" t="n"/>
-      <c r="U33" s="27" t="n"/>
-      <c r="V33" s="27" t="n"/>
-      <c r="W33" s="27" t="n"/>
-      <c r="X33" s="27" t="n"/>
-      <c r="Y33" s="27" t="n"/>
-      <c r="Z33" s="27" t="n"/>
-      <c r="AA33" s="27" t="n"/>
-      <c r="AB33" s="27" t="n"/>
-      <c r="AC33" s="27" t="n"/>
-      <c r="AD33" s="27" t="n"/>
-      <c r="AE33" s="27" t="n"/>
-      <c r="AF33" s="27" t="n"/>
-      <c r="AG33" s="27" t="n"/>
-      <c r="AH33" s="27" t="n"/>
-      <c r="AI33" s="27" t="n"/>
-      <c r="AJ33" s="27" t="n"/>
-      <c r="AK33" s="27" t="n"/>
-      <c r="AL33" s="27" t="n"/>
-      <c r="AM33" s="27" t="n"/>
-      <c r="AN33" s="28" t="n"/>
+      <c r="B33" s="289" t="n"/>
+      <c r="C33" s="289" t="n"/>
+      <c r="D33" s="289" t="n"/>
+      <c r="E33" s="289" t="n"/>
+      <c r="F33" s="289" t="n"/>
+      <c r="G33" s="289" t="n"/>
+      <c r="H33" s="289" t="n"/>
+      <c r="I33" s="289" t="n"/>
+      <c r="J33" s="289" t="n"/>
+      <c r="K33" s="289" t="n"/>
+      <c r="L33" s="289" t="n"/>
+      <c r="M33" s="289" t="n"/>
+      <c r="N33" s="289" t="n"/>
+      <c r="O33" s="289" t="n"/>
+      <c r="P33" s="289" t="n"/>
+      <c r="Q33" s="289" t="n"/>
+      <c r="R33" s="289" t="n"/>
+      <c r="S33" s="289" t="n"/>
+      <c r="T33" s="289" t="n"/>
+      <c r="U33" s="289" t="n"/>
+      <c r="V33" s="289" t="n"/>
+      <c r="W33" s="289" t="n"/>
+      <c r="X33" s="289" t="n"/>
+      <c r="Y33" s="289" t="n"/>
+      <c r="Z33" s="289" t="n"/>
+      <c r="AA33" s="289" t="n"/>
+      <c r="AB33" s="289" t="n"/>
+      <c r="AC33" s="289" t="n"/>
+      <c r="AD33" s="289" t="n"/>
+      <c r="AE33" s="289" t="n"/>
+      <c r="AF33" s="289" t="n"/>
+      <c r="AG33" s="289" t="n"/>
+      <c r="AH33" s="289" t="n"/>
+      <c r="AI33" s="289" t="n"/>
+      <c r="AJ33" s="289" t="n"/>
+      <c r="AK33" s="289" t="n"/>
+      <c r="AL33" s="289" t="n"/>
+      <c r="AM33" s="289" t="n"/>
+      <c r="AN33" s="290" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="301" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="B34" s="272" t="n"/>
+      <c r="C34" s="302" t="inlineStr">
         <is>
           <t>Control Field</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="37" t="inlineStr">
+      <c r="D34" s="271" t="n"/>
+      <c r="E34" s="271" t="n"/>
+      <c r="F34" s="271" t="n"/>
+      <c r="G34" s="271" t="n"/>
+      <c r="H34" s="271" t="n"/>
+      <c r="I34" s="271" t="n"/>
+      <c r="J34" s="271" t="n"/>
+      <c r="K34" s="271" t="n"/>
+      <c r="L34" s="272" t="n"/>
+      <c r="M34" s="302" t="inlineStr">
         <is>
           <t>Required Record</t>
         </is>
       </c>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="6" t="n"/>
-      <c r="Y34" s="37" t="inlineStr">
+      <c r="N34" s="271" t="n"/>
+      <c r="O34" s="271" t="n"/>
+      <c r="P34" s="271" t="n"/>
+      <c r="Q34" s="271" t="n"/>
+      <c r="R34" s="271" t="n"/>
+      <c r="S34" s="271" t="n"/>
+      <c r="T34" s="271" t="n"/>
+      <c r="U34" s="271" t="n"/>
+      <c r="V34" s="271" t="n"/>
+      <c r="W34" s="271" t="n"/>
+      <c r="X34" s="272" t="n"/>
+      <c r="Y34" s="302" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="5" t="n"/>
-      <c r="AB34" s="5" t="n"/>
-      <c r="AC34" s="6" t="n"/>
-      <c r="AD34" s="37" t="inlineStr">
+      <c r="Z34" s="271" t="n"/>
+      <c r="AA34" s="271" t="n"/>
+      <c r="AB34" s="271" t="n"/>
+      <c r="AC34" s="272" t="n"/>
+      <c r="AD34" s="302" t="inlineStr">
         <is>
           <t>Event State</t>
         </is>
       </c>
-      <c r="AE34" s="5" t="n"/>
-      <c r="AF34" s="5" t="n"/>
-      <c r="AG34" s="5" t="n"/>
-      <c r="AH34" s="6" t="n"/>
-      <c r="AI34" s="37" t="inlineStr">
+      <c r="AE34" s="271" t="n"/>
+      <c r="AF34" s="271" t="n"/>
+      <c r="AG34" s="271" t="n"/>
+      <c r="AH34" s="272" t="n"/>
+      <c r="AI34" s="302" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AJ34" s="5" t="n"/>
-      <c r="AK34" s="6" t="n"/>
-      <c r="AL34" s="37" t="inlineStr">
+      <c r="AJ34" s="271" t="n"/>
+      <c r="AK34" s="272" t="n"/>
+      <c r="AL34" s="303" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="AM34" s="5" t="n"/>
-      <c r="AN34" s="8" t="n"/>
+      <c r="AM34" s="271" t="n"/>
+      <c r="AN34" s="274" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="514">
+      <c r="A35" s="545">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="B35" s="272" t="n"/>
+      <c r="C35" s="292" t="inlineStr">
         <is>
           <t>Released by</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="M35" s="30" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="5" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="6" t="n"/>
-      <c r="Y35" s="517" t="n"/>
-      <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="5" t="n"/>
-      <c r="AB35" s="5" t="n"/>
-      <c r="AC35" s="6" t="n"/>
-      <c r="AD35" s="517" t="n"/>
-      <c r="AE35" s="5" t="n"/>
-      <c r="AF35" s="5" t="n"/>
-      <c r="AG35" s="5" t="n"/>
-      <c r="AH35" s="6" t="n"/>
-      <c r="AI35" s="517" t="n"/>
-      <c r="AJ35" s="5" t="n"/>
-      <c r="AK35" s="6" t="n"/>
-      <c r="AL35" s="517" t="n"/>
-      <c r="AM35" s="5" t="n"/>
-      <c r="AN35" s="8" t="n"/>
+      <c r="D35" s="271" t="n"/>
+      <c r="E35" s="271" t="n"/>
+      <c r="F35" s="271" t="n"/>
+      <c r="G35" s="271" t="n"/>
+      <c r="H35" s="271" t="n"/>
+      <c r="I35" s="271" t="n"/>
+      <c r="J35" s="271" t="n"/>
+      <c r="K35" s="271" t="n"/>
+      <c r="L35" s="272" t="n"/>
+      <c r="M35" s="292" t="n"/>
+      <c r="N35" s="271" t="n"/>
+      <c r="O35" s="271" t="n"/>
+      <c r="P35" s="271" t="n"/>
+      <c r="Q35" s="271" t="n"/>
+      <c r="R35" s="271" t="n"/>
+      <c r="S35" s="271" t="n"/>
+      <c r="T35" s="271" t="n"/>
+      <c r="U35" s="271" t="n"/>
+      <c r="V35" s="271" t="n"/>
+      <c r="W35" s="271" t="n"/>
+      <c r="X35" s="272" t="n"/>
+      <c r="Y35" s="548" t="n"/>
+      <c r="Z35" s="271" t="n"/>
+      <c r="AA35" s="271" t="n"/>
+      <c r="AB35" s="271" t="n"/>
+      <c r="AC35" s="272" t="n"/>
+      <c r="AD35" s="548" t="n"/>
+      <c r="AE35" s="271" t="n"/>
+      <c r="AF35" s="271" t="n"/>
+      <c r="AG35" s="271" t="n"/>
+      <c r="AH35" s="272" t="n"/>
+      <c r="AI35" s="548" t="n"/>
+      <c r="AJ35" s="271" t="n"/>
+      <c r="AK35" s="272" t="n"/>
+      <c r="AL35" s="552" t="n"/>
+      <c r="AM35" s="271" t="n"/>
+      <c r="AN35" s="274" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="519">
+      <c r="A36" s="550">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="B36" s="278" t="n"/>
+      <c r="C36" s="296" t="inlineStr">
         <is>
           <t>Printed by</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="13" t="n"/>
-      <c r="M36" s="14" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="12" t="n"/>
-      <c r="U36" s="12" t="n"/>
-      <c r="V36" s="12" t="n"/>
-      <c r="W36" s="12" t="n"/>
-      <c r="X36" s="13" t="n"/>
-      <c r="Y36" s="41" t="n"/>
-      <c r="Z36" s="12" t="n"/>
-      <c r="AA36" s="12" t="n"/>
-      <c r="AB36" s="12" t="n"/>
-      <c r="AC36" s="13" t="n"/>
-      <c r="AD36" s="41" t="n"/>
-      <c r="AE36" s="12" t="n"/>
-      <c r="AF36" s="12" t="n"/>
-      <c r="AG36" s="12" t="n"/>
-      <c r="AH36" s="13" t="n"/>
-      <c r="AI36" s="41" t="n"/>
-      <c r="AJ36" s="12" t="n"/>
-      <c r="AK36" s="13" t="n"/>
-      <c r="AL36" s="41" t="n"/>
-      <c r="AM36" s="12" t="n"/>
-      <c r="AN36" s="15" t="n"/>
+      <c r="D36" s="277" t="n"/>
+      <c r="E36" s="277" t="n"/>
+      <c r="F36" s="277" t="n"/>
+      <c r="G36" s="277" t="n"/>
+      <c r="H36" s="277" t="n"/>
+      <c r="I36" s="277" t="n"/>
+      <c r="J36" s="277" t="n"/>
+      <c r="K36" s="277" t="n"/>
+      <c r="L36" s="278" t="n"/>
+      <c r="M36" s="296" t="n"/>
+      <c r="N36" s="277" t="n"/>
+      <c r="O36" s="277" t="n"/>
+      <c r="P36" s="277" t="n"/>
+      <c r="Q36" s="277" t="n"/>
+      <c r="R36" s="277" t="n"/>
+      <c r="S36" s="277" t="n"/>
+      <c r="T36" s="277" t="n"/>
+      <c r="U36" s="277" t="n"/>
+      <c r="V36" s="277" t="n"/>
+      <c r="W36" s="277" t="n"/>
+      <c r="X36" s="278" t="n"/>
+      <c r="Y36" s="307" t="n"/>
+      <c r="Z36" s="277" t="n"/>
+      <c r="AA36" s="277" t="n"/>
+      <c r="AB36" s="277" t="n"/>
+      <c r="AC36" s="278" t="n"/>
+      <c r="AD36" s="307" t="n"/>
+      <c r="AE36" s="277" t="n"/>
+      <c r="AF36" s="277" t="n"/>
+      <c r="AG36" s="277" t="n"/>
+      <c r="AH36" s="278" t="n"/>
+      <c r="AI36" s="307" t="n"/>
+      <c r="AJ36" s="277" t="n"/>
+      <c r="AK36" s="278" t="n"/>
+      <c r="AL36" s="316" t="n"/>
+      <c r="AM36" s="277" t="n"/>
+      <c r="AN36" s="280" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="519">
+      <c r="A37" s="550">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="B37" s="278" t="n"/>
+      <c r="C37" s="296" t="inlineStr">
         <is>
           <t>Verified application</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="13" t="n"/>
-      <c r="M37" s="14" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
-      <c r="T37" s="12" t="n"/>
-      <c r="U37" s="12" t="n"/>
-      <c r="V37" s="12" t="n"/>
-      <c r="W37" s="12" t="n"/>
-      <c r="X37" s="13" t="n"/>
-      <c r="Y37" s="41" t="n"/>
-      <c r="Z37" s="12" t="n"/>
-      <c r="AA37" s="12" t="n"/>
-      <c r="AB37" s="12" t="n"/>
-      <c r="AC37" s="13" t="n"/>
-      <c r="AD37" s="41" t="n"/>
-      <c r="AE37" s="12" t="n"/>
-      <c r="AF37" s="12" t="n"/>
-      <c r="AG37" s="12" t="n"/>
-      <c r="AH37" s="13" t="n"/>
-      <c r="AI37" s="41" t="n"/>
-      <c r="AJ37" s="12" t="n"/>
-      <c r="AK37" s="13" t="n"/>
-      <c r="AL37" s="41" t="n"/>
-      <c r="AM37" s="12" t="n"/>
-      <c r="AN37" s="15" t="n"/>
+      <c r="D37" s="277" t="n"/>
+      <c r="E37" s="277" t="n"/>
+      <c r="F37" s="277" t="n"/>
+      <c r="G37" s="277" t="n"/>
+      <c r="H37" s="277" t="n"/>
+      <c r="I37" s="277" t="n"/>
+      <c r="J37" s="277" t="n"/>
+      <c r="K37" s="277" t="n"/>
+      <c r="L37" s="278" t="n"/>
+      <c r="M37" s="296" t="n"/>
+      <c r="N37" s="277" t="n"/>
+      <c r="O37" s="277" t="n"/>
+      <c r="P37" s="277" t="n"/>
+      <c r="Q37" s="277" t="n"/>
+      <c r="R37" s="277" t="n"/>
+      <c r="S37" s="277" t="n"/>
+      <c r="T37" s="277" t="n"/>
+      <c r="U37" s="277" t="n"/>
+      <c r="V37" s="277" t="n"/>
+      <c r="W37" s="277" t="n"/>
+      <c r="X37" s="278" t="n"/>
+      <c r="Y37" s="307" t="n"/>
+      <c r="Z37" s="277" t="n"/>
+      <c r="AA37" s="277" t="n"/>
+      <c r="AB37" s="277" t="n"/>
+      <c r="AC37" s="278" t="n"/>
+      <c r="AD37" s="307" t="n"/>
+      <c r="AE37" s="277" t="n"/>
+      <c r="AF37" s="277" t="n"/>
+      <c r="AG37" s="277" t="n"/>
+      <c r="AH37" s="278" t="n"/>
+      <c r="AI37" s="307" t="n"/>
+      <c r="AJ37" s="277" t="n"/>
+      <c r="AK37" s="278" t="n"/>
+      <c r="AL37" s="316" t="n"/>
+      <c r="AM37" s="277" t="n"/>
+      <c r="AN37" s="280" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="519">
+      <c r="A38" s="550">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="B38" s="278" t="n"/>
+      <c r="C38" s="296" t="inlineStr">
         <is>
           <t>Void / scrap</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="13" t="n"/>
-      <c r="M38" s="14" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
-      <c r="T38" s="12" t="n"/>
-      <c r="U38" s="12" t="n"/>
-      <c r="V38" s="12" t="n"/>
-      <c r="W38" s="12" t="n"/>
-      <c r="X38" s="13" t="n"/>
-      <c r="Y38" s="41" t="n"/>
-      <c r="Z38" s="12" t="n"/>
-      <c r="AA38" s="12" t="n"/>
-      <c r="AB38" s="12" t="n"/>
-      <c r="AC38" s="13" t="n"/>
-      <c r="AD38" s="41" t="n"/>
-      <c r="AE38" s="12" t="n"/>
-      <c r="AF38" s="12" t="n"/>
-      <c r="AG38" s="12" t="n"/>
-      <c r="AH38" s="13" t="n"/>
-      <c r="AI38" s="41" t="n"/>
-      <c r="AJ38" s="12" t="n"/>
-      <c r="AK38" s="13" t="n"/>
-      <c r="AL38" s="41" t="n"/>
-      <c r="AM38" s="12" t="n"/>
-      <c r="AN38" s="15" t="n"/>
+      <c r="D38" s="277" t="n"/>
+      <c r="E38" s="277" t="n"/>
+      <c r="F38" s="277" t="n"/>
+      <c r="G38" s="277" t="n"/>
+      <c r="H38" s="277" t="n"/>
+      <c r="I38" s="277" t="n"/>
+      <c r="J38" s="277" t="n"/>
+      <c r="K38" s="277" t="n"/>
+      <c r="L38" s="278" t="n"/>
+      <c r="M38" s="296" t="n"/>
+      <c r="N38" s="277" t="n"/>
+      <c r="O38" s="277" t="n"/>
+      <c r="P38" s="277" t="n"/>
+      <c r="Q38" s="277" t="n"/>
+      <c r="R38" s="277" t="n"/>
+      <c r="S38" s="277" t="n"/>
+      <c r="T38" s="277" t="n"/>
+      <c r="U38" s="277" t="n"/>
+      <c r="V38" s="277" t="n"/>
+      <c r="W38" s="277" t="n"/>
+      <c r="X38" s="278" t="n"/>
+      <c r="Y38" s="307" t="n"/>
+      <c r="Z38" s="277" t="n"/>
+      <c r="AA38" s="277" t="n"/>
+      <c r="AB38" s="277" t="n"/>
+      <c r="AC38" s="278" t="n"/>
+      <c r="AD38" s="307" t="n"/>
+      <c r="AE38" s="277" t="n"/>
+      <c r="AF38" s="277" t="n"/>
+      <c r="AG38" s="277" t="n"/>
+      <c r="AH38" s="278" t="n"/>
+      <c r="AI38" s="307" t="n"/>
+      <c r="AJ38" s="277" t="n"/>
+      <c r="AK38" s="278" t="n"/>
+      <c r="AL38" s="316" t="n"/>
+      <c r="AM38" s="277" t="n"/>
+      <c r="AN38" s="280" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="520">
+      <c r="A39" s="551">
         <f>ROW()-ROW($A$35)+1</f>
         <v/>
       </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="B39" s="285" t="n"/>
+      <c r="C39" s="299" t="inlineStr">
         <is>
           <t>Reprint justification</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-      <c r="L39" s="22" t="n"/>
-      <c r="M39" s="23" t="n"/>
-      <c r="N39" s="19" t="n"/>
-      <c r="O39" s="19" t="n"/>
-      <c r="P39" s="19" t="n"/>
-      <c r="Q39" s="19" t="n"/>
-      <c r="R39" s="19" t="n"/>
-      <c r="S39" s="19" t="n"/>
-      <c r="T39" s="19" t="n"/>
-      <c r="U39" s="19" t="n"/>
-      <c r="V39" s="19" t="n"/>
-      <c r="W39" s="19" t="n"/>
-      <c r="X39" s="22" t="n"/>
-      <c r="Y39" s="48" t="n"/>
-      <c r="Z39" s="19" t="n"/>
-      <c r="AA39" s="19" t="n"/>
-      <c r="AB39" s="19" t="n"/>
-      <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="48" t="n"/>
-      <c r="AE39" s="19" t="n"/>
-      <c r="AF39" s="19" t="n"/>
-      <c r="AG39" s="19" t="n"/>
-      <c r="AH39" s="22" t="n"/>
-      <c r="AI39" s="48" t="n"/>
-      <c r="AJ39" s="19" t="n"/>
-      <c r="AK39" s="22" t="n"/>
-      <c r="AL39" s="48" t="n"/>
-      <c r="AM39" s="19" t="n"/>
-      <c r="AN39" s="24" t="n"/>
+      <c r="D39" s="283" t="n"/>
+      <c r="E39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="n"/>
+      <c r="J39" s="283" t="n"/>
+      <c r="K39" s="283" t="n"/>
+      <c r="L39" s="285" t="n"/>
+      <c r="M39" s="299" t="n"/>
+      <c r="N39" s="283" t="n"/>
+      <c r="O39" s="283" t="n"/>
+      <c r="P39" s="283" t="n"/>
+      <c r="Q39" s="283" t="n"/>
+      <c r="R39" s="283" t="n"/>
+      <c r="S39" s="283" t="n"/>
+      <c r="T39" s="283" t="n"/>
+      <c r="U39" s="283" t="n"/>
+      <c r="V39" s="283" t="n"/>
+      <c r="W39" s="283" t="n"/>
+      <c r="X39" s="285" t="n"/>
+      <c r="Y39" s="314" t="n"/>
+      <c r="Z39" s="283" t="n"/>
+      <c r="AA39" s="283" t="n"/>
+      <c r="AB39" s="283" t="n"/>
+      <c r="AC39" s="285" t="n"/>
+      <c r="AD39" s="314" t="n"/>
+      <c r="AE39" s="283" t="n"/>
+      <c r="AF39" s="283" t="n"/>
+      <c r="AG39" s="283" t="n"/>
+      <c r="AH39" s="285" t="n"/>
+      <c r="AI39" s="314" t="n"/>
+      <c r="AJ39" s="283" t="n"/>
+      <c r="AK39" s="285" t="n"/>
+      <c r="AL39" s="317" t="n"/>
+      <c r="AM39" s="283" t="n"/>
+      <c r="AN39" s="287" t="n"/>
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="513" t="n"/>
@@ -8349,239 +8464,169 @@
       <c r="AN40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="506" t="inlineStr">
+      <c r="A41" s="538" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPLICATION STATUS / NOTES</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
-      <c r="H41" s="27" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="27" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="27" t="n"/>
-      <c r="O41" s="27" t="n"/>
-      <c r="P41" s="27" t="n"/>
-      <c r="Q41" s="27" t="n"/>
-      <c r="R41" s="27" t="n"/>
-      <c r="S41" s="27" t="n"/>
-      <c r="T41" s="27" t="n"/>
-      <c r="U41" s="27" t="n"/>
-      <c r="V41" s="27" t="n"/>
-      <c r="W41" s="27" t="n"/>
-      <c r="X41" s="27" t="n"/>
-      <c r="Y41" s="27" t="n"/>
-      <c r="Z41" s="27" t="n"/>
-      <c r="AA41" s="27" t="n"/>
-      <c r="AB41" s="27" t="n"/>
-      <c r="AC41" s="27" t="n"/>
-      <c r="AD41" s="27" t="n"/>
-      <c r="AE41" s="27" t="n"/>
-      <c r="AF41" s="27" t="n"/>
-      <c r="AG41" s="27" t="n"/>
-      <c r="AH41" s="27" t="n"/>
-      <c r="AI41" s="27" t="n"/>
-      <c r="AJ41" s="27" t="n"/>
-      <c r="AK41" s="27" t="n"/>
-      <c r="AL41" s="27" t="n"/>
-      <c r="AM41" s="27" t="n"/>
-      <c r="AN41" s="28" t="n"/>
+      <c r="B41" s="289" t="n"/>
+      <c r="C41" s="289" t="n"/>
+      <c r="D41" s="289" t="n"/>
+      <c r="E41" s="289" t="n"/>
+      <c r="F41" s="289" t="n"/>
+      <c r="G41" s="289" t="n"/>
+      <c r="H41" s="289" t="n"/>
+      <c r="I41" s="289" t="n"/>
+      <c r="J41" s="289" t="n"/>
+      <c r="K41" s="289" t="n"/>
+      <c r="L41" s="289" t="n"/>
+      <c r="M41" s="289" t="n"/>
+      <c r="N41" s="289" t="n"/>
+      <c r="O41" s="289" t="n"/>
+      <c r="P41" s="289" t="n"/>
+      <c r="Q41" s="289" t="n"/>
+      <c r="R41" s="289" t="n"/>
+      <c r="S41" s="289" t="n"/>
+      <c r="T41" s="289" t="n"/>
+      <c r="U41" s="289" t="n"/>
+      <c r="V41" s="289" t="n"/>
+      <c r="W41" s="289" t="n"/>
+      <c r="X41" s="289" t="n"/>
+      <c r="Y41" s="289" t="n"/>
+      <c r="Z41" s="289" t="n"/>
+      <c r="AA41" s="289" t="n"/>
+      <c r="AB41" s="289" t="n"/>
+      <c r="AC41" s="289" t="n"/>
+      <c r="AD41" s="289" t="n"/>
+      <c r="AE41" s="289" t="n"/>
+      <c r="AF41" s="289" t="n"/>
+      <c r="AG41" s="289" t="n"/>
+      <c r="AH41" s="289" t="n"/>
+      <c r="AI41" s="289" t="n"/>
+      <c r="AJ41" s="289" t="n"/>
+      <c r="AK41" s="289" t="n"/>
+      <c r="AL41" s="289" t="n"/>
+      <c r="AM41" s="289" t="n"/>
+      <c r="AN41" s="290" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="514" t="inlineStr">
+      <c r="A42" s="545" t="inlineStr">
         <is>
           <t>Released by / Date-Time</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="521" t="inlineStr">
+      <c r="B42" s="271" t="n"/>
+      <c r="C42" s="271" t="n"/>
+      <c r="D42" s="271" t="n"/>
+      <c r="E42" s="271" t="n"/>
+      <c r="F42" s="271" t="n"/>
+      <c r="G42" s="271" t="n"/>
+      <c r="H42" s="271" t="n"/>
+      <c r="I42" s="271" t="n"/>
+      <c r="J42" s="271" t="n"/>
+      <c r="K42" s="271" t="n"/>
+      <c r="L42" s="271" t="n"/>
+      <c r="M42" s="272" t="n"/>
+      <c r="N42" s="553" t="inlineStr">
         <is>
           <t>Printed by / Date-Time</t>
         </is>
       </c>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="5" t="n"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-      <c r="Y42" s="5" t="n"/>
-      <c r="Z42" s="6" t="n"/>
-      <c r="AA42" s="521" t="inlineStr">
+      <c r="O42" s="271" t="n"/>
+      <c r="P42" s="271" t="n"/>
+      <c r="Q42" s="271" t="n"/>
+      <c r="R42" s="271" t="n"/>
+      <c r="S42" s="271" t="n"/>
+      <c r="T42" s="271" t="n"/>
+      <c r="U42" s="271" t="n"/>
+      <c r="V42" s="271" t="n"/>
+      <c r="W42" s="271" t="n"/>
+      <c r="X42" s="271" t="n"/>
+      <c r="Y42" s="271" t="n"/>
+      <c r="Z42" s="272" t="n"/>
+      <c r="AA42" s="554" t="inlineStr">
         <is>
           <t>Print Event State</t>
         </is>
       </c>
-      <c r="AB42" s="5" t="n"/>
-      <c r="AC42" s="5" t="n"/>
-      <c r="AD42" s="5" t="n"/>
-      <c r="AE42" s="5" t="n"/>
-      <c r="AF42" s="5" t="n"/>
-      <c r="AG42" s="5" t="n"/>
-      <c r="AH42" s="5" t="n"/>
-      <c r="AI42" s="5" t="n"/>
-      <c r="AJ42" s="5" t="n"/>
-      <c r="AK42" s="5" t="n"/>
-      <c r="AL42" s="5" t="n"/>
-      <c r="AM42" s="5" t="n"/>
-      <c r="AN42" s="8" t="n"/>
+      <c r="AB42" s="271" t="n"/>
+      <c r="AC42" s="271" t="n"/>
+      <c r="AD42" s="271" t="n"/>
+      <c r="AE42" s="271" t="n"/>
+      <c r="AF42" s="271" t="n"/>
+      <c r="AG42" s="271" t="n"/>
+      <c r="AH42" s="271" t="n"/>
+      <c r="AI42" s="271" t="n"/>
+      <c r="AJ42" s="271" t="n"/>
+      <c r="AK42" s="271" t="n"/>
+      <c r="AL42" s="271" t="n"/>
+      <c r="AM42" s="271" t="n"/>
+      <c r="AN42" s="274" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="522">
+      <c r="A43" s="555">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="13" t="n"/>
-      <c r="N43" s="523">
+      <c r="M43" s="556" t="n"/>
+      <c r="N43" s="557">
         <f>IF(PRINT_CONTROL!$B$6="","",PRINT_CONTROL!$B$6)</f>
         <v/>
       </c>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="12" t="n"/>
-      <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
-      <c r="T43" s="12" t="n"/>
-      <c r="U43" s="12" t="n"/>
-      <c r="V43" s="12" t="n"/>
-      <c r="W43" s="12" t="n"/>
-      <c r="X43" s="12" t="n"/>
-      <c r="Y43" s="12" t="n"/>
-      <c r="Z43" s="13" t="n"/>
-      <c r="AA43" s="523">
+      <c r="Z43" s="556" t="n"/>
+      <c r="AA43" s="558">
         <f>IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</f>
         <v/>
       </c>
-      <c r="AB43" s="12" t="n"/>
-      <c r="AC43" s="12" t="n"/>
-      <c r="AD43" s="12" t="n"/>
-      <c r="AE43" s="12" t="n"/>
-      <c r="AF43" s="12" t="n"/>
-      <c r="AG43" s="12" t="n"/>
-      <c r="AH43" s="12" t="n"/>
-      <c r="AI43" s="12" t="n"/>
-      <c r="AJ43" s="12" t="n"/>
-      <c r="AK43" s="12" t="n"/>
-      <c r="AL43" s="12" t="n"/>
-      <c r="AM43" s="12" t="n"/>
-      <c r="AN43" s="15" t="n"/>
+      <c r="AN43" s="321" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
-      <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="12" t="n"/>
-      <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
-      <c r="T44" s="12" t="n"/>
-      <c r="U44" s="12" t="n"/>
-      <c r="V44" s="12" t="n"/>
-      <c r="W44" s="12" t="n"/>
-      <c r="X44" s="12" t="n"/>
-      <c r="Y44" s="12" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-      <c r="AA44" s="12" t="n"/>
-      <c r="AB44" s="12" t="n"/>
-      <c r="AC44" s="12" t="n"/>
-      <c r="AD44" s="12" t="n"/>
-      <c r="AE44" s="12" t="n"/>
-      <c r="AF44" s="12" t="n"/>
-      <c r="AG44" s="12" t="n"/>
-      <c r="AH44" s="12" t="n"/>
-      <c r="AI44" s="12" t="n"/>
-      <c r="AJ44" s="12" t="n"/>
-      <c r="AK44" s="12" t="n"/>
-      <c r="AL44" s="12" t="n"/>
-      <c r="AM44" s="12" t="n"/>
-      <c r="AN44" s="15" t="n"/>
+      <c r="A44" s="275" t="n"/>
+      <c r="M44" s="556" t="n"/>
+      <c r="Z44" s="556" t="n"/>
+      <c r="AN44" s="321" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="18" t="n"/>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="19" t="n"/>
-      <c r="M45" s="22" t="n"/>
-      <c r="N45" s="19" t="n"/>
-      <c r="O45" s="19" t="n"/>
-      <c r="P45" s="19" t="n"/>
-      <c r="Q45" s="19" t="n"/>
-      <c r="R45" s="19" t="n"/>
-      <c r="S45" s="19" t="n"/>
-      <c r="T45" s="19" t="n"/>
-      <c r="U45" s="19" t="n"/>
-      <c r="V45" s="19" t="n"/>
-      <c r="W45" s="19" t="n"/>
-      <c r="X45" s="19" t="n"/>
-      <c r="Y45" s="19" t="n"/>
-      <c r="Z45" s="22" t="n"/>
-      <c r="AA45" s="19" t="n"/>
-      <c r="AB45" s="19" t="n"/>
-      <c r="AC45" s="19" t="n"/>
-      <c r="AD45" s="19" t="n"/>
-      <c r="AE45" s="19" t="n"/>
-      <c r="AF45" s="19" t="n"/>
-      <c r="AG45" s="19" t="n"/>
-      <c r="AH45" s="19" t="n"/>
-      <c r="AI45" s="19" t="n"/>
-      <c r="AJ45" s="19" t="n"/>
-      <c r="AK45" s="19" t="n"/>
-      <c r="AL45" s="19" t="n"/>
-      <c r="AM45" s="19" t="n"/>
-      <c r="AN45" s="24" t="n"/>
+      <c r="A45" s="281" t="n"/>
+      <c r="B45" s="277" t="n"/>
+      <c r="C45" s="277" t="n"/>
+      <c r="D45" s="277" t="n"/>
+      <c r="E45" s="277" t="n"/>
+      <c r="F45" s="277" t="n"/>
+      <c r="G45" s="277" t="n"/>
+      <c r="H45" s="277" t="n"/>
+      <c r="I45" s="277" t="n"/>
+      <c r="J45" s="277" t="n"/>
+      <c r="K45" s="277" t="n"/>
+      <c r="L45" s="277" t="n"/>
+      <c r="M45" s="278" t="n"/>
+      <c r="N45" s="277" t="n"/>
+      <c r="O45" s="277" t="n"/>
+      <c r="P45" s="277" t="n"/>
+      <c r="Q45" s="277" t="n"/>
+      <c r="R45" s="277" t="n"/>
+      <c r="S45" s="277" t="n"/>
+      <c r="T45" s="277" t="n"/>
+      <c r="U45" s="277" t="n"/>
+      <c r="V45" s="277" t="n"/>
+      <c r="W45" s="277" t="n"/>
+      <c r="X45" s="277" t="n"/>
+      <c r="Y45" s="277" t="n"/>
+      <c r="Z45" s="278" t="n"/>
+      <c r="AA45" s="277" t="n"/>
+      <c r="AB45" s="277" t="n"/>
+      <c r="AC45" s="277" t="n"/>
+      <c r="AD45" s="277" t="n"/>
+      <c r="AE45" s="277" t="n"/>
+      <c r="AF45" s="277" t="n"/>
+      <c r="AG45" s="277" t="n"/>
+      <c r="AH45" s="277" t="n"/>
+      <c r="AI45" s="277" t="n"/>
+      <c r="AJ45" s="277" t="n"/>
+      <c r="AK45" s="277" t="n"/>
+      <c r="AL45" s="277" t="n"/>
+      <c r="AM45" s="277" t="n"/>
+      <c r="AN45" s="280" t="n"/>
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="513" t="n"/>
@@ -8626,50 +8671,50 @@
       <c r="AN46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="506" t="inlineStr">
+      <c r="A47" s="538" t="inlineStr">
         <is>
           <t>NOTICE: Printed face only. No signature on the printed face. Record release, print, verify, void or scrap event in PRINT_CONTROL and PRINT_LOG.</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="27" t="n"/>
-      <c r="K47" s="27" t="n"/>
-      <c r="L47" s="27" t="n"/>
-      <c r="M47" s="27" t="n"/>
-      <c r="N47" s="27" t="n"/>
-      <c r="O47" s="27" t="n"/>
-      <c r="P47" s="27" t="n"/>
-      <c r="Q47" s="27" t="n"/>
-      <c r="R47" s="27" t="n"/>
-      <c r="S47" s="27" t="n"/>
-      <c r="T47" s="27" t="n"/>
-      <c r="U47" s="27" t="n"/>
-      <c r="V47" s="27" t="n"/>
-      <c r="W47" s="27" t="n"/>
-      <c r="X47" s="27" t="n"/>
-      <c r="Y47" s="27" t="n"/>
-      <c r="Z47" s="27" t="n"/>
-      <c r="AA47" s="27" t="n"/>
-      <c r="AB47" s="27" t="n"/>
-      <c r="AC47" s="27" t="n"/>
-      <c r="AD47" s="27" t="n"/>
-      <c r="AE47" s="27" t="n"/>
-      <c r="AF47" s="27" t="n"/>
-      <c r="AG47" s="27" t="n"/>
-      <c r="AH47" s="27" t="n"/>
-      <c r="AI47" s="27" t="n"/>
-      <c r="AJ47" s="27" t="n"/>
-      <c r="AK47" s="27" t="n"/>
-      <c r="AL47" s="27" t="n"/>
-      <c r="AM47" s="27" t="n"/>
-      <c r="AN47" s="28" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
+      <c r="K47" s="289" t="n"/>
+      <c r="L47" s="289" t="n"/>
+      <c r="M47" s="289" t="n"/>
+      <c r="N47" s="289" t="n"/>
+      <c r="O47" s="289" t="n"/>
+      <c r="P47" s="289" t="n"/>
+      <c r="Q47" s="289" t="n"/>
+      <c r="R47" s="289" t="n"/>
+      <c r="S47" s="289" t="n"/>
+      <c r="T47" s="289" t="n"/>
+      <c r="U47" s="289" t="n"/>
+      <c r="V47" s="289" t="n"/>
+      <c r="W47" s="289" t="n"/>
+      <c r="X47" s="289" t="n"/>
+      <c r="Y47" s="289" t="n"/>
+      <c r="Z47" s="289" t="n"/>
+      <c r="AA47" s="289" t="n"/>
+      <c r="AB47" s="289" t="n"/>
+      <c r="AC47" s="289" t="n"/>
+      <c r="AD47" s="289" t="n"/>
+      <c r="AE47" s="289" t="n"/>
+      <c r="AF47" s="289" t="n"/>
+      <c r="AG47" s="289" t="n"/>
+      <c r="AH47" s="289" t="n"/>
+      <c r="AI47" s="289" t="n"/>
+      <c r="AJ47" s="289" t="n"/>
+      <c r="AK47" s="289" t="n"/>
+      <c r="AL47" s="289" t="n"/>
+      <c r="AM47" s="289" t="n"/>
+      <c r="AN47" s="290" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="181">
@@ -8875,7 +8920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9066,7 +9111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU22"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10229,7 +10274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10869,7 +10914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11621,7 +11666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="veryHidden" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -21,10 +21,510 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+  <si>
+    <t>  1. PRINT REQUEST / CONTROL CONTEXT</t>
+  </si>
+  <si>
+    <t>  2. PRINTED FACE / CONTROLLED IDENTITY</t>
+  </si>
+  <si>
+    <t>  3. VERIFICATION / APPLICATION CHECK</t>
+  </si>
+  <si>
+    <t>  4. PRINT CONTROL REFERENCE</t>
+  </si>
+  <si>
+    <t>  5. APPLICATION STATUS / NOTES</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$12="","",GENERATOR!$B$12)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$13="","",GENERATOR!$B$13)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$14="","",GENERATOR!$B$14)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$15="","",GENERATOR!$B$15)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$16="","",GENERATOR!$B$16)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$19="","",GENERATOR!$B$19)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$20="","",GENERATOR!$B$20)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$21="","",GENERATOR!$B$21)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$22="","",GENERATOR!$B$22)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$23="","",GENERATOR!$B$23)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$24="","",GENERATOR!$B$24)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$25="","",GENERATOR!$B$25)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$26="","",GENERATOR!$B$26)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$5="","",GENERATOR!$B$5)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$6="","",GENERATOR!$B$6)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$7="","",GENERATOR!$B$7)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$8="","",GENERATOR!$B$8)</t>
+  </si>
+  <si>
+    <t>=IF(GENERATOR!$B$9="","",GENERATOR!$B$9)</t>
+  </si>
+  <si>
+    <t>=IF(PRINT_CONTROL!$B$5="","",PRINT_CONTROL!$B$5)</t>
+  </si>
+  <si>
+    <t>=IF(PRINT_CONTROL!$B$6="","",PRINT_CONTROL!$B$6)</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$22)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$35)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-007</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-007 — Từ điển dữ liệu GS1/SSCC, quy tắc cấp mã và đối soát kiện hàng</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-014</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-014 — Chỉ mục put-thru / pass-through / tuyến đặc biệt và yêu cầu hồ sơ đi kèm</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-017</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-017 — Chương trình phòng ngừa FOD</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-001</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-002</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-002 — Quy tắc vị trí kho, zoning, FIFO/FEFO, staging và cycle count</t>
+  </si>
+  <si>
+    <t>APPLIED</t>
+  </si>
+  <si>
+    <t>APPLY</t>
+  </si>
+  <si>
+    <t>Acceptance Rule</t>
+  </si>
+  <si>
+    <t>Application Location / Lot</t>
+  </si>
+  <si>
+    <t>Application Note</t>
+  </si>
+  <si>
+    <t>Application status</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Area / Location</t>
+  </si>
+  <si>
+    <t>Area / Location / Room</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close after the label / card is printed, verified, applied or voided, with reprint and scrap events controlled.</t>
+  </si>
+  <si>
+    <t>Control Field</t>
+  </si>
+  <si>
+    <t>Controlled WIP tag print object. Keep printed face limited to approved identity and status only.</t>
+  </si>
+  <si>
+    <t>Controlled generator sheet for fixed print face. Edit only approved generator fields.</t>
+  </si>
+  <si>
+    <t>Controlled generator/source field for printed face</t>
+  </si>
+  <si>
+    <t>Controlled print record and application evidence</t>
+  </si>
+  <si>
+    <t>Correct quantity</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>Current Operation / Qty</t>
+  </si>
+  <si>
+    <t>Date-Time</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Encoded Data Ref</t>
+  </si>
+  <si>
+    <t>Encoded String / Barcode Ref</t>
+  </si>
+  <si>
+    <t>Epicor transaction + M365 evidence</t>
+  </si>
+  <si>
+    <t>Event State</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>FRM-703</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Identity match</t>
+  </si>
+  <si>
+    <t>Job / Lot / Part / Revision</t>
+  </si>
+  <si>
+    <t>Job / Route Step</t>
+  </si>
+  <si>
+    <t>Lot / Quantity</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>NOTICE: Printed face only. No signature on the printed face. Record release, print, verify, void or scrap event in PRINT_CONTROL and PRINT_LOG.</t>
+  </si>
+  <si>
+    <t>No signature on printed face. Control release / print / verify / void here.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open only from the approved print trigger or parent release transaction; do not open ad hoc for uncontrolled printing.</t>
+  </si>
+  <si>
+    <t>Operation / Workcenter</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PRINT</t>
+  </si>
+  <si>
+    <t>PRINTED</t>
+  </si>
+  <si>
+    <t>PRINT_EVENT_STATE</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Print Control</t>
+  </si>
+  <si>
+    <t>Print Event Log</t>
+  </si>
+  <si>
+    <t>Print Event State</t>
+  </si>
+  <si>
+    <t>Print Generator</t>
+  </si>
+  <si>
+    <t>Print Qty / Application Status</t>
+  </si>
+  <si>
+    <t>Print State</t>
+  </si>
+  <si>
+    <t>Print Status</t>
+  </si>
+  <si>
+    <t>Printed by</t>
+  </si>
+  <si>
+    <t>Printed by / Date-Time</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REPRINT</t>
+  </si>
+  <si>
+    <t>REQUESTED</t>
+  </si>
+  <si>
+    <t>REQUESTED / PRINTED / VERIFIED / APPLIED / VOID / SCRAP / REPRINT</t>
+  </si>
+  <si>
+    <t>Readable print</t>
+  </si>
+  <si>
+    <t>Reason / Event Ref</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Released by</t>
+  </si>
+  <si>
+    <t>Released by / Date-Time</t>
+  </si>
+  <si>
+    <t>Reprint justification</t>
+  </si>
+  <si>
+    <t>Required Record</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SCRAP</t>
+  </si>
+  <si>
+    <t>SOP-701</t>
+  </si>
+  <si>
+    <t>SOP-701 — Tiếp nhận, kho, đóng gói, thao tác và bảo quản | HESEM QMS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Source / Boundary Guidance</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Tag Face / Status</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-701; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-702; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-WHS-001/002 + ANNEX-QMS-007/014/017; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>Value / Source</t>
+  </si>
+  <si>
+    <t>Verification Check</t>
+  </si>
+  <si>
+    <t>Verified application</t>
+  </si>
+  <si>
+    <t>Verified by</t>
+  </si>
+  <si>
+    <t>Void / Scrap by</t>
+  </si>
+  <si>
+    <t>Void / scrap</t>
+  </si>
+  <si>
+    <t>Void / scrap control</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI-702</t>
+  </si>
+  <si>
+    <t>WI-702 — Bảo quản, môi trường kho/xưởng, vị trí, FIFO/FEFO và kiểm soát chạm hỏng</t>
+  </si>
+  <si>
+    <t>WIP Tag</t>
+  </si>
+  <si>
+    <t>WIP Tag ID</t>
+  </si>
+  <si>
+    <t>Warehouse + QA</t>
+  </si>
+  <si>
+    <t>Warehouse Owner</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-701-receiving-packaging-handling-and-storage.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-702-storage-environment-location-and-fifo-control.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-007-gs1-sscc-data-dictionary-and-pack-reconciliation.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-014-put-thru-index.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-017-fod-prevention-program.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-002-warehouse-location-fifo-rules.html</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="87">
+  <fonts count="88">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -516,8 +1016,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -774,8 +1279,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="368">
+  <borders count="371">
     <border>
       <left/>
       <right/>
@@ -4742,11 +5252,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="562">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6043,6 +6587,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8670,51 +9223,51 @@
       <c r="AM46" s="10" t="n"/>
       <c r="AN46" s="10" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="538" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="559" t="inlineStr">
         <is>
           <t>NOTICE: Printed face only. No signature on the printed face. Record release, print, verify, void or scrap event in PRINT_CONTROL and PRINT_LOG.</t>
         </is>
       </c>
-      <c r="B47" s="289" t="n"/>
-      <c r="C47" s="289" t="n"/>
-      <c r="D47" s="289" t="n"/>
-      <c r="E47" s="289" t="n"/>
-      <c r="F47" s="289" t="n"/>
-      <c r="G47" s="289" t="n"/>
-      <c r="H47" s="289" t="n"/>
-      <c r="I47" s="289" t="n"/>
-      <c r="J47" s="289" t="n"/>
-      <c r="K47" s="289" t="n"/>
-      <c r="L47" s="289" t="n"/>
-      <c r="M47" s="289" t="n"/>
-      <c r="N47" s="289" t="n"/>
-      <c r="O47" s="289" t="n"/>
-      <c r="P47" s="289" t="n"/>
-      <c r="Q47" s="289" t="n"/>
-      <c r="R47" s="289" t="n"/>
-      <c r="S47" s="289" t="n"/>
-      <c r="T47" s="289" t="n"/>
-      <c r="U47" s="289" t="n"/>
-      <c r="V47" s="289" t="n"/>
-      <c r="W47" s="289" t="n"/>
-      <c r="X47" s="289" t="n"/>
-      <c r="Y47" s="289" t="n"/>
-      <c r="Z47" s="289" t="n"/>
-      <c r="AA47" s="289" t="n"/>
-      <c r="AB47" s="289" t="n"/>
-      <c r="AC47" s="289" t="n"/>
-      <c r="AD47" s="289" t="n"/>
-      <c r="AE47" s="289" t="n"/>
-      <c r="AF47" s="289" t="n"/>
-      <c r="AG47" s="289" t="n"/>
-      <c r="AH47" s="289" t="n"/>
-      <c r="AI47" s="289" t="n"/>
-      <c r="AJ47" s="289" t="n"/>
-      <c r="AK47" s="289" t="n"/>
-      <c r="AL47" s="289" t="n"/>
-      <c r="AM47" s="289" t="n"/>
-      <c r="AN47" s="290" t="n"/>
+      <c r="B47" s="560" t="n"/>
+      <c r="C47" s="560" t="n"/>
+      <c r="D47" s="560" t="n"/>
+      <c r="E47" s="560" t="n"/>
+      <c r="F47" s="560" t="n"/>
+      <c r="G47" s="560" t="n"/>
+      <c r="H47" s="560" t="n"/>
+      <c r="I47" s="560" t="n"/>
+      <c r="J47" s="560" t="n"/>
+      <c r="K47" s="560" t="n"/>
+      <c r="L47" s="560" t="n"/>
+      <c r="M47" s="560" t="n"/>
+      <c r="N47" s="560" t="n"/>
+      <c r="O47" s="560" t="n"/>
+      <c r="P47" s="560" t="n"/>
+      <c r="Q47" s="560" t="n"/>
+      <c r="R47" s="560" t="n"/>
+      <c r="S47" s="560" t="n"/>
+      <c r="T47" s="560" t="n"/>
+      <c r="U47" s="560" t="n"/>
+      <c r="V47" s="560" t="n"/>
+      <c r="W47" s="560" t="n"/>
+      <c r="X47" s="560" t="n"/>
+      <c r="Y47" s="560" t="n"/>
+      <c r="Z47" s="560" t="n"/>
+      <c r="AA47" s="560" t="n"/>
+      <c r="AB47" s="560" t="n"/>
+      <c r="AC47" s="560" t="n"/>
+      <c r="AD47" s="560" t="n"/>
+      <c r="AE47" s="560" t="n"/>
+      <c r="AF47" s="560" t="n"/>
+      <c r="AG47" s="560" t="n"/>
+      <c r="AH47" s="560" t="n"/>
+      <c r="AI47" s="560" t="n"/>
+      <c r="AJ47" s="560" t="n"/>
+      <c r="AK47" s="560" t="n"/>
+      <c r="AL47" s="560" t="n"/>
+      <c r="AM47" s="560" t="n"/>
+      <c r="AN47" s="561" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="181">

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -1285,7 +1285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="371">
+  <borders count="376">
     <border>
       <left/>
       <right/>
@@ -5285,6 +5285,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_FACE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PRINT_FACE'!$A$1:$AN$47</definedName>

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -4909,7 +4909,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="279" t="inlineStr">
         <is>
-          <t>Warehouse + QA</t>
+          <t>SCM</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_FACE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="veryHidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="veryHidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GENERATOR" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_CONTROL" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRINT_LOG" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_REF" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PRINT_FACE'!$A$1:$AN$47</definedName>
@@ -4317,6 +4318,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4728,7 +4764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -4840,7 +4876,7 @@
       <c r="AH2" s="278" t="n"/>
       <c r="AI2" s="279" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AJ2" s="277" t="n"/>
@@ -4883,7 +4919,7 @@
       <c r="AH3" s="278" t="n"/>
       <c r="AI3" s="279" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AJ3" s="277" t="n"/>
@@ -4909,7 +4945,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="279" t="inlineStr">
         <is>
-          <t>SCM</t>
+          <t>Warehouse + QA</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>
@@ -5248,7 +5284,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="298" t="inlineStr">
         <is>
-          <t>Encoded Data Ref</t>
+          <t>Linked FRM-203</t>
         </is>
       </c>
       <c r="B12" s="283" t="n"/>
@@ -5275,7 +5311,7 @@
       <c r="T12" s="285" t="n"/>
       <c r="U12" s="300" t="inlineStr">
         <is>
-          <t>Warehouse Owner</t>
+          <t>Ref: SOP-701</t>
         </is>
       </c>
       <c r="V12" s="283" t="n"/>
@@ -5284,9 +5320,10 @@
       <c r="Y12" s="283" t="n"/>
       <c r="Z12" s="283" t="n"/>
       <c r="AA12" s="285" t="n"/>
-      <c r="AB12" s="286">
-        <f>IF(GENERATOR!$B$16="","",GENERATOR!$B$16)</f>
-        <v/>
+      <c r="AB12" s="286" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
       </c>
       <c r="AC12" s="283" t="n"/>
       <c r="AD12" s="283" t="n"/>
@@ -6995,6 +7032,28 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="H16:T16"/>
   </mergeCells>
+  <conditionalFormatting sqref="AF22:AF31">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD35:AD39">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8055,4 +8114,84 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-203; Parent ref: SOP-701; CF: checklist Result; CF: action Status</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-703_WIP_Tag.xlsx
@@ -4812,6 +4812,64 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Số Job
+</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Mã chi tiết
+</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Số lượng
+</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Nguyên công
+Operation hiện tại.</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Máy
+Máy đang chạy.</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>Trạng thái
+IN PROCESS / HOLD / WAITING / COMPLETE.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Operator
+</t>
+      </text>
+    </comment>
+    <comment ref="U12" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Ngày
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5757,7 +5815,7 @@
     <row r="15" ht="17" customHeight="1" s="264">
       <c r="A15" s="494" t="inlineStr">
         <is>
-          <t>Prepared by</t>
+          <t>Operator</t>
         </is>
       </c>
       <c r="B15" s="471" t="n"/>
@@ -5781,7 +5839,7 @@
       <c r="T15" s="472" t="n"/>
       <c r="U15" s="494" t="inlineStr">
         <is>
-          <t>Verified by</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="V15" s="471" t="n"/>
@@ -5947,7 +6005,7 @@
     <row r="20" ht="24" customHeight="1" s="264">
       <c r="A20" s="501" t="inlineStr">
         <is>
-          <t>NOTICE — Print label. Ref: SOP-701. Retain: 5 years.</t>
+          <t>NOTICE — Attach to WIP container. Update status at each operation.</t>
         </is>
       </c>
       <c r="B20" s="471" t="n"/>
@@ -6036,6 +6094,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
